--- a/data/macro/USA/Retail Sales.xlsx
+++ b/data/macro/USA/Retail Sales.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/AlternativeData/data/macro/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/AlternativeData/data/macro/USA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B16700DA-F494-3E43-A9B9-F998AC2F3A40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A45120B6-69E3-9048-B54F-B96354C58595}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18000" yWindow="780" windowWidth="18000" windowHeight="20760" xr2:uid="{30656A32-0D37-469D-885D-F50C8A2BA9DC}"/>
+    <workbookView xWindow="11480" yWindow="780" windowWidth="18000" windowHeight="20680" xr2:uid="{30656A32-0D37-469D-885D-F50C8A2BA9DC}"/>
   </bookViews>
   <sheets>
     <sheet name="Retail Sales" sheetId="1" r:id="rId1"/>
@@ -21,12 +21,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="12">
   <si>
     <t>Release Date</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -62,6 +73,15 @@
   <si>
     <t>Time</t>
   </si>
+  <si>
+    <t>Time Zone</t>
+  </si>
+  <si>
+    <t>UTC-5</t>
+  </si>
+  <si>
+    <t>UTC-4</t>
+  </si>
 </sst>
 </file>
 
@@ -70,9 +90,9 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="170" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="166" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -122,6 +142,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -154,7 +182,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -182,10 +210,22 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -505,1384 +545,2060 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A423BD41-4AF5-471C-B1B1-976B1BB48C33}">
-  <dimension ref="A1:G407"/>
+  <dimension ref="A1:H407"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.1640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.5" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.1640625" style="5" customWidth="1"/>
-    <col min="6" max="6" width="9.1640625" style="5"/>
-    <col min="7" max="7" width="10.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.1640625" style="2"/>
+    <col min="4" max="4" width="10.1640625" style="9" customWidth="1"/>
+    <col min="5" max="5" width="9.5" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.1640625" style="5" customWidth="1"/>
+    <col min="7" max="7" width="9.1640625" style="5"/>
+    <col min="8" max="8" width="10.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.1640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8">
+      <c r="A1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="14" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:8">
       <c r="A2" s="1">
         <v>33604</v>
       </c>
+      <c r="B2" s="4">
+        <v>33635</v>
+      </c>
       <c r="C2" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="6">
         <v>159177</v>
       </c>
-      <c r="G2" s="3"/>
-    </row>
-    <row r="3" spans="1:7">
+      <c r="H2" s="3"/>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="1">
         <v>33635</v>
       </c>
+      <c r="B3" s="4">
+        <v>33664</v>
+      </c>
       <c r="C3" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="6">
         <v>159189</v>
       </c>
-      <c r="G3" s="3"/>
-    </row>
-    <row r="4" spans="1:7">
+      <c r="H3" s="3"/>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="1">
         <v>33664</v>
       </c>
+      <c r="B4" s="4">
+        <v>33695</v>
+      </c>
       <c r="C4" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="6">
         <v>158647</v>
       </c>
-      <c r="G4" s="3"/>
-    </row>
-    <row r="5" spans="1:7">
+      <c r="H4" s="3"/>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="1">
         <v>33695</v>
       </c>
+      <c r="B5" s="4">
+        <v>33725</v>
+      </c>
       <c r="C5" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="6">
         <v>159921</v>
       </c>
-      <c r="G5" s="3"/>
-    </row>
-    <row r="6" spans="1:7">
+      <c r="H5" s="3"/>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="1">
         <v>33725</v>
       </c>
+      <c r="B6" s="4">
+        <v>33756</v>
+      </c>
       <c r="C6" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="6">
         <v>160471</v>
       </c>
-      <c r="G6" s="3"/>
-    </row>
-    <row r="7" spans="1:7">
+      <c r="H6" s="3"/>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="1">
         <v>33756</v>
       </c>
+      <c r="B7" s="4">
+        <v>33786</v>
+      </c>
       <c r="C7" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="6">
         <v>161205</v>
       </c>
-      <c r="G7" s="3"/>
-    </row>
-    <row r="8" spans="1:7">
+      <c r="H7" s="3"/>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="1">
         <v>33786</v>
       </c>
+      <c r="B8" s="4">
+        <v>33817</v>
+      </c>
       <c r="C8" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="6">
         <v>162855</v>
       </c>
-      <c r="G8" s="3"/>
-    </row>
-    <row r="9" spans="1:7">
+      <c r="H8" s="3"/>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="1">
         <v>33817</v>
       </c>
+      <c r="B9" s="4">
+        <v>33848</v>
+      </c>
       <c r="C9" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="6">
         <v>162412</v>
       </c>
-      <c r="G9" s="3"/>
-    </row>
-    <row r="10" spans="1:7">
+      <c r="H9" s="3"/>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="1">
         <v>33848</v>
       </c>
+      <c r="B10" s="4">
+        <v>33878</v>
+      </c>
       <c r="C10" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="6">
         <v>164361</v>
       </c>
-      <c r="G10" s="3"/>
-    </row>
-    <row r="11" spans="1:7">
+      <c r="H10" s="3"/>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="1">
         <v>33878</v>
       </c>
+      <c r="B11" s="4">
+        <v>33909</v>
+      </c>
       <c r="C11" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="6">
         <v>166063</v>
       </c>
-      <c r="G11" s="3"/>
-    </row>
-    <row r="12" spans="1:7">
+      <c r="H11" s="3"/>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" s="1">
         <v>33909</v>
       </c>
+      <c r="B12" s="4">
+        <v>33939</v>
+      </c>
       <c r="C12" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="6">
         <v>166124</v>
       </c>
-      <c r="G12" s="3"/>
-    </row>
-    <row r="13" spans="1:7">
+      <c r="H12" s="3"/>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" s="1">
         <v>33939</v>
       </c>
+      <c r="B13" s="4">
+        <v>33970</v>
+      </c>
       <c r="C13" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="6">
         <v>167691</v>
       </c>
-      <c r="G13" s="3"/>
-    </row>
-    <row r="14" spans="1:7">
+      <c r="H13" s="3"/>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" s="1">
         <v>33970</v>
       </c>
+      <c r="B14" s="4">
+        <v>34001</v>
+      </c>
       <c r="C14" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="6">
         <v>169500</v>
       </c>
-      <c r="G14" s="3"/>
-    </row>
-    <row r="15" spans="1:7">
+      <c r="H14" s="3"/>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" s="1">
         <v>34001</v>
       </c>
+      <c r="B15" s="4">
+        <v>34029</v>
+      </c>
       <c r="C15" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="6">
         <v>168840</v>
       </c>
-      <c r="G15" s="3"/>
-    </row>
-    <row r="16" spans="1:7">
+      <c r="H15" s="3"/>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" s="1">
         <v>34029</v>
       </c>
+      <c r="B16" s="4">
+        <v>34060</v>
+      </c>
       <c r="C16" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D16" s="6">
+      <c r="D16" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" s="6">
         <v>167682</v>
       </c>
-      <c r="G16" s="3"/>
-    </row>
-    <row r="17" spans="1:7">
+      <c r="H16" s="3"/>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" s="1">
         <v>34060</v>
       </c>
+      <c r="B17" s="4">
+        <v>34090</v>
+      </c>
       <c r="C17" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D17" s="6">
+      <c r="D17" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" s="6">
         <v>172102</v>
       </c>
-      <c r="G17" s="3"/>
-    </row>
-    <row r="18" spans="1:7">
+      <c r="H17" s="3"/>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" s="1">
         <v>34090</v>
       </c>
+      <c r="B18" s="4">
+        <v>34121</v>
+      </c>
       <c r="C18" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D18" s="6">
+      <c r="D18" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" s="6">
         <v>172960</v>
       </c>
-      <c r="G18" s="3"/>
-    </row>
-    <row r="19" spans="1:7">
+      <c r="H18" s="3"/>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" s="1">
         <v>34121</v>
       </c>
+      <c r="B19" s="4">
+        <v>34151</v>
+      </c>
       <c r="C19" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D19" s="6">
+      <c r="D19" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" s="6">
         <v>173018</v>
       </c>
-      <c r="G19" s="3"/>
-    </row>
-    <row r="20" spans="1:7">
+      <c r="H19" s="3"/>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" s="1">
         <v>34151</v>
       </c>
+      <c r="B20" s="4">
+        <v>34182</v>
+      </c>
       <c r="C20" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D20" s="6">
+      <c r="D20" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" s="6">
         <v>175822</v>
       </c>
-      <c r="G20" s="3"/>
-    </row>
-    <row r="21" spans="1:7">
+      <c r="H20" s="3"/>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" s="1">
         <v>34182</v>
       </c>
+      <c r="B21" s="4">
+        <v>34213</v>
+      </c>
       <c r="C21" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D21" s="6">
+      <c r="D21" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" s="6">
         <v>175233</v>
       </c>
-      <c r="G21" s="3"/>
-    </row>
-    <row r="22" spans="1:7">
+      <c r="H21" s="3"/>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" s="1">
         <v>34213</v>
       </c>
+      <c r="B22" s="4">
+        <v>34243</v>
+      </c>
       <c r="C22" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D22" s="6">
+      <c r="D22" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" s="6">
         <v>176608</v>
       </c>
-      <c r="G22" s="3"/>
-    </row>
-    <row r="23" spans="1:7">
+      <c r="H22" s="3"/>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" s="1">
         <v>34243</v>
       </c>
+      <c r="B23" s="4">
+        <v>34274</v>
+      </c>
       <c r="C23" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D23" s="6">
+      <c r="D23" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E23" s="6">
         <v>177588</v>
       </c>
-      <c r="G23" s="3"/>
-    </row>
-    <row r="24" spans="1:7">
+      <c r="H23" s="3"/>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" s="1">
         <v>34274</v>
       </c>
+      <c r="B24" s="4">
+        <v>34304</v>
+      </c>
       <c r="C24" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D24" s="6">
+      <c r="D24" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E24" s="6">
         <v>179758</v>
       </c>
-      <c r="G24" s="3"/>
-    </row>
-    <row r="25" spans="1:7">
+      <c r="H24" s="3"/>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" s="1">
         <v>34304</v>
       </c>
+      <c r="B25" s="4">
+        <v>34335</v>
+      </c>
       <c r="C25" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D25" s="6">
+      <c r="D25" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E25" s="6">
         <v>181077</v>
       </c>
-      <c r="G25" s="3"/>
-    </row>
-    <row r="26" spans="1:7">
+      <c r="H25" s="3"/>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" s="1">
         <v>34335</v>
       </c>
+      <c r="B26" s="4">
+        <v>34366</v>
+      </c>
       <c r="C26" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D26" s="6">
+      <c r="D26" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E26" s="6">
         <v>179615</v>
       </c>
-      <c r="G26" s="3"/>
-    </row>
-    <row r="27" spans="1:7">
+      <c r="H26" s="3"/>
+    </row>
+    <row r="27" spans="1:8">
       <c r="A27" s="1">
         <v>34366</v>
       </c>
+      <c r="B27" s="4">
+        <v>34394</v>
+      </c>
       <c r="C27" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D27" s="6">
+      <c r="D27" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E27" s="6">
         <v>183101</v>
       </c>
-      <c r="G27" s="3"/>
-    </row>
-    <row r="28" spans="1:7">
+      <c r="H27" s="3"/>
+    </row>
+    <row r="28" spans="1:8">
       <c r="A28" s="1">
         <v>34394</v>
       </c>
+      <c r="B28" s="4">
+        <v>34425</v>
+      </c>
       <c r="C28" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D28" s="6">
+      <c r="D28" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E28" s="6">
         <v>186721</v>
       </c>
-      <c r="G28" s="3"/>
-    </row>
-    <row r="29" spans="1:7">
+      <c r="H28" s="3"/>
+    </row>
+    <row r="29" spans="1:8">
       <c r="A29" s="1">
         <v>34425</v>
       </c>
+      <c r="B29" s="4">
+        <v>34455</v>
+      </c>
       <c r="C29" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D29" s="6">
+      <c r="D29" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" s="6">
         <v>186423</v>
       </c>
-      <c r="G29" s="3"/>
-    </row>
-    <row r="30" spans="1:7">
+      <c r="H29" s="3"/>
+    </row>
+    <row r="30" spans="1:8">
       <c r="A30" s="1">
         <v>34455</v>
       </c>
+      <c r="B30" s="4">
+        <v>34486</v>
+      </c>
       <c r="C30" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D30" s="6">
+      <c r="D30" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" s="6">
         <v>185616</v>
       </c>
-      <c r="G30" s="3"/>
-    </row>
-    <row r="31" spans="1:7">
+      <c r="H30" s="3"/>
+    </row>
+    <row r="31" spans="1:8">
       <c r="A31" s="1">
         <v>34486</v>
       </c>
+      <c r="B31" s="4">
+        <v>34516</v>
+      </c>
       <c r="C31" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D31" s="6">
+      <c r="D31" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E31" s="6">
         <v>187800</v>
       </c>
-      <c r="G31" s="3"/>
-    </row>
-    <row r="32" spans="1:7">
+      <c r="H31" s="3"/>
+    </row>
+    <row r="32" spans="1:8">
       <c r="A32" s="1">
         <v>34516</v>
       </c>
+      <c r="B32" s="4">
+        <v>34547</v>
+      </c>
       <c r="C32" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D32" s="6">
+      <c r="D32" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E32" s="6">
         <v>188062</v>
       </c>
-      <c r="G32" s="3"/>
-    </row>
-    <row r="33" spans="1:7">
+      <c r="H32" s="3"/>
+    </row>
+    <row r="33" spans="1:8">
       <c r="A33" s="1">
         <v>34547</v>
       </c>
+      <c r="B33" s="4">
+        <v>34578</v>
+      </c>
       <c r="C33" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D33" s="6">
+      <c r="D33" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" s="6">
         <v>190771</v>
       </c>
-      <c r="G33" s="3"/>
-    </row>
-    <row r="34" spans="1:7">
+      <c r="H33" s="3"/>
+    </row>
+    <row r="34" spans="1:8">
       <c r="A34" s="1">
         <v>34578</v>
       </c>
+      <c r="B34" s="4">
+        <v>34608</v>
+      </c>
       <c r="C34" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D34" s="6">
+      <c r="D34" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" s="6">
         <v>192585</v>
       </c>
-      <c r="G34" s="3"/>
-    </row>
-    <row r="35" spans="1:7">
+      <c r="H34" s="3"/>
+    </row>
+    <row r="35" spans="1:8">
       <c r="A35" s="1">
         <v>34608</v>
       </c>
+      <c r="B35" s="4">
+        <v>34639</v>
+      </c>
       <c r="C35" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D35" s="6">
+      <c r="D35" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E35" s="6">
         <v>193914</v>
       </c>
-      <c r="G35" s="3"/>
-    </row>
-    <row r="36" spans="1:7">
+      <c r="H35" s="3"/>
+    </row>
+    <row r="36" spans="1:8">
       <c r="A36" s="1">
         <v>34639</v>
       </c>
+      <c r="B36" s="4">
+        <v>34669</v>
+      </c>
       <c r="C36" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D36" s="6">
+      <c r="D36" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E36" s="6">
         <v>194425</v>
       </c>
-      <c r="G36" s="3"/>
-    </row>
-    <row r="37" spans="1:7">
+      <c r="H36" s="3"/>
+    </row>
+    <row r="37" spans="1:8">
       <c r="A37" s="1">
         <v>34669</v>
       </c>
+      <c r="B37" s="4">
+        <v>34700</v>
+      </c>
       <c r="C37" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D37" s="6">
+      <c r="D37" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E37" s="6">
         <v>194939</v>
       </c>
-      <c r="G37" s="3"/>
-    </row>
-    <row r="38" spans="1:7">
+      <c r="H37" s="3"/>
+    </row>
+    <row r="38" spans="1:8">
       <c r="A38" s="1">
         <v>34700</v>
       </c>
+      <c r="B38" s="4">
+        <v>34731</v>
+      </c>
       <c r="C38" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D38" s="6">
+      <c r="D38" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E38" s="6">
         <v>195908</v>
       </c>
-      <c r="G38" s="3"/>
-    </row>
-    <row r="39" spans="1:7">
+      <c r="H38" s="3"/>
+    </row>
+    <row r="39" spans="1:8">
       <c r="A39" s="1">
         <v>34731</v>
       </c>
+      <c r="B39" s="4">
+        <v>34759</v>
+      </c>
       <c r="C39" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D39" s="6">
+      <c r="D39" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E39" s="6">
         <v>193068</v>
       </c>
-      <c r="G39" s="3"/>
-    </row>
-    <row r="40" spans="1:7">
+      <c r="H39" s="3"/>
+    </row>
+    <row r="40" spans="1:8">
       <c r="A40" s="1">
         <v>34759</v>
       </c>
+      <c r="B40" s="4">
+        <v>34790</v>
+      </c>
       <c r="C40" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D40" s="6">
+      <c r="D40" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E40" s="6">
         <v>195179</v>
       </c>
-      <c r="G40" s="3"/>
-    </row>
-    <row r="41" spans="1:7">
+      <c r="H40" s="3"/>
+    </row>
+    <row r="41" spans="1:8">
       <c r="A41" s="1">
         <v>34790</v>
       </c>
+      <c r="B41" s="4">
+        <v>34820</v>
+      </c>
       <c r="C41" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D41" s="6">
+      <c r="D41" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E41" s="6">
         <v>195310</v>
       </c>
-      <c r="G41" s="3"/>
-    </row>
-    <row r="42" spans="1:7">
+      <c r="H41" s="3"/>
+    </row>
+    <row r="42" spans="1:8">
       <c r="A42" s="1">
         <v>34820</v>
       </c>
+      <c r="B42" s="4">
+        <v>34851</v>
+      </c>
       <c r="C42" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D42" s="6">
+      <c r="D42" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" s="6">
         <v>198060</v>
       </c>
-      <c r="G42" s="3"/>
-    </row>
-    <row r="43" spans="1:7">
+      <c r="H42" s="3"/>
+    </row>
+    <row r="43" spans="1:8">
       <c r="A43" s="1">
         <v>34851</v>
       </c>
+      <c r="B43" s="4">
+        <v>34881</v>
+      </c>
       <c r="C43" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D43" s="6">
+      <c r="D43" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E43" s="6">
         <v>200383</v>
       </c>
-      <c r="G43" s="3"/>
-    </row>
-    <row r="44" spans="1:7">
+      <c r="H43" s="3"/>
+    </row>
+    <row r="44" spans="1:8">
       <c r="A44" s="1">
         <v>34881</v>
       </c>
+      <c r="B44" s="4">
+        <v>34912</v>
+      </c>
       <c r="C44" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D44" s="6">
+      <c r="D44" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E44" s="6">
         <v>199110</v>
       </c>
-      <c r="G44" s="3"/>
-    </row>
-    <row r="45" spans="1:7">
+      <c r="H44" s="3"/>
+    </row>
+    <row r="45" spans="1:8">
       <c r="A45" s="1">
         <v>34912</v>
       </c>
+      <c r="B45" s="4">
+        <v>34943</v>
+      </c>
       <c r="C45" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D45" s="6">
+      <c r="D45" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E45" s="6">
         <v>201078</v>
       </c>
-      <c r="G45" s="3"/>
-    </row>
-    <row r="46" spans="1:7">
+      <c r="H45" s="3"/>
+    </row>
+    <row r="46" spans="1:8">
       <c r="A46" s="1">
         <v>34943</v>
       </c>
+      <c r="B46" s="4">
+        <v>34973</v>
+      </c>
       <c r="C46" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D46" s="6">
+      <c r="D46" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E46" s="6">
         <v>201337</v>
       </c>
-      <c r="G46" s="3"/>
-    </row>
-    <row r="47" spans="1:7">
+      <c r="H46" s="3"/>
+    </row>
+    <row r="47" spans="1:8">
       <c r="A47" s="1">
         <v>34973</v>
       </c>
+      <c r="B47" s="4">
+        <v>35004</v>
+      </c>
       <c r="C47" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D47" s="6">
+      <c r="D47" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E47" s="6">
         <v>200597</v>
       </c>
-      <c r="G47" s="3"/>
-    </row>
-    <row r="48" spans="1:7">
+      <c r="H47" s="3"/>
+    </row>
+    <row r="48" spans="1:8">
       <c r="A48" s="1">
         <v>35004</v>
       </c>
+      <c r="B48" s="4">
+        <v>35034</v>
+      </c>
       <c r="C48" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D48" s="6">
+      <c r="D48" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E48" s="6">
         <v>203545</v>
       </c>
-      <c r="G48" s="3"/>
-    </row>
-    <row r="49" spans="1:7">
+      <c r="H48" s="3"/>
+    </row>
+    <row r="49" spans="1:8">
       <c r="A49" s="1">
         <v>35034</v>
       </c>
+      <c r="B49" s="4">
+        <v>35065</v>
+      </c>
       <c r="C49" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D49" s="6">
+      <c r="D49" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E49" s="6">
         <v>204032</v>
       </c>
-      <c r="G49" s="3"/>
-    </row>
-    <row r="50" spans="1:7">
+      <c r="H49" s="3"/>
+    </row>
+    <row r="50" spans="1:8">
       <c r="A50" s="1">
         <v>35065</v>
       </c>
+      <c r="B50" s="4">
+        <v>35096</v>
+      </c>
       <c r="C50" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D50" s="6">
+      <c r="D50" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E50" s="6">
         <v>203793</v>
       </c>
-      <c r="G50" s="3"/>
-    </row>
-    <row r="51" spans="1:7">
+      <c r="H50" s="3"/>
+    </row>
+    <row r="51" spans="1:8">
       <c r="A51" s="1">
         <v>35096</v>
       </c>
+      <c r="B51" s="4">
+        <v>35125</v>
+      </c>
       <c r="C51" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D51" s="6">
+      <c r="D51" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E51" s="6">
         <v>206875</v>
       </c>
-      <c r="G51" s="3"/>
-    </row>
-    <row r="52" spans="1:7">
+      <c r="H51" s="3"/>
+    </row>
+    <row r="52" spans="1:8">
       <c r="A52" s="1">
         <v>35125</v>
       </c>
+      <c r="B52" s="4">
+        <v>35156</v>
+      </c>
       <c r="C52" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D52" s="6">
+      <c r="D52" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E52" s="6">
         <v>207650</v>
       </c>
-      <c r="G52" s="3"/>
-    </row>
-    <row r="53" spans="1:7">
+      <c r="H52" s="3"/>
+    </row>
+    <row r="53" spans="1:8">
       <c r="A53" s="1">
         <v>35156</v>
       </c>
+      <c r="B53" s="4">
+        <v>35186</v>
+      </c>
       <c r="C53" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D53" s="6">
+      <c r="D53" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E53" s="6">
         <v>209294</v>
       </c>
-      <c r="G53" s="3"/>
-    </row>
-    <row r="54" spans="1:7">
+      <c r="H53" s="3"/>
+    </row>
+    <row r="54" spans="1:8">
       <c r="A54" s="1">
         <v>35186</v>
       </c>
+      <c r="B54" s="4">
+        <v>35217</v>
+      </c>
       <c r="C54" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D54" s="6">
+      <c r="D54" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E54" s="6">
         <v>211157</v>
       </c>
-      <c r="G54" s="3"/>
-    </row>
-    <row r="55" spans="1:7">
+      <c r="H54" s="3"/>
+    </row>
+    <row r="55" spans="1:8">
       <c r="A55" s="1">
         <v>35217</v>
       </c>
+      <c r="B55" s="4">
+        <v>35247</v>
+      </c>
       <c r="C55" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D55" s="6">
+      <c r="D55" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E55" s="6">
         <v>209474</v>
       </c>
-      <c r="G55" s="3"/>
-    </row>
-    <row r="56" spans="1:7">
+      <c r="H55" s="3"/>
+    </row>
+    <row r="56" spans="1:8">
       <c r="A56" s="1">
         <v>35247</v>
       </c>
+      <c r="B56" s="4">
+        <v>35278</v>
+      </c>
       <c r="C56" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D56" s="6">
+      <c r="D56" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E56" s="6">
         <v>210827</v>
       </c>
-      <c r="G56" s="3"/>
-    </row>
-    <row r="57" spans="1:7">
+      <c r="H56" s="3"/>
+    </row>
+    <row r="57" spans="1:8">
       <c r="A57" s="1">
         <v>35278</v>
       </c>
+      <c r="B57" s="4">
+        <v>35309</v>
+      </c>
       <c r="C57" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D57" s="6">
+      <c r="D57" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E57" s="6">
         <v>210846</v>
       </c>
-      <c r="G57" s="3"/>
-    </row>
-    <row r="58" spans="1:7">
+      <c r="H57" s="3"/>
+    </row>
+    <row r="58" spans="1:8">
       <c r="A58" s="1">
         <v>35309</v>
       </c>
+      <c r="B58" s="4">
+        <v>35339</v>
+      </c>
       <c r="C58" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D58" s="6">
+      <c r="D58" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E58" s="6">
         <v>213233</v>
       </c>
-      <c r="G58" s="3"/>
-    </row>
-    <row r="59" spans="1:7">
+      <c r="H58" s="3"/>
+    </row>
+    <row r="59" spans="1:8">
       <c r="A59" s="1">
         <v>35339</v>
       </c>
+      <c r="B59" s="4">
+        <v>35370</v>
+      </c>
       <c r="C59" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D59" s="6">
+      <c r="D59" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E59" s="6">
         <v>215526</v>
       </c>
-      <c r="G59" s="3"/>
-    </row>
-    <row r="60" spans="1:7">
+      <c r="H59" s="3"/>
+    </row>
+    <row r="60" spans="1:8">
       <c r="A60" s="1">
         <v>35370</v>
       </c>
+      <c r="B60" s="4">
+        <v>35400</v>
+      </c>
       <c r="C60" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D60" s="6">
+      <c r="D60" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E60" s="6">
         <v>215167</v>
       </c>
-      <c r="G60" s="3"/>
-    </row>
-    <row r="61" spans="1:7">
+      <c r="H60" s="3"/>
+    </row>
+    <row r="61" spans="1:8">
       <c r="A61" s="1">
         <v>35400</v>
       </c>
+      <c r="B61" s="4">
+        <v>35431</v>
+      </c>
       <c r="C61" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D61" s="6">
+      <c r="D61" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E61" s="6">
         <v>215690</v>
       </c>
-      <c r="G61" s="3"/>
-    </row>
-    <row r="62" spans="1:7">
+      <c r="H61" s="3"/>
+    </row>
+    <row r="62" spans="1:8">
       <c r="A62" s="1">
         <v>35431</v>
       </c>
+      <c r="B62" s="4">
+        <v>35462</v>
+      </c>
       <c r="C62" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D62" s="6">
+      <c r="D62" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E62" s="6">
         <v>218124</v>
       </c>
-      <c r="G62" s="3"/>
-    </row>
-    <row r="63" spans="1:7">
+      <c r="H62" s="3"/>
+    </row>
+    <row r="63" spans="1:8">
       <c r="A63" s="1">
         <v>35462</v>
       </c>
+      <c r="B63" s="4">
+        <v>35490</v>
+      </c>
       <c r="C63" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D63" s="6">
+      <c r="D63" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E63" s="6">
         <v>219587</v>
       </c>
-      <c r="G63" s="3"/>
-    </row>
-    <row r="64" spans="1:7">
+      <c r="H63" s="3"/>
+    </row>
+    <row r="64" spans="1:8">
       <c r="A64" s="1">
         <v>35490</v>
       </c>
+      <c r="B64" s="4">
+        <v>35521</v>
+      </c>
       <c r="C64" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D64" s="6">
+      <c r="D64" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E64" s="6">
         <v>221189</v>
       </c>
-      <c r="G64" s="3"/>
-    </row>
-    <row r="65" spans="1:7">
+      <c r="H64" s="3"/>
+    </row>
+    <row r="65" spans="1:8">
       <c r="A65" s="1">
         <v>35521</v>
       </c>
+      <c r="B65" s="4">
+        <v>35551</v>
+      </c>
       <c r="C65" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D65" s="6">
+      <c r="D65" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E65" s="6">
         <v>217925</v>
       </c>
-      <c r="G65" s="3"/>
-    </row>
-    <row r="66" spans="1:7">
+      <c r="H65" s="3"/>
+    </row>
+    <row r="66" spans="1:8">
       <c r="A66" s="1">
         <v>35551</v>
       </c>
+      <c r="B66" s="4">
+        <v>35582</v>
+      </c>
       <c r="C66" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D66" s="6">
+      <c r="D66" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E66" s="6">
         <v>217771</v>
       </c>
-      <c r="G66" s="3"/>
-    </row>
-    <row r="67" spans="1:7">
+      <c r="H66" s="3"/>
+    </row>
+    <row r="67" spans="1:8">
       <c r="A67" s="1">
         <v>35582</v>
       </c>
+      <c r="B67" s="4">
+        <v>35612</v>
+      </c>
       <c r="C67" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D67" s="6">
+      <c r="D67" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E67" s="6">
         <v>220233</v>
       </c>
-      <c r="G67" s="3"/>
-    </row>
-    <row r="68" spans="1:7">
+      <c r="H67" s="3"/>
+    </row>
+    <row r="68" spans="1:8">
       <c r="A68" s="1">
         <v>35612</v>
       </c>
+      <c r="B68" s="4">
+        <v>35643</v>
+      </c>
       <c r="C68" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D68" s="6">
+      <c r="D68" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E68" s="6">
         <v>222985</v>
       </c>
-      <c r="G68" s="3"/>
-    </row>
-    <row r="69" spans="1:7">
+      <c r="H68" s="3"/>
+    </row>
+    <row r="69" spans="1:8">
       <c r="A69" s="1">
         <v>35643</v>
       </c>
+      <c r="B69" s="4">
+        <v>35674</v>
+      </c>
       <c r="C69" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D69" s="6">
+      <c r="D69" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E69" s="6">
         <v>223120</v>
       </c>
-      <c r="G69" s="3"/>
-    </row>
-    <row r="70" spans="1:7">
+      <c r="H69" s="3"/>
+    </row>
+    <row r="70" spans="1:8">
       <c r="A70" s="1">
         <v>35674</v>
       </c>
+      <c r="B70" s="4">
+        <v>35704</v>
+      </c>
       <c r="C70" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D70" s="6">
+      <c r="D70" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E70" s="6">
         <v>224509</v>
       </c>
-      <c r="G70" s="3"/>
-    </row>
-    <row r="71" spans="1:7">
+      <c r="H70" s="3"/>
+    </row>
+    <row r="71" spans="1:8">
       <c r="A71" s="1">
         <v>35704</v>
       </c>
+      <c r="B71" s="4">
+        <v>35735</v>
+      </c>
       <c r="C71" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D71" s="6">
+      <c r="D71" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E71" s="6">
         <v>224300</v>
       </c>
-      <c r="G71" s="3"/>
-    </row>
-    <row r="72" spans="1:7">
+      <c r="H71" s="3"/>
+    </row>
+    <row r="72" spans="1:8">
       <c r="A72" s="1">
         <v>35735</v>
       </c>
+      <c r="B72" s="4">
+        <v>35765</v>
+      </c>
       <c r="C72" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D72" s="6">
+      <c r="D72" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E72" s="6">
         <v>223718</v>
       </c>
-      <c r="G72" s="3"/>
-    </row>
-    <row r="73" spans="1:7">
+      <c r="H72" s="3"/>
+    </row>
+    <row r="73" spans="1:8">
       <c r="A73" s="1">
         <v>35765</v>
       </c>
+      <c r="B73" s="4">
+        <v>35796</v>
+      </c>
       <c r="C73" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D73" s="6">
+      <c r="D73" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E73" s="6">
         <v>225236</v>
       </c>
-      <c r="G73" s="3"/>
-    </row>
-    <row r="74" spans="1:7">
+      <c r="H73" s="3"/>
+    </row>
+    <row r="74" spans="1:8">
       <c r="A74" s="1">
         <v>35796</v>
       </c>
+      <c r="B74" s="4">
+        <v>35827</v>
+      </c>
       <c r="C74" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D74" s="6">
+      <c r="D74" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E74" s="6">
         <v>225954</v>
       </c>
-      <c r="G74" s="3"/>
-    </row>
-    <row r="75" spans="1:7">
+      <c r="H74" s="3"/>
+    </row>
+    <row r="75" spans="1:8">
       <c r="A75" s="1">
         <v>35827</v>
       </c>
+      <c r="B75" s="4">
+        <v>35855</v>
+      </c>
       <c r="C75" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D75" s="6">
+      <c r="D75" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E75" s="6">
         <v>225746</v>
       </c>
-      <c r="G75" s="3"/>
-    </row>
-    <row r="76" spans="1:7">
+      <c r="H75" s="3"/>
+    </row>
+    <row r="76" spans="1:8">
       <c r="A76" s="1">
         <v>35855</v>
       </c>
+      <c r="B76" s="4">
+        <v>35886</v>
+      </c>
       <c r="C76" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D76" s="6">
+      <c r="D76" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E76" s="6">
         <v>226889</v>
       </c>
-      <c r="G76" s="3"/>
-    </row>
-    <row r="77" spans="1:7">
+      <c r="H76" s="3"/>
+    </row>
+    <row r="77" spans="1:8">
       <c r="A77" s="1">
         <v>35886</v>
       </c>
+      <c r="B77" s="4">
+        <v>35916</v>
+      </c>
       <c r="C77" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D77" s="6">
+      <c r="D77" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E77" s="6">
         <v>230409</v>
       </c>
-      <c r="G77" s="3"/>
-    </row>
-    <row r="78" spans="1:7">
+      <c r="H77" s="3"/>
+    </row>
+    <row r="78" spans="1:8">
       <c r="A78" s="1">
         <v>35916</v>
       </c>
+      <c r="B78" s="4">
+        <v>35947</v>
+      </c>
       <c r="C78" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D78" s="6">
+      <c r="D78" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E78" s="6">
         <v>230995</v>
       </c>
-      <c r="G78" s="3"/>
-    </row>
-    <row r="79" spans="1:7">
+      <c r="H78" s="3"/>
+    </row>
+    <row r="79" spans="1:8">
       <c r="A79" s="1">
         <v>35947</v>
       </c>
+      <c r="B79" s="4">
+        <v>35977</v>
+      </c>
       <c r="C79" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D79" s="6">
+      <c r="D79" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E79" s="6">
         <v>233207</v>
       </c>
-      <c r="G79" s="3"/>
-    </row>
-    <row r="80" spans="1:7">
+      <c r="H79" s="3"/>
+    </row>
+    <row r="80" spans="1:8">
       <c r="A80" s="1">
         <v>35977</v>
       </c>
+      <c r="B80" s="4">
+        <v>36008</v>
+      </c>
       <c r="C80" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D80" s="6">
+      <c r="D80" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E80" s="6">
         <v>231551</v>
       </c>
-      <c r="G80" s="3"/>
-    </row>
-    <row r="81" spans="1:7">
+      <c r="H80" s="3"/>
+    </row>
+    <row r="81" spans="1:8">
       <c r="A81" s="1">
         <v>36008</v>
       </c>
+      <c r="B81" s="4">
+        <v>36039</v>
+      </c>
       <c r="C81" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D81" s="6">
+      <c r="D81" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E81" s="6">
         <v>229792</v>
       </c>
-      <c r="G81" s="3"/>
-    </row>
-    <row r="82" spans="1:7">
+      <c r="H81" s="3"/>
+    </row>
+    <row r="82" spans="1:8">
       <c r="A82" s="1">
         <v>36039</v>
       </c>
+      <c r="B82" s="4">
+        <v>36069</v>
+      </c>
       <c r="C82" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D82" s="6">
+      <c r="D82" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E82" s="6">
         <v>232308</v>
       </c>
-      <c r="G82" s="3"/>
-    </row>
-    <row r="83" spans="1:7">
+      <c r="H82" s="3"/>
+    </row>
+    <row r="83" spans="1:8">
       <c r="A83" s="1">
         <v>36069</v>
       </c>
+      <c r="B83" s="4">
+        <v>36100</v>
+      </c>
       <c r="C83" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D83" s="6">
+      <c r="D83" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E83" s="6">
         <v>236174</v>
       </c>
-      <c r="G83" s="3"/>
-    </row>
-    <row r="84" spans="1:7">
+      <c r="H83" s="3"/>
+    </row>
+    <row r="84" spans="1:8">
       <c r="A84" s="1">
         <v>36100</v>
       </c>
+      <c r="B84" s="4">
+        <v>36130</v>
+      </c>
       <c r="C84" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D84" s="6">
+      <c r="D84" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E84" s="6">
         <v>237592</v>
       </c>
-      <c r="G84" s="3"/>
-    </row>
-    <row r="85" spans="1:7">
+      <c r="H84" s="3"/>
+    </row>
+    <row r="85" spans="1:8">
       <c r="A85" s="1">
         <v>36130</v>
       </c>
+      <c r="B85" s="4">
+        <v>36161</v>
+      </c>
       <c r="C85" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D85" s="6">
+      <c r="D85" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E85" s="6">
         <v>240140</v>
       </c>
-      <c r="G85" s="3"/>
-    </row>
-    <row r="86" spans="1:7">
+      <c r="H85" s="3"/>
+    </row>
+    <row r="86" spans="1:8">
       <c r="A86" s="1">
         <v>36161</v>
       </c>
+      <c r="B86" s="4">
+        <v>36192</v>
+      </c>
       <c r="C86" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D86" s="6">
+      <c r="D86" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E86" s="6">
         <v>240269</v>
       </c>
-      <c r="G86" s="3"/>
-    </row>
-    <row r="87" spans="1:7">
+      <c r="H86" s="3"/>
+    </row>
+    <row r="87" spans="1:8">
       <c r="A87" s="1">
         <v>36192</v>
       </c>
+      <c r="B87" s="4">
+        <v>36220</v>
+      </c>
       <c r="C87" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D87" s="6">
+      <c r="D87" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E87" s="6">
         <v>243346</v>
       </c>
-      <c r="G87" s="3"/>
-    </row>
-    <row r="88" spans="1:7">
+      <c r="H87" s="3"/>
+    </row>
+    <row r="88" spans="1:8">
       <c r="A88" s="1">
         <v>36220</v>
       </c>
+      <c r="B88" s="4">
+        <v>36251</v>
+      </c>
       <c r="C88" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D88" s="6">
+      <c r="D88" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E88" s="6">
         <v>244687</v>
       </c>
-      <c r="G88" s="3"/>
-    </row>
-    <row r="89" spans="1:7">
+      <c r="H88" s="3"/>
+    </row>
+    <row r="89" spans="1:8">
       <c r="A89" s="1">
         <v>36251</v>
       </c>
+      <c r="B89" s="4">
+        <v>36281</v>
+      </c>
       <c r="C89" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D89" s="6">
+      <c r="D89" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E89" s="6">
         <v>246628</v>
       </c>
-      <c r="G89" s="3"/>
-    </row>
-    <row r="90" spans="1:7">
+      <c r="H89" s="3"/>
+    </row>
+    <row r="90" spans="1:8">
       <c r="A90" s="1">
         <v>36281</v>
       </c>
+      <c r="B90" s="4">
+        <v>36312</v>
+      </c>
       <c r="C90" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D90" s="6">
+      <c r="D90" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E90" s="6">
         <v>248367</v>
       </c>
-      <c r="G90" s="3"/>
-    </row>
-    <row r="91" spans="1:7">
+      <c r="H90" s="3"/>
+    </row>
+    <row r="91" spans="1:8">
       <c r="A91" s="1">
         <v>36312</v>
       </c>
+      <c r="B91" s="4">
+        <v>36342</v>
+      </c>
       <c r="C91" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D91" s="6">
+      <c r="D91" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E91" s="6">
         <v>249329</v>
       </c>
-      <c r="G91" s="3"/>
-    </row>
-    <row r="92" spans="1:7">
+      <c r="H91" s="3"/>
+    </row>
+    <row r="92" spans="1:8">
       <c r="A92" s="1">
         <v>36342</v>
       </c>
+      <c r="B92" s="4">
+        <v>36373</v>
+      </c>
       <c r="C92" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D92" s="6">
+      <c r="D92" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E92" s="6">
         <v>251263</v>
       </c>
-      <c r="G92" s="3"/>
-    </row>
-    <row r="93" spans="1:7">
+      <c r="H92" s="3"/>
+    </row>
+    <row r="93" spans="1:8">
       <c r="A93" s="1">
         <v>36373</v>
       </c>
+      <c r="B93" s="4">
+        <v>36404</v>
+      </c>
       <c r="C93" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D93" s="6">
+      <c r="D93" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E93" s="6">
         <v>253844</v>
       </c>
-      <c r="G93" s="3"/>
-    </row>
-    <row r="94" spans="1:7">
+      <c r="H93" s="3"/>
+    </row>
+    <row r="94" spans="1:8">
       <c r="A94" s="1">
         <v>36404</v>
       </c>
+      <c r="B94" s="4">
+        <v>36434</v>
+      </c>
       <c r="C94" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D94" s="6">
+      <c r="D94" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E94" s="6">
         <v>255029</v>
       </c>
-      <c r="G94" s="3"/>
-    </row>
-    <row r="95" spans="1:7">
+      <c r="H94" s="3"/>
+    </row>
+    <row r="95" spans="1:8">
       <c r="A95" s="1">
         <v>36434</v>
       </c>
+      <c r="B95" s="4">
+        <v>36465</v>
+      </c>
       <c r="C95" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D95" s="6">
+      <c r="D95" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E95" s="6">
         <v>254816</v>
       </c>
-      <c r="G95" s="3"/>
-    </row>
-    <row r="96" spans="1:7">
+      <c r="H95" s="3"/>
+    </row>
+    <row r="96" spans="1:8">
       <c r="A96" s="1">
         <v>36465</v>
       </c>
+      <c r="B96" s="4">
+        <v>36495</v>
+      </c>
       <c r="C96" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D96" s="6">
+      <c r="D96" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E96" s="6">
         <v>258133</v>
       </c>
-      <c r="G96" s="3"/>
-    </row>
-    <row r="97" spans="1:7">
+      <c r="H96" s="3"/>
+    </row>
+    <row r="97" spans="1:8">
       <c r="A97" s="1">
         <v>36495</v>
       </c>
+      <c r="B97" s="4">
+        <v>36526</v>
+      </c>
       <c r="C97" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D97" s="6">
+      <c r="D97" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E97" s="6">
         <v>263311</v>
       </c>
-      <c r="G97" s="3"/>
-    </row>
-    <row r="98" spans="1:7">
+      <c r="H97" s="3"/>
+    </row>
+    <row r="98" spans="1:8">
       <c r="A98" s="1">
         <v>36526</v>
       </c>
+      <c r="B98" s="4">
+        <v>36557</v>
+      </c>
       <c r="C98" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D98" s="6">
+      <c r="D98" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E98" s="6">
         <v>261545</v>
       </c>
-      <c r="G98" s="3"/>
-    </row>
-    <row r="99" spans="1:7">
+      <c r="H98" s="3"/>
+    </row>
+    <row r="99" spans="1:8">
       <c r="A99" s="1">
         <v>36557</v>
       </c>
+      <c r="B99" s="4">
+        <v>36586</v>
+      </c>
       <c r="C99" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D99" s="6">
+      <c r="D99" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E99" s="6">
         <v>265686</v>
       </c>
-      <c r="G99" s="3"/>
-    </row>
-    <row r="100" spans="1:7">
+      <c r="H99" s="3"/>
+    </row>
+    <row r="100" spans="1:8">
       <c r="A100" s="1">
         <v>36586</v>
       </c>
+      <c r="B100" s="4">
+        <v>36617</v>
+      </c>
       <c r="C100" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D100" s="6">
+      <c r="D100" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E100" s="6">
         <v>269019</v>
       </c>
-      <c r="G100" s="3"/>
-    </row>
-    <row r="101" spans="1:7">
+      <c r="H100" s="3"/>
+    </row>
+    <row r="101" spans="1:8">
       <c r="A101" s="1">
         <v>36617</v>
       </c>
+      <c r="B101" s="4">
+        <v>36647</v>
+      </c>
       <c r="C101" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D101" s="6">
+      <c r="D101" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E101" s="6">
         <v>264067</v>
       </c>
-      <c r="G101" s="3"/>
-    </row>
-    <row r="102" spans="1:7">
+      <c r="H101" s="3"/>
+    </row>
+    <row r="102" spans="1:8">
       <c r="A102" s="1">
         <v>36647</v>
       </c>
+      <c r="B102" s="4">
+        <v>36678</v>
+      </c>
       <c r="C102" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D102" s="6">
+      <c r="D102" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E102" s="6">
         <v>265992</v>
       </c>
-      <c r="G102" s="3"/>
-    </row>
-    <row r="103" spans="1:7">
+      <c r="H102" s="3"/>
+    </row>
+    <row r="103" spans="1:8">
       <c r="A103" s="1">
         <v>36678</v>
       </c>
+      <c r="B103" s="4">
+        <v>36708</v>
+      </c>
       <c r="C103" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D103" s="6">
+      <c r="D103" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E103" s="6">
         <v>267750</v>
       </c>
-      <c r="G103" s="3"/>
-    </row>
-    <row r="104" spans="1:7">
+      <c r="H103" s="3"/>
+    </row>
+    <row r="104" spans="1:8">
       <c r="A104" s="1">
         <v>36708</v>
       </c>
+      <c r="B104" s="4">
+        <v>36739</v>
+      </c>
       <c r="C104" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D104" s="6">
+      <c r="D104" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E104" s="6">
         <v>265683</v>
       </c>
-      <c r="G104" s="3"/>
-    </row>
-    <row r="105" spans="1:7">
+      <c r="H104" s="3"/>
+    </row>
+    <row r="105" spans="1:8">
       <c r="A105" s="1">
         <v>36739</v>
       </c>
+      <c r="B105" s="4">
+        <v>36770</v>
+      </c>
       <c r="C105" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D105" s="6">
+      <c r="D105" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E105" s="6">
         <v>266885</v>
       </c>
-      <c r="G105" s="3"/>
-    </row>
-    <row r="106" spans="1:7">
+      <c r="H105" s="3"/>
+    </row>
+    <row r="106" spans="1:8">
       <c r="A106" s="1">
         <v>36770</v>
       </c>
+      <c r="B106" s="4">
+        <v>36800</v>
+      </c>
       <c r="C106" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D106" s="6">
+      <c r="D106" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E106" s="6">
         <v>270523</v>
       </c>
-      <c r="G106" s="3"/>
-    </row>
-    <row r="107" spans="1:7">
+      <c r="H106" s="3"/>
+    </row>
+    <row r="107" spans="1:8">
       <c r="A107" s="1">
         <v>36800</v>
       </c>
+      <c r="B107" s="4">
+        <v>36831</v>
+      </c>
       <c r="C107" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D107" s="6">
+      <c r="D107" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E107" s="6">
         <v>270339</v>
       </c>
-      <c r="G107" s="3"/>
-    </row>
-    <row r="108" spans="1:7">
+      <c r="H107" s="3"/>
+    </row>
+    <row r="108" spans="1:8">
       <c r="A108" s="1">
         <v>36831</v>
       </c>
+      <c r="B108" s="4">
+        <v>36861</v>
+      </c>
       <c r="C108" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D108" s="6">
+      <c r="D108" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E108" s="6">
         <v>268850</v>
       </c>
-      <c r="G108" s="3"/>
-    </row>
-    <row r="109" spans="1:7">
+      <c r="H108" s="3"/>
+    </row>
+    <row r="109" spans="1:8">
       <c r="A109" s="1">
         <v>36861</v>
       </c>
+      <c r="B109" s="4">
+        <v>36892</v>
+      </c>
       <c r="C109" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D109" s="6">
+      <c r="D109" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E109" s="6">
         <v>268338</v>
       </c>
-      <c r="G109" s="3"/>
-    </row>
-    <row r="110" spans="1:7">
+      <c r="H109" s="3"/>
+    </row>
+    <row r="110" spans="1:8">
       <c r="A110" s="1">
         <v>36892</v>
       </c>
+      <c r="B110" s="4">
+        <v>36923</v>
+      </c>
       <c r="C110" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D110" s="6">
+      <c r="D110" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E110" s="6">
         <v>272881</v>
       </c>
-      <c r="G110" s="3"/>
-    </row>
-    <row r="111" spans="1:7">
+      <c r="H110" s="3"/>
+    </row>
+    <row r="111" spans="1:8">
       <c r="A111" s="1">
         <v>36923</v>
       </c>
+      <c r="B111" s="4">
+        <v>36951</v>
+      </c>
       <c r="C111" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D111" s="6">
+      <c r="D111" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E111" s="6">
         <v>272627</v>
       </c>
-      <c r="G111" s="3"/>
-    </row>
-    <row r="112" spans="1:7">
+      <c r="H111" s="3"/>
+    </row>
+    <row r="112" spans="1:8">
       <c r="A112" s="1">
         <v>36951</v>
       </c>
+      <c r="B112" s="4">
+        <v>36982</v>
+      </c>
       <c r="C112" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D112" s="6">
+      <c r="D112" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E112" s="6">
         <v>269820</v>
       </c>
-      <c r="G112" s="3"/>
-    </row>
-    <row r="113" spans="1:7">
+      <c r="H112" s="3"/>
+    </row>
+    <row r="113" spans="1:8">
       <c r="A113" s="1">
         <v>36982</v>
       </c>
+      <c r="B113" s="4">
+        <v>37012</v>
+      </c>
       <c r="C113" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D113" s="6">
+      <c r="D113" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E113" s="6">
         <v>274410</v>
       </c>
-      <c r="G113" s="3"/>
-    </row>
-    <row r="114" spans="1:7">
+      <c r="H113" s="3"/>
+    </row>
+    <row r="114" spans="1:8">
       <c r="A114" s="1">
         <v>37012</v>
       </c>
@@ -1892,12 +2608,15 @@
       <c r="C114" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D114" s="6">
+      <c r="D114" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E114" s="6">
         <v>275769</v>
       </c>
-      <c r="G114" s="3"/>
-    </row>
-    <row r="115" spans="1:7">
+      <c r="H114" s="3"/>
+    </row>
+    <row r="115" spans="1:8">
       <c r="A115" s="1">
         <v>37043</v>
       </c>
@@ -1907,12 +2626,15 @@
       <c r="C115" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D115" s="6">
+      <c r="D115" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E115" s="6">
         <v>274474</v>
       </c>
-      <c r="G115" s="3"/>
-    </row>
-    <row r="116" spans="1:7">
+      <c r="H115" s="3"/>
+    </row>
+    <row r="116" spans="1:8">
       <c r="A116" s="1">
         <v>37073</v>
       </c>
@@ -1922,12 +2644,15 @@
       <c r="C116" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D116" s="6">
+      <c r="D116" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E116" s="6">
         <v>273098</v>
       </c>
-      <c r="G116" s="3"/>
-    </row>
-    <row r="117" spans="1:7">
+      <c r="H116" s="3"/>
+    </row>
+    <row r="117" spans="1:8">
       <c r="A117" s="1">
         <v>37104</v>
       </c>
@@ -1937,12 +2662,15 @@
       <c r="C117" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D117" s="6">
+      <c r="D117" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E117" s="6">
         <v>275659</v>
       </c>
-      <c r="G117" s="3"/>
-    </row>
-    <row r="118" spans="1:7">
+      <c r="H117" s="3"/>
+    </row>
+    <row r="118" spans="1:8">
       <c r="A118" s="1">
         <v>37135</v>
       </c>
@@ -1952,12 +2680,15 @@
       <c r="C118" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D118" s="6">
+      <c r="D118" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E118" s="6">
         <v>268652</v>
       </c>
-      <c r="G118" s="3"/>
-    </row>
-    <row r="119" spans="1:7">
+      <c r="H118" s="3"/>
+    </row>
+    <row r="119" spans="1:8">
       <c r="A119" s="1">
         <v>37165</v>
       </c>
@@ -1967,12 +2698,15 @@
       <c r="C119" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D119" s="6">
+      <c r="D119" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E119" s="6">
         <v>288632</v>
       </c>
-      <c r="G119" s="3"/>
-    </row>
-    <row r="120" spans="1:7">
+      <c r="H119" s="3"/>
+    </row>
+    <row r="120" spans="1:8">
       <c r="A120" s="1">
         <v>37196</v>
       </c>
@@ -1982,12 +2716,15 @@
       <c r="C120" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D120" s="6">
+      <c r="D120" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E120" s="6">
         <v>280033</v>
       </c>
-      <c r="G120" s="3"/>
-    </row>
-    <row r="121" spans="1:7">
+      <c r="H120" s="3"/>
+    </row>
+    <row r="121" spans="1:8">
       <c r="A121" s="1">
         <v>37226</v>
       </c>
@@ -1997,12 +2734,15 @@
       <c r="C121" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D121" s="6">
+      <c r="D121" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E121" s="6">
         <v>276302</v>
       </c>
-      <c r="G121" s="3"/>
-    </row>
-    <row r="122" spans="1:7">
+      <c r="H121" s="3"/>
+    </row>
+    <row r="122" spans="1:8">
       <c r="A122" s="1">
         <v>37257</v>
       </c>
@@ -2012,12 +2752,15 @@
       <c r="C122" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D122" s="6">
+      <c r="D122" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E122" s="6">
         <v>277135</v>
       </c>
-      <c r="G122" s="3"/>
-    </row>
-    <row r="123" spans="1:7">
+      <c r="H122" s="3"/>
+    </row>
+    <row r="123" spans="1:8">
       <c r="A123" s="1">
         <v>37288</v>
       </c>
@@ -2027,12 +2770,15 @@
       <c r="C123" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D123" s="6">
+      <c r="D123" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E123" s="6">
         <v>278869</v>
       </c>
-      <c r="G123" s="3"/>
-    </row>
-    <row r="124" spans="1:7">
+      <c r="H123" s="3"/>
+    </row>
+    <row r="124" spans="1:8">
       <c r="A124" s="1">
         <v>37316</v>
       </c>
@@ -2042,12 +2788,15 @@
       <c r="C124" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D124" s="6">
+      <c r="D124" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E124" s="6">
         <v>278079</v>
       </c>
-      <c r="G124" s="3"/>
-    </row>
-    <row r="125" spans="1:7">
+      <c r="H124" s="3"/>
+    </row>
+    <row r="125" spans="1:8">
       <c r="A125" s="1">
         <v>37347</v>
       </c>
@@ -2057,12 +2806,15 @@
       <c r="C125" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D125" s="6">
+      <c r="D125" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E125" s="6">
         <v>281147</v>
       </c>
-      <c r="G125" s="3"/>
-    </row>
-    <row r="126" spans="1:7">
+      <c r="H125" s="3"/>
+    </row>
+    <row r="126" spans="1:8">
       <c r="A126" s="1">
         <v>37377</v>
       </c>
@@ -2072,12 +2824,15 @@
       <c r="C126" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D126" s="6">
+      <c r="D126" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E126" s="6">
         <v>278966</v>
       </c>
-      <c r="G126" s="3"/>
-    </row>
-    <row r="127" spans="1:7">
+      <c r="H126" s="3"/>
+    </row>
+    <row r="127" spans="1:8">
       <c r="A127" s="1">
         <v>37408</v>
       </c>
@@ -2087,12 +2842,15 @@
       <c r="C127" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D127" s="6">
+      <c r="D127" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E127" s="6">
         <v>280426</v>
       </c>
-      <c r="G127" s="3"/>
-    </row>
-    <row r="128" spans="1:7">
+      <c r="H127" s="3"/>
+    </row>
+    <row r="128" spans="1:8">
       <c r="A128" s="1">
         <v>37438</v>
       </c>
@@ -2102,12 +2860,15 @@
       <c r="C128" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D128" s="6">
+      <c r="D128" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E128" s="6">
         <v>284161</v>
       </c>
-      <c r="G128" s="3"/>
-    </row>
-    <row r="129" spans="1:7">
+      <c r="H128" s="3"/>
+    </row>
+    <row r="129" spans="1:8">
       <c r="A129" s="1">
         <v>37469</v>
       </c>
@@ -2117,12 +2878,15 @@
       <c r="C129" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D129" s="6">
+      <c r="D129" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E129" s="6">
         <v>285884</v>
       </c>
-      <c r="G129" s="3"/>
-    </row>
-    <row r="130" spans="1:7">
+      <c r="H129" s="3"/>
+    </row>
+    <row r="130" spans="1:8">
       <c r="A130" s="1">
         <v>37500</v>
       </c>
@@ -2132,12 +2896,15 @@
       <c r="C130" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D130" s="6">
+      <c r="D130" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E130" s="6">
         <v>281064</v>
       </c>
-      <c r="G130" s="3"/>
-    </row>
-    <row r="131" spans="1:7">
+      <c r="H130" s="3"/>
+    </row>
+    <row r="131" spans="1:8">
       <c r="A131" s="1">
         <v>37530</v>
       </c>
@@ -2147,12 +2914,15 @@
       <c r="C131" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D131" s="6">
+      <c r="D131" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E131" s="6">
         <v>282940</v>
       </c>
-      <c r="G131" s="3"/>
-    </row>
-    <row r="132" spans="1:7">
+      <c r="H131" s="3"/>
+    </row>
+    <row r="132" spans="1:8">
       <c r="A132" s="1">
         <v>37561</v>
       </c>
@@ -2162,12 +2932,15 @@
       <c r="C132" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D132" s="6">
+      <c r="D132" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E132" s="6">
         <v>283408</v>
       </c>
-      <c r="G132" s="3"/>
-    </row>
-    <row r="133" spans="1:7">
+      <c r="H132" s="3"/>
+    </row>
+    <row r="133" spans="1:8">
       <c r="A133" s="1">
         <v>37591</v>
       </c>
@@ -2177,12 +2950,15 @@
       <c r="C133" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D133" s="6">
+      <c r="D133" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E133" s="6">
         <v>286646</v>
       </c>
-      <c r="G133" s="3"/>
-    </row>
-    <row r="134" spans="1:7">
+      <c r="H133" s="3"/>
+    </row>
+    <row r="134" spans="1:8">
       <c r="A134" s="1">
         <v>37622</v>
       </c>
@@ -2192,12 +2968,15 @@
       <c r="C134" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D134" s="6">
+      <c r="D134" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E134" s="6">
         <v>288657</v>
       </c>
-      <c r="G134" s="3"/>
-    </row>
-    <row r="135" spans="1:7">
+      <c r="H134" s="3"/>
+    </row>
+    <row r="135" spans="1:8">
       <c r="A135" s="1">
         <v>37653</v>
       </c>
@@ -2207,12 +2986,15 @@
       <c r="C135" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D135" s="6">
+      <c r="D135" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E135" s="6">
         <v>284696</v>
       </c>
-      <c r="G135" s="3"/>
-    </row>
-    <row r="136" spans="1:7">
+      <c r="H135" s="3"/>
+    </row>
+    <row r="136" spans="1:8">
       <c r="A136" s="1">
         <v>37681</v>
       </c>
@@ -2222,12 +3004,15 @@
       <c r="C136" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D136" s="6">
+      <c r="D136" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E136" s="6">
         <v>288177</v>
       </c>
-      <c r="G136" s="3"/>
-    </row>
-    <row r="137" spans="1:7">
+      <c r="H136" s="3"/>
+    </row>
+    <row r="137" spans="1:8">
       <c r="A137" s="1">
         <v>37712</v>
       </c>
@@ -2237,12 +3022,15 @@
       <c r="C137" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D137" s="6">
+      <c r="D137" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E137" s="6">
         <v>289053</v>
       </c>
-      <c r="G137" s="3"/>
-    </row>
-    <row r="138" spans="1:7">
+      <c r="H137" s="3"/>
+    </row>
+    <row r="138" spans="1:8">
       <c r="A138" s="1">
         <v>37742</v>
       </c>
@@ -2252,12 +3040,15 @@
       <c r="C138" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D138" s="6">
+      <c r="D138" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E138" s="6">
         <v>289619</v>
       </c>
-      <c r="G138" s="3"/>
-    </row>
-    <row r="139" spans="1:7">
+      <c r="H138" s="3"/>
+    </row>
+    <row r="139" spans="1:8">
       <c r="A139" s="1">
         <v>37773</v>
       </c>
@@ -2267,12 +3058,15 @@
       <c r="C139" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D139" s="6">
+      <c r="D139" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E139" s="6">
         <v>293671</v>
       </c>
-      <c r="G139" s="3"/>
-    </row>
-    <row r="140" spans="1:7">
+      <c r="H139" s="3"/>
+    </row>
+    <row r="140" spans="1:8">
       <c r="A140" s="1">
         <v>37803</v>
       </c>
@@ -2282,12 +3076,15 @@
       <c r="C140" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D140" s="6">
+      <c r="D140" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E140" s="6">
         <v>296207</v>
       </c>
-      <c r="G140" s="3"/>
-    </row>
-    <row r="141" spans="1:7">
+      <c r="H140" s="3"/>
+    </row>
+    <row r="141" spans="1:8">
       <c r="A141" s="1">
         <v>37834</v>
       </c>
@@ -2297,12 +3094,15 @@
       <c r="C141" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D141" s="6">
+      <c r="D141" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E141" s="6">
         <v>299592</v>
       </c>
-      <c r="G141" s="3"/>
-    </row>
-    <row r="142" spans="1:7">
+      <c r="H141" s="3"/>
+    </row>
+    <row r="142" spans="1:8">
       <c r="A142" s="1">
         <v>37865</v>
       </c>
@@ -2312,12 +3112,15 @@
       <c r="C142" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D142" s="6">
+      <c r="D142" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E142" s="6">
         <v>298921</v>
       </c>
-      <c r="G142" s="3"/>
-    </row>
-    <row r="143" spans="1:7">
+      <c r="H142" s="3"/>
+    </row>
+    <row r="143" spans="1:8">
       <c r="A143" s="1">
         <v>37895</v>
       </c>
@@ -2327,12 +3130,15 @@
       <c r="C143" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D143" s="6">
+      <c r="D143" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E143" s="6">
         <v>298205</v>
       </c>
-      <c r="G143" s="3"/>
-    </row>
-    <row r="144" spans="1:7">
+      <c r="H143" s="3"/>
+    </row>
+    <row r="144" spans="1:8">
       <c r="A144" s="1">
         <v>37926</v>
       </c>
@@ -2342,12 +3148,15 @@
       <c r="C144" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D144" s="6">
+      <c r="D144" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E144" s="6">
         <v>299433</v>
       </c>
-      <c r="G144" s="3"/>
-    </row>
-    <row r="145" spans="1:7">
+      <c r="H144" s="3"/>
+    </row>
+    <row r="145" spans="1:8">
       <c r="A145" s="1">
         <v>37956</v>
       </c>
@@ -2357,12 +3166,15 @@
       <c r="C145" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D145" s="6">
+      <c r="D145" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E145" s="6">
         <v>300702</v>
       </c>
-      <c r="G145" s="3"/>
-    </row>
-    <row r="146" spans="1:7">
+      <c r="H145" s="3"/>
+    </row>
+    <row r="146" spans="1:8">
       <c r="A146" s="1">
         <v>37987</v>
       </c>
@@ -2372,12 +3184,15 @@
       <c r="C146" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D146" s="6">
+      <c r="D146" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E146" s="6">
         <v>301993</v>
       </c>
-      <c r="G146" s="3"/>
-    </row>
-    <row r="147" spans="1:7">
+      <c r="H146" s="3"/>
+    </row>
+    <row r="147" spans="1:8">
       <c r="A147" s="1">
         <v>38018</v>
       </c>
@@ -2387,12 +3202,15 @@
       <c r="C147" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D147" s="6">
+      <c r="D147" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E147" s="6">
         <v>303915</v>
       </c>
-      <c r="G147" s="3"/>
-    </row>
-    <row r="148" spans="1:7">
+      <c r="H147" s="3"/>
+    </row>
+    <row r="148" spans="1:8">
       <c r="A148" s="1">
         <v>38047</v>
       </c>
@@ -2402,12 +3220,15 @@
       <c r="C148" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D148" s="6">
+      <c r="D148" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E148" s="6">
         <v>309471</v>
       </c>
-      <c r="G148" s="3"/>
-    </row>
-    <row r="149" spans="1:7">
+      <c r="H148" s="3"/>
+    </row>
+    <row r="149" spans="1:8">
       <c r="A149" s="1">
         <v>38078</v>
       </c>
@@ -2417,12 +3238,15 @@
       <c r="C149" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D149" s="6">
+      <c r="D149" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E149" s="6">
         <v>307358</v>
       </c>
-      <c r="G149" s="3"/>
-    </row>
-    <row r="150" spans="1:7">
+      <c r="H149" s="3"/>
+    </row>
+    <row r="150" spans="1:8">
       <c r="A150" s="1">
         <v>38108</v>
       </c>
@@ -2432,12 +3256,15 @@
       <c r="C150" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D150" s="6">
+      <c r="D150" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E150" s="6">
         <v>311088</v>
       </c>
-      <c r="G150" s="3"/>
-    </row>
-    <row r="151" spans="1:7">
+      <c r="H150" s="3"/>
+    </row>
+    <row r="151" spans="1:8">
       <c r="A151" s="1">
         <v>38139</v>
       </c>
@@ -2447,12 +3274,15 @@
       <c r="C151" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D151" s="6">
+      <c r="D151" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E151" s="6">
         <v>309127</v>
       </c>
-      <c r="G151" s="3"/>
-    </row>
-    <row r="152" spans="1:7">
+      <c r="H151" s="3"/>
+    </row>
+    <row r="152" spans="1:8">
       <c r="A152" s="1">
         <v>38169</v>
       </c>
@@ -2462,12 +3292,15 @@
       <c r="C152" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D152" s="6">
+      <c r="D152" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E152" s="6">
         <v>311681</v>
       </c>
-      <c r="G152" s="3"/>
-    </row>
-    <row r="153" spans="1:7">
+      <c r="H152" s="3"/>
+    </row>
+    <row r="153" spans="1:8">
       <c r="A153" s="1">
         <v>38200</v>
       </c>
@@ -2477,12 +3310,15 @@
       <c r="C153" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D153" s="6">
+      <c r="D153" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E153" s="6">
         <v>311192</v>
       </c>
-      <c r="G153" s="3"/>
-    </row>
-    <row r="154" spans="1:7">
+      <c r="H153" s="3"/>
+    </row>
+    <row r="154" spans="1:8">
       <c r="A154" s="1">
         <v>38231</v>
       </c>
@@ -2492,12 +3328,15 @@
       <c r="C154" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D154" s="6">
+      <c r="D154" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E154" s="6">
         <v>317446</v>
       </c>
-      <c r="G154" s="3"/>
-    </row>
-    <row r="155" spans="1:7">
+      <c r="H154" s="3"/>
+    </row>
+    <row r="155" spans="1:8">
       <c r="A155" s="1">
         <v>38261</v>
       </c>
@@ -2507,12 +3346,15 @@
       <c r="C155" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D155" s="6">
+      <c r="D155" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E155" s="6">
         <v>318476</v>
       </c>
-      <c r="G155" s="3"/>
-    </row>
-    <row r="156" spans="1:7">
+      <c r="H155" s="3"/>
+    </row>
+    <row r="156" spans="1:8">
       <c r="A156" s="1">
         <v>38292</v>
       </c>
@@ -2522,12 +3364,15 @@
       <c r="C156" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D156" s="6">
+      <c r="D156" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E156" s="6">
         <v>320520</v>
       </c>
-      <c r="G156" s="3"/>
-    </row>
-    <row r="157" spans="1:7">
+      <c r="H156" s="3"/>
+    </row>
+    <row r="157" spans="1:8">
       <c r="A157" s="1">
         <v>38322</v>
       </c>
@@ -2537,12 +3382,15 @@
       <c r="C157" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D157" s="6">
+      <c r="D157" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E157" s="6">
         <v>324672</v>
       </c>
-      <c r="G157" s="3"/>
-    </row>
-    <row r="158" spans="1:7">
+      <c r="H157" s="3"/>
+    </row>
+    <row r="158" spans="1:8">
       <c r="A158" s="1">
         <v>38353</v>
       </c>
@@ -2552,12 +3400,15 @@
       <c r="C158" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D158" s="6">
+      <c r="D158" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E158" s="6">
         <v>321272</v>
       </c>
-      <c r="G158" s="3"/>
-    </row>
-    <row r="159" spans="1:7">
+      <c r="H158" s="3"/>
+    </row>
+    <row r="159" spans="1:8">
       <c r="A159" s="1">
         <v>38384</v>
       </c>
@@ -2567,12 +3418,15 @@
       <c r="C159" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D159" s="6">
+      <c r="D159" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E159" s="6">
         <v>325308</v>
       </c>
-      <c r="G159" s="3"/>
-    </row>
-    <row r="160" spans="1:7">
+      <c r="H159" s="3"/>
+    </row>
+    <row r="160" spans="1:8">
       <c r="A160" s="1">
         <v>38412</v>
       </c>
@@ -2582,12 +3436,15 @@
       <c r="C160" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D160" s="6">
+      <c r="D160" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E160" s="6">
         <v>326179</v>
       </c>
-      <c r="G160" s="3"/>
-    </row>
-    <row r="161" spans="1:7">
+      <c r="H160" s="3"/>
+    </row>
+    <row r="161" spans="1:8">
       <c r="A161" s="1">
         <v>38443</v>
       </c>
@@ -2597,12 +3454,15 @@
       <c r="C161" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D161" s="6">
+      <c r="D161" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E161" s="6">
         <v>329124</v>
       </c>
-      <c r="G161" s="3"/>
-    </row>
-    <row r="162" spans="1:7">
+      <c r="H161" s="3"/>
+    </row>
+    <row r="162" spans="1:8">
       <c r="A162" s="1">
         <v>38473</v>
       </c>
@@ -2612,12 +3472,15 @@
       <c r="C162" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D162" s="6">
+      <c r="D162" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E162" s="6">
         <v>327233</v>
       </c>
-      <c r="G162" s="3"/>
-    </row>
-    <row r="163" spans="1:7">
+      <c r="H162" s="3"/>
+    </row>
+    <row r="163" spans="1:8">
       <c r="A163" s="1">
         <v>38504</v>
       </c>
@@ -2627,12 +3490,15 @@
       <c r="C163" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D163" s="6">
+      <c r="D163" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E163" s="6">
         <v>337219</v>
       </c>
-      <c r="G163" s="3"/>
-    </row>
-    <row r="164" spans="1:7">
+      <c r="H163" s="3"/>
+    </row>
+    <row r="164" spans="1:8">
       <c r="A164" s="1">
         <v>38534</v>
       </c>
@@ -2642,12 +3508,15 @@
       <c r="C164" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D164" s="6">
+      <c r="D164" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E164" s="6">
         <v>339529</v>
       </c>
-      <c r="G164" s="3"/>
-    </row>
-    <row r="165" spans="1:7">
+      <c r="H164" s="3"/>
+    </row>
+    <row r="165" spans="1:8">
       <c r="A165" s="1">
         <v>38565</v>
       </c>
@@ -2657,12 +3526,15 @@
       <c r="C165" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D165" s="6">
+      <c r="D165" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E165" s="6">
         <v>335605</v>
       </c>
-      <c r="G165" s="3"/>
-    </row>
-    <row r="166" spans="1:7">
+      <c r="H165" s="3"/>
+    </row>
+    <row r="166" spans="1:8">
       <c r="A166" s="1">
         <v>38596</v>
       </c>
@@ -2672,12 +3544,15 @@
       <c r="C166" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D166" s="6">
+      <c r="D166" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E166" s="6">
         <v>336600</v>
       </c>
-      <c r="G166" s="3"/>
-    </row>
-    <row r="167" spans="1:7">
+      <c r="H166" s="3"/>
+    </row>
+    <row r="167" spans="1:8">
       <c r="A167" s="1">
         <v>38626</v>
       </c>
@@ -2687,12 +3562,15 @@
       <c r="C167" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D167" s="6">
+      <c r="D167" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E167" s="6">
         <v>336753</v>
       </c>
-      <c r="G167" s="3"/>
-    </row>
-    <row r="168" spans="1:7">
+      <c r="H167" s="3"/>
+    </row>
+    <row r="168" spans="1:8">
       <c r="A168" s="1">
         <v>38657</v>
       </c>
@@ -2702,12 +3580,15 @@
       <c r="C168" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D168" s="6">
+      <c r="D168" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E168" s="6">
         <v>339719</v>
       </c>
-      <c r="G168" s="3"/>
-    </row>
-    <row r="169" spans="1:7">
+      <c r="H168" s="3"/>
+    </row>
+    <row r="169" spans="1:8">
       <c r="A169" s="1">
         <v>38687</v>
       </c>
@@ -2717,12 +3598,15 @@
       <c r="C169" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D169" s="6">
+      <c r="D169" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E169" s="6">
         <v>339895</v>
       </c>
-      <c r="G169" s="3"/>
-    </row>
-    <row r="170" spans="1:7">
+      <c r="H169" s="3"/>
+    </row>
+    <row r="170" spans="1:8">
       <c r="A170" s="1">
         <v>38718</v>
       </c>
@@ -2732,12 +3616,15 @@
       <c r="C170" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D170" s="6">
+      <c r="D170" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E170" s="6">
         <v>349664</v>
       </c>
-      <c r="G170" s="3"/>
-    </row>
-    <row r="171" spans="1:7">
+      <c r="H170" s="3"/>
+    </row>
+    <row r="171" spans="1:8">
       <c r="A171" s="1">
         <v>38749</v>
       </c>
@@ -2747,12 +3634,15 @@
       <c r="C171" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D171" s="6">
+      <c r="D171" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E171" s="6">
         <v>347021</v>
       </c>
-      <c r="G171" s="3"/>
-    </row>
-    <row r="172" spans="1:7">
+      <c r="H171" s="3"/>
+    </row>
+    <row r="172" spans="1:8">
       <c r="A172" s="1">
         <v>38777</v>
       </c>
@@ -2762,12 +3652,15 @@
       <c r="C172" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D172" s="6">
+      <c r="D172" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E172" s="6">
         <v>348357</v>
       </c>
-      <c r="G172" s="3"/>
-    </row>
-    <row r="173" spans="1:7">
+      <c r="H172" s="3"/>
+    </row>
+    <row r="173" spans="1:8">
       <c r="A173" s="1">
         <v>38808</v>
       </c>
@@ -2777,12 +3670,15 @@
       <c r="C173" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D173" s="6">
+      <c r="D173" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E173" s="6">
         <v>350072</v>
       </c>
-      <c r="G173" s="3"/>
-    </row>
-    <row r="174" spans="1:7">
+      <c r="H173" s="3"/>
+    </row>
+    <row r="174" spans="1:8">
       <c r="A174" s="1">
         <v>38838</v>
       </c>
@@ -2792,12 +3688,15 @@
       <c r="C174" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D174" s="6">
+      <c r="D174" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E174" s="6">
         <v>348889</v>
       </c>
-      <c r="G174" s="3"/>
-    </row>
-    <row r="175" spans="1:7">
+      <c r="H174" s="3"/>
+    </row>
+    <row r="175" spans="1:8">
       <c r="A175" s="1">
         <v>38869</v>
       </c>
@@ -2807,12 +3706,15 @@
       <c r="C175" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D175" s="6">
+      <c r="D175" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E175" s="6">
         <v>350795</v>
       </c>
-      <c r="G175" s="3"/>
-    </row>
-    <row r="176" spans="1:7">
+      <c r="H175" s="3"/>
+    </row>
+    <row r="176" spans="1:8">
       <c r="A176" s="1">
         <v>38899</v>
       </c>
@@ -2822,12 +3724,15 @@
       <c r="C176" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D176" s="6">
+      <c r="D176" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E176" s="6">
         <v>351916</v>
       </c>
-      <c r="G176" s="3"/>
-    </row>
-    <row r="177" spans="1:7">
+      <c r="H176" s="3"/>
+    </row>
+    <row r="177" spans="1:8">
       <c r="A177" s="1">
         <v>38930</v>
       </c>
@@ -2837,12 +3742,15 @@
       <c r="C177" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D177" s="6">
+      <c r="D177" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E177" s="6">
         <v>353285</v>
       </c>
-      <c r="G177" s="3"/>
-    </row>
-    <row r="178" spans="1:7">
+      <c r="H177" s="3"/>
+    </row>
+    <row r="178" spans="1:8">
       <c r="A178" s="1">
         <v>38961</v>
       </c>
@@ -2852,12 +3760,15 @@
       <c r="C178" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D178" s="6">
+      <c r="D178" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E178" s="6">
         <v>351240</v>
       </c>
-      <c r="G178" s="3"/>
-    </row>
-    <row r="179" spans="1:7">
+      <c r="H178" s="3"/>
+    </row>
+    <row r="179" spans="1:8">
       <c r="A179" s="1">
         <v>38991</v>
       </c>
@@ -2867,12 +3778,15 @@
       <c r="C179" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D179" s="6">
+      <c r="D179" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E179" s="6">
         <v>351035</v>
       </c>
-      <c r="G179" s="3"/>
-    </row>
-    <row r="180" spans="1:7">
+      <c r="H179" s="3"/>
+    </row>
+    <row r="180" spans="1:8">
       <c r="A180" s="1">
         <v>39022</v>
       </c>
@@ -2882,12 +3796,15 @@
       <c r="C180" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D180" s="6">
+      <c r="D180" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E180" s="6">
         <v>352116</v>
       </c>
-      <c r="G180" s="3"/>
-    </row>
-    <row r="181" spans="1:7">
+      <c r="H180" s="3"/>
+    </row>
+    <row r="181" spans="1:8">
       <c r="A181" s="1">
         <v>39052</v>
       </c>
@@ -2897,12 +3814,15 @@
       <c r="C181" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D181" s="6">
+      <c r="D181" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E181" s="6">
         <v>356367</v>
       </c>
-      <c r="G181" s="3"/>
-    </row>
-    <row r="182" spans="1:7">
+      <c r="H181" s="3"/>
+    </row>
+    <row r="182" spans="1:8">
       <c r="A182" s="1">
         <v>39083</v>
       </c>
@@ -2912,12 +3832,15 @@
       <c r="C182" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D182" s="6">
+      <c r="D182" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E182" s="6">
         <v>355792</v>
       </c>
-      <c r="G182" s="3"/>
-    </row>
-    <row r="183" spans="1:7">
+      <c r="H182" s="3"/>
+    </row>
+    <row r="183" spans="1:8">
       <c r="A183" s="1">
         <v>39114</v>
       </c>
@@ -2927,12 +3850,15 @@
       <c r="C183" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D183" s="6">
+      <c r="D183" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E183" s="6">
         <v>356545</v>
       </c>
-      <c r="G183" s="3"/>
-    </row>
-    <row r="184" spans="1:7">
+      <c r="H183" s="3"/>
+    </row>
+    <row r="184" spans="1:8">
       <c r="A184" s="1">
         <v>39142</v>
       </c>
@@ -2942,12 +3868,15 @@
       <c r="C184" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D184" s="6">
+      <c r="D184" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E184" s="6">
         <v>359415</v>
       </c>
-      <c r="G184" s="3"/>
-    </row>
-    <row r="185" spans="1:7">
+      <c r="H184" s="3"/>
+    </row>
+    <row r="185" spans="1:8">
       <c r="A185" s="1">
         <v>39173</v>
       </c>
@@ -2957,12 +3886,15 @@
       <c r="C185" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D185" s="6">
+      <c r="D185" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E185" s="6">
         <v>358562</v>
       </c>
-      <c r="G185" s="3"/>
-    </row>
-    <row r="186" spans="1:7">
+      <c r="H185" s="3"/>
+    </row>
+    <row r="186" spans="1:8">
       <c r="A186" s="1">
         <v>39203</v>
       </c>
@@ -2972,12 +3904,15 @@
       <c r="C186" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D186" s="6">
+      <c r="D186" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E186" s="6">
         <v>363085</v>
       </c>
-      <c r="G186" s="3"/>
-    </row>
-    <row r="187" spans="1:7">
+      <c r="H186" s="3"/>
+    </row>
+    <row r="187" spans="1:8">
       <c r="A187" s="1">
         <v>39234</v>
       </c>
@@ -2987,12 +3922,15 @@
       <c r="C187" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D187" s="6">
+      <c r="D187" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E187" s="6">
         <v>360234</v>
       </c>
-      <c r="G187" s="3"/>
-    </row>
-    <row r="188" spans="1:7">
+      <c r="H187" s="3"/>
+    </row>
+    <row r="188" spans="1:8">
       <c r="A188" s="1">
         <v>39264</v>
       </c>
@@ -3002,12 +3940,15 @@
       <c r="C188" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D188" s="6">
+      <c r="D188" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E188" s="6">
         <v>361770</v>
       </c>
-      <c r="G188" s="3"/>
-    </row>
-    <row r="189" spans="1:7">
+      <c r="H188" s="3"/>
+    </row>
+    <row r="189" spans="1:8">
       <c r="A189" s="1">
         <v>39295</v>
       </c>
@@ -3017,12 +3958,15 @@
       <c r="C189" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D189" s="6">
+      <c r="D189" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E189" s="6">
         <v>363676</v>
       </c>
-      <c r="G189" s="3"/>
-    </row>
-    <row r="190" spans="1:7">
+      <c r="H189" s="3"/>
+    </row>
+    <row r="190" spans="1:8">
       <c r="A190" s="1">
         <v>39326</v>
       </c>
@@ -3032,12 +3976,15 @@
       <c r="C190" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D190" s="6">
+      <c r="D190" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E190" s="6">
         <v>365178</v>
       </c>
-      <c r="G190" s="3"/>
-    </row>
-    <row r="191" spans="1:7">
+      <c r="H190" s="3"/>
+    </row>
+    <row r="191" spans="1:8">
       <c r="A191" s="1">
         <v>39356</v>
       </c>
@@ -3047,12 +3994,15 @@
       <c r="C191" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D191" s="6">
+      <c r="D191" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E191" s="6">
         <v>367322</v>
       </c>
-      <c r="G191" s="3"/>
-    </row>
-    <row r="192" spans="1:7">
+      <c r="H191" s="3"/>
+    </row>
+    <row r="192" spans="1:8">
       <c r="A192" s="1">
         <v>39387</v>
       </c>
@@ -3062,12 +4012,15 @@
       <c r="C192" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D192" s="6">
+      <c r="D192" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E192" s="6">
         <v>370776</v>
       </c>
-      <c r="G192" s="3"/>
-    </row>
-    <row r="193" spans="1:7">
+      <c r="H192" s="3"/>
+    </row>
+    <row r="193" spans="1:8">
       <c r="A193" s="1">
         <v>39417</v>
       </c>
@@ -3077,12 +4030,15 @@
       <c r="C193" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D193" s="6">
+      <c r="D193" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E193" s="6">
         <v>366569</v>
       </c>
-      <c r="G193" s="3"/>
-    </row>
-    <row r="194" spans="1:7">
+      <c r="H193" s="3"/>
+    </row>
+    <row r="194" spans="1:8">
       <c r="A194" s="1">
         <v>39448</v>
       </c>
@@ -3092,12 +4048,15 @@
       <c r="C194" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D194" s="6">
+      <c r="D194" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E194" s="6">
         <v>367368</v>
       </c>
-      <c r="G194" s="3"/>
-    </row>
-    <row r="195" spans="1:7">
+      <c r="H194" s="3"/>
+    </row>
+    <row r="195" spans="1:8">
       <c r="A195" s="1">
         <v>39479</v>
       </c>
@@ -3107,12 +4066,15 @@
       <c r="C195" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D195" s="6">
+      <c r="D195" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E195" s="6">
         <v>364126</v>
       </c>
-      <c r="G195" s="3"/>
-    </row>
-    <row r="196" spans="1:7">
+      <c r="H195" s="3"/>
+    </row>
+    <row r="196" spans="1:8">
       <c r="A196" s="1">
         <v>39508</v>
       </c>
@@ -3122,12 +4084,15 @@
       <c r="C196" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D196" s="6">
+      <c r="D196" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E196" s="6">
         <v>365164</v>
       </c>
-      <c r="G196" s="3"/>
-    </row>
-    <row r="197" spans="1:7">
+      <c r="H196" s="3"/>
+    </row>
+    <row r="197" spans="1:8">
       <c r="A197" s="1">
         <v>39539</v>
       </c>
@@ -3137,12 +4102,15 @@
       <c r="C197" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D197" s="6">
+      <c r="D197" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E197" s="6">
         <v>364816</v>
       </c>
-      <c r="G197" s="3"/>
-    </row>
-    <row r="198" spans="1:7">
+      <c r="H197" s="3"/>
+    </row>
+    <row r="198" spans="1:8">
       <c r="A198" s="1">
         <v>39569</v>
       </c>
@@ -3152,12 +4120,15 @@
       <c r="C198" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D198" s="6">
+      <c r="D198" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E198" s="6">
         <v>368255</v>
       </c>
-      <c r="G198" s="3"/>
-    </row>
-    <row r="199" spans="1:7">
+      <c r="H198" s="3"/>
+    </row>
+    <row r="199" spans="1:8">
       <c r="A199" s="1">
         <v>39600</v>
       </c>
@@ -3167,12 +4138,15 @@
       <c r="C199" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D199" s="6">
+      <c r="D199" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E199" s="6">
         <v>368926</v>
       </c>
-      <c r="G199" s="3"/>
-    </row>
-    <row r="200" spans="1:7">
+      <c r="H199" s="3"/>
+    </row>
+    <row r="200" spans="1:8">
       <c r="A200" s="1">
         <v>39630</v>
       </c>
@@ -3182,12 +4156,15 @@
       <c r="C200" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D200" s="6">
+      <c r="D200" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E200" s="6">
         <v>367594</v>
       </c>
-      <c r="G200" s="3"/>
-    </row>
-    <row r="201" spans="1:7">
+      <c r="H200" s="3"/>
+    </row>
+    <row r="201" spans="1:8">
       <c r="A201" s="1">
         <v>39661</v>
       </c>
@@ -3197,12 +4174,15 @@
       <c r="C201" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D201" s="6">
+      <c r="D201" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E201" s="6">
         <v>364611</v>
       </c>
-      <c r="G201" s="3"/>
-    </row>
-    <row r="202" spans="1:7">
+      <c r="H201" s="3"/>
+    </row>
+    <row r="202" spans="1:8">
       <c r="A202" s="1">
         <v>39692</v>
       </c>
@@ -3212,12 +4192,15 @@
       <c r="C202" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D202" s="6">
+      <c r="D202" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E202" s="6">
         <v>358991</v>
       </c>
-      <c r="G202" s="3"/>
-    </row>
-    <row r="203" spans="1:7">
+      <c r="H202" s="3"/>
+    </row>
+    <row r="203" spans="1:8">
       <c r="A203" s="1">
         <v>39722</v>
       </c>
@@ -3227,12 +4210,15 @@
       <c r="C203" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D203" s="6">
+      <c r="D203" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E203" s="6">
         <v>346137</v>
       </c>
-      <c r="G203" s="3"/>
-    </row>
-    <row r="204" spans="1:7">
+      <c r="H203" s="3"/>
+    </row>
+    <row r="204" spans="1:8">
       <c r="A204" s="1">
         <v>39753</v>
       </c>
@@ -3242,12 +4228,15 @@
       <c r="C204" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D204" s="6">
+      <c r="D204" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E204" s="6">
         <v>332498</v>
       </c>
-      <c r="G204" s="3"/>
-    </row>
-    <row r="205" spans="1:7">
+      <c r="H204" s="3"/>
+    </row>
+    <row r="205" spans="1:8">
       <c r="A205" s="1">
         <v>39783</v>
       </c>
@@ -3257,12 +4246,15 @@
       <c r="C205" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D205" s="6">
+      <c r="D205" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E205" s="6">
         <v>324767</v>
       </c>
-      <c r="G205" s="3"/>
-    </row>
-    <row r="206" spans="1:7">
+      <c r="H205" s="3"/>
+    </row>
+    <row r="206" spans="1:8">
       <c r="A206" s="1">
         <v>39814</v>
       </c>
@@ -3272,12 +4264,15 @@
       <c r="C206" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D206" s="6">
+      <c r="D206" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E206" s="6">
         <v>329787</v>
       </c>
-      <c r="G206" s="3"/>
-    </row>
-    <row r="207" spans="1:7">
+      <c r="H206" s="3"/>
+    </row>
+    <row r="207" spans="1:8">
       <c r="A207" s="1">
         <v>39845</v>
       </c>
@@ -3287,12 +4282,15 @@
       <c r="C207" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D207" s="6">
+      <c r="D207" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E207" s="6">
         <v>328376</v>
       </c>
-      <c r="G207" s="3"/>
-    </row>
-    <row r="208" spans="1:7">
+      <c r="H207" s="3"/>
+    </row>
+    <row r="208" spans="1:8">
       <c r="A208" s="1">
         <v>39873</v>
       </c>
@@ -3302,12 +4300,15 @@
       <c r="C208" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D208" s="6">
+      <c r="D208" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E208" s="6">
         <v>322634</v>
       </c>
-      <c r="G208" s="3"/>
-    </row>
-    <row r="209" spans="1:7">
+      <c r="H208" s="3"/>
+    </row>
+    <row r="209" spans="1:8">
       <c r="A209" s="1">
         <v>39904</v>
       </c>
@@ -3317,12 +4318,15 @@
       <c r="C209" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D209" s="6">
+      <c r="D209" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E209" s="6">
         <v>324323</v>
       </c>
-      <c r="G209" s="3"/>
-    </row>
-    <row r="210" spans="1:7">
+      <c r="H209" s="3"/>
+    </row>
+    <row r="210" spans="1:8">
       <c r="A210" s="1">
         <v>39934</v>
       </c>
@@ -3332,12 +4336,15 @@
       <c r="C210" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D210" s="6">
+      <c r="D210" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E210" s="6">
         <v>327011</v>
       </c>
-      <c r="G210" s="3"/>
-    </row>
-    <row r="211" spans="1:7">
+      <c r="H210" s="3"/>
+    </row>
+    <row r="211" spans="1:8">
       <c r="A211" s="1">
         <v>39965</v>
       </c>
@@ -3347,12 +4354,15 @@
       <c r="C211" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D211" s="6">
+      <c r="D211" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E211" s="6">
         <v>332227</v>
       </c>
-      <c r="G211" s="3"/>
-    </row>
-    <row r="212" spans="1:7">
+      <c r="H211" s="3"/>
+    </row>
+    <row r="212" spans="1:8">
       <c r="A212" s="1">
         <v>39995</v>
       </c>
@@ -3362,12 +4372,15 @@
       <c r="C212" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D212" s="6">
+      <c r="D212" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E212" s="6">
         <v>333670</v>
       </c>
-      <c r="G212" s="3"/>
-    </row>
-    <row r="213" spans="1:7">
+      <c r="H212" s="3"/>
+    </row>
+    <row r="213" spans="1:8">
       <c r="A213" s="1">
         <v>40026</v>
       </c>
@@ -3377,12 +4390,15 @@
       <c r="C213" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D213" s="6">
+      <c r="D213" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E213" s="6">
         <v>339586</v>
       </c>
-      <c r="G213" s="3"/>
-    </row>
-    <row r="214" spans="1:7">
+      <c r="H213" s="3"/>
+    </row>
+    <row r="214" spans="1:8">
       <c r="A214" s="1">
         <v>40057</v>
       </c>
@@ -3392,12 +4408,15 @@
       <c r="C214" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D214" s="6">
+      <c r="D214" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E214" s="6">
         <v>330998</v>
       </c>
-      <c r="G214" s="3"/>
-    </row>
-    <row r="215" spans="1:7">
+      <c r="H214" s="3"/>
+    </row>
+    <row r="215" spans="1:8">
       <c r="A215" s="1">
         <v>40087</v>
       </c>
@@ -3407,12 +4426,15 @@
       <c r="C215" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D215" s="6">
+      <c r="D215" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E215" s="6">
         <v>334595</v>
       </c>
-      <c r="G215" s="3"/>
-    </row>
-    <row r="216" spans="1:7">
+      <c r="H215" s="3"/>
+    </row>
+    <row r="216" spans="1:8">
       <c r="A216" s="1">
         <v>40118</v>
       </c>
@@ -3422,12 +4444,15 @@
       <c r="C216" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D216" s="6">
+      <c r="D216" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E216" s="6">
         <v>337321</v>
       </c>
-      <c r="G216" s="3"/>
-    </row>
-    <row r="217" spans="1:7">
+      <c r="H216" s="3"/>
+    </row>
+    <row r="217" spans="1:8">
       <c r="A217" s="1">
         <v>40148</v>
       </c>
@@ -3437,12 +4462,15 @@
       <c r="C217" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D217" s="6">
+      <c r="D217" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E217" s="6">
         <v>338736</v>
       </c>
-      <c r="G217" s="3"/>
-    </row>
-    <row r="218" spans="1:7">
+      <c r="H217" s="3"/>
+    </row>
+    <row r="218" spans="1:8">
       <c r="A218" s="1">
         <v>40179</v>
       </c>
@@ -3452,12 +4480,15 @@
       <c r="C218" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D218" s="6">
+      <c r="D218" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E218" s="6">
         <v>339093</v>
       </c>
-      <c r="G218" s="3"/>
-    </row>
-    <row r="219" spans="1:7">
+      <c r="H218" s="3"/>
+    </row>
+    <row r="219" spans="1:8">
       <c r="A219" s="1">
         <v>40210</v>
       </c>
@@ -3467,12 +4498,15 @@
       <c r="C219" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D219" s="6">
+      <c r="D219" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E219" s="6">
         <v>339580</v>
       </c>
-      <c r="G219" s="3"/>
-    </row>
-    <row r="220" spans="1:7">
+      <c r="H219" s="3"/>
+    </row>
+    <row r="220" spans="1:8">
       <c r="A220" s="1">
         <v>40238</v>
       </c>
@@ -3482,12 +4516,15 @@
       <c r="C220" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D220" s="6">
+      <c r="D220" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E220" s="6">
         <v>346974</v>
       </c>
-      <c r="G220" s="3"/>
-    </row>
-    <row r="221" spans="1:7">
+      <c r="H220" s="3"/>
+    </row>
+    <row r="221" spans="1:8">
       <c r="A221" s="1">
         <v>40269</v>
       </c>
@@ -3497,12 +4534,15 @@
       <c r="C221" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D221" s="6">
+      <c r="D221" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E221" s="6">
         <v>349869</v>
       </c>
-      <c r="G221" s="3"/>
-    </row>
-    <row r="222" spans="1:7">
+      <c r="H221" s="3"/>
+    </row>
+    <row r="222" spans="1:8">
       <c r="A222" s="1">
         <v>40299</v>
       </c>
@@ -3512,12 +4552,15 @@
       <c r="C222" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D222" s="6">
+      <c r="D222" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E222" s="6">
         <v>346858</v>
       </c>
-      <c r="G222" s="3"/>
-    </row>
-    <row r="223" spans="1:7">
+      <c r="H222" s="3"/>
+    </row>
+    <row r="223" spans="1:8">
       <c r="A223" s="1">
         <v>40330</v>
       </c>
@@ -3527,12 +4570,15 @@
       <c r="C223" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D223" s="6">
+      <c r="D223" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E223" s="6">
         <v>346516</v>
       </c>
-      <c r="G223" s="3"/>
-    </row>
-    <row r="224" spans="1:7">
+      <c r="H223" s="3"/>
+    </row>
+    <row r="224" spans="1:8">
       <c r="A224" s="1">
         <v>40360</v>
       </c>
@@ -3542,12 +4588,15 @@
       <c r="C224" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D224" s="6">
+      <c r="D224" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E224" s="6">
         <v>347612</v>
       </c>
-      <c r="G224" s="3"/>
-    </row>
-    <row r="225" spans="1:7">
+      <c r="H224" s="3"/>
+    </row>
+    <row r="225" spans="1:8">
       <c r="A225" s="1">
         <v>40391</v>
       </c>
@@ -3557,12 +4606,15 @@
       <c r="C225" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D225" s="6">
+      <c r="D225" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E225" s="6">
         <v>349188</v>
       </c>
-      <c r="G225" s="3"/>
-    </row>
-    <row r="226" spans="1:7">
+      <c r="H225" s="3"/>
+    </row>
+    <row r="226" spans="1:8">
       <c r="A226" s="1">
         <v>40422</v>
       </c>
@@ -3572,12 +4624,15 @@
       <c r="C226" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D226" s="6">
+      <c r="D226" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E226" s="6">
         <v>352179</v>
       </c>
-      <c r="G226" s="3"/>
-    </row>
-    <row r="227" spans="1:7">
+      <c r="H226" s="3"/>
+    </row>
+    <row r="227" spans="1:8">
       <c r="A227" s="1">
         <v>40452</v>
       </c>
@@ -3587,12 +4642,15 @@
       <c r="C227" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D227" s="6">
+      <c r="D227" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E227" s="6">
         <v>356215</v>
       </c>
-      <c r="G227" s="3"/>
-    </row>
-    <row r="228" spans="1:7">
+      <c r="H227" s="3"/>
+    </row>
+    <row r="228" spans="1:8">
       <c r="A228" s="1">
         <v>40483</v>
       </c>
@@ -3602,12 +4660,15 @@
       <c r="C228" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D228" s="6">
+      <c r="D228" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E228" s="6">
         <v>359450</v>
       </c>
-      <c r="G228" s="3"/>
-    </row>
-    <row r="229" spans="1:7">
+      <c r="H228" s="3"/>
+    </row>
+    <row r="229" spans="1:8">
       <c r="A229" s="1">
         <v>40513</v>
       </c>
@@ -3617,12 +4678,15 @@
       <c r="C229" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D229" s="6">
+      <c r="D229" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E229" s="6">
         <v>361979</v>
       </c>
-      <c r="G229" s="3"/>
-    </row>
-    <row r="230" spans="1:7">
+      <c r="H229" s="3"/>
+    </row>
+    <row r="230" spans="1:8">
       <c r="A230" s="1">
         <v>40544</v>
       </c>
@@ -3632,12 +4696,15 @@
       <c r="C230" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D230" s="6">
+      <c r="D230" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E230" s="6">
         <v>364394</v>
       </c>
-      <c r="G230" s="3"/>
-    </row>
-    <row r="231" spans="1:7">
+      <c r="H230" s="3"/>
+    </row>
+    <row r="231" spans="1:8">
       <c r="A231" s="1">
         <v>40575</v>
       </c>
@@ -3647,12 +4714,15 @@
       <c r="C231" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D231" s="6">
+      <c r="D231" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E231" s="6">
         <v>367475</v>
       </c>
-      <c r="G231" s="3"/>
-    </row>
-    <row r="232" spans="1:7">
+      <c r="H231" s="3"/>
+    </row>
+    <row r="232" spans="1:8">
       <c r="A232" s="1">
         <v>40603</v>
       </c>
@@ -3662,12 +4732,15 @@
       <c r="C232" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D232" s="6">
+      <c r="D232" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E232" s="6">
         <v>370775</v>
       </c>
-      <c r="G232" s="3"/>
-    </row>
-    <row r="233" spans="1:7">
+      <c r="H232" s="3"/>
+    </row>
+    <row r="233" spans="1:8">
       <c r="A233" s="1">
         <v>40634</v>
       </c>
@@ -3677,12 +4750,15 @@
       <c r="C233" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D233" s="6">
+      <c r="D233" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E233" s="6">
         <v>372820</v>
       </c>
-      <c r="G233" s="3"/>
-    </row>
-    <row r="234" spans="1:7">
+      <c r="H233" s="3"/>
+    </row>
+    <row r="234" spans="1:8">
       <c r="A234" s="1">
         <v>40664</v>
       </c>
@@ -3692,12 +4768,15 @@
       <c r="C234" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D234" s="6">
+      <c r="D234" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E234" s="6">
         <v>372505</v>
       </c>
-      <c r="G234" s="3"/>
-    </row>
-    <row r="235" spans="1:7">
+      <c r="H234" s="3"/>
+    </row>
+    <row r="235" spans="1:8">
       <c r="A235" s="1">
         <v>40695</v>
       </c>
@@ -3707,12 +4786,15 @@
       <c r="C235" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D235" s="6">
+      <c r="D235" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E235" s="6">
         <v>375587</v>
       </c>
-      <c r="G235" s="3"/>
-    </row>
-    <row r="236" spans="1:7">
+      <c r="H235" s="3"/>
+    </row>
+    <row r="236" spans="1:8">
       <c r="A236" s="1">
         <v>40725</v>
       </c>
@@ -3722,12 +4804,15 @@
       <c r="C236" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D236" s="6">
+      <c r="D236" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E236" s="6">
         <v>375442</v>
       </c>
-      <c r="G236" s="3"/>
-    </row>
-    <row r="237" spans="1:7">
+      <c r="H236" s="3"/>
+    </row>
+    <row r="237" spans="1:8">
       <c r="A237" s="1">
         <v>40756</v>
       </c>
@@ -3737,12 +4822,15 @@
       <c r="C237" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D237" s="6">
+      <c r="D237" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E237" s="6">
         <v>375860</v>
       </c>
-      <c r="G237" s="3"/>
-    </row>
-    <row r="238" spans="1:7">
+      <c r="H237" s="3"/>
+    </row>
+    <row r="238" spans="1:8">
       <c r="A238" s="1">
         <v>40787</v>
       </c>
@@ -3752,12 +4840,15 @@
       <c r="C238" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D238" s="6">
+      <c r="D238" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E238" s="6">
         <v>380042</v>
       </c>
-      <c r="G238" s="3"/>
-    </row>
-    <row r="239" spans="1:7">
+      <c r="H238" s="3"/>
+    </row>
+    <row r="239" spans="1:8">
       <c r="A239" s="1">
         <v>40817</v>
       </c>
@@ -3767,12 +4858,15 @@
       <c r="C239" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D239" s="6">
+      <c r="D239" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E239" s="6">
         <v>382207</v>
       </c>
-      <c r="G239" s="3"/>
-    </row>
-    <row r="240" spans="1:7">
+      <c r="H239" s="3"/>
+    </row>
+    <row r="240" spans="1:8">
       <c r="A240" s="1">
         <v>40848</v>
       </c>
@@ -3782,12 +4876,15 @@
       <c r="C240" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D240" s="6">
+      <c r="D240" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E240" s="6">
         <v>383422</v>
       </c>
-      <c r="G240" s="3"/>
-    </row>
-    <row r="241" spans="1:7">
+      <c r="H240" s="3"/>
+    </row>
+    <row r="241" spans="1:8">
       <c r="A241" s="1">
         <v>40878</v>
       </c>
@@ -3797,12 +4894,15 @@
       <c r="C241" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D241" s="6">
+      <c r="D241" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E241" s="6">
         <v>383985</v>
       </c>
-      <c r="G241" s="3"/>
-    </row>
-    <row r="242" spans="1:7">
+      <c r="H241" s="3"/>
+    </row>
+    <row r="242" spans="1:8">
       <c r="A242" s="1">
         <v>40909</v>
       </c>
@@ -3812,12 +4912,15 @@
       <c r="C242" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D242" s="6">
+      <c r="D242" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E242" s="6">
         <v>387531</v>
       </c>
-      <c r="G242" s="3"/>
-    </row>
-    <row r="243" spans="1:7">
+      <c r="H242" s="3"/>
+    </row>
+    <row r="243" spans="1:8">
       <c r="A243" s="1">
         <v>40940</v>
       </c>
@@ -3827,12 +4930,15 @@
       <c r="C243" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D243" s="6">
+      <c r="D243" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E243" s="6">
         <v>392310</v>
       </c>
-      <c r="G243" s="3"/>
-    </row>
-    <row r="244" spans="1:7">
+      <c r="H243" s="3"/>
+    </row>
+    <row r="244" spans="1:8">
       <c r="A244" s="1">
         <v>40969</v>
       </c>
@@ -3842,12 +4948,15 @@
       <c r="C244" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D244" s="6">
+      <c r="D244" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E244" s="6">
         <v>393698</v>
       </c>
-      <c r="G244" s="3"/>
-    </row>
-    <row r="245" spans="1:7">
+      <c r="H244" s="3"/>
+    </row>
+    <row r="245" spans="1:8">
       <c r="A245" s="1">
         <v>41000</v>
       </c>
@@ -3857,12 +4966,15 @@
       <c r="C245" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D245" s="6">
+      <c r="D245" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E245" s="6">
         <v>392073</v>
       </c>
-      <c r="G245" s="3"/>
-    </row>
-    <row r="246" spans="1:7">
+      <c r="H245" s="3"/>
+    </row>
+    <row r="246" spans="1:8">
       <c r="A246" s="1">
         <v>41030</v>
       </c>
@@ -3872,12 +4984,15 @@
       <c r="C246" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D246" s="6">
+      <c r="D246" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E246" s="6">
         <v>391376</v>
       </c>
-      <c r="G246" s="3"/>
-    </row>
-    <row r="247" spans="1:7">
+      <c r="H246" s="3"/>
+    </row>
+    <row r="247" spans="1:8">
       <c r="A247" s="1">
         <v>41061</v>
       </c>
@@ -3887,12 +5002,15 @@
       <c r="C247" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D247" s="6">
+      <c r="D247" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E247" s="6">
         <v>387901</v>
       </c>
-      <c r="G247" s="3"/>
-    </row>
-    <row r="248" spans="1:7">
+      <c r="H247" s="3"/>
+    </row>
+    <row r="248" spans="1:8">
       <c r="A248" s="1">
         <v>41091</v>
       </c>
@@ -3902,12 +5020,15 @@
       <c r="C248" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D248" s="6">
+      <c r="D248" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E248" s="6">
         <v>389686</v>
       </c>
-      <c r="G248" s="3"/>
-    </row>
-    <row r="249" spans="1:7">
+      <c r="H248" s="3"/>
+    </row>
+    <row r="249" spans="1:8">
       <c r="A249" s="1">
         <v>41122</v>
       </c>
@@ -3917,12 +5038,15 @@
       <c r="C249" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D249" s="6">
+      <c r="D249" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E249" s="6">
         <v>394524</v>
       </c>
-      <c r="G249" s="3"/>
-    </row>
-    <row r="250" spans="1:7">
+      <c r="H249" s="3"/>
+    </row>
+    <row r="250" spans="1:8">
       <c r="A250" s="1">
         <v>41153</v>
       </c>
@@ -3932,12 +5056,15 @@
       <c r="C250" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D250" s="6">
+      <c r="D250" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E250" s="6">
         <v>397681</v>
       </c>
-      <c r="G250" s="3"/>
-    </row>
-    <row r="251" spans="1:7">
+      <c r="H250" s="3"/>
+    </row>
+    <row r="251" spans="1:8">
       <c r="A251" s="1">
         <v>41183</v>
       </c>
@@ -3947,12 +5074,15 @@
       <c r="C251" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D251" s="6">
+      <c r="D251" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E251" s="6">
         <v>397494</v>
       </c>
-      <c r="G251" s="3"/>
-    </row>
-    <row r="252" spans="1:7">
+      <c r="H251" s="3"/>
+    </row>
+    <row r="252" spans="1:8">
       <c r="A252" s="1">
         <v>41214</v>
       </c>
@@ -3962,12 +5092,15 @@
       <c r="C252" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D252" s="6">
+      <c r="D252" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E252" s="6">
         <v>399708</v>
       </c>
-      <c r="G252" s="3"/>
-    </row>
-    <row r="253" spans="1:7">
+      <c r="H252" s="3"/>
+    </row>
+    <row r="253" spans="1:8">
       <c r="A253" s="1">
         <v>41244</v>
       </c>
@@ -3977,12 +5110,15 @@
       <c r="C253" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D253" s="6">
+      <c r="D253" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E253" s="6">
         <v>401093</v>
       </c>
-      <c r="G253" s="3"/>
-    </row>
-    <row r="254" spans="1:7">
+      <c r="H253" s="3"/>
+    </row>
+    <row r="254" spans="1:8">
       <c r="A254" s="1">
         <v>41275</v>
       </c>
@@ -3992,12 +5128,15 @@
       <c r="C254" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D254" s="6">
+      <c r="D254" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E254" s="6">
         <v>404434</v>
       </c>
-      <c r="G254" s="3"/>
-    </row>
-    <row r="255" spans="1:7">
+      <c r="H254" s="3"/>
+    </row>
+    <row r="255" spans="1:8">
       <c r="A255" s="1">
         <v>41306</v>
       </c>
@@ -4007,12 +5146,15 @@
       <c r="C255" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D255" s="6">
+      <c r="D255" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E255" s="6">
         <v>409118</v>
       </c>
-      <c r="G255" s="3"/>
-    </row>
-    <row r="256" spans="1:7">
+      <c r="H255" s="3"/>
+    </row>
+    <row r="256" spans="1:8">
       <c r="A256" s="1">
         <v>41334</v>
       </c>
@@ -4022,12 +5164,15 @@
       <c r="C256" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D256" s="6">
+      <c r="D256" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E256" s="6">
         <v>406223</v>
       </c>
-      <c r="G256" s="3"/>
-    </row>
-    <row r="257" spans="1:7">
+      <c r="H256" s="3"/>
+    </row>
+    <row r="257" spans="1:8">
       <c r="A257" s="1">
         <v>41365</v>
       </c>
@@ -4037,12 +5182,15 @@
       <c r="C257" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D257" s="6">
+      <c r="D257" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E257" s="6">
         <v>404231</v>
       </c>
-      <c r="G257" s="3"/>
-    </row>
-    <row r="258" spans="1:7">
+      <c r="H257" s="3"/>
+    </row>
+    <row r="258" spans="1:8">
       <c r="A258" s="1">
         <v>41395</v>
       </c>
@@ -4052,12 +5200,15 @@
       <c r="C258" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D258" s="6">
+      <c r="D258" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E258" s="6">
         <v>406677</v>
       </c>
-      <c r="G258" s="3"/>
-    </row>
-    <row r="259" spans="1:7">
+      <c r="H258" s="3"/>
+    </row>
+    <row r="259" spans="1:8">
       <c r="A259" s="1">
         <v>41426</v>
       </c>
@@ -4067,12 +5218,15 @@
       <c r="C259" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D259" s="6">
+      <c r="D259" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E259" s="6">
         <v>407921</v>
       </c>
-      <c r="G259" s="3"/>
-    </row>
-    <row r="260" spans="1:7">
+      <c r="H259" s="3"/>
+    </row>
+    <row r="260" spans="1:8">
       <c r="A260" s="1">
         <v>41456</v>
       </c>
@@ -4082,12 +5236,15 @@
       <c r="C260" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D260" s="6">
+      <c r="D260" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E260" s="6">
         <v>410268</v>
       </c>
-      <c r="G260" s="3"/>
-    </row>
-    <row r="261" spans="1:7">
+      <c r="H260" s="3"/>
+    </row>
+    <row r="261" spans="1:8">
       <c r="A261" s="1">
         <v>41487</v>
       </c>
@@ -4097,12 +5254,15 @@
       <c r="C261" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D261" s="6">
+      <c r="D261" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E261" s="6">
         <v>409691</v>
       </c>
-      <c r="G261" s="3"/>
-    </row>
-    <row r="262" spans="1:7">
+      <c r="H261" s="3"/>
+    </row>
+    <row r="262" spans="1:8">
       <c r="A262" s="1">
         <v>41518</v>
       </c>
@@ -4112,12 +5272,15 @@
       <c r="C262" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D262" s="6">
+      <c r="D262" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E262" s="6">
         <v>410044</v>
       </c>
-      <c r="G262" s="3"/>
-    </row>
-    <row r="263" spans="1:7">
+      <c r="H262" s="3"/>
+    </row>
+    <row r="263" spans="1:8">
       <c r="A263" s="1">
         <v>41548</v>
       </c>
@@ -4127,12 +5290,15 @@
       <c r="C263" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D263" s="6">
+      <c r="D263" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E263" s="6">
         <v>411399</v>
       </c>
-      <c r="G263" s="3"/>
-    </row>
-    <row r="264" spans="1:7">
+      <c r="H263" s="3"/>
+    </row>
+    <row r="264" spans="1:8">
       <c r="A264" s="1">
         <v>41579</v>
       </c>
@@ -4142,12 +5308,15 @@
       <c r="C264" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D264" s="6">
+      <c r="D264" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E264" s="6">
         <v>412561</v>
       </c>
-      <c r="G264" s="3"/>
-    </row>
-    <row r="265" spans="1:7">
+      <c r="H264" s="3"/>
+    </row>
+    <row r="265" spans="1:8">
       <c r="A265" s="1">
         <v>41609</v>
       </c>
@@ -4157,12 +5326,15 @@
       <c r="C265" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D265" s="6">
+      <c r="D265" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E265" s="6">
         <v>414812</v>
       </c>
-      <c r="G265" s="3"/>
-    </row>
-    <row r="266" spans="1:7">
+      <c r="H265" s="3"/>
+    </row>
+    <row r="266" spans="1:8">
       <c r="A266" s="1">
         <v>41640</v>
       </c>
@@ -4172,12 +5344,15 @@
       <c r="C266" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D266" s="6">
+      <c r="D266" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E266" s="6">
         <v>411561</v>
       </c>
-      <c r="G266" s="3"/>
-    </row>
-    <row r="267" spans="1:7">
+      <c r="H266" s="3"/>
+    </row>
+    <row r="267" spans="1:8">
       <c r="A267" s="1">
         <v>41671</v>
       </c>
@@ -4187,12 +5362,15 @@
       <c r="C267" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D267" s="6">
+      <c r="D267" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E267" s="6">
         <v>416736</v>
       </c>
-      <c r="G267" s="3"/>
-    </row>
-    <row r="268" spans="1:7">
+      <c r="H267" s="3"/>
+    </row>
+    <row r="268" spans="1:8">
       <c r="A268" s="1">
         <v>41699</v>
       </c>
@@ -4202,12 +5380,15 @@
       <c r="C268" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D268" s="6">
+      <c r="D268" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E268" s="6">
         <v>421230</v>
       </c>
-      <c r="G268" s="3"/>
-    </row>
-    <row r="269" spans="1:7">
+      <c r="H268" s="3"/>
+    </row>
+    <row r="269" spans="1:8">
       <c r="A269" s="1">
         <v>41730</v>
       </c>
@@ -4217,12 +5398,15 @@
       <c r="C269" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D269" s="6">
+      <c r="D269" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E269" s="6">
         <v>425546</v>
       </c>
-      <c r="G269" s="3"/>
-    </row>
-    <row r="270" spans="1:7">
+      <c r="H269" s="3"/>
+    </row>
+    <row r="270" spans="1:8">
       <c r="A270" s="1">
         <v>41760</v>
       </c>
@@ -4232,12 +5416,15 @@
       <c r="C270" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D270" s="6">
+      <c r="D270" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E270" s="6">
         <v>426253</v>
       </c>
-      <c r="G270" s="3"/>
-    </row>
-    <row r="271" spans="1:7">
+      <c r="H270" s="3"/>
+    </row>
+    <row r="271" spans="1:8">
       <c r="A271" s="1">
         <v>41791</v>
       </c>
@@ -4247,12 +5434,15 @@
       <c r="C271" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D271" s="6">
+      <c r="D271" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E271" s="6">
         <v>427305</v>
       </c>
-      <c r="G271" s="3"/>
-    </row>
-    <row r="272" spans="1:7">
+      <c r="H271" s="3"/>
+    </row>
+    <row r="272" spans="1:8">
       <c r="A272" s="1">
         <v>41821</v>
       </c>
@@ -4262,12 +5452,15 @@
       <c r="C272" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D272" s="6">
+      <c r="D272" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E272" s="6">
         <v>428079</v>
       </c>
-      <c r="G272" s="3"/>
-    </row>
-    <row r="273" spans="1:7">
+      <c r="H272" s="3"/>
+    </row>
+    <row r="273" spans="1:8">
       <c r="A273" s="1">
         <v>41852</v>
       </c>
@@ -4277,12 +5470,15 @@
       <c r="C273" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D273" s="6">
+      <c r="D273" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E273" s="6">
         <v>431379</v>
       </c>
-      <c r="G273" s="3"/>
-    </row>
-    <row r="274" spans="1:7">
+      <c r="H273" s="3"/>
+    </row>
+    <row r="274" spans="1:8">
       <c r="A274" s="1">
         <v>41883</v>
       </c>
@@ -4292,12 +5488,15 @@
       <c r="C274" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D274" s="6">
+      <c r="D274" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E274" s="6">
         <v>430189</v>
       </c>
-      <c r="G274" s="3"/>
-    </row>
-    <row r="275" spans="1:7">
+      <c r="H274" s="3"/>
+    </row>
+    <row r="275" spans="1:8">
       <c r="A275" s="1">
         <v>41913</v>
       </c>
@@ -4307,12 +5506,15 @@
       <c r="C275" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D275" s="6">
+      <c r="D275" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E275" s="6">
         <v>431903</v>
       </c>
-      <c r="G275" s="3"/>
-    </row>
-    <row r="276" spans="1:7">
+      <c r="H275" s="3"/>
+    </row>
+    <row r="276" spans="1:8">
       <c r="A276" s="1">
         <v>41944</v>
       </c>
@@ -4322,12 +5524,15 @@
       <c r="C276" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D276" s="6">
+      <c r="D276" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E276" s="6">
         <v>433113</v>
       </c>
-      <c r="G276" s="3"/>
-    </row>
-    <row r="277" spans="1:7">
+      <c r="H276" s="3"/>
+    </row>
+    <row r="277" spans="1:8">
       <c r="A277" s="1">
         <v>41974</v>
       </c>
@@ -4337,12 +5542,15 @@
       <c r="C277" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D277" s="6">
+      <c r="D277" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E277" s="6">
         <v>430110</v>
       </c>
-      <c r="G277" s="3"/>
-    </row>
-    <row r="278" spans="1:7">
+      <c r="H277" s="3"/>
+    </row>
+    <row r="278" spans="1:8">
       <c r="A278" s="1">
         <v>42005</v>
       </c>
@@ -4352,12 +5560,15 @@
       <c r="C278" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D278" s="6">
+      <c r="D278" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E278" s="6">
         <v>428208</v>
       </c>
-      <c r="G278" s="3"/>
-    </row>
-    <row r="279" spans="1:7">
+      <c r="H278" s="3"/>
+    </row>
+    <row r="279" spans="1:8">
       <c r="A279" s="1">
         <v>42036</v>
       </c>
@@ -4367,12 +5578,15 @@
       <c r="C279" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D279" s="6">
+      <c r="D279" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E279" s="6">
         <v>427119</v>
       </c>
-      <c r="G279" s="3"/>
-    </row>
-    <row r="280" spans="1:7">
+      <c r="H279" s="3"/>
+    </row>
+    <row r="280" spans="1:8">
       <c r="A280" s="1">
         <v>42064</v>
       </c>
@@ -4382,12 +5596,15 @@
       <c r="C280" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D280" s="6">
+      <c r="D280" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E280" s="6">
         <v>433647</v>
       </c>
-      <c r="G280" s="3"/>
-    </row>
-    <row r="281" spans="1:7">
+      <c r="H280" s="3"/>
+    </row>
+    <row r="281" spans="1:8">
       <c r="A281" s="1">
         <v>42095</v>
       </c>
@@ -4397,12 +5614,15 @@
       <c r="C281" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D281" s="6">
+      <c r="D281" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E281" s="6">
         <v>434470</v>
       </c>
-      <c r="G281" s="3"/>
-    </row>
-    <row r="282" spans="1:7">
+      <c r="H281" s="3"/>
+    </row>
+    <row r="282" spans="1:8">
       <c r="A282" s="1">
         <v>42125</v>
       </c>
@@ -4412,12 +5632,15 @@
       <c r="C282" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D282" s="6">
+      <c r="D282" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E282" s="6">
         <v>437865</v>
       </c>
-      <c r="G282" s="3"/>
-    </row>
-    <row r="283" spans="1:7">
+      <c r="H282" s="3"/>
+    </row>
+    <row r="283" spans="1:8">
       <c r="A283" s="1">
         <v>42156</v>
       </c>
@@ -4427,12 +5650,15 @@
       <c r="C283" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D283" s="6">
+      <c r="D283" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E283" s="6">
         <v>437951</v>
       </c>
-      <c r="G283" s="3"/>
-    </row>
-    <row r="284" spans="1:7">
+      <c r="H283" s="3"/>
+    </row>
+    <row r="284" spans="1:8">
       <c r="A284" s="1">
         <v>42186</v>
       </c>
@@ -4442,12 +5668,15 @@
       <c r="C284" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D284" s="6">
+      <c r="D284" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E284" s="6">
         <v>441942</v>
       </c>
-      <c r="G284" s="3"/>
-    </row>
-    <row r="285" spans="1:7">
+      <c r="H284" s="3"/>
+    </row>
+    <row r="285" spans="1:8">
       <c r="A285" s="1">
         <v>42217</v>
       </c>
@@ -4457,12 +5686,15 @@
       <c r="C285" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D285" s="6">
+      <c r="D285" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E285" s="6">
         <v>441849</v>
       </c>
-      <c r="G285" s="3"/>
-    </row>
-    <row r="286" spans="1:7">
+      <c r="H285" s="3"/>
+    </row>
+    <row r="286" spans="1:8">
       <c r="A286" s="1">
         <v>42248</v>
       </c>
@@ -4472,12 +5704,15 @@
       <c r="C286" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D286" s="6">
+      <c r="D286" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E286" s="6">
         <v>439867</v>
       </c>
-      <c r="G286" s="3"/>
-    </row>
-    <row r="287" spans="1:7">
+      <c r="H286" s="3"/>
+    </row>
+    <row r="287" spans="1:8">
       <c r="A287" s="1">
         <v>42278</v>
       </c>
@@ -4487,12 +5722,15 @@
       <c r="C287" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D287" s="6">
+      <c r="D287" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E287" s="6">
         <v>438693</v>
       </c>
-      <c r="G287" s="3"/>
-    </row>
-    <row r="288" spans="1:7">
+      <c r="H287" s="3"/>
+    </row>
+    <row r="288" spans="1:8">
       <c r="A288" s="1">
         <v>42309</v>
       </c>
@@ -4502,12 +5740,15 @@
       <c r="C288" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D288" s="6">
+      <c r="D288" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E288" s="6">
         <v>440303</v>
       </c>
-      <c r="G288" s="3"/>
-    </row>
-    <row r="289" spans="1:7">
+      <c r="H288" s="3"/>
+    </row>
+    <row r="289" spans="1:8">
       <c r="A289" s="1">
         <v>42339</v>
       </c>
@@ -4517,12 +5758,15 @@
       <c r="C289" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D289" s="6">
+      <c r="D289" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E289" s="6">
         <v>442149</v>
       </c>
-      <c r="G289" s="3"/>
-    </row>
-    <row r="290" spans="1:7">
+      <c r="H289" s="3"/>
+    </row>
+    <row r="290" spans="1:8">
       <c r="A290" s="1">
         <v>42370</v>
       </c>
@@ -4532,12 +5776,15 @@
       <c r="C290" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D290" s="6">
+      <c r="D290" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E290" s="6">
         <v>439466</v>
       </c>
-      <c r="G290" s="3"/>
-    </row>
-    <row r="291" spans="1:7">
+      <c r="H290" s="3"/>
+    </row>
+    <row r="291" spans="1:8">
       <c r="A291" s="1">
         <v>42401</v>
       </c>
@@ -4547,12 +5794,15 @@
       <c r="C291" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D291" s="6">
+      <c r="D291" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E291" s="6">
         <v>443117</v>
       </c>
-      <c r="G291" s="3"/>
-    </row>
-    <row r="292" spans="1:7">
+      <c r="H291" s="3"/>
+    </row>
+    <row r="292" spans="1:8">
       <c r="A292" s="1">
         <v>42430</v>
       </c>
@@ -4562,12 +5812,15 @@
       <c r="C292" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D292" s="6">
+      <c r="D292" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E292" s="6">
         <v>441856</v>
       </c>
-      <c r="G292" s="3"/>
-    </row>
-    <row r="293" spans="1:7">
+      <c r="H292" s="3"/>
+    </row>
+    <row r="293" spans="1:8">
       <c r="A293" s="1">
         <v>42461</v>
       </c>
@@ -4577,12 +5830,15 @@
       <c r="C293" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D293" s="6">
+      <c r="D293" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E293" s="6">
         <v>444254</v>
       </c>
-      <c r="G293" s="3"/>
-    </row>
-    <row r="294" spans="1:7">
+      <c r="H293" s="3"/>
+    </row>
+    <row r="294" spans="1:8">
       <c r="A294" s="1">
         <v>42491</v>
       </c>
@@ -4592,12 +5848,15 @@
       <c r="C294" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D294" s="6">
+      <c r="D294" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E294" s="6">
         <v>445490</v>
       </c>
-      <c r="G294" s="3"/>
-    </row>
-    <row r="295" spans="1:7">
+      <c r="H294" s="3"/>
+    </row>
+    <row r="295" spans="1:8">
       <c r="A295" s="1">
         <v>42522</v>
       </c>
@@ -4607,12 +5866,15 @@
       <c r="C295" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D295" s="6">
+      <c r="D295" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E295" s="6">
         <v>450237</v>
       </c>
-      <c r="G295" s="3"/>
-    </row>
-    <row r="296" spans="1:7">
+      <c r="H295" s="3"/>
+    </row>
+    <row r="296" spans="1:8">
       <c r="A296" s="1">
         <v>42552</v>
       </c>
@@ -4622,12 +5884,15 @@
       <c r="C296" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D296" s="6">
+      <c r="D296" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E296" s="6">
         <v>449789</v>
       </c>
-      <c r="G296" s="3"/>
-    </row>
-    <row r="297" spans="1:7">
+      <c r="H296" s="3"/>
+    </row>
+    <row r="297" spans="1:8">
       <c r="A297" s="1">
         <v>42583</v>
       </c>
@@ -4637,12 +5902,15 @@
       <c r="C297" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D297" s="6">
+      <c r="D297" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E297" s="6">
         <v>449946</v>
       </c>
-      <c r="G297" s="3"/>
-    </row>
-    <row r="298" spans="1:7">
+      <c r="H297" s="3"/>
+    </row>
+    <row r="298" spans="1:8">
       <c r="A298" s="1">
         <v>42614</v>
       </c>
@@ -4652,12 +5920,15 @@
       <c r="C298" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D298" s="6">
+      <c r="D298" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E298" s="6">
         <v>453056</v>
       </c>
-      <c r="G298" s="3"/>
-    </row>
-    <row r="299" spans="1:7">
+      <c r="H298" s="3"/>
+    </row>
+    <row r="299" spans="1:8">
       <c r="A299" s="1">
         <v>42644</v>
       </c>
@@ -4667,12 +5938,15 @@
       <c r="C299" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D299" s="6">
+      <c r="D299" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E299" s="6">
         <v>453847</v>
       </c>
-      <c r="G299" s="3"/>
-    </row>
-    <row r="300" spans="1:7">
+      <c r="H299" s="3"/>
+    </row>
+    <row r="300" spans="1:8">
       <c r="A300" s="1">
         <v>42675</v>
       </c>
@@ -4682,12 +5956,15 @@
       <c r="C300" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D300" s="6">
+      <c r="D300" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E300" s="6">
         <v>453892</v>
       </c>
-      <c r="G300" s="3"/>
-    </row>
-    <row r="301" spans="1:7">
+      <c r="H300" s="3"/>
+    </row>
+    <row r="301" spans="1:8">
       <c r="A301" s="1">
         <v>42705</v>
       </c>
@@ -4697,12 +5974,15 @@
       <c r="C301" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D301" s="6">
+      <c r="D301" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E301" s="6">
         <v>459305</v>
       </c>
-      <c r="G301" s="3"/>
-    </row>
-    <row r="302" spans="1:7">
+      <c r="H301" s="3"/>
+    </row>
+    <row r="302" spans="1:8">
       <c r="A302" s="1">
         <v>42736</v>
       </c>
@@ -4712,12 +5992,15 @@
       <c r="C302" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D302" s="6">
+      <c r="D302" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E302" s="6">
         <v>464412</v>
       </c>
-      <c r="G302" s="3"/>
-    </row>
-    <row r="303" spans="1:7">
+      <c r="H302" s="3"/>
+    </row>
+    <row r="303" spans="1:8">
       <c r="A303" s="1">
         <v>42767</v>
       </c>
@@ -4727,12 +6010,15 @@
       <c r="C303" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D303" s="6">
+      <c r="D303" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E303" s="6">
         <v>464284</v>
       </c>
-      <c r="G303" s="3"/>
-    </row>
-    <row r="304" spans="1:7">
+      <c r="H303" s="3"/>
+    </row>
+    <row r="304" spans="1:8">
       <c r="A304" s="1">
         <v>42795</v>
       </c>
@@ -4742,12 +6028,15 @@
       <c r="C304" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D304" s="6">
+      <c r="D304" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E304" s="6">
         <v>463674</v>
       </c>
-      <c r="G304" s="3"/>
-    </row>
-    <row r="305" spans="1:7">
+      <c r="H304" s="3"/>
+    </row>
+    <row r="305" spans="1:8">
       <c r="A305" s="1">
         <v>42826</v>
       </c>
@@ -4757,12 +6046,15 @@
       <c r="C305" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D305" s="6">
+      <c r="D305" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E305" s="6">
         <v>465276</v>
       </c>
-      <c r="G305" s="3"/>
-    </row>
-    <row r="306" spans="1:7">
+      <c r="H305" s="3"/>
+    </row>
+    <row r="306" spans="1:8">
       <c r="A306" s="1">
         <v>42856</v>
       </c>
@@ -4772,12 +6064,15 @@
       <c r="C306" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D306" s="6">
+      <c r="D306" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E306" s="6">
         <v>462754</v>
       </c>
-      <c r="G306" s="3"/>
-    </row>
-    <row r="307" spans="1:7">
+      <c r="H306" s="3"/>
+    </row>
+    <row r="307" spans="1:8">
       <c r="A307" s="1">
         <v>42887</v>
       </c>
@@ -4787,12 +6082,15 @@
       <c r="C307" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D307" s="6">
+      <c r="D307" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E307" s="6">
         <v>465130</v>
       </c>
-      <c r="G307" s="3"/>
-    </row>
-    <row r="308" spans="1:7">
+      <c r="H307" s="3"/>
+    </row>
+    <row r="308" spans="1:8">
       <c r="A308" s="1">
         <v>42917</v>
       </c>
@@ -4802,12 +6100,15 @@
       <c r="C308" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D308" s="6">
+      <c r="D308" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E308" s="6">
         <v>465089</v>
       </c>
-      <c r="G308" s="3"/>
-    </row>
-    <row r="309" spans="1:7">
+      <c r="H308" s="3"/>
+    </row>
+    <row r="309" spans="1:8">
       <c r="A309" s="1">
         <v>42948</v>
       </c>
@@ -4817,12 +6118,15 @@
       <c r="C309" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D309" s="6">
+      <c r="D309" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E309" s="6">
         <v>466020</v>
       </c>
-      <c r="G309" s="3"/>
-    </row>
-    <row r="310" spans="1:7">
+      <c r="H309" s="3"/>
+    </row>
+    <row r="310" spans="1:8">
       <c r="A310" s="1">
         <v>42979</v>
       </c>
@@ -4832,12 +6136,15 @@
       <c r="C310" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D310" s="6">
+      <c r="D310" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E310" s="6">
         <v>475724</v>
       </c>
-      <c r="G310" s="3"/>
-    </row>
-    <row r="311" spans="1:7">
+      <c r="H310" s="3"/>
+    </row>
+    <row r="311" spans="1:8">
       <c r="A311" s="1">
         <v>43009</v>
       </c>
@@ -4847,12 +6154,15 @@
       <c r="C311" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D311" s="6">
+      <c r="D311" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E311" s="6">
         <v>476107</v>
       </c>
-      <c r="G311" s="3"/>
-    </row>
-    <row r="312" spans="1:7">
+      <c r="H311" s="3"/>
+    </row>
+    <row r="312" spans="1:8">
       <c r="A312" s="1">
         <v>43040</v>
       </c>
@@ -4862,12 +6172,15 @@
       <c r="C312" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D312" s="6">
+      <c r="D312" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E312" s="6">
         <v>480949</v>
       </c>
-      <c r="G312" s="3"/>
-    </row>
-    <row r="313" spans="1:7">
+      <c r="H312" s="3"/>
+    </row>
+    <row r="313" spans="1:8">
       <c r="A313" s="1">
         <v>43070</v>
       </c>
@@ -4877,12 +6190,15 @@
       <c r="C313" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D313" s="6">
+      <c r="D313" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E313" s="6">
         <v>483586</v>
       </c>
-      <c r="G313" s="3"/>
-    </row>
-    <row r="314" spans="1:7">
+      <c r="H313" s="3"/>
+    </row>
+    <row r="314" spans="1:8">
       <c r="A314" s="1">
         <v>43101</v>
       </c>
@@ -4892,12 +6208,15 @@
       <c r="C314" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D314" s="6">
+      <c r="D314" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E314" s="6">
         <v>481414</v>
       </c>
-      <c r="G314" s="3"/>
-    </row>
-    <row r="315" spans="1:7">
+      <c r="H314" s="3"/>
+    </row>
+    <row r="315" spans="1:8">
       <c r="A315" s="1">
         <v>43132</v>
       </c>
@@ -4907,11 +6226,14 @@
       <c r="C315" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D315" s="6">
+      <c r="D315" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E315" s="6">
         <v>484031</v>
       </c>
     </row>
-    <row r="316" spans="1:7">
+    <row r="316" spans="1:8">
       <c r="A316" s="1">
         <v>43160</v>
       </c>
@@ -4921,11 +6243,14 @@
       <c r="C316" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D316" s="6">
+      <c r="D316" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E316" s="6">
         <v>484110</v>
       </c>
     </row>
-    <row r="317" spans="1:7">
+    <row r="317" spans="1:8">
       <c r="A317" s="1">
         <v>43191</v>
       </c>
@@ -4935,11 +6260,14 @@
       <c r="C317" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D317" s="6">
+      <c r="D317" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E317" s="6">
         <v>484154</v>
       </c>
     </row>
-    <row r="318" spans="1:7">
+    <row r="318" spans="1:8">
       <c r="A318" s="1">
         <v>43221</v>
       </c>
@@ -4949,11 +6277,14 @@
       <c r="C318" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D318" s="6">
+      <c r="D318" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E318" s="6">
         <v>491960</v>
       </c>
     </row>
-    <row r="319" spans="1:7">
+    <row r="319" spans="1:8">
       <c r="A319" s="1">
         <v>43252</v>
       </c>
@@ -4963,11 +6294,14 @@
       <c r="C319" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D319" s="6">
+      <c r="D319" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E319" s="6">
         <v>490228</v>
       </c>
     </row>
-    <row r="320" spans="1:7">
+    <row r="320" spans="1:8">
       <c r="A320" s="1">
         <v>43282</v>
       </c>
@@ -4977,11 +6311,14 @@
       <c r="C320" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D320" s="6">
+      <c r="D320" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E320" s="6">
         <v>493142</v>
       </c>
     </row>
-    <row r="321" spans="1:4">
+    <row r="321" spans="1:5">
       <c r="A321" s="1">
         <v>43313</v>
       </c>
@@ -4991,11 +6328,14 @@
       <c r="C321" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D321" s="6">
+      <c r="D321" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E321" s="6">
         <v>493445</v>
       </c>
     </row>
-    <row r="322" spans="1:4">
+    <row r="322" spans="1:5">
       <c r="A322" s="1">
         <v>43344</v>
       </c>
@@ -5005,11 +6345,14 @@
       <c r="C322" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D322" s="6">
+      <c r="D322" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E322" s="6">
         <v>491507</v>
       </c>
     </row>
-    <row r="323" spans="1:4">
+    <row r="323" spans="1:5">
       <c r="A323" s="1">
         <v>43374</v>
       </c>
@@ -5019,11 +6362,14 @@
       <c r="C323" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D323" s="6">
+      <c r="D323" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E323" s="6">
         <v>496416</v>
       </c>
     </row>
-    <row r="324" spans="1:4">
+    <row r="324" spans="1:5">
       <c r="A324" s="1">
         <v>43405</v>
       </c>
@@ -5033,11 +6379,14 @@
       <c r="C324" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D324" s="6">
+      <c r="D324" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E324" s="6">
         <v>498854</v>
       </c>
     </row>
-    <row r="325" spans="1:4">
+    <row r="325" spans="1:5">
       <c r="A325" s="1">
         <v>43435</v>
       </c>
@@ -5047,11 +6396,14 @@
       <c r="C325" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D325" s="6">
+      <c r="D325" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E325" s="6">
         <v>489113</v>
       </c>
     </row>
-    <row r="326" spans="1:4">
+    <row r="326" spans="1:5">
       <c r="A326" s="1">
         <v>43466</v>
       </c>
@@ -5061,11 +6413,14 @@
       <c r="C326" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D326" s="6">
+      <c r="D326" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E326" s="6">
         <v>490440</v>
       </c>
     </row>
-    <row r="327" spans="1:4">
+    <row r="327" spans="1:5">
       <c r="A327" s="1">
         <v>43497</v>
       </c>
@@ -5075,11 +6430,14 @@
       <c r="C327" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D327" s="6">
+      <c r="D327" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E327" s="6">
         <v>491751</v>
       </c>
     </row>
-    <row r="328" spans="1:4">
+    <row r="328" spans="1:5">
       <c r="A328" s="1">
         <v>43525</v>
       </c>
@@ -5089,11 +6447,14 @@
       <c r="C328" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D328" s="6">
+      <c r="D328" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E328" s="6">
         <v>499292</v>
       </c>
     </row>
-    <row r="329" spans="1:4">
+    <row r="329" spans="1:5">
       <c r="A329" s="1">
         <v>43556</v>
       </c>
@@ -5103,11 +6464,14 @@
       <c r="C329" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D329" s="6">
+      <c r="D329" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E329" s="6">
         <v>499343</v>
       </c>
     </row>
-    <row r="330" spans="1:4">
+    <row r="330" spans="1:5">
       <c r="A330" s="1">
         <v>43586</v>
       </c>
@@ -5117,11 +6481,14 @@
       <c r="C330" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D330" s="6">
+      <c r="D330" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E330" s="6">
         <v>504741</v>
       </c>
     </row>
-    <row r="331" spans="1:4">
+    <row r="331" spans="1:5">
       <c r="A331" s="1">
         <v>43617</v>
       </c>
@@ -5131,11 +6498,14 @@
       <c r="C331" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D331" s="6">
+      <c r="D331" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E331" s="6">
         <v>505251</v>
       </c>
     </row>
-    <row r="332" spans="1:4">
+    <row r="332" spans="1:5">
       <c r="A332" s="1">
         <v>43647</v>
       </c>
@@ -5145,11 +6515,14 @@
       <c r="C332" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D332" s="6">
+      <c r="D332" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E332" s="6">
         <v>509091</v>
       </c>
     </row>
-    <row r="333" spans="1:4">
+    <row r="333" spans="1:5">
       <c r="A333" s="1">
         <v>43678</v>
       </c>
@@ -5159,11 +6532,14 @@
       <c r="C333" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D333" s="6">
+      <c r="D333" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E333" s="6">
         <v>512561</v>
       </c>
     </row>
-    <row r="334" spans="1:4">
+    <row r="334" spans="1:5">
       <c r="A334" s="1">
         <v>43709</v>
       </c>
@@ -5173,11 +6549,14 @@
       <c r="C334" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D334" s="6">
+      <c r="D334" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E334" s="6">
         <v>509282</v>
       </c>
     </row>
-    <row r="335" spans="1:4">
+    <row r="335" spans="1:5">
       <c r="A335" s="1">
         <v>43739</v>
       </c>
@@ -5187,11 +6566,14 @@
       <c r="C335" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D335" s="6">
+      <c r="D335" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E335" s="6">
         <v>510648</v>
       </c>
     </row>
-    <row r="336" spans="1:4">
+    <row r="336" spans="1:5">
       <c r="A336" s="1">
         <v>43770</v>
       </c>
@@ -5201,11 +6583,14 @@
       <c r="C336" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D336" s="6">
+      <c r="D336" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E336" s="6">
         <v>514215</v>
       </c>
     </row>
-    <row r="337" spans="1:6">
+    <row r="337" spans="1:7">
       <c r="A337" s="1">
         <v>43800</v>
       </c>
@@ -5215,11 +6600,14 @@
       <c r="C337" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D337" s="6">
+      <c r="D337" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E337" s="6">
         <v>515866</v>
       </c>
     </row>
-    <row r="338" spans="1:6">
+    <row r="338" spans="1:7">
       <c r="A338" s="1">
         <v>43831</v>
       </c>
@@ -5229,11 +6617,14 @@
       <c r="C338" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D338" s="6">
+      <c r="D338" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E338" s="6">
         <v>515119</v>
       </c>
     </row>
-    <row r="339" spans="1:6">
+    <row r="339" spans="1:7">
       <c r="A339" s="1">
         <v>43862</v>
       </c>
@@ -5243,11 +6634,14 @@
       <c r="C339" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D339" s="6">
+      <c r="D339" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E339" s="6">
         <v>515330</v>
       </c>
     </row>
-    <row r="340" spans="1:6">
+    <row r="340" spans="1:7">
       <c r="A340" s="1">
         <v>43891</v>
       </c>
@@ -5257,11 +6651,14 @@
       <c r="C340" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D340" s="6">
+      <c r="D340" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E340" s="6">
         <v>468324</v>
       </c>
     </row>
-    <row r="341" spans="1:6">
+    <row r="341" spans="1:7">
       <c r="A341" s="1">
         <v>43922</v>
       </c>
@@ -5271,11 +6668,14 @@
       <c r="C341" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D341" s="6">
+      <c r="D341" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E341" s="6">
         <v>401028</v>
       </c>
     </row>
-    <row r="342" spans="1:6">
+    <row r="342" spans="1:7">
       <c r="A342" s="1">
         <v>43952</v>
       </c>
@@ -5285,11 +6685,14 @@
       <c r="C342" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D342" s="6">
+      <c r="D342" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E342" s="6">
         <v>478449</v>
       </c>
     </row>
-    <row r="343" spans="1:6">
+    <row r="343" spans="1:7">
       <c r="A343" s="1">
         <v>43983</v>
       </c>
@@ -5299,11 +6702,14 @@
       <c r="C343" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D343" s="6">
+      <c r="D343" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E343" s="6">
         <v>518038</v>
       </c>
     </row>
-    <row r="344" spans="1:6">
+    <row r="344" spans="1:7">
       <c r="A344" s="1">
         <v>44013</v>
       </c>
@@ -5313,11 +6719,14 @@
       <c r="C344" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D344" s="6">
+      <c r="D344" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E344" s="6">
         <v>526304</v>
       </c>
     </row>
-    <row r="345" spans="1:6">
+    <row r="345" spans="1:7">
       <c r="A345" s="1">
         <v>44044</v>
       </c>
@@ -5327,11 +6736,14 @@
       <c r="C345" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D345" s="6">
+      <c r="D345" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E345" s="6">
         <v>530735</v>
       </c>
     </row>
-    <row r="346" spans="1:6">
+    <row r="346" spans="1:7">
       <c r="A346" s="1">
         <v>44075</v>
       </c>
@@ -5341,11 +6753,14 @@
       <c r="C346" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D346" s="6">
+      <c r="D346" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E346" s="6">
         <v>541302</v>
       </c>
     </row>
-    <row r="347" spans="1:6">
+    <row r="347" spans="1:7">
       <c r="A347" s="1">
         <v>44105</v>
       </c>
@@ -5355,11 +6770,14 @@
       <c r="C347" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D347" s="6">
+      <c r="D347" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E347" s="6">
         <v>539114</v>
       </c>
     </row>
-    <row r="348" spans="1:6">
+    <row r="348" spans="1:7">
       <c r="A348" s="1">
         <v>44136</v>
       </c>
@@ -5369,17 +6787,20 @@
       <c r="C348" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D348" s="6">
+      <c r="D348" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E348" s="6">
         <v>533941</v>
       </c>
-      <c r="E348" s="5">
+      <c r="F348" s="5">
         <v>4.1000000000000002E-2</v>
       </c>
-      <c r="F348" s="5">
+      <c r="G348" s="5">
         <v>5.4899999999999997E-2</v>
       </c>
     </row>
-    <row r="349" spans="1:6">
+    <row r="349" spans="1:7">
       <c r="A349" s="1">
         <v>44166</v>
       </c>
@@ -5389,17 +6810,20 @@
       <c r="C349" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D349" s="6">
+      <c r="D349" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E349" s="6">
         <v>538548</v>
       </c>
-      <c r="E349" s="5">
+      <c r="F349" s="5">
         <v>2.9000000000000001E-2</v>
       </c>
-      <c r="F349" s="5">
+      <c r="G349" s="5">
         <v>3.6799999999999999E-2</v>
       </c>
     </row>
-    <row r="350" spans="1:6">
+    <row r="350" spans="1:7">
       <c r="A350" s="1">
         <v>44197</v>
       </c>
@@ -5409,17 +6833,20 @@
       <c r="C350" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D350" s="6">
+      <c r="D350" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E350" s="6">
         <v>559230</v>
       </c>
-      <c r="E350" s="5">
+      <c r="F350" s="5">
         <v>7.4300000000000005E-2</v>
       </c>
-      <c r="F350" s="5">
+      <c r="G350" s="5">
         <v>2.53E-2</v>
       </c>
     </row>
-    <row r="351" spans="1:6">
+    <row r="351" spans="1:7">
       <c r="A351" s="1">
         <v>44228</v>
       </c>
@@ -5429,17 +6856,20 @@
       <c r="C351" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D351" s="6">
+      <c r="D351" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E351" s="6">
         <v>544891</v>
       </c>
-      <c r="E351" s="5">
+      <c r="F351" s="5">
         <v>6.2700000000000006E-2</v>
       </c>
-      <c r="F351" s="5">
+      <c r="G351" s="5">
         <v>9.5100000000000004E-2</v>
       </c>
     </row>
-    <row r="352" spans="1:6">
+    <row r="352" spans="1:7">
       <c r="A352" s="1">
         <v>44256</v>
       </c>
@@ -5449,17 +6879,20 @@
       <c r="C352" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D352" s="6">
+      <c r="D352" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E352" s="6">
         <v>603581</v>
       </c>
-      <c r="E352" s="5">
+      <c r="F352" s="5">
         <v>0.28160000000000002</v>
       </c>
-      <c r="F352" s="5">
+      <c r="G352" s="5">
         <v>6.6600000000000006E-2</v>
       </c>
     </row>
-    <row r="353" spans="1:6">
+    <row r="353" spans="1:7">
       <c r="A353" s="1">
         <v>44287</v>
       </c>
@@ -5469,17 +6902,20 @@
       <c r="C353" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D353" s="6">
+      <c r="D353" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E353" s="6">
         <v>608961</v>
       </c>
-      <c r="E353" s="5">
+      <c r="F353" s="5">
         <v>0.51219999999999999</v>
       </c>
-      <c r="F353" s="5">
+      <c r="G353" s="5">
         <v>0.29010000000000002</v>
       </c>
     </row>
-    <row r="354" spans="1:6">
+    <row r="354" spans="1:7">
       <c r="A354" s="1">
         <v>44317</v>
       </c>
@@ -5489,17 +6925,20 @@
       <c r="C354" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D354" s="6">
+      <c r="D354" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E354" s="6">
         <v>605282</v>
       </c>
-      <c r="E354" s="5">
+      <c r="F354" s="5">
         <v>0.28149999999999997</v>
       </c>
-      <c r="F354" s="5">
+      <c r="G354" s="5">
         <v>0.53400000000000003</v>
       </c>
     </row>
-    <row r="355" spans="1:6">
+    <row r="355" spans="1:7">
       <c r="A355" s="1">
         <v>44348</v>
       </c>
@@ -5509,17 +6948,20 @@
       <c r="C355" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D355" s="6">
+      <c r="D355" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E355" s="6">
         <v>611950</v>
       </c>
-      <c r="E355" s="5">
+      <c r="F355" s="5">
         <v>0.17979999999999999</v>
       </c>
-      <c r="F355" s="5">
+      <c r="G355" s="5">
         <v>0.27600000000000002</v>
       </c>
     </row>
-    <row r="356" spans="1:6">
+    <row r="356" spans="1:7">
       <c r="A356" s="1">
         <v>44378</v>
       </c>
@@ -5529,17 +6971,20 @@
       <c r="C356" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D356" s="6">
+      <c r="D356" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E356" s="6">
         <v>601817</v>
       </c>
-      <c r="E356" s="5">
+      <c r="F356" s="5">
         <v>0.1578</v>
       </c>
-      <c r="F356" s="5">
+      <c r="G356" s="5">
         <v>0.18729999999999999</v>
       </c>
     </row>
-    <row r="357" spans="1:6">
+    <row r="357" spans="1:7">
       <c r="A357" s="1">
         <v>44409</v>
       </c>
@@ -5549,17 +6994,20 @@
       <c r="C357" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D357" s="6">
+      <c r="D357" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E357" s="6">
         <v>605533</v>
       </c>
-      <c r="E357" s="5">
+      <c r="F357" s="5">
         <v>0.13450000000000001</v>
       </c>
-      <c r="F357" s="5">
+      <c r="G357" s="5">
         <v>0.15140000000000001</v>
       </c>
     </row>
-    <row r="358" spans="1:6">
+    <row r="358" spans="1:7">
       <c r="A358" s="1">
         <v>44440</v>
       </c>
@@ -5569,17 +7017,20 @@
       <c r="C358" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D358" s="6">
+      <c r="D358" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E358" s="6">
         <v>609671</v>
       </c>
-      <c r="E358" s="5">
+      <c r="F358" s="5">
         <v>0.13950000000000001</v>
       </c>
-      <c r="F358" s="5">
+      <c r="G358" s="5">
         <v>0.154</v>
       </c>
     </row>
-    <row r="359" spans="1:6">
+    <row r="359" spans="1:7">
       <c r="A359" s="1">
         <v>44470</v>
       </c>
@@ -5589,17 +7040,20 @@
       <c r="C359" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D359" s="6">
+      <c r="D359" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E359" s="6">
         <v>618573</v>
       </c>
-      <c r="E359" s="5">
+      <c r="F359" s="5">
         <v>0.16309999999999999</v>
       </c>
-      <c r="F359" s="5">
+      <c r="G359" s="5">
         <v>0.1426</v>
       </c>
     </row>
-    <row r="360" spans="1:6">
+    <row r="360" spans="1:7">
       <c r="A360" s="1">
         <v>44501</v>
       </c>
@@ -5609,17 +7063,20 @@
       <c r="C360" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D360" s="6">
+      <c r="D360" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E360" s="6">
         <v>624874</v>
       </c>
-      <c r="E360" s="5">
+      <c r="F360" s="5">
         <v>0.18210000000000001</v>
       </c>
-      <c r="F360" s="5">
+      <c r="G360" s="5">
         <v>0.16259999999999999</v>
       </c>
     </row>
-    <row r="361" spans="1:6">
+    <row r="361" spans="1:7">
       <c r="A361" s="1">
         <v>44531</v>
       </c>
@@ -5629,17 +7086,20 @@
       <c r="C361" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D361" s="6">
+      <c r="D361" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E361" s="6">
         <v>619938</v>
       </c>
-      <c r="E361" s="5">
+      <c r="F361" s="5">
         <v>0.16950000000000001</v>
       </c>
-      <c r="F361" s="5">
+      <c r="G361" s="5">
         <v>0.18240000000000001</v>
       </c>
     </row>
-    <row r="362" spans="1:6">
+    <row r="362" spans="1:7">
       <c r="A362" s="1">
         <v>44562</v>
       </c>
@@ -5649,17 +7109,20 @@
       <c r="C362" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D362" s="6">
+      <c r="D362" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E362" s="6">
         <v>631509</v>
       </c>
-      <c r="E362" s="5">
+      <c r="F362" s="5">
         <v>0.12959999999999999</v>
       </c>
-      <c r="F362" s="5">
+      <c r="G362" s="5">
         <v>0.1671</v>
       </c>
     </row>
-    <row r="363" spans="1:6">
+    <row r="363" spans="1:7">
       <c r="A363" s="1">
         <v>44593</v>
       </c>
@@ -5669,17 +7132,20 @@
       <c r="C363" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D363" s="6">
+      <c r="D363" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E363" s="6">
         <v>638101</v>
       </c>
-      <c r="E363" s="5">
+      <c r="F363" s="5">
         <v>0.1762</v>
       </c>
-      <c r="F363" s="5">
+      <c r="G363" s="5">
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="364" spans="1:6">
+    <row r="364" spans="1:7">
       <c r="A364" s="1">
         <v>44621</v>
       </c>
@@ -5689,17 +7155,20 @@
       <c r="C364" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D364" s="6">
+      <c r="D364" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E364" s="6">
         <v>651027</v>
       </c>
-      <c r="E364" s="5">
+      <c r="F364" s="5">
         <v>6.88E-2</v>
       </c>
-      <c r="F364" s="5">
+      <c r="G364" s="5">
         <v>0.18179999999999999</v>
       </c>
     </row>
-    <row r="365" spans="1:6">
+    <row r="365" spans="1:7">
       <c r="A365" s="1">
         <v>44652</v>
       </c>
@@ -5709,17 +7178,20 @@
       <c r="C365" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D365" s="6">
+      <c r="D365" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E365" s="6">
         <v>660194</v>
       </c>
-      <c r="E365" s="5">
+      <c r="F365" s="5">
         <v>8.1900000000000001E-2</v>
       </c>
-      <c r="F365" s="5">
+      <c r="G365" s="5">
         <v>7.3400000000000007E-2</v>
       </c>
     </row>
-    <row r="366" spans="1:6">
+    <row r="366" spans="1:7">
       <c r="A366" s="1">
         <v>44682</v>
       </c>
@@ -5729,17 +7201,20 @@
       <c r="C366" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D366" s="6">
+      <c r="D366" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E366" s="6">
         <v>659847</v>
       </c>
-      <c r="E366" s="5">
+      <c r="F366" s="5">
         <v>8.09E-2</v>
       </c>
-      <c r="F366" s="5">
+      <c r="G366" s="5">
         <v>7.8200000000000006E-2</v>
       </c>
     </row>
-    <row r="367" spans="1:6">
+    <row r="367" spans="1:7">
       <c r="A367" s="1">
         <v>44713</v>
       </c>
@@ -5749,17 +7224,20 @@
       <c r="C367" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D367" s="6">
+      <c r="D367" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E367" s="6">
         <v>666113</v>
       </c>
-      <c r="E367" s="5">
+      <c r="F367" s="5">
         <v>8.4199999999999997E-2</v>
       </c>
-      <c r="F367" s="5">
+      <c r="G367" s="5">
         <v>8.1799999999999998E-2</v>
       </c>
     </row>
-    <row r="368" spans="1:6">
+    <row r="368" spans="1:7">
       <c r="A368" s="1">
         <v>44743</v>
       </c>
@@ -5769,17 +7247,20 @@
       <c r="C368" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D368" s="6">
+      <c r="D368" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E368" s="6">
         <v>659550</v>
       </c>
-      <c r="E368" s="5">
+      <c r="F368" s="5">
         <v>0.1002</v>
       </c>
-      <c r="F368" s="5">
+      <c r="G368" s="5">
         <v>8.5400000000000004E-2</v>
       </c>
     </row>
-    <row r="369" spans="1:6">
+    <row r="369" spans="1:7">
       <c r="A369" s="1">
         <v>44774</v>
       </c>
@@ -5789,17 +7270,20 @@
       <c r="C369" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D369" s="6">
+      <c r="D369" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E369" s="6">
         <v>663566</v>
       </c>
-      <c r="E369" s="5">
+      <c r="F369" s="5">
         <v>9.0999999999999998E-2</v>
       </c>
-      <c r="F369" s="5">
+      <c r="G369" s="5">
         <v>0.10059999999999999</v>
       </c>
     </row>
-    <row r="370" spans="1:6">
+    <row r="370" spans="1:7">
       <c r="A370" s="1">
         <v>44805</v>
       </c>
@@ -5809,17 +7293,20 @@
       <c r="C370" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D370" s="6">
+      <c r="D370" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E370" s="6">
         <v>661854</v>
       </c>
-      <c r="E370" s="5">
+      <c r="F370" s="5">
         <v>8.4099999999999994E-2</v>
       </c>
-      <c r="F370" s="5">
+      <c r="G370" s="5">
         <v>9.4399999999999998E-2</v>
       </c>
     </row>
-    <row r="371" spans="1:6">
+    <row r="371" spans="1:7">
       <c r="A371" s="1">
         <v>44835</v>
       </c>
@@ -5829,17 +7316,20 @@
       <c r="C371" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D371" s="6">
+      <c r="D371" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E371" s="6">
         <v>668671</v>
       </c>
-      <c r="E371" s="5">
+      <c r="F371" s="5">
         <v>8.3699999999999997E-2</v>
       </c>
-      <c r="F371" s="5">
+      <c r="G371" s="5">
         <v>8.5900000000000004E-2</v>
       </c>
     </row>
-    <row r="372" spans="1:6">
+    <row r="372" spans="1:7">
       <c r="A372" s="1">
         <v>44866</v>
       </c>
@@ -5849,17 +7339,20 @@
       <c r="C372" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D372" s="6">
+      <c r="D372" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E372" s="6">
         <v>659458</v>
       </c>
-      <c r="E372" s="5">
+      <c r="F372" s="5">
         <v>7.5999999999999998E-2</v>
       </c>
-      <c r="F372" s="5">
+      <c r="G372" s="5">
         <v>7.51E-2</v>
       </c>
     </row>
-    <row r="373" spans="1:6">
+    <row r="373" spans="1:7">
       <c r="A373" s="1">
         <v>44896</v>
       </c>
@@ -5869,17 +7362,20 @@
       <c r="C373" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D373" s="6">
+      <c r="D373" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E373" s="6">
         <v>651763</v>
       </c>
-      <c r="E373" s="5">
+      <c r="F373" s="5">
         <v>6.0199999999999997E-2</v>
       </c>
-      <c r="F373" s="5">
+      <c r="G373" s="5">
         <v>6.0100000000000001E-2</v>
       </c>
     </row>
-    <row r="374" spans="1:6">
+    <row r="374" spans="1:7">
       <c r="A374" s="1">
         <v>44927</v>
       </c>
@@ -5889,17 +7385,20 @@
       <c r="C374" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D374" s="6">
+      <c r="D374" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E374" s="6">
         <v>680253</v>
       </c>
-      <c r="E374" s="5">
+      <c r="F374" s="5">
         <v>6.3799999999999996E-2</v>
       </c>
-      <c r="F374" s="5">
+      <c r="G374" s="5">
         <v>5.8900000000000001E-2</v>
       </c>
     </row>
-    <row r="375" spans="1:6">
+    <row r="375" spans="1:7">
       <c r="A375" s="1">
         <v>44958</v>
       </c>
@@ -5909,17 +7408,20 @@
       <c r="C375" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D375" s="6">
+      <c r="D375" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E375" s="6">
         <v>672152</v>
       </c>
-      <c r="E375" s="5">
+      <c r="F375" s="5">
         <v>5.3900000000000003E-2</v>
       </c>
-      <c r="F375" s="5">
+      <c r="G375" s="5">
         <v>7.6799999999999993E-2</v>
       </c>
     </row>
-    <row r="376" spans="1:6">
+    <row r="376" spans="1:7">
       <c r="A376" s="1">
         <v>44986</v>
       </c>
@@ -5929,17 +7431,20 @@
       <c r="C376" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D376" s="6">
+      <c r="D376" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E376" s="6">
         <v>665071</v>
       </c>
-      <c r="E376" s="5">
+      <c r="F376" s="5">
         <v>2.9399999999999999E-2</v>
       </c>
-      <c r="F376" s="5">
+      <c r="G376" s="5">
         <v>5.8799999999999998E-2</v>
       </c>
     </row>
-    <row r="377" spans="1:6">
+    <row r="377" spans="1:7">
       <c r="A377" s="1">
         <v>45017</v>
       </c>
@@ -5949,17 +7454,20 @@
       <c r="C377" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D377" s="6">
+      <c r="D377" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E377" s="6">
         <v>670494</v>
       </c>
-      <c r="E377" s="5">
+      <c r="F377" s="5">
         <v>1.6E-2</v>
       </c>
-      <c r="F377" s="5">
+      <c r="G377" s="5">
         <v>2.4199999999999999E-2</v>
       </c>
     </row>
-    <row r="378" spans="1:6">
+    <row r="378" spans="1:7">
       <c r="A378" s="1">
         <v>45047</v>
       </c>
@@ -5969,17 +7477,20 @@
       <c r="C378" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D378" s="6">
+      <c r="D378" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E378" s="6">
         <v>673902</v>
       </c>
-      <c r="E378" s="5">
+      <c r="F378" s="5">
         <v>1.61E-2</v>
       </c>
-      <c r="F378" s="5">
+      <c r="G378" s="5">
         <v>1.23E-2</v>
       </c>
     </row>
-    <row r="379" spans="1:6">
+    <row r="379" spans="1:7">
       <c r="A379" s="1">
         <v>45078</v>
       </c>
@@ -5989,17 +7500,20 @@
       <c r="C379" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D379" s="6">
+      <c r="D379" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E379" s="6">
         <v>677117</v>
       </c>
-      <c r="E379" s="5">
+      <c r="F379" s="5">
         <v>1.49E-2</v>
       </c>
-      <c r="F379" s="5">
+      <c r="G379" s="5">
         <v>1.9599999999999999E-2</v>
       </c>
     </row>
-    <row r="380" spans="1:6">
+    <row r="380" spans="1:7">
       <c r="A380" s="1">
         <v>45108</v>
       </c>
@@ -6009,17 +7523,20 @@
       <c r="C380" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D380" s="6">
+      <c r="D380" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E380" s="6">
         <v>678424</v>
       </c>
-      <c r="E380" s="5">
+      <c r="F380" s="5">
         <v>3.1699999999999999E-2</v>
       </c>
-      <c r="F380" s="5">
+      <c r="G380" s="5">
         <v>1.5900000000000001E-2</v>
       </c>
     </row>
-    <row r="381" spans="1:6">
+    <row r="381" spans="1:7">
       <c r="A381" s="1">
         <v>45139</v>
       </c>
@@ -6029,17 +7546,20 @@
       <c r="C381" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D381" s="6">
+      <c r="D381" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E381" s="6">
         <v>684755</v>
       </c>
-      <c r="E381" s="5">
+      <c r="F381" s="5">
         <v>2.4899999999999999E-2</v>
       </c>
-      <c r="F381" s="5">
+      <c r="G381" s="5">
         <v>2.64E-2</v>
       </c>
     </row>
-    <row r="382" spans="1:6">
+    <row r="382" spans="1:7">
       <c r="A382" s="1">
         <v>45170</v>
       </c>
@@ -6049,17 +7569,20 @@
       <c r="C382" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D382" s="6">
+      <c r="D382" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E382" s="6">
         <v>689403</v>
       </c>
-      <c r="E382" s="5">
+      <c r="F382" s="5">
         <v>3.7499999999999999E-2</v>
       </c>
-      <c r="F382" s="5">
+      <c r="G382" s="5">
         <v>2.8899999999999999E-2</v>
       </c>
     </row>
-    <row r="383" spans="1:6">
+    <row r="383" spans="1:7">
       <c r="A383" s="1">
         <v>45200</v>
       </c>
@@ -6069,17 +7592,20 @@
       <c r="C383" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D383" s="6">
+      <c r="D383" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E383" s="6">
         <v>686148</v>
       </c>
-      <c r="E383" s="5">
+      <c r="F383" s="5">
         <v>2.4799999999999999E-2</v>
       </c>
-      <c r="F383" s="5">
+      <c r="G383" s="5">
         <v>4.0500000000000001E-2</v>
       </c>
     </row>
-    <row r="384" spans="1:6">
+    <row r="384" spans="1:7">
       <c r="A384" s="1">
         <v>45231</v>
       </c>
@@ -6089,17 +7615,20 @@
       <c r="C384" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D384" s="6">
+      <c r="D384" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E384" s="6">
         <v>685328</v>
       </c>
-      <c r="E384" s="5">
+      <c r="F384" s="5">
         <v>4.0899999999999999E-2</v>
       </c>
-      <c r="F384" s="5">
+      <c r="G384" s="5">
         <v>2.24E-2</v>
       </c>
     </row>
-    <row r="385" spans="1:6">
+    <row r="385" spans="1:7">
       <c r="A385" s="1">
         <v>45261</v>
       </c>
@@ -6109,17 +7638,20 @@
       <c r="C385" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D385" s="6">
+      <c r="D385" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E385" s="6">
         <v>686277</v>
       </c>
-      <c r="E385" s="5">
+      <c r="F385" s="5">
         <v>5.5899999999999998E-2</v>
       </c>
-      <c r="F385" s="5">
+      <c r="G385" s="5">
         <v>3.9699999999999999E-2</v>
       </c>
     </row>
-    <row r="386" spans="1:6">
+    <row r="386" spans="1:7">
       <c r="A386" s="1">
         <v>45292</v>
       </c>
@@ -6129,17 +7661,20 @@
       <c r="C386" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D386" s="6">
+      <c r="D386" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E386" s="6">
         <v>680456</v>
       </c>
-      <c r="E386" s="5">
+      <c r="F386" s="5">
         <v>6.4999999999999997E-3</v>
       </c>
-      <c r="F386" s="5">
+      <c r="G386" s="5">
         <v>5.3100000000000001E-2</v>
       </c>
     </row>
-    <row r="387" spans="1:6">
+    <row r="387" spans="1:7">
       <c r="A387" s="1">
         <v>45323</v>
       </c>
@@ -6149,17 +7684,20 @@
       <c r="C387" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D387" s="6">
+      <c r="D387" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E387" s="6">
         <v>685280</v>
       </c>
-      <c r="E387" s="5">
+      <c r="F387" s="5">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="F387" s="5">
+      <c r="G387" s="5">
         <v>4.0000000000000002E-4</v>
       </c>
     </row>
-    <row r="388" spans="1:6">
+    <row r="388" spans="1:7">
       <c r="A388" s="1">
         <v>45352</v>
       </c>
@@ -6169,17 +7707,20 @@
       <c r="C388" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D388" s="6">
+      <c r="D388" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E388" s="6">
         <v>687641</v>
       </c>
-      <c r="E388" s="5">
+      <c r="F388" s="5">
         <v>4.02E-2</v>
       </c>
-      <c r="F388" s="5">
+      <c r="G388" s="5">
         <v>2.1100000000000001E-2</v>
       </c>
     </row>
-    <row r="389" spans="1:6">
+    <row r="389" spans="1:7">
       <c r="A389" s="1">
         <v>45383</v>
       </c>
@@ -6189,17 +7730,20 @@
       <c r="C389" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D389" s="6">
+      <c r="D389" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E389" s="6">
         <v>687602</v>
       </c>
-      <c r="E389" s="5">
+      <c r="F389" s="5">
         <v>3.04E-2</v>
       </c>
-      <c r="F389" s="5">
+      <c r="G389" s="5">
         <v>3.8300000000000001E-2</v>
       </c>
     </row>
-    <row r="390" spans="1:6">
+    <row r="390" spans="1:7">
       <c r="A390" s="1">
         <v>45413</v>
       </c>
@@ -6209,17 +7753,20 @@
       <c r="C390" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D390" s="6">
+      <c r="D390" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E390" s="6">
         <v>692774</v>
       </c>
-      <c r="E390" s="5">
+      <c r="F390" s="5">
         <v>2.2700000000000001E-2</v>
       </c>
-      <c r="F390" s="5">
+      <c r="G390" s="5">
         <v>2.7400000000000001E-2</v>
       </c>
     </row>
-    <row r="391" spans="1:6">
+    <row r="391" spans="1:7">
       <c r="A391" s="1">
         <v>45444</v>
       </c>
@@ -6229,17 +7776,20 @@
       <c r="C391" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D391" s="6">
+      <c r="D391" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E391" s="6">
         <v>692449</v>
       </c>
-      <c r="E391" s="5">
+      <c r="F391" s="5">
         <v>2.2800000000000001E-2</v>
       </c>
-      <c r="F391" s="5">
+      <c r="G391" s="5">
         <v>2.5899999999999999E-2</v>
       </c>
     </row>
-    <row r="392" spans="1:6">
+    <row r="392" spans="1:7">
       <c r="A392" s="1">
         <v>45474</v>
       </c>
@@ -6249,17 +7799,20 @@
       <c r="C392" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D392" s="6">
+      <c r="D392" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E392" s="6">
         <v>698835</v>
       </c>
-      <c r="E392" s="5">
+      <c r="F392" s="5">
         <v>2.6599999999999999E-2</v>
       </c>
-      <c r="F392" s="5">
+      <c r="G392" s="5">
         <v>2.0400000000000001E-2</v>
       </c>
     </row>
-    <row r="393" spans="1:6">
+    <row r="393" spans="1:7">
       <c r="A393" s="1">
         <v>45505</v>
       </c>
@@ -6269,17 +7822,20 @@
       <c r="C393" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D393" s="6">
+      <c r="D393" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E393" s="6">
         <v>697039</v>
       </c>
-      <c r="E393" s="5">
+      <c r="F393" s="5">
         <v>2.1299999999999999E-2</v>
       </c>
-      <c r="F393" s="5">
+      <c r="G393" s="5">
         <v>2.86E-2</v>
       </c>
     </row>
-    <row r="394" spans="1:6">
+    <row r="394" spans="1:7">
       <c r="A394" s="1">
         <v>45536</v>
       </c>
@@ -6289,17 +7845,20 @@
       <c r="C394" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D394" s="6">
+      <c r="D394" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E394" s="6">
         <v>703285</v>
       </c>
-      <c r="E394" s="5">
+      <c r="F394" s="5">
         <v>1.7399999999999999E-2</v>
       </c>
-      <c r="F394" s="5">
+      <c r="G394" s="5">
         <v>2.1600000000000001E-2</v>
       </c>
     </row>
-    <row r="395" spans="1:6">
+    <row r="395" spans="1:7">
       <c r="A395" s="1">
         <v>45566</v>
       </c>
@@ -6309,17 +7868,20 @@
       <c r="C395" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D395" s="6">
+      <c r="D395" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E395" s="6">
         <v>707613</v>
       </c>
-      <c r="E395" s="5">
+      <c r="F395" s="5">
         <v>2.8500000000000001E-2</v>
       </c>
-      <c r="F395" s="5">
+      <c r="G395" s="5">
         <v>1.9800000000000002E-2</v>
       </c>
     </row>
-    <row r="396" spans="1:6">
+    <row r="396" spans="1:7">
       <c r="A396" s="1">
         <v>45597</v>
       </c>
@@ -6329,17 +7891,20 @@
       <c r="C396" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D396" s="6">
+      <c r="D396" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E396" s="6">
         <v>712145</v>
       </c>
-      <c r="E396" s="5">
+      <c r="F396" s="5">
         <v>3.7999999999999999E-2</v>
       </c>
-      <c r="F396" s="5">
+      <c r="G396" s="5">
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="397" spans="1:6">
+    <row r="397" spans="1:7">
       <c r="A397" s="1">
         <v>45627</v>
       </c>
@@ -6349,17 +7914,20 @@
       <c r="C397" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D397" s="6">
+      <c r="D397" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E397" s="6">
         <v>717662</v>
       </c>
-      <c r="E397" s="5">
+      <c r="F397" s="5">
         <v>3.9199999999999999E-2</v>
       </c>
-      <c r="F397" s="5">
+      <c r="G397" s="5">
         <v>4.1200000000000001E-2</v>
       </c>
     </row>
-    <row r="398" spans="1:6">
+    <row r="398" spans="1:7">
       <c r="A398" s="1">
         <v>45658</v>
       </c>
@@ -6369,17 +7937,20 @@
       <c r="C398" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D398" s="6">
+      <c r="D398" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E398" s="6">
         <v>711461</v>
       </c>
-      <c r="E398" s="5">
+      <c r="F398" s="5">
         <v>4.2000000000000003E-2</v>
       </c>
-      <c r="F398" s="5">
+      <c r="G398" s="5">
         <v>4.36E-2</v>
       </c>
     </row>
-    <row r="399" spans="1:6">
+    <row r="399" spans="1:7">
       <c r="A399" s="1">
         <v>45689</v>
       </c>
@@ -6389,17 +7960,20 @@
       <c r="C399" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D399" s="6">
+      <c r="D399" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E399" s="6">
         <v>711757</v>
       </c>
-      <c r="E399" s="5">
+      <c r="F399" s="5">
         <v>3.1E-2</v>
       </c>
-      <c r="F399" s="5">
+      <c r="G399" s="5">
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="400" spans="1:6">
+    <row r="400" spans="1:7">
       <c r="A400" s="1">
         <v>45717</v>
       </c>
@@ -6409,17 +7983,20 @@
       <c r="C400" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D400" s="6">
+      <c r="D400" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E400" s="6">
         <v>722572</v>
       </c>
-      <c r="E400" s="5">
+      <c r="F400" s="5">
         <v>4.5999999999999999E-2</v>
       </c>
-      <c r="F400" s="5">
+      <c r="G400" s="5">
         <v>3.5400000000000001E-2</v>
       </c>
     </row>
-    <row r="401" spans="1:6">
+    <row r="401" spans="1:7">
       <c r="A401" s="1">
         <v>45748</v>
       </c>
@@ -6429,17 +8006,20 @@
       <c r="C401" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D401" s="6">
+      <c r="D401" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E401" s="6">
         <v>721789</v>
       </c>
-      <c r="E401" s="5">
+      <c r="F401" s="5">
         <v>5.16E-2</v>
       </c>
-      <c r="F401" s="5">
+      <c r="G401" s="5">
         <v>5.2499999999999998E-2</v>
       </c>
     </row>
-    <row r="402" spans="1:6">
+    <row r="402" spans="1:7">
       <c r="A402" s="1">
         <v>45778</v>
       </c>
@@ -6449,17 +8029,20 @@
       <c r="C402" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D402" s="6">
+      <c r="D402" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E402" s="6">
         <v>716101</v>
       </c>
-      <c r="E402" s="5">
+      <c r="F402" s="5">
         <v>3.2899999999999999E-2</v>
       </c>
-      <c r="F402" s="5">
+      <c r="G402" s="5">
         <v>0.05</v>
       </c>
     </row>
-    <row r="403" spans="1:6">
+    <row r="403" spans="1:7">
       <c r="A403" s="1">
         <v>45809</v>
       </c>
@@ -6469,17 +8052,20 @@
       <c r="C403" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D403" s="6">
+      <c r="D403" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E403" s="6">
         <v>723033</v>
       </c>
-      <c r="E403" s="5">
+      <c r="F403" s="5">
         <v>3.9199999999999999E-2</v>
       </c>
-      <c r="F403" s="5">
+      <c r="G403" s="5">
         <v>3.2899999999999999E-2</v>
       </c>
     </row>
-    <row r="404" spans="1:6">
+    <row r="404" spans="1:7">
       <c r="A404" s="1">
         <v>45839</v>
       </c>
@@ -6489,17 +8075,20 @@
       <c r="C404" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D404" s="6">
+      <c r="D404" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E404" s="6">
         <v>727727</v>
       </c>
-      <c r="E404" s="5">
+      <c r="F404" s="5">
         <v>3.9199999999999999E-2</v>
       </c>
-      <c r="F404" s="5">
+      <c r="G404" s="5">
         <v>4.3499999999999997E-2</v>
       </c>
     </row>
-    <row r="405" spans="1:6">
+    <row r="405" spans="1:7">
       <c r="A405" s="1">
         <v>45870</v>
       </c>
@@ -6509,17 +8098,20 @@
       <c r="C405" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D405" s="6">
+      <c r="D405" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E405" s="6">
         <v>732059</v>
       </c>
-      <c r="E405" s="5">
+      <c r="F405" s="5">
         <v>0.05</v>
       </c>
-      <c r="F405" s="5">
+      <c r="G405" s="5">
         <v>4.0899999999999999E-2</v>
       </c>
     </row>
-    <row r="406" spans="1:6">
+    <row r="406" spans="1:7">
       <c r="A406" s="1">
         <v>45901</v>
       </c>
@@ -6529,17 +8121,20 @@
       <c r="C406" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D406" s="6">
+      <c r="D406" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E406" s="6">
         <v>733258</v>
       </c>
-      <c r="E406" s="5">
+      <c r="F406" s="5">
         <v>4.2599999999999999E-2</v>
       </c>
-      <c r="F406" s="5">
+      <c r="G406" s="5">
         <v>5.0200000000000002E-2</v>
       </c>
     </row>
-    <row r="407" spans="1:6">
+    <row r="407" spans="1:7">
       <c r="A407" s="1">
         <v>45931</v>
       </c>
@@ -6549,13 +8144,16 @@
       <c r="C407" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D407" s="6">
+      <c r="D407" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E407" s="6">
         <v>732633</v>
       </c>
-      <c r="E407" s="5">
+      <c r="F407" s="5">
         <v>3.4700000000000002E-2</v>
       </c>
-      <c r="F407" s="5">
+      <c r="G407" s="5">
         <v>4.1799999999999997E-2</v>
       </c>
     </row>

--- a/data/macro/USA/Retail Sales.xlsx
+++ b/data/macro/USA/Retail Sales.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/AlternativeData/data/macro/USA/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\macro\USA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A45120B6-69E3-9048-B54F-B96354C58595}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4256254-57F8-47B7-87AB-6522226514BC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11480" yWindow="780" windowWidth="18000" windowHeight="20680" xr2:uid="{30656A32-0D37-469D-885D-F50C8A2BA9DC}"/>
+    <workbookView xWindow="11475" yWindow="780" windowWidth="18000" windowHeight="20685" xr2:uid="{30656A32-0D37-469D-885D-F50C8A2BA9DC}"/>
   </bookViews>
   <sheets>
     <sheet name="Retail Sales" sheetId="1" r:id="rId1"/>
@@ -21,23 +21,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="12">
   <si>
     <t>Release Date</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -88,11 +77,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="166" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="176" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -172,7 +161,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -186,7 +175,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -195,13 +184,13 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3">
@@ -210,19 +199,19 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -230,10 +219,10 @@
     </xf>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="Hyperlink" xfId="3" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="2" builtinId="5"/>
+    <cellStyle name="백분율" xfId="2" builtinId="5"/>
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="3" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -249,9 +238,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -289,7 +278,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -395,7 +384,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -537,7 +526,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -545,21 +534,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A423BD41-4AF5-471C-B1B1-976B1BB48C33}">
-  <dimension ref="A1:H407"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
+  <dimension ref="A1:H408"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.1640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.1640625" style="9" customWidth="1"/>
-    <col min="5" max="5" width="9.5" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.1640625" style="5" customWidth="1"/>
-    <col min="7" max="7" width="9.1640625" style="5"/>
-    <col min="8" max="8" width="10.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="9.1640625" style="2"/>
+    <col min="3" max="3" width="11.42578125" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" style="9" customWidth="1"/>
+    <col min="5" max="5" width="9.42578125" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.140625" style="5" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" style="5"/>
+    <col min="8" max="8" width="10.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>1</v>
       </c>
@@ -582,7 +571,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>33604</v>
       </c>
@@ -600,7 +589,7 @@
       </c>
       <c r="H2" s="3"/>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>33635</v>
       </c>
@@ -618,7 +607,7 @@
       </c>
       <c r="H3" s="3"/>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>33664</v>
       </c>
@@ -636,7 +625,7 @@
       </c>
       <c r="H4" s="3"/>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>33695</v>
       </c>
@@ -654,7 +643,7 @@
       </c>
       <c r="H5" s="3"/>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>33725</v>
       </c>
@@ -672,7 +661,7 @@
       </c>
       <c r="H6" s="3"/>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>33756</v>
       </c>
@@ -690,7 +679,7 @@
       </c>
       <c r="H7" s="3"/>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>33786</v>
       </c>
@@ -708,7 +697,7 @@
       </c>
       <c r="H8" s="3"/>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>33817</v>
       </c>
@@ -726,7 +715,7 @@
       </c>
       <c r="H9" s="3"/>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>33848</v>
       </c>
@@ -744,7 +733,7 @@
       </c>
       <c r="H10" s="3"/>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>33878</v>
       </c>
@@ -762,7 +751,7 @@
       </c>
       <c r="H11" s="3"/>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>33909</v>
       </c>
@@ -780,7 +769,7 @@
       </c>
       <c r="H12" s="3"/>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>33939</v>
       </c>
@@ -798,7 +787,7 @@
       </c>
       <c r="H13" s="3"/>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>33970</v>
       </c>
@@ -816,7 +805,7 @@
       </c>
       <c r="H14" s="3"/>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>34001</v>
       </c>
@@ -834,7 +823,7 @@
       </c>
       <c r="H15" s="3"/>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>34029</v>
       </c>
@@ -852,7 +841,7 @@
       </c>
       <c r="H16" s="3"/>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>34060</v>
       </c>
@@ -870,7 +859,7 @@
       </c>
       <c r="H17" s="3"/>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>34090</v>
       </c>
@@ -888,7 +877,7 @@
       </c>
       <c r="H18" s="3"/>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>34121</v>
       </c>
@@ -906,7 +895,7 @@
       </c>
       <c r="H19" s="3"/>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>34151</v>
       </c>
@@ -924,7 +913,7 @@
       </c>
       <c r="H20" s="3"/>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>34182</v>
       </c>
@@ -942,7 +931,7 @@
       </c>
       <c r="H21" s="3"/>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>34213</v>
       </c>
@@ -960,7 +949,7 @@
       </c>
       <c r="H22" s="3"/>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>34243</v>
       </c>
@@ -978,7 +967,7 @@
       </c>
       <c r="H23" s="3"/>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>34274</v>
       </c>
@@ -996,7 +985,7 @@
       </c>
       <c r="H24" s="3"/>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>34304</v>
       </c>
@@ -1014,7 +1003,7 @@
       </c>
       <c r="H25" s="3"/>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>34335</v>
       </c>
@@ -1032,7 +1021,7 @@
       </c>
       <c r="H26" s="3"/>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>34366</v>
       </c>
@@ -1050,7 +1039,7 @@
       </c>
       <c r="H27" s="3"/>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>34394</v>
       </c>
@@ -1068,7 +1057,7 @@
       </c>
       <c r="H28" s="3"/>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>34425</v>
       </c>
@@ -1086,7 +1075,7 @@
       </c>
       <c r="H29" s="3"/>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>34455</v>
       </c>
@@ -1104,7 +1093,7 @@
       </c>
       <c r="H30" s="3"/>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>34486</v>
       </c>
@@ -1122,7 +1111,7 @@
       </c>
       <c r="H31" s="3"/>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>34516</v>
       </c>
@@ -1140,7 +1129,7 @@
       </c>
       <c r="H32" s="3"/>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>34547</v>
       </c>
@@ -1158,7 +1147,7 @@
       </c>
       <c r="H33" s="3"/>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>34578</v>
       </c>
@@ -1176,7 +1165,7 @@
       </c>
       <c r="H34" s="3"/>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>34608</v>
       </c>
@@ -1194,7 +1183,7 @@
       </c>
       <c r="H35" s="3"/>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>34639</v>
       </c>
@@ -1212,7 +1201,7 @@
       </c>
       <c r="H36" s="3"/>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>34669</v>
       </c>
@@ -1230,7 +1219,7 @@
       </c>
       <c r="H37" s="3"/>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>34700</v>
       </c>
@@ -1248,7 +1237,7 @@
       </c>
       <c r="H38" s="3"/>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>34731</v>
       </c>
@@ -1266,7 +1255,7 @@
       </c>
       <c r="H39" s="3"/>
     </row>
-    <row r="40" spans="1:8">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>34759</v>
       </c>
@@ -1284,7 +1273,7 @@
       </c>
       <c r="H40" s="3"/>
     </row>
-    <row r="41" spans="1:8">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>34790</v>
       </c>
@@ -1302,7 +1291,7 @@
       </c>
       <c r="H41" s="3"/>
     </row>
-    <row r="42" spans="1:8">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>34820</v>
       </c>
@@ -1320,7 +1309,7 @@
       </c>
       <c r="H42" s="3"/>
     </row>
-    <row r="43" spans="1:8">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>34851</v>
       </c>
@@ -1338,7 +1327,7 @@
       </c>
       <c r="H43" s="3"/>
     </row>
-    <row r="44" spans="1:8">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>34881</v>
       </c>
@@ -1356,7 +1345,7 @@
       </c>
       <c r="H44" s="3"/>
     </row>
-    <row r="45" spans="1:8">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>34912</v>
       </c>
@@ -1374,7 +1363,7 @@
       </c>
       <c r="H45" s="3"/>
     </row>
-    <row r="46" spans="1:8">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>34943</v>
       </c>
@@ -1392,7 +1381,7 @@
       </c>
       <c r="H46" s="3"/>
     </row>
-    <row r="47" spans="1:8">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>34973</v>
       </c>
@@ -1410,7 +1399,7 @@
       </c>
       <c r="H47" s="3"/>
     </row>
-    <row r="48" spans="1:8">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>35004</v>
       </c>
@@ -1428,7 +1417,7 @@
       </c>
       <c r="H48" s="3"/>
     </row>
-    <row r="49" spans="1:8">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>35034</v>
       </c>
@@ -1446,7 +1435,7 @@
       </c>
       <c r="H49" s="3"/>
     </row>
-    <row r="50" spans="1:8">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>35065</v>
       </c>
@@ -1464,7 +1453,7 @@
       </c>
       <c r="H50" s="3"/>
     </row>
-    <row r="51" spans="1:8">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>35096</v>
       </c>
@@ -1482,7 +1471,7 @@
       </c>
       <c r="H51" s="3"/>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>35125</v>
       </c>
@@ -1500,7 +1489,7 @@
       </c>
       <c r="H52" s="3"/>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>35156</v>
       </c>
@@ -1518,7 +1507,7 @@
       </c>
       <c r="H53" s="3"/>
     </row>
-    <row r="54" spans="1:8">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>35186</v>
       </c>
@@ -1536,7 +1525,7 @@
       </c>
       <c r="H54" s="3"/>
     </row>
-    <row r="55" spans="1:8">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>35217</v>
       </c>
@@ -1554,7 +1543,7 @@
       </c>
       <c r="H55" s="3"/>
     </row>
-    <row r="56" spans="1:8">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>35247</v>
       </c>
@@ -1572,7 +1561,7 @@
       </c>
       <c r="H56" s="3"/>
     </row>
-    <row r="57" spans="1:8">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>35278</v>
       </c>
@@ -1590,7 +1579,7 @@
       </c>
       <c r="H57" s="3"/>
     </row>
-    <row r="58" spans="1:8">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>35309</v>
       </c>
@@ -1608,7 +1597,7 @@
       </c>
       <c r="H58" s="3"/>
     </row>
-    <row r="59" spans="1:8">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>35339</v>
       </c>
@@ -1626,7 +1615,7 @@
       </c>
       <c r="H59" s="3"/>
     </row>
-    <row r="60" spans="1:8">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>35370</v>
       </c>
@@ -1644,7 +1633,7 @@
       </c>
       <c r="H60" s="3"/>
     </row>
-    <row r="61" spans="1:8">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>35400</v>
       </c>
@@ -1662,7 +1651,7 @@
       </c>
       <c r="H61" s="3"/>
     </row>
-    <row r="62" spans="1:8">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>35431</v>
       </c>
@@ -1680,7 +1669,7 @@
       </c>
       <c r="H62" s="3"/>
     </row>
-    <row r="63" spans="1:8">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>35462</v>
       </c>
@@ -1698,7 +1687,7 @@
       </c>
       <c r="H63" s="3"/>
     </row>
-    <row r="64" spans="1:8">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>35490</v>
       </c>
@@ -1716,7 +1705,7 @@
       </c>
       <c r="H64" s="3"/>
     </row>
-    <row r="65" spans="1:8">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>35521</v>
       </c>
@@ -1734,7 +1723,7 @@
       </c>
       <c r="H65" s="3"/>
     </row>
-    <row r="66" spans="1:8">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>35551</v>
       </c>
@@ -1752,7 +1741,7 @@
       </c>
       <c r="H66" s="3"/>
     </row>
-    <row r="67" spans="1:8">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>35582</v>
       </c>
@@ -1770,7 +1759,7 @@
       </c>
       <c r="H67" s="3"/>
     </row>
-    <row r="68" spans="1:8">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>35612</v>
       </c>
@@ -1788,7 +1777,7 @@
       </c>
       <c r="H68" s="3"/>
     </row>
-    <row r="69" spans="1:8">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>35643</v>
       </c>
@@ -1806,7 +1795,7 @@
       </c>
       <c r="H69" s="3"/>
     </row>
-    <row r="70" spans="1:8">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>35674</v>
       </c>
@@ -1824,7 +1813,7 @@
       </c>
       <c r="H70" s="3"/>
     </row>
-    <row r="71" spans="1:8">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>35704</v>
       </c>
@@ -1842,7 +1831,7 @@
       </c>
       <c r="H71" s="3"/>
     </row>
-    <row r="72" spans="1:8">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>35735</v>
       </c>
@@ -1860,7 +1849,7 @@
       </c>
       <c r="H72" s="3"/>
     </row>
-    <row r="73" spans="1:8">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>35765</v>
       </c>
@@ -1878,7 +1867,7 @@
       </c>
       <c r="H73" s="3"/>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>35796</v>
       </c>
@@ -1896,7 +1885,7 @@
       </c>
       <c r="H74" s="3"/>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>35827</v>
       </c>
@@ -1914,7 +1903,7 @@
       </c>
       <c r="H75" s="3"/>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>35855</v>
       </c>
@@ -1932,7 +1921,7 @@
       </c>
       <c r="H76" s="3"/>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>35886</v>
       </c>
@@ -1950,7 +1939,7 @@
       </c>
       <c r="H77" s="3"/>
     </row>
-    <row r="78" spans="1:8">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>35916</v>
       </c>
@@ -1968,7 +1957,7 @@
       </c>
       <c r="H78" s="3"/>
     </row>
-    <row r="79" spans="1:8">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>35947</v>
       </c>
@@ -1986,7 +1975,7 @@
       </c>
       <c r="H79" s="3"/>
     </row>
-    <row r="80" spans="1:8">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>35977</v>
       </c>
@@ -2004,7 +1993,7 @@
       </c>
       <c r="H80" s="3"/>
     </row>
-    <row r="81" spans="1:8">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>36008</v>
       </c>
@@ -2022,7 +2011,7 @@
       </c>
       <c r="H81" s="3"/>
     </row>
-    <row r="82" spans="1:8">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>36039</v>
       </c>
@@ -2040,7 +2029,7 @@
       </c>
       <c r="H82" s="3"/>
     </row>
-    <row r="83" spans="1:8">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>36069</v>
       </c>
@@ -2058,7 +2047,7 @@
       </c>
       <c r="H83" s="3"/>
     </row>
-    <row r="84" spans="1:8">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>36100</v>
       </c>
@@ -2076,7 +2065,7 @@
       </c>
       <c r="H84" s="3"/>
     </row>
-    <row r="85" spans="1:8">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>36130</v>
       </c>
@@ -2094,7 +2083,7 @@
       </c>
       <c r="H85" s="3"/>
     </row>
-    <row r="86" spans="1:8">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>36161</v>
       </c>
@@ -2112,7 +2101,7 @@
       </c>
       <c r="H86" s="3"/>
     </row>
-    <row r="87" spans="1:8">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>36192</v>
       </c>
@@ -2130,7 +2119,7 @@
       </c>
       <c r="H87" s="3"/>
     </row>
-    <row r="88" spans="1:8">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>36220</v>
       </c>
@@ -2148,7 +2137,7 @@
       </c>
       <c r="H88" s="3"/>
     </row>
-    <row r="89" spans="1:8">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>36251</v>
       </c>
@@ -2166,7 +2155,7 @@
       </c>
       <c r="H89" s="3"/>
     </row>
-    <row r="90" spans="1:8">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>36281</v>
       </c>
@@ -2184,7 +2173,7 @@
       </c>
       <c r="H90" s="3"/>
     </row>
-    <row r="91" spans="1:8">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>36312</v>
       </c>
@@ -2202,7 +2191,7 @@
       </c>
       <c r="H91" s="3"/>
     </row>
-    <row r="92" spans="1:8">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>36342</v>
       </c>
@@ -2220,7 +2209,7 @@
       </c>
       <c r="H92" s="3"/>
     </row>
-    <row r="93" spans="1:8">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>36373</v>
       </c>
@@ -2238,7 +2227,7 @@
       </c>
       <c r="H93" s="3"/>
     </row>
-    <row r="94" spans="1:8">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>36404</v>
       </c>
@@ -2256,7 +2245,7 @@
       </c>
       <c r="H94" s="3"/>
     </row>
-    <row r="95" spans="1:8">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>36434</v>
       </c>
@@ -2274,7 +2263,7 @@
       </c>
       <c r="H95" s="3"/>
     </row>
-    <row r="96" spans="1:8">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>36465</v>
       </c>
@@ -2292,7 +2281,7 @@
       </c>
       <c r="H96" s="3"/>
     </row>
-    <row r="97" spans="1:8">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>36495</v>
       </c>
@@ -2310,7 +2299,7 @@
       </c>
       <c r="H97" s="3"/>
     </row>
-    <row r="98" spans="1:8">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>36526</v>
       </c>
@@ -2328,7 +2317,7 @@
       </c>
       <c r="H98" s="3"/>
     </row>
-    <row r="99" spans="1:8">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>36557</v>
       </c>
@@ -2346,7 +2335,7 @@
       </c>
       <c r="H99" s="3"/>
     </row>
-    <row r="100" spans="1:8">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>36586</v>
       </c>
@@ -2364,7 +2353,7 @@
       </c>
       <c r="H100" s="3"/>
     </row>
-    <row r="101" spans="1:8">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>36617</v>
       </c>
@@ -2382,7 +2371,7 @@
       </c>
       <c r="H101" s="3"/>
     </row>
-    <row r="102" spans="1:8">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>36647</v>
       </c>
@@ -2400,7 +2389,7 @@
       </c>
       <c r="H102" s="3"/>
     </row>
-    <row r="103" spans="1:8">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>36678</v>
       </c>
@@ -2418,7 +2407,7 @@
       </c>
       <c r="H103" s="3"/>
     </row>
-    <row r="104" spans="1:8">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>36708</v>
       </c>
@@ -2436,7 +2425,7 @@
       </c>
       <c r="H104" s="3"/>
     </row>
-    <row r="105" spans="1:8">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>36739</v>
       </c>
@@ -2454,7 +2443,7 @@
       </c>
       <c r="H105" s="3"/>
     </row>
-    <row r="106" spans="1:8">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>36770</v>
       </c>
@@ -2472,7 +2461,7 @@
       </c>
       <c r="H106" s="3"/>
     </row>
-    <row r="107" spans="1:8">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>36800</v>
       </c>
@@ -2490,7 +2479,7 @@
       </c>
       <c r="H107" s="3"/>
     </row>
-    <row r="108" spans="1:8">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>36831</v>
       </c>
@@ -2508,7 +2497,7 @@
       </c>
       <c r="H108" s="3"/>
     </row>
-    <row r="109" spans="1:8">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>36861</v>
       </c>
@@ -2526,7 +2515,7 @@
       </c>
       <c r="H109" s="3"/>
     </row>
-    <row r="110" spans="1:8">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>36892</v>
       </c>
@@ -2544,7 +2533,7 @@
       </c>
       <c r="H110" s="3"/>
     </row>
-    <row r="111" spans="1:8">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>36923</v>
       </c>
@@ -2562,7 +2551,7 @@
       </c>
       <c r="H111" s="3"/>
     </row>
-    <row r="112" spans="1:8">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>36951</v>
       </c>
@@ -2580,7 +2569,7 @@
       </c>
       <c r="H112" s="3"/>
     </row>
-    <row r="113" spans="1:8">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>36982</v>
       </c>
@@ -2598,7 +2587,7 @@
       </c>
       <c r="H113" s="3"/>
     </row>
-    <row r="114" spans="1:8">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>37012</v>
       </c>
@@ -2616,7 +2605,7 @@
       </c>
       <c r="H114" s="3"/>
     </row>
-    <row r="115" spans="1:8">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>37043</v>
       </c>
@@ -2634,7 +2623,7 @@
       </c>
       <c r="H115" s="3"/>
     </row>
-    <row r="116" spans="1:8">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>37073</v>
       </c>
@@ -2652,7 +2641,7 @@
       </c>
       <c r="H116" s="3"/>
     </row>
-    <row r="117" spans="1:8">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>37104</v>
       </c>
@@ -2670,7 +2659,7 @@
       </c>
       <c r="H117" s="3"/>
     </row>
-    <row r="118" spans="1:8">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>37135</v>
       </c>
@@ -2688,7 +2677,7 @@
       </c>
       <c r="H118" s="3"/>
     </row>
-    <row r="119" spans="1:8">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>37165</v>
       </c>
@@ -2706,7 +2695,7 @@
       </c>
       <c r="H119" s="3"/>
     </row>
-    <row r="120" spans="1:8">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>37196</v>
       </c>
@@ -2724,7 +2713,7 @@
       </c>
       <c r="H120" s="3"/>
     </row>
-    <row r="121" spans="1:8">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>37226</v>
       </c>
@@ -2742,7 +2731,7 @@
       </c>
       <c r="H121" s="3"/>
     </row>
-    <row r="122" spans="1:8">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>37257</v>
       </c>
@@ -2760,7 +2749,7 @@
       </c>
       <c r="H122" s="3"/>
     </row>
-    <row r="123" spans="1:8">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>37288</v>
       </c>
@@ -2778,7 +2767,7 @@
       </c>
       <c r="H123" s="3"/>
     </row>
-    <row r="124" spans="1:8">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>37316</v>
       </c>
@@ -2796,7 +2785,7 @@
       </c>
       <c r="H124" s="3"/>
     </row>
-    <row r="125" spans="1:8">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>37347</v>
       </c>
@@ -2814,7 +2803,7 @@
       </c>
       <c r="H125" s="3"/>
     </row>
-    <row r="126" spans="1:8">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>37377</v>
       </c>
@@ -2832,7 +2821,7 @@
       </c>
       <c r="H126" s="3"/>
     </row>
-    <row r="127" spans="1:8">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>37408</v>
       </c>
@@ -2850,7 +2839,7 @@
       </c>
       <c r="H127" s="3"/>
     </row>
-    <row r="128" spans="1:8">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>37438</v>
       </c>
@@ -2868,7 +2857,7 @@
       </c>
       <c r="H128" s="3"/>
     </row>
-    <row r="129" spans="1:8">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <v>37469</v>
       </c>
@@ -2886,7 +2875,7 @@
       </c>
       <c r="H129" s="3"/>
     </row>
-    <row r="130" spans="1:8">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>37500</v>
       </c>
@@ -2904,7 +2893,7 @@
       </c>
       <c r="H130" s="3"/>
     </row>
-    <row r="131" spans="1:8">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <v>37530</v>
       </c>
@@ -2922,7 +2911,7 @@
       </c>
       <c r="H131" s="3"/>
     </row>
-    <row r="132" spans="1:8">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <v>37561</v>
       </c>
@@ -2940,7 +2929,7 @@
       </c>
       <c r="H132" s="3"/>
     </row>
-    <row r="133" spans="1:8">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <v>37591</v>
       </c>
@@ -2958,7 +2947,7 @@
       </c>
       <c r="H133" s="3"/>
     </row>
-    <row r="134" spans="1:8">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <v>37622</v>
       </c>
@@ -2976,7 +2965,7 @@
       </c>
       <c r="H134" s="3"/>
     </row>
-    <row r="135" spans="1:8">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <v>37653</v>
       </c>
@@ -2994,7 +2983,7 @@
       </c>
       <c r="H135" s="3"/>
     </row>
-    <row r="136" spans="1:8">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <v>37681</v>
       </c>
@@ -3012,7 +3001,7 @@
       </c>
       <c r="H136" s="3"/>
     </row>
-    <row r="137" spans="1:8">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
         <v>37712</v>
       </c>
@@ -3030,7 +3019,7 @@
       </c>
       <c r="H137" s="3"/>
     </row>
-    <row r="138" spans="1:8">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>37742</v>
       </c>
@@ -3048,7 +3037,7 @@
       </c>
       <c r="H138" s="3"/>
     </row>
-    <row r="139" spans="1:8">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
         <v>37773</v>
       </c>
@@ -3066,7 +3055,7 @@
       </c>
       <c r="H139" s="3"/>
     </row>
-    <row r="140" spans="1:8">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
         <v>37803</v>
       </c>
@@ -3084,7 +3073,7 @@
       </c>
       <c r="H140" s="3"/>
     </row>
-    <row r="141" spans="1:8">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
         <v>37834</v>
       </c>
@@ -3102,7 +3091,7 @@
       </c>
       <c r="H141" s="3"/>
     </row>
-    <row r="142" spans="1:8">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
         <v>37865</v>
       </c>
@@ -3120,7 +3109,7 @@
       </c>
       <c r="H142" s="3"/>
     </row>
-    <row r="143" spans="1:8">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
         <v>37895</v>
       </c>
@@ -3138,7 +3127,7 @@
       </c>
       <c r="H143" s="3"/>
     </row>
-    <row r="144" spans="1:8">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
         <v>37926</v>
       </c>
@@ -3156,7 +3145,7 @@
       </c>
       <c r="H144" s="3"/>
     </row>
-    <row r="145" spans="1:8">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
         <v>37956</v>
       </c>
@@ -3174,7 +3163,7 @@
       </c>
       <c r="H145" s="3"/>
     </row>
-    <row r="146" spans="1:8">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
         <v>37987</v>
       </c>
@@ -3192,7 +3181,7 @@
       </c>
       <c r="H146" s="3"/>
     </row>
-    <row r="147" spans="1:8">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
         <v>38018</v>
       </c>
@@ -3210,7 +3199,7 @@
       </c>
       <c r="H147" s="3"/>
     </row>
-    <row r="148" spans="1:8">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
         <v>38047</v>
       </c>
@@ -3228,7 +3217,7 @@
       </c>
       <c r="H148" s="3"/>
     </row>
-    <row r="149" spans="1:8">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
         <v>38078</v>
       </c>
@@ -3246,7 +3235,7 @@
       </c>
       <c r="H149" s="3"/>
     </row>
-    <row r="150" spans="1:8">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
         <v>38108</v>
       </c>
@@ -3264,7 +3253,7 @@
       </c>
       <c r="H150" s="3"/>
     </row>
-    <row r="151" spans="1:8">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
         <v>38139</v>
       </c>
@@ -3282,7 +3271,7 @@
       </c>
       <c r="H151" s="3"/>
     </row>
-    <row r="152" spans="1:8">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
         <v>38169</v>
       </c>
@@ -3300,7 +3289,7 @@
       </c>
       <c r="H152" s="3"/>
     </row>
-    <row r="153" spans="1:8">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
         <v>38200</v>
       </c>
@@ -3318,7 +3307,7 @@
       </c>
       <c r="H153" s="3"/>
     </row>
-    <row r="154" spans="1:8">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
         <v>38231</v>
       </c>
@@ -3336,7 +3325,7 @@
       </c>
       <c r="H154" s="3"/>
     </row>
-    <row r="155" spans="1:8">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
         <v>38261</v>
       </c>
@@ -3354,7 +3343,7 @@
       </c>
       <c r="H155" s="3"/>
     </row>
-    <row r="156" spans="1:8">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
         <v>38292</v>
       </c>
@@ -3372,7 +3361,7 @@
       </c>
       <c r="H156" s="3"/>
     </row>
-    <row r="157" spans="1:8">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
         <v>38322</v>
       </c>
@@ -3390,7 +3379,7 @@
       </c>
       <c r="H157" s="3"/>
     </row>
-    <row r="158" spans="1:8">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
         <v>38353</v>
       </c>
@@ -3408,7 +3397,7 @@
       </c>
       <c r="H158" s="3"/>
     </row>
-    <row r="159" spans="1:8">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
         <v>38384</v>
       </c>
@@ -3426,7 +3415,7 @@
       </c>
       <c r="H159" s="3"/>
     </row>
-    <row r="160" spans="1:8">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
         <v>38412</v>
       </c>
@@ -3444,7 +3433,7 @@
       </c>
       <c r="H160" s="3"/>
     </row>
-    <row r="161" spans="1:8">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
         <v>38443</v>
       </c>
@@ -3462,7 +3451,7 @@
       </c>
       <c r="H161" s="3"/>
     </row>
-    <row r="162" spans="1:8">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
         <v>38473</v>
       </c>
@@ -3480,7 +3469,7 @@
       </c>
       <c r="H162" s="3"/>
     </row>
-    <row r="163" spans="1:8">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
         <v>38504</v>
       </c>
@@ -3498,7 +3487,7 @@
       </c>
       <c r="H163" s="3"/>
     </row>
-    <row r="164" spans="1:8">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
         <v>38534</v>
       </c>
@@ -3516,7 +3505,7 @@
       </c>
       <c r="H164" s="3"/>
     </row>
-    <row r="165" spans="1:8">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
         <v>38565</v>
       </c>
@@ -3534,7 +3523,7 @@
       </c>
       <c r="H165" s="3"/>
     </row>
-    <row r="166" spans="1:8">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
         <v>38596</v>
       </c>
@@ -3552,7 +3541,7 @@
       </c>
       <c r="H166" s="3"/>
     </row>
-    <row r="167" spans="1:8">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
         <v>38626</v>
       </c>
@@ -3570,7 +3559,7 @@
       </c>
       <c r="H167" s="3"/>
     </row>
-    <row r="168" spans="1:8">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
         <v>38657</v>
       </c>
@@ -3588,7 +3577,7 @@
       </c>
       <c r="H168" s="3"/>
     </row>
-    <row r="169" spans="1:8">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169" s="1">
         <v>38687</v>
       </c>
@@ -3606,7 +3595,7 @@
       </c>
       <c r="H169" s="3"/>
     </row>
-    <row r="170" spans="1:8">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
         <v>38718</v>
       </c>
@@ -3624,7 +3613,7 @@
       </c>
       <c r="H170" s="3"/>
     </row>
-    <row r="171" spans="1:8">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
         <v>38749</v>
       </c>
@@ -3642,7 +3631,7 @@
       </c>
       <c r="H171" s="3"/>
     </row>
-    <row r="172" spans="1:8">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
         <v>38777</v>
       </c>
@@ -3660,7 +3649,7 @@
       </c>
       <c r="H172" s="3"/>
     </row>
-    <row r="173" spans="1:8">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173" s="1">
         <v>38808</v>
       </c>
@@ -3678,7 +3667,7 @@
       </c>
       <c r="H173" s="3"/>
     </row>
-    <row r="174" spans="1:8">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174" s="1">
         <v>38838</v>
       </c>
@@ -3696,7 +3685,7 @@
       </c>
       <c r="H174" s="3"/>
     </row>
-    <row r="175" spans="1:8">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175" s="1">
         <v>38869</v>
       </c>
@@ -3714,7 +3703,7 @@
       </c>
       <c r="H175" s="3"/>
     </row>
-    <row r="176" spans="1:8">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176" s="1">
         <v>38899</v>
       </c>
@@ -3732,7 +3721,7 @@
       </c>
       <c r="H176" s="3"/>
     </row>
-    <row r="177" spans="1:8">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A177" s="1">
         <v>38930</v>
       </c>
@@ -3750,7 +3739,7 @@
       </c>
       <c r="H177" s="3"/>
     </row>
-    <row r="178" spans="1:8">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A178" s="1">
         <v>38961</v>
       </c>
@@ -3768,7 +3757,7 @@
       </c>
       <c r="H178" s="3"/>
     </row>
-    <row r="179" spans="1:8">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179" s="1">
         <v>38991</v>
       </c>
@@ -3786,7 +3775,7 @@
       </c>
       <c r="H179" s="3"/>
     </row>
-    <row r="180" spans="1:8">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A180" s="1">
         <v>39022</v>
       </c>
@@ -3804,7 +3793,7 @@
       </c>
       <c r="H180" s="3"/>
     </row>
-    <row r="181" spans="1:8">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181" s="1">
         <v>39052</v>
       </c>
@@ -3822,7 +3811,7 @@
       </c>
       <c r="H181" s="3"/>
     </row>
-    <row r="182" spans="1:8">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182" s="1">
         <v>39083</v>
       </c>
@@ -3840,7 +3829,7 @@
       </c>
       <c r="H182" s="3"/>
     </row>
-    <row r="183" spans="1:8">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183" s="1">
         <v>39114</v>
       </c>
@@ -3858,7 +3847,7 @@
       </c>
       <c r="H183" s="3"/>
     </row>
-    <row r="184" spans="1:8">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A184" s="1">
         <v>39142</v>
       </c>
@@ -3876,7 +3865,7 @@
       </c>
       <c r="H184" s="3"/>
     </row>
-    <row r="185" spans="1:8">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A185" s="1">
         <v>39173</v>
       </c>
@@ -3894,7 +3883,7 @@
       </c>
       <c r="H185" s="3"/>
     </row>
-    <row r="186" spans="1:8">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186" s="1">
         <v>39203</v>
       </c>
@@ -3912,7 +3901,7 @@
       </c>
       <c r="H186" s="3"/>
     </row>
-    <row r="187" spans="1:8">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A187" s="1">
         <v>39234</v>
       </c>
@@ -3930,7 +3919,7 @@
       </c>
       <c r="H187" s="3"/>
     </row>
-    <row r="188" spans="1:8">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188" s="1">
         <v>39264</v>
       </c>
@@ -3948,7 +3937,7 @@
       </c>
       <c r="H188" s="3"/>
     </row>
-    <row r="189" spans="1:8">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189" s="1">
         <v>39295</v>
       </c>
@@ -3966,7 +3955,7 @@
       </c>
       <c r="H189" s="3"/>
     </row>
-    <row r="190" spans="1:8">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A190" s="1">
         <v>39326</v>
       </c>
@@ -3984,7 +3973,7 @@
       </c>
       <c r="H190" s="3"/>
     </row>
-    <row r="191" spans="1:8">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A191" s="1">
         <v>39356</v>
       </c>
@@ -4002,7 +3991,7 @@
       </c>
       <c r="H191" s="3"/>
     </row>
-    <row r="192" spans="1:8">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A192" s="1">
         <v>39387</v>
       </c>
@@ -4020,7 +4009,7 @@
       </c>
       <c r="H192" s="3"/>
     </row>
-    <row r="193" spans="1:8">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193" s="1">
         <v>39417</v>
       </c>
@@ -4038,7 +4027,7 @@
       </c>
       <c r="H193" s="3"/>
     </row>
-    <row r="194" spans="1:8">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194" s="1">
         <v>39448</v>
       </c>
@@ -4056,7 +4045,7 @@
       </c>
       <c r="H194" s="3"/>
     </row>
-    <row r="195" spans="1:8">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195" s="1">
         <v>39479</v>
       </c>
@@ -4074,7 +4063,7 @@
       </c>
       <c r="H195" s="3"/>
     </row>
-    <row r="196" spans="1:8">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196" s="1">
         <v>39508</v>
       </c>
@@ -4092,7 +4081,7 @@
       </c>
       <c r="H196" s="3"/>
     </row>
-    <row r="197" spans="1:8">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A197" s="1">
         <v>39539</v>
       </c>
@@ -4110,7 +4099,7 @@
       </c>
       <c r="H197" s="3"/>
     </row>
-    <row r="198" spans="1:8">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198" s="1">
         <v>39569</v>
       </c>
@@ -4128,7 +4117,7 @@
       </c>
       <c r="H198" s="3"/>
     </row>
-    <row r="199" spans="1:8">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A199" s="1">
         <v>39600</v>
       </c>
@@ -4146,7 +4135,7 @@
       </c>
       <c r="H199" s="3"/>
     </row>
-    <row r="200" spans="1:8">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A200" s="1">
         <v>39630</v>
       </c>
@@ -4164,7 +4153,7 @@
       </c>
       <c r="H200" s="3"/>
     </row>
-    <row r="201" spans="1:8">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A201" s="1">
         <v>39661</v>
       </c>
@@ -4182,7 +4171,7 @@
       </c>
       <c r="H201" s="3"/>
     </row>
-    <row r="202" spans="1:8">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A202" s="1">
         <v>39692</v>
       </c>
@@ -4200,7 +4189,7 @@
       </c>
       <c r="H202" s="3"/>
     </row>
-    <row r="203" spans="1:8">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A203" s="1">
         <v>39722</v>
       </c>
@@ -4218,7 +4207,7 @@
       </c>
       <c r="H203" s="3"/>
     </row>
-    <row r="204" spans="1:8">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A204" s="1">
         <v>39753</v>
       </c>
@@ -4236,7 +4225,7 @@
       </c>
       <c r="H204" s="3"/>
     </row>
-    <row r="205" spans="1:8">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A205" s="1">
         <v>39783</v>
       </c>
@@ -4254,7 +4243,7 @@
       </c>
       <c r="H205" s="3"/>
     </row>
-    <row r="206" spans="1:8">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A206" s="1">
         <v>39814</v>
       </c>
@@ -4272,7 +4261,7 @@
       </c>
       <c r="H206" s="3"/>
     </row>
-    <row r="207" spans="1:8">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A207" s="1">
         <v>39845</v>
       </c>
@@ -4290,7 +4279,7 @@
       </c>
       <c r="H207" s="3"/>
     </row>
-    <row r="208" spans="1:8">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A208" s="1">
         <v>39873</v>
       </c>
@@ -4308,7 +4297,7 @@
       </c>
       <c r="H208" s="3"/>
     </row>
-    <row r="209" spans="1:8">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A209" s="1">
         <v>39904</v>
       </c>
@@ -4326,7 +4315,7 @@
       </c>
       <c r="H209" s="3"/>
     </row>
-    <row r="210" spans="1:8">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A210" s="1">
         <v>39934</v>
       </c>
@@ -4344,7 +4333,7 @@
       </c>
       <c r="H210" s="3"/>
     </row>
-    <row r="211" spans="1:8">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A211" s="1">
         <v>39965</v>
       </c>
@@ -4362,7 +4351,7 @@
       </c>
       <c r="H211" s="3"/>
     </row>
-    <row r="212" spans="1:8">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A212" s="1">
         <v>39995</v>
       </c>
@@ -4380,7 +4369,7 @@
       </c>
       <c r="H212" s="3"/>
     </row>
-    <row r="213" spans="1:8">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A213" s="1">
         <v>40026</v>
       </c>
@@ -4398,7 +4387,7 @@
       </c>
       <c r="H213" s="3"/>
     </row>
-    <row r="214" spans="1:8">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A214" s="1">
         <v>40057</v>
       </c>
@@ -4416,7 +4405,7 @@
       </c>
       <c r="H214" s="3"/>
     </row>
-    <row r="215" spans="1:8">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A215" s="1">
         <v>40087</v>
       </c>
@@ -4434,7 +4423,7 @@
       </c>
       <c r="H215" s="3"/>
     </row>
-    <row r="216" spans="1:8">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A216" s="1">
         <v>40118</v>
       </c>
@@ -4452,7 +4441,7 @@
       </c>
       <c r="H216" s="3"/>
     </row>
-    <row r="217" spans="1:8">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A217" s="1">
         <v>40148</v>
       </c>
@@ -4470,7 +4459,7 @@
       </c>
       <c r="H217" s="3"/>
     </row>
-    <row r="218" spans="1:8">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A218" s="1">
         <v>40179</v>
       </c>
@@ -4488,7 +4477,7 @@
       </c>
       <c r="H218" s="3"/>
     </row>
-    <row r="219" spans="1:8">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A219" s="1">
         <v>40210</v>
       </c>
@@ -4506,7 +4495,7 @@
       </c>
       <c r="H219" s="3"/>
     </row>
-    <row r="220" spans="1:8">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A220" s="1">
         <v>40238</v>
       </c>
@@ -4524,7 +4513,7 @@
       </c>
       <c r="H220" s="3"/>
     </row>
-    <row r="221" spans="1:8">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A221" s="1">
         <v>40269</v>
       </c>
@@ -4542,7 +4531,7 @@
       </c>
       <c r="H221" s="3"/>
     </row>
-    <row r="222" spans="1:8">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A222" s="1">
         <v>40299</v>
       </c>
@@ -4560,7 +4549,7 @@
       </c>
       <c r="H222" s="3"/>
     </row>
-    <row r="223" spans="1:8">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A223" s="1">
         <v>40330</v>
       </c>
@@ -4578,7 +4567,7 @@
       </c>
       <c r="H223" s="3"/>
     </row>
-    <row r="224" spans="1:8">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A224" s="1">
         <v>40360</v>
       </c>
@@ -4596,7 +4585,7 @@
       </c>
       <c r="H224" s="3"/>
     </row>
-    <row r="225" spans="1:8">
+    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A225" s="1">
         <v>40391</v>
       </c>
@@ -4614,7 +4603,7 @@
       </c>
       <c r="H225" s="3"/>
     </row>
-    <row r="226" spans="1:8">
+    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A226" s="1">
         <v>40422</v>
       </c>
@@ -4632,7 +4621,7 @@
       </c>
       <c r="H226" s="3"/>
     </row>
-    <row r="227" spans="1:8">
+    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A227" s="1">
         <v>40452</v>
       </c>
@@ -4650,7 +4639,7 @@
       </c>
       <c r="H227" s="3"/>
     </row>
-    <row r="228" spans="1:8">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A228" s="1">
         <v>40483</v>
       </c>
@@ -4668,7 +4657,7 @@
       </c>
       <c r="H228" s="3"/>
     </row>
-    <row r="229" spans="1:8">
+    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A229" s="1">
         <v>40513</v>
       </c>
@@ -4686,7 +4675,7 @@
       </c>
       <c r="H229" s="3"/>
     </row>
-    <row r="230" spans="1:8">
+    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A230" s="1">
         <v>40544</v>
       </c>
@@ -4704,7 +4693,7 @@
       </c>
       <c r="H230" s="3"/>
     </row>
-    <row r="231" spans="1:8">
+    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A231" s="1">
         <v>40575</v>
       </c>
@@ -4722,7 +4711,7 @@
       </c>
       <c r="H231" s="3"/>
     </row>
-    <row r="232" spans="1:8">
+    <row r="232" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A232" s="1">
         <v>40603</v>
       </c>
@@ -4740,7 +4729,7 @@
       </c>
       <c r="H232" s="3"/>
     </row>
-    <row r="233" spans="1:8">
+    <row r="233" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A233" s="1">
         <v>40634</v>
       </c>
@@ -4758,7 +4747,7 @@
       </c>
       <c r="H233" s="3"/>
     </row>
-    <row r="234" spans="1:8">
+    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A234" s="1">
         <v>40664</v>
       </c>
@@ -4776,7 +4765,7 @@
       </c>
       <c r="H234" s="3"/>
     </row>
-    <row r="235" spans="1:8">
+    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A235" s="1">
         <v>40695</v>
       </c>
@@ -4794,7 +4783,7 @@
       </c>
       <c r="H235" s="3"/>
     </row>
-    <row r="236" spans="1:8">
+    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A236" s="1">
         <v>40725</v>
       </c>
@@ -4812,7 +4801,7 @@
       </c>
       <c r="H236" s="3"/>
     </row>
-    <row r="237" spans="1:8">
+    <row r="237" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A237" s="1">
         <v>40756</v>
       </c>
@@ -4830,7 +4819,7 @@
       </c>
       <c r="H237" s="3"/>
     </row>
-    <row r="238" spans="1:8">
+    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A238" s="1">
         <v>40787</v>
       </c>
@@ -4848,7 +4837,7 @@
       </c>
       <c r="H238" s="3"/>
     </row>
-    <row r="239" spans="1:8">
+    <row r="239" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A239" s="1">
         <v>40817</v>
       </c>
@@ -4866,7 +4855,7 @@
       </c>
       <c r="H239" s="3"/>
     </row>
-    <row r="240" spans="1:8">
+    <row r="240" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A240" s="1">
         <v>40848</v>
       </c>
@@ -4884,7 +4873,7 @@
       </c>
       <c r="H240" s="3"/>
     </row>
-    <row r="241" spans="1:8">
+    <row r="241" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A241" s="1">
         <v>40878</v>
       </c>
@@ -4902,7 +4891,7 @@
       </c>
       <c r="H241" s="3"/>
     </row>
-    <row r="242" spans="1:8">
+    <row r="242" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A242" s="1">
         <v>40909</v>
       </c>
@@ -4920,7 +4909,7 @@
       </c>
       <c r="H242" s="3"/>
     </row>
-    <row r="243" spans="1:8">
+    <row r="243" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A243" s="1">
         <v>40940</v>
       </c>
@@ -4938,7 +4927,7 @@
       </c>
       <c r="H243" s="3"/>
     </row>
-    <row r="244" spans="1:8">
+    <row r="244" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A244" s="1">
         <v>40969</v>
       </c>
@@ -4956,7 +4945,7 @@
       </c>
       <c r="H244" s="3"/>
     </row>
-    <row r="245" spans="1:8">
+    <row r="245" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A245" s="1">
         <v>41000</v>
       </c>
@@ -4974,7 +4963,7 @@
       </c>
       <c r="H245" s="3"/>
     </row>
-    <row r="246" spans="1:8">
+    <row r="246" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A246" s="1">
         <v>41030</v>
       </c>
@@ -4992,7 +4981,7 @@
       </c>
       <c r="H246" s="3"/>
     </row>
-    <row r="247" spans="1:8">
+    <row r="247" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A247" s="1">
         <v>41061</v>
       </c>
@@ -5010,7 +4999,7 @@
       </c>
       <c r="H247" s="3"/>
     </row>
-    <row r="248" spans="1:8">
+    <row r="248" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A248" s="1">
         <v>41091</v>
       </c>
@@ -5028,7 +5017,7 @@
       </c>
       <c r="H248" s="3"/>
     </row>
-    <row r="249" spans="1:8">
+    <row r="249" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A249" s="1">
         <v>41122</v>
       </c>
@@ -5046,7 +5035,7 @@
       </c>
       <c r="H249" s="3"/>
     </row>
-    <row r="250" spans="1:8">
+    <row r="250" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A250" s="1">
         <v>41153</v>
       </c>
@@ -5064,7 +5053,7 @@
       </c>
       <c r="H250" s="3"/>
     </row>
-    <row r="251" spans="1:8">
+    <row r="251" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A251" s="1">
         <v>41183</v>
       </c>
@@ -5082,7 +5071,7 @@
       </c>
       <c r="H251" s="3"/>
     </row>
-    <row r="252" spans="1:8">
+    <row r="252" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A252" s="1">
         <v>41214</v>
       </c>
@@ -5100,7 +5089,7 @@
       </c>
       <c r="H252" s="3"/>
     </row>
-    <row r="253" spans="1:8">
+    <row r="253" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A253" s="1">
         <v>41244</v>
       </c>
@@ -5118,7 +5107,7 @@
       </c>
       <c r="H253" s="3"/>
     </row>
-    <row r="254" spans="1:8">
+    <row r="254" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A254" s="1">
         <v>41275</v>
       </c>
@@ -5136,7 +5125,7 @@
       </c>
       <c r="H254" s="3"/>
     </row>
-    <row r="255" spans="1:8">
+    <row r="255" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A255" s="1">
         <v>41306</v>
       </c>
@@ -5154,7 +5143,7 @@
       </c>
       <c r="H255" s="3"/>
     </row>
-    <row r="256" spans="1:8">
+    <row r="256" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A256" s="1">
         <v>41334</v>
       </c>
@@ -5172,7 +5161,7 @@
       </c>
       <c r="H256" s="3"/>
     </row>
-    <row r="257" spans="1:8">
+    <row r="257" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A257" s="1">
         <v>41365</v>
       </c>
@@ -5190,7 +5179,7 @@
       </c>
       <c r="H257" s="3"/>
     </row>
-    <row r="258" spans="1:8">
+    <row r="258" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A258" s="1">
         <v>41395</v>
       </c>
@@ -5208,7 +5197,7 @@
       </c>
       <c r="H258" s="3"/>
     </row>
-    <row r="259" spans="1:8">
+    <row r="259" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A259" s="1">
         <v>41426</v>
       </c>
@@ -5226,7 +5215,7 @@
       </c>
       <c r="H259" s="3"/>
     </row>
-    <row r="260" spans="1:8">
+    <row r="260" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A260" s="1">
         <v>41456</v>
       </c>
@@ -5244,7 +5233,7 @@
       </c>
       <c r="H260" s="3"/>
     </row>
-    <row r="261" spans="1:8">
+    <row r="261" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A261" s="1">
         <v>41487</v>
       </c>
@@ -5262,7 +5251,7 @@
       </c>
       <c r="H261" s="3"/>
     </row>
-    <row r="262" spans="1:8">
+    <row r="262" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A262" s="1">
         <v>41518</v>
       </c>
@@ -5280,7 +5269,7 @@
       </c>
       <c r="H262" s="3"/>
     </row>
-    <row r="263" spans="1:8">
+    <row r="263" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A263" s="1">
         <v>41548</v>
       </c>
@@ -5298,7 +5287,7 @@
       </c>
       <c r="H263" s="3"/>
     </row>
-    <row r="264" spans="1:8">
+    <row r="264" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A264" s="1">
         <v>41579</v>
       </c>
@@ -5316,7 +5305,7 @@
       </c>
       <c r="H264" s="3"/>
     </row>
-    <row r="265" spans="1:8">
+    <row r="265" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A265" s="1">
         <v>41609</v>
       </c>
@@ -5334,7 +5323,7 @@
       </c>
       <c r="H265" s="3"/>
     </row>
-    <row r="266" spans="1:8">
+    <row r="266" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A266" s="1">
         <v>41640</v>
       </c>
@@ -5352,7 +5341,7 @@
       </c>
       <c r="H266" s="3"/>
     </row>
-    <row r="267" spans="1:8">
+    <row r="267" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A267" s="1">
         <v>41671</v>
       </c>
@@ -5370,7 +5359,7 @@
       </c>
       <c r="H267" s="3"/>
     </row>
-    <row r="268" spans="1:8">
+    <row r="268" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A268" s="1">
         <v>41699</v>
       </c>
@@ -5388,7 +5377,7 @@
       </c>
       <c r="H268" s="3"/>
     </row>
-    <row r="269" spans="1:8">
+    <row r="269" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A269" s="1">
         <v>41730</v>
       </c>
@@ -5406,7 +5395,7 @@
       </c>
       <c r="H269" s="3"/>
     </row>
-    <row r="270" spans="1:8">
+    <row r="270" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A270" s="1">
         <v>41760</v>
       </c>
@@ -5424,7 +5413,7 @@
       </c>
       <c r="H270" s="3"/>
     </row>
-    <row r="271" spans="1:8">
+    <row r="271" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A271" s="1">
         <v>41791</v>
       </c>
@@ -5442,7 +5431,7 @@
       </c>
       <c r="H271" s="3"/>
     </row>
-    <row r="272" spans="1:8">
+    <row r="272" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A272" s="1">
         <v>41821</v>
       </c>
@@ -5460,7 +5449,7 @@
       </c>
       <c r="H272" s="3"/>
     </row>
-    <row r="273" spans="1:8">
+    <row r="273" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A273" s="1">
         <v>41852</v>
       </c>
@@ -5478,7 +5467,7 @@
       </c>
       <c r="H273" s="3"/>
     </row>
-    <row r="274" spans="1:8">
+    <row r="274" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A274" s="1">
         <v>41883</v>
       </c>
@@ -5496,7 +5485,7 @@
       </c>
       <c r="H274" s="3"/>
     </row>
-    <row r="275" spans="1:8">
+    <row r="275" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A275" s="1">
         <v>41913</v>
       </c>
@@ -5514,7 +5503,7 @@
       </c>
       <c r="H275" s="3"/>
     </row>
-    <row r="276" spans="1:8">
+    <row r="276" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A276" s="1">
         <v>41944</v>
       </c>
@@ -5532,7 +5521,7 @@
       </c>
       <c r="H276" s="3"/>
     </row>
-    <row r="277" spans="1:8">
+    <row r="277" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A277" s="1">
         <v>41974</v>
       </c>
@@ -5550,7 +5539,7 @@
       </c>
       <c r="H277" s="3"/>
     </row>
-    <row r="278" spans="1:8">
+    <row r="278" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A278" s="1">
         <v>42005</v>
       </c>
@@ -5568,7 +5557,7 @@
       </c>
       <c r="H278" s="3"/>
     </row>
-    <row r="279" spans="1:8">
+    <row r="279" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A279" s="1">
         <v>42036</v>
       </c>
@@ -5586,7 +5575,7 @@
       </c>
       <c r="H279" s="3"/>
     </row>
-    <row r="280" spans="1:8">
+    <row r="280" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A280" s="1">
         <v>42064</v>
       </c>
@@ -5604,7 +5593,7 @@
       </c>
       <c r="H280" s="3"/>
     </row>
-    <row r="281" spans="1:8">
+    <row r="281" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A281" s="1">
         <v>42095</v>
       </c>
@@ -5622,7 +5611,7 @@
       </c>
       <c r="H281" s="3"/>
     </row>
-    <row r="282" spans="1:8">
+    <row r="282" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A282" s="1">
         <v>42125</v>
       </c>
@@ -5640,7 +5629,7 @@
       </c>
       <c r="H282" s="3"/>
     </row>
-    <row r="283" spans="1:8">
+    <row r="283" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A283" s="1">
         <v>42156</v>
       </c>
@@ -5658,7 +5647,7 @@
       </c>
       <c r="H283" s="3"/>
     </row>
-    <row r="284" spans="1:8">
+    <row r="284" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A284" s="1">
         <v>42186</v>
       </c>
@@ -5676,7 +5665,7 @@
       </c>
       <c r="H284" s="3"/>
     </row>
-    <row r="285" spans="1:8">
+    <row r="285" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A285" s="1">
         <v>42217</v>
       </c>
@@ -5694,7 +5683,7 @@
       </c>
       <c r="H285" s="3"/>
     </row>
-    <row r="286" spans="1:8">
+    <row r="286" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A286" s="1">
         <v>42248</v>
       </c>
@@ -5712,7 +5701,7 @@
       </c>
       <c r="H286" s="3"/>
     </row>
-    <row r="287" spans="1:8">
+    <row r="287" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A287" s="1">
         <v>42278</v>
       </c>
@@ -5730,7 +5719,7 @@
       </c>
       <c r="H287" s="3"/>
     </row>
-    <row r="288" spans="1:8">
+    <row r="288" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A288" s="1">
         <v>42309</v>
       </c>
@@ -5748,7 +5737,7 @@
       </c>
       <c r="H288" s="3"/>
     </row>
-    <row r="289" spans="1:8">
+    <row r="289" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A289" s="1">
         <v>42339</v>
       </c>
@@ -5766,7 +5755,7 @@
       </c>
       <c r="H289" s="3"/>
     </row>
-    <row r="290" spans="1:8">
+    <row r="290" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A290" s="1">
         <v>42370</v>
       </c>
@@ -5784,7 +5773,7 @@
       </c>
       <c r="H290" s="3"/>
     </row>
-    <row r="291" spans="1:8">
+    <row r="291" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A291" s="1">
         <v>42401</v>
       </c>
@@ -5802,7 +5791,7 @@
       </c>
       <c r="H291" s="3"/>
     </row>
-    <row r="292" spans="1:8">
+    <row r="292" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A292" s="1">
         <v>42430</v>
       </c>
@@ -5820,7 +5809,7 @@
       </c>
       <c r="H292" s="3"/>
     </row>
-    <row r="293" spans="1:8">
+    <row r="293" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A293" s="1">
         <v>42461</v>
       </c>
@@ -5838,7 +5827,7 @@
       </c>
       <c r="H293" s="3"/>
     </row>
-    <row r="294" spans="1:8">
+    <row r="294" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A294" s="1">
         <v>42491</v>
       </c>
@@ -5856,7 +5845,7 @@
       </c>
       <c r="H294" s="3"/>
     </row>
-    <row r="295" spans="1:8">
+    <row r="295" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A295" s="1">
         <v>42522</v>
       </c>
@@ -5874,7 +5863,7 @@
       </c>
       <c r="H295" s="3"/>
     </row>
-    <row r="296" spans="1:8">
+    <row r="296" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A296" s="1">
         <v>42552</v>
       </c>
@@ -5892,7 +5881,7 @@
       </c>
       <c r="H296" s="3"/>
     </row>
-    <row r="297" spans="1:8">
+    <row r="297" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A297" s="1">
         <v>42583</v>
       </c>
@@ -5910,7 +5899,7 @@
       </c>
       <c r="H297" s="3"/>
     </row>
-    <row r="298" spans="1:8">
+    <row r="298" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A298" s="1">
         <v>42614</v>
       </c>
@@ -5928,7 +5917,7 @@
       </c>
       <c r="H298" s="3"/>
     </row>
-    <row r="299" spans="1:8">
+    <row r="299" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A299" s="1">
         <v>42644</v>
       </c>
@@ -5946,7 +5935,7 @@
       </c>
       <c r="H299" s="3"/>
     </row>
-    <row r="300" spans="1:8">
+    <row r="300" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A300" s="1">
         <v>42675</v>
       </c>
@@ -5964,7 +5953,7 @@
       </c>
       <c r="H300" s="3"/>
     </row>
-    <row r="301" spans="1:8">
+    <row r="301" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A301" s="1">
         <v>42705</v>
       </c>
@@ -5982,7 +5971,7 @@
       </c>
       <c r="H301" s="3"/>
     </row>
-    <row r="302" spans="1:8">
+    <row r="302" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A302" s="1">
         <v>42736</v>
       </c>
@@ -6000,7 +5989,7 @@
       </c>
       <c r="H302" s="3"/>
     </row>
-    <row r="303" spans="1:8">
+    <row r="303" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A303" s="1">
         <v>42767</v>
       </c>
@@ -6018,7 +6007,7 @@
       </c>
       <c r="H303" s="3"/>
     </row>
-    <row r="304" spans="1:8">
+    <row r="304" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A304" s="1">
         <v>42795</v>
       </c>
@@ -6036,7 +6025,7 @@
       </c>
       <c r="H304" s="3"/>
     </row>
-    <row r="305" spans="1:8">
+    <row r="305" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A305" s="1">
         <v>42826</v>
       </c>
@@ -6054,7 +6043,7 @@
       </c>
       <c r="H305" s="3"/>
     </row>
-    <row r="306" spans="1:8">
+    <row r="306" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A306" s="1">
         <v>42856</v>
       </c>
@@ -6072,7 +6061,7 @@
       </c>
       <c r="H306" s="3"/>
     </row>
-    <row r="307" spans="1:8">
+    <row r="307" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A307" s="1">
         <v>42887</v>
       </c>
@@ -6090,7 +6079,7 @@
       </c>
       <c r="H307" s="3"/>
     </row>
-    <row r="308" spans="1:8">
+    <row r="308" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A308" s="1">
         <v>42917</v>
       </c>
@@ -6108,7 +6097,7 @@
       </c>
       <c r="H308" s="3"/>
     </row>
-    <row r="309" spans="1:8">
+    <row r="309" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A309" s="1">
         <v>42948</v>
       </c>
@@ -6126,7 +6115,7 @@
       </c>
       <c r="H309" s="3"/>
     </row>
-    <row r="310" spans="1:8">
+    <row r="310" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A310" s="1">
         <v>42979</v>
       </c>
@@ -6144,7 +6133,7 @@
       </c>
       <c r="H310" s="3"/>
     </row>
-    <row r="311" spans="1:8">
+    <row r="311" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A311" s="1">
         <v>43009</v>
       </c>
@@ -6162,7 +6151,7 @@
       </c>
       <c r="H311" s="3"/>
     </row>
-    <row r="312" spans="1:8">
+    <row r="312" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A312" s="1">
         <v>43040</v>
       </c>
@@ -6180,7 +6169,7 @@
       </c>
       <c r="H312" s="3"/>
     </row>
-    <row r="313" spans="1:8">
+    <row r="313" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A313" s="1">
         <v>43070</v>
       </c>
@@ -6198,7 +6187,7 @@
       </c>
       <c r="H313" s="3"/>
     </row>
-    <row r="314" spans="1:8">
+    <row r="314" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A314" s="1">
         <v>43101</v>
       </c>
@@ -6216,7 +6205,7 @@
       </c>
       <c r="H314" s="3"/>
     </row>
-    <row r="315" spans="1:8">
+    <row r="315" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A315" s="1">
         <v>43132</v>
       </c>
@@ -6233,7 +6222,7 @@
         <v>484031</v>
       </c>
     </row>
-    <row r="316" spans="1:8">
+    <row r="316" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A316" s="1">
         <v>43160</v>
       </c>
@@ -6250,7 +6239,7 @@
         <v>484110</v>
       </c>
     </row>
-    <row r="317" spans="1:8">
+    <row r="317" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A317" s="1">
         <v>43191</v>
       </c>
@@ -6267,7 +6256,7 @@
         <v>484154</v>
       </c>
     </row>
-    <row r="318" spans="1:8">
+    <row r="318" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A318" s="1">
         <v>43221</v>
       </c>
@@ -6284,7 +6273,7 @@
         <v>491960</v>
       </c>
     </row>
-    <row r="319" spans="1:8">
+    <row r="319" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A319" s="1">
         <v>43252</v>
       </c>
@@ -6301,7 +6290,7 @@
         <v>490228</v>
       </c>
     </row>
-    <row r="320" spans="1:8">
+    <row r="320" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A320" s="1">
         <v>43282</v>
       </c>
@@ -6318,7 +6307,7 @@
         <v>493142</v>
       </c>
     </row>
-    <row r="321" spans="1:5">
+    <row r="321" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A321" s="1">
         <v>43313</v>
       </c>
@@ -6335,7 +6324,7 @@
         <v>493445</v>
       </c>
     </row>
-    <row r="322" spans="1:5">
+    <row r="322" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A322" s="1">
         <v>43344</v>
       </c>
@@ -6352,7 +6341,7 @@
         <v>491507</v>
       </c>
     </row>
-    <row r="323" spans="1:5">
+    <row r="323" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A323" s="1">
         <v>43374</v>
       </c>
@@ -6369,7 +6358,7 @@
         <v>496416</v>
       </c>
     </row>
-    <row r="324" spans="1:5">
+    <row r="324" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A324" s="1">
         <v>43405</v>
       </c>
@@ -6386,7 +6375,7 @@
         <v>498854</v>
       </c>
     </row>
-    <row r="325" spans="1:5">
+    <row r="325" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A325" s="1">
         <v>43435</v>
       </c>
@@ -6403,7 +6392,7 @@
         <v>489113</v>
       </c>
     </row>
-    <row r="326" spans="1:5">
+    <row r="326" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A326" s="1">
         <v>43466</v>
       </c>
@@ -6420,7 +6409,7 @@
         <v>490440</v>
       </c>
     </row>
-    <row r="327" spans="1:5">
+    <row r="327" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A327" s="1">
         <v>43497</v>
       </c>
@@ -6437,7 +6426,7 @@
         <v>491751</v>
       </c>
     </row>
-    <row r="328" spans="1:5">
+    <row r="328" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A328" s="1">
         <v>43525</v>
       </c>
@@ -6454,7 +6443,7 @@
         <v>499292</v>
       </c>
     </row>
-    <row r="329" spans="1:5">
+    <row r="329" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A329" s="1">
         <v>43556</v>
       </c>
@@ -6471,7 +6460,7 @@
         <v>499343</v>
       </c>
     </row>
-    <row r="330" spans="1:5">
+    <row r="330" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A330" s="1">
         <v>43586</v>
       </c>
@@ -6488,7 +6477,7 @@
         <v>504741</v>
       </c>
     </row>
-    <row r="331" spans="1:5">
+    <row r="331" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A331" s="1">
         <v>43617</v>
       </c>
@@ -6505,7 +6494,7 @@
         <v>505251</v>
       </c>
     </row>
-    <row r="332" spans="1:5">
+    <row r="332" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A332" s="1">
         <v>43647</v>
       </c>
@@ -6522,7 +6511,7 @@
         <v>509091</v>
       </c>
     </row>
-    <row r="333" spans="1:5">
+    <row r="333" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A333" s="1">
         <v>43678</v>
       </c>
@@ -6539,7 +6528,7 @@
         <v>512561</v>
       </c>
     </row>
-    <row r="334" spans="1:5">
+    <row r="334" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A334" s="1">
         <v>43709</v>
       </c>
@@ -6556,7 +6545,7 @@
         <v>509282</v>
       </c>
     </row>
-    <row r="335" spans="1:5">
+    <row r="335" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A335" s="1">
         <v>43739</v>
       </c>
@@ -6573,7 +6562,7 @@
         <v>510648</v>
       </c>
     </row>
-    <row r="336" spans="1:5">
+    <row r="336" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A336" s="1">
         <v>43770</v>
       </c>
@@ -6590,7 +6579,7 @@
         <v>514215</v>
       </c>
     </row>
-    <row r="337" spans="1:7">
+    <row r="337" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A337" s="1">
         <v>43800</v>
       </c>
@@ -6607,7 +6596,7 @@
         <v>515866</v>
       </c>
     </row>
-    <row r="338" spans="1:7">
+    <row r="338" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A338" s="1">
         <v>43831</v>
       </c>
@@ -6624,7 +6613,7 @@
         <v>515119</v>
       </c>
     </row>
-    <row r="339" spans="1:7">
+    <row r="339" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A339" s="1">
         <v>43862</v>
       </c>
@@ -6641,7 +6630,7 @@
         <v>515330</v>
       </c>
     </row>
-    <row r="340" spans="1:7">
+    <row r="340" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A340" s="1">
         <v>43891</v>
       </c>
@@ -6658,7 +6647,7 @@
         <v>468324</v>
       </c>
     </row>
-    <row r="341" spans="1:7">
+    <row r="341" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A341" s="1">
         <v>43922</v>
       </c>
@@ -6675,7 +6664,7 @@
         <v>401028</v>
       </c>
     </row>
-    <row r="342" spans="1:7">
+    <row r="342" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A342" s="1">
         <v>43952</v>
       </c>
@@ -6692,7 +6681,7 @@
         <v>478449</v>
       </c>
     </row>
-    <row r="343" spans="1:7">
+    <row r="343" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A343" s="1">
         <v>43983</v>
       </c>
@@ -6709,7 +6698,7 @@
         <v>518038</v>
       </c>
     </row>
-    <row r="344" spans="1:7">
+    <row r="344" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A344" s="1">
         <v>44013</v>
       </c>
@@ -6726,7 +6715,7 @@
         <v>526304</v>
       </c>
     </row>
-    <row r="345" spans="1:7">
+    <row r="345" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A345" s="1">
         <v>44044</v>
       </c>
@@ -6743,7 +6732,7 @@
         <v>530735</v>
       </c>
     </row>
-    <row r="346" spans="1:7">
+    <row r="346" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A346" s="1">
         <v>44075</v>
       </c>
@@ -6760,7 +6749,7 @@
         <v>541302</v>
       </c>
     </row>
-    <row r="347" spans="1:7">
+    <row r="347" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A347" s="1">
         <v>44105</v>
       </c>
@@ -6777,7 +6766,7 @@
         <v>539114</v>
       </c>
     </row>
-    <row r="348" spans="1:7">
+    <row r="348" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A348" s="1">
         <v>44136</v>
       </c>
@@ -6800,7 +6789,7 @@
         <v>5.4899999999999997E-2</v>
       </c>
     </row>
-    <row r="349" spans="1:7">
+    <row r="349" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A349" s="1">
         <v>44166</v>
       </c>
@@ -6823,7 +6812,7 @@
         <v>3.6799999999999999E-2</v>
       </c>
     </row>
-    <row r="350" spans="1:7">
+    <row r="350" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A350" s="1">
         <v>44197</v>
       </c>
@@ -6846,7 +6835,7 @@
         <v>2.53E-2</v>
       </c>
     </row>
-    <row r="351" spans="1:7">
+    <row r="351" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A351" s="1">
         <v>44228</v>
       </c>
@@ -6869,7 +6858,7 @@
         <v>9.5100000000000004E-2</v>
       </c>
     </row>
-    <row r="352" spans="1:7">
+    <row r="352" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A352" s="1">
         <v>44256</v>
       </c>
@@ -6892,7 +6881,7 @@
         <v>6.6600000000000006E-2</v>
       </c>
     </row>
-    <row r="353" spans="1:7">
+    <row r="353" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A353" s="1">
         <v>44287</v>
       </c>
@@ -6915,7 +6904,7 @@
         <v>0.29010000000000002</v>
       </c>
     </row>
-    <row r="354" spans="1:7">
+    <row r="354" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A354" s="1">
         <v>44317</v>
       </c>
@@ -6938,7 +6927,7 @@
         <v>0.53400000000000003</v>
       </c>
     </row>
-    <row r="355" spans="1:7">
+    <row r="355" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A355" s="1">
         <v>44348</v>
       </c>
@@ -6961,7 +6950,7 @@
         <v>0.27600000000000002</v>
       </c>
     </row>
-    <row r="356" spans="1:7">
+    <row r="356" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A356" s="1">
         <v>44378</v>
       </c>
@@ -6984,7 +6973,7 @@
         <v>0.18729999999999999</v>
       </c>
     </row>
-    <row r="357" spans="1:7">
+    <row r="357" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A357" s="1">
         <v>44409</v>
       </c>
@@ -7007,7 +6996,7 @@
         <v>0.15140000000000001</v>
       </c>
     </row>
-    <row r="358" spans="1:7">
+    <row r="358" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A358" s="1">
         <v>44440</v>
       </c>
@@ -7030,7 +7019,7 @@
         <v>0.154</v>
       </c>
     </row>
-    <row r="359" spans="1:7">
+    <row r="359" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A359" s="1">
         <v>44470</v>
       </c>
@@ -7053,7 +7042,7 @@
         <v>0.1426</v>
       </c>
     </row>
-    <row r="360" spans="1:7">
+    <row r="360" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A360" s="1">
         <v>44501</v>
       </c>
@@ -7076,7 +7065,7 @@
         <v>0.16259999999999999</v>
       </c>
     </row>
-    <row r="361" spans="1:7">
+    <row r="361" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A361" s="1">
         <v>44531</v>
       </c>
@@ -7099,7 +7088,7 @@
         <v>0.18240000000000001</v>
       </c>
     </row>
-    <row r="362" spans="1:7">
+    <row r="362" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A362" s="1">
         <v>44562</v>
       </c>
@@ -7122,7 +7111,7 @@
         <v>0.1671</v>
       </c>
     </row>
-    <row r="363" spans="1:7">
+    <row r="363" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A363" s="1">
         <v>44593</v>
       </c>
@@ -7145,7 +7134,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="364" spans="1:7">
+    <row r="364" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A364" s="1">
         <v>44621</v>
       </c>
@@ -7168,7 +7157,7 @@
         <v>0.18179999999999999</v>
       </c>
     </row>
-    <row r="365" spans="1:7">
+    <row r="365" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A365" s="1">
         <v>44652</v>
       </c>
@@ -7191,7 +7180,7 @@
         <v>7.3400000000000007E-2</v>
       </c>
     </row>
-    <row r="366" spans="1:7">
+    <row r="366" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A366" s="1">
         <v>44682</v>
       </c>
@@ -7214,7 +7203,7 @@
         <v>7.8200000000000006E-2</v>
       </c>
     </row>
-    <row r="367" spans="1:7">
+    <row r="367" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A367" s="1">
         <v>44713</v>
       </c>
@@ -7237,7 +7226,7 @@
         <v>8.1799999999999998E-2</v>
       </c>
     </row>
-    <row r="368" spans="1:7">
+    <row r="368" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A368" s="1">
         <v>44743</v>
       </c>
@@ -7260,7 +7249,7 @@
         <v>8.5400000000000004E-2</v>
       </c>
     </row>
-    <row r="369" spans="1:7">
+    <row r="369" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A369" s="1">
         <v>44774</v>
       </c>
@@ -7283,7 +7272,7 @@
         <v>0.10059999999999999</v>
       </c>
     </row>
-    <row r="370" spans="1:7">
+    <row r="370" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A370" s="1">
         <v>44805</v>
       </c>
@@ -7306,7 +7295,7 @@
         <v>9.4399999999999998E-2</v>
       </c>
     </row>
-    <row r="371" spans="1:7">
+    <row r="371" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A371" s="1">
         <v>44835</v>
       </c>
@@ -7329,7 +7318,7 @@
         <v>8.5900000000000004E-2</v>
       </c>
     </row>
-    <row r="372" spans="1:7">
+    <row r="372" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A372" s="1">
         <v>44866</v>
       </c>
@@ -7352,7 +7341,7 @@
         <v>7.51E-2</v>
       </c>
     </row>
-    <row r="373" spans="1:7">
+    <row r="373" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A373" s="1">
         <v>44896</v>
       </c>
@@ -7375,7 +7364,7 @@
         <v>6.0100000000000001E-2</v>
       </c>
     </row>
-    <row r="374" spans="1:7">
+    <row r="374" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A374" s="1">
         <v>44927</v>
       </c>
@@ -7398,7 +7387,7 @@
         <v>5.8900000000000001E-2</v>
       </c>
     </row>
-    <row r="375" spans="1:7">
+    <row r="375" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A375" s="1">
         <v>44958</v>
       </c>
@@ -7421,7 +7410,7 @@
         <v>7.6799999999999993E-2</v>
       </c>
     </row>
-    <row r="376" spans="1:7">
+    <row r="376" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A376" s="1">
         <v>44986</v>
       </c>
@@ -7444,7 +7433,7 @@
         <v>5.8799999999999998E-2</v>
       </c>
     </row>
-    <row r="377" spans="1:7">
+    <row r="377" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A377" s="1">
         <v>45017</v>
       </c>
@@ -7467,7 +7456,7 @@
         <v>2.4199999999999999E-2</v>
       </c>
     </row>
-    <row r="378" spans="1:7">
+    <row r="378" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A378" s="1">
         <v>45047</v>
       </c>
@@ -7490,7 +7479,7 @@
         <v>1.23E-2</v>
       </c>
     </row>
-    <row r="379" spans="1:7">
+    <row r="379" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A379" s="1">
         <v>45078</v>
       </c>
@@ -7513,7 +7502,7 @@
         <v>1.9599999999999999E-2</v>
       </c>
     </row>
-    <row r="380" spans="1:7">
+    <row r="380" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A380" s="1">
         <v>45108</v>
       </c>
@@ -7536,7 +7525,7 @@
         <v>1.5900000000000001E-2</v>
       </c>
     </row>
-    <row r="381" spans="1:7">
+    <row r="381" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A381" s="1">
         <v>45139</v>
       </c>
@@ -7559,7 +7548,7 @@
         <v>2.64E-2</v>
       </c>
     </row>
-    <row r="382" spans="1:7">
+    <row r="382" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A382" s="1">
         <v>45170</v>
       </c>
@@ -7582,7 +7571,7 @@
         <v>2.8899999999999999E-2</v>
       </c>
     </row>
-    <row r="383" spans="1:7">
+    <row r="383" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A383" s="1">
         <v>45200</v>
       </c>
@@ -7605,7 +7594,7 @@
         <v>4.0500000000000001E-2</v>
       </c>
     </row>
-    <row r="384" spans="1:7">
+    <row r="384" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A384" s="1">
         <v>45231</v>
       </c>
@@ -7628,7 +7617,7 @@
         <v>2.24E-2</v>
       </c>
     </row>
-    <row r="385" spans="1:7">
+    <row r="385" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A385" s="1">
         <v>45261</v>
       </c>
@@ -7651,7 +7640,7 @@
         <v>3.9699999999999999E-2</v>
       </c>
     </row>
-    <row r="386" spans="1:7">
+    <row r="386" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A386" s="1">
         <v>45292</v>
       </c>
@@ -7674,7 +7663,7 @@
         <v>5.3100000000000001E-2</v>
       </c>
     </row>
-    <row r="387" spans="1:7">
+    <row r="387" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A387" s="1">
         <v>45323</v>
       </c>
@@ -7697,7 +7686,7 @@
         <v>4.0000000000000002E-4</v>
       </c>
     </row>
-    <row r="388" spans="1:7">
+    <row r="388" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A388" s="1">
         <v>45352</v>
       </c>
@@ -7720,7 +7709,7 @@
         <v>2.1100000000000001E-2</v>
       </c>
     </row>
-    <row r="389" spans="1:7">
+    <row r="389" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A389" s="1">
         <v>45383</v>
       </c>
@@ -7743,7 +7732,7 @@
         <v>3.8300000000000001E-2</v>
       </c>
     </row>
-    <row r="390" spans="1:7">
+    <row r="390" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A390" s="1">
         <v>45413</v>
       </c>
@@ -7766,7 +7755,7 @@
         <v>2.7400000000000001E-2</v>
       </c>
     </row>
-    <row r="391" spans="1:7">
+    <row r="391" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A391" s="1">
         <v>45444</v>
       </c>
@@ -7789,7 +7778,7 @@
         <v>2.5899999999999999E-2</v>
       </c>
     </row>
-    <row r="392" spans="1:7">
+    <row r="392" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A392" s="1">
         <v>45474</v>
       </c>
@@ -7812,7 +7801,7 @@
         <v>2.0400000000000001E-2</v>
       </c>
     </row>
-    <row r="393" spans="1:7">
+    <row r="393" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A393" s="1">
         <v>45505</v>
       </c>
@@ -7835,7 +7824,7 @@
         <v>2.86E-2</v>
       </c>
     </row>
-    <row r="394" spans="1:7">
+    <row r="394" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A394" s="1">
         <v>45536</v>
       </c>
@@ -7858,7 +7847,7 @@
         <v>2.1600000000000001E-2</v>
       </c>
     </row>
-    <row r="395" spans="1:7">
+    <row r="395" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A395" s="1">
         <v>45566</v>
       </c>
@@ -7881,7 +7870,7 @@
         <v>1.9800000000000002E-2</v>
       </c>
     </row>
-    <row r="396" spans="1:7">
+    <row r="396" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A396" s="1">
         <v>45597</v>
       </c>
@@ -7904,7 +7893,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="397" spans="1:7">
+    <row r="397" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A397" s="1">
         <v>45627</v>
       </c>
@@ -7927,7 +7916,7 @@
         <v>4.1200000000000001E-2</v>
       </c>
     </row>
-    <row r="398" spans="1:7">
+    <row r="398" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A398" s="1">
         <v>45658</v>
       </c>
@@ -7950,7 +7939,7 @@
         <v>4.36E-2</v>
       </c>
     </row>
-    <row r="399" spans="1:7">
+    <row r="399" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A399" s="1">
         <v>45689</v>
       </c>
@@ -7973,7 +7962,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="400" spans="1:7">
+    <row r="400" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A400" s="1">
         <v>45717</v>
       </c>
@@ -7996,7 +7985,7 @@
         <v>3.5400000000000001E-2</v>
       </c>
     </row>
-    <row r="401" spans="1:7">
+    <row r="401" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A401" s="1">
         <v>45748</v>
       </c>
@@ -8019,7 +8008,7 @@
         <v>5.2499999999999998E-2</v>
       </c>
     </row>
-    <row r="402" spans="1:7">
+    <row r="402" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A402" s="1">
         <v>45778</v>
       </c>
@@ -8042,7 +8031,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="403" spans="1:7">
+    <row r="403" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A403" s="1">
         <v>45809</v>
       </c>
@@ -8065,7 +8054,7 @@
         <v>3.2899999999999999E-2</v>
       </c>
     </row>
-    <row r="404" spans="1:7">
+    <row r="404" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A404" s="1">
         <v>45839</v>
       </c>
@@ -8088,7 +8077,7 @@
         <v>4.3499999999999997E-2</v>
       </c>
     </row>
-    <row r="405" spans="1:7">
+    <row r="405" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A405" s="1">
         <v>45870</v>
       </c>
@@ -8111,7 +8100,7 @@
         <v>4.0899999999999999E-2</v>
       </c>
     </row>
-    <row r="406" spans="1:7">
+    <row r="406" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A406" s="1">
         <v>45901</v>
       </c>
@@ -8134,7 +8123,7 @@
         <v>5.0200000000000002E-2</v>
       </c>
     </row>
-    <row r="407" spans="1:7">
+    <row r="407" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A407" s="1">
         <v>45931</v>
       </c>
@@ -8155,20 +8144,38 @@
       </c>
       <c r="G407" s="5">
         <v>4.1799999999999997E-2</v>
+      </c>
+    </row>
+    <row r="408" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A408" s="1">
+        <v>45962</v>
+      </c>
+      <c r="B408" s="4">
+        <v>46036</v>
+      </c>
+      <c r="C408" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D408" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G408" s="5">
+        <v>3.4700000000000002E-2</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D57F73F-5FFC-47C2-9B16-318BC0BDC7A6}">
   <dimension ref="B2:C3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="2:3">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" s="8" t="s">
         <v>5</v>
       </c>
@@ -8176,7 +8183,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="2:3">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C3" s="7" t="s">
         <v>7</v>
       </c>

--- a/data/macro/USA/Retail Sales.xlsx
+++ b/data/macro/USA/Retail Sales.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\macro\USA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4256254-57F8-47B7-87AB-6522226514BC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64EFA29B-39C0-4CA2-9518-78792984D266}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11475" yWindow="780" windowWidth="18000" windowHeight="20685" xr2:uid="{30656A32-0D37-469D-885D-F50C8A2BA9DC}"/>
   </bookViews>
@@ -77,9 +77,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="176" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="177" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -93,13 +93,6 @@
       <sz val="8"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
       <charset val="129"/>
     </font>
     <font>
@@ -126,18 +119,23 @@
       <charset val="129"/>
     </font>
     <font>
+      <b/>
       <sz val="10"/>
-      <color rgb="FF333333"/>
-      <name val="Arial"/>
+      <color theme="1"/>
+      <name val="Verdana"/>
       <family val="2"/>
     </font>
     <font>
-      <b/>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Verdana"/>
       <family val="2"/>
-      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF333333"/>
+      <name val="Verdana"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -161,13 +159,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -175,46 +173,46 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="10" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -535,47 +533,46 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A423BD41-4AF5-471C-B1B1-976B1BB48C33}">
   <dimension ref="A1:H408"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.140625" style="9" customWidth="1"/>
-    <col min="5" max="5" width="9.42578125" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.140625" style="5" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" style="5"/>
-    <col min="8" max="8" width="10.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="13.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="13" style="14" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.85546875" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11" style="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
+      <c r="A2" s="8">
         <v>33604</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="9">
         <v>33635</v>
       </c>
       <c r="C2" s="10">
@@ -584,16 +581,16 @@
       <c r="D2" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="11">
         <v>159177</v>
       </c>
-      <c r="H2" s="3"/>
+      <c r="H2" s="13"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
+      <c r="A3" s="8">
         <v>33635</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="9">
         <v>33664</v>
       </c>
       <c r="C3" s="10">
@@ -602,16 +599,16 @@
       <c r="D3" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="11">
         <v>159189</v>
       </c>
-      <c r="H3" s="3"/>
+      <c r="H3" s="13"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
+      <c r="A4" s="8">
         <v>33664</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="9">
         <v>33695</v>
       </c>
       <c r="C4" s="10">
@@ -620,16 +617,16 @@
       <c r="D4" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="11">
         <v>158647</v>
       </c>
-      <c r="H4" s="3"/>
+      <c r="H4" s="13"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
+      <c r="A5" s="8">
         <v>33695</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="9">
         <v>33725</v>
       </c>
       <c r="C5" s="10">
@@ -638,16 +635,16 @@
       <c r="D5" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="11">
         <v>159921</v>
       </c>
-      <c r="H5" s="3"/>
+      <c r="H5" s="13"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
+      <c r="A6" s="8">
         <v>33725</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="9">
         <v>33756</v>
       </c>
       <c r="C6" s="10">
@@ -656,16 +653,16 @@
       <c r="D6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="11">
         <v>160471</v>
       </c>
-      <c r="H6" s="3"/>
+      <c r="H6" s="13"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
+      <c r="A7" s="8">
         <v>33756</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="9">
         <v>33786</v>
       </c>
       <c r="C7" s="10">
@@ -674,16 +671,16 @@
       <c r="D7" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="11">
         <v>161205</v>
       </c>
-      <c r="H7" s="3"/>
+      <c r="H7" s="13"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
+      <c r="A8" s="8">
         <v>33786</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="9">
         <v>33817</v>
       </c>
       <c r="C8" s="10">
@@ -692,16 +689,16 @@
       <c r="D8" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="11">
         <v>162855</v>
       </c>
-      <c r="H8" s="3"/>
+      <c r="H8" s="13"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
+      <c r="A9" s="8">
         <v>33817</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="9">
         <v>33848</v>
       </c>
       <c r="C9" s="10">
@@ -710,16 +707,16 @@
       <c r="D9" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="11">
         <v>162412</v>
       </c>
-      <c r="H9" s="3"/>
+      <c r="H9" s="13"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
+      <c r="A10" s="8">
         <v>33848</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="9">
         <v>33878</v>
       </c>
       <c r="C10" s="10">
@@ -728,16 +725,16 @@
       <c r="D10" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="11">
         <v>164361</v>
       </c>
-      <c r="H10" s="3"/>
+      <c r="H10" s="13"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
+      <c r="A11" s="8">
         <v>33878</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B11" s="9">
         <v>33909</v>
       </c>
       <c r="C11" s="10">
@@ -746,16 +743,16 @@
       <c r="D11" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="11">
         <v>166063</v>
       </c>
-      <c r="H11" s="3"/>
+      <c r="H11" s="13"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
+      <c r="A12" s="8">
         <v>33909</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12" s="9">
         <v>33939</v>
       </c>
       <c r="C12" s="10">
@@ -764,16 +761,16 @@
       <c r="D12" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="11">
         <v>166124</v>
       </c>
-      <c r="H12" s="3"/>
+      <c r="H12" s="13"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
+      <c r="A13" s="8">
         <v>33939</v>
       </c>
-      <c r="B13" s="4">
+      <c r="B13" s="9">
         <v>33970</v>
       </c>
       <c r="C13" s="10">
@@ -782,16 +779,16 @@
       <c r="D13" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="11">
         <v>167691</v>
       </c>
-      <c r="H13" s="3"/>
+      <c r="H13" s="13"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
+      <c r="A14" s="8">
         <v>33970</v>
       </c>
-      <c r="B14" s="4">
+      <c r="B14" s="9">
         <v>34001</v>
       </c>
       <c r="C14" s="10">
@@ -800,16 +797,16 @@
       <c r="D14" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="11">
         <v>169500</v>
       </c>
-      <c r="H14" s="3"/>
+      <c r="H14" s="13"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
+      <c r="A15" s="8">
         <v>34001</v>
       </c>
-      <c r="B15" s="4">
+      <c r="B15" s="9">
         <v>34029</v>
       </c>
       <c r="C15" s="10">
@@ -818,16 +815,16 @@
       <c r="D15" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E15" s="11">
         <v>168840</v>
       </c>
-      <c r="H15" s="3"/>
+      <c r="H15" s="13"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
+      <c r="A16" s="8">
         <v>34029</v>
       </c>
-      <c r="B16" s="4">
+      <c r="B16" s="9">
         <v>34060</v>
       </c>
       <c r="C16" s="10">
@@ -836,16 +833,16 @@
       <c r="D16" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E16" s="6">
+      <c r="E16" s="11">
         <v>167682</v>
       </c>
-      <c r="H16" s="3"/>
+      <c r="H16" s="13"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
+      <c r="A17" s="8">
         <v>34060</v>
       </c>
-      <c r="B17" s="4">
+      <c r="B17" s="9">
         <v>34090</v>
       </c>
       <c r="C17" s="10">
@@ -854,16 +851,16 @@
       <c r="D17" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E17" s="6">
+      <c r="E17" s="11">
         <v>172102</v>
       </c>
-      <c r="H17" s="3"/>
+      <c r="H17" s="13"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
+      <c r="A18" s="8">
         <v>34090</v>
       </c>
-      <c r="B18" s="4">
+      <c r="B18" s="9">
         <v>34121</v>
       </c>
       <c r="C18" s="10">
@@ -872,16 +869,16 @@
       <c r="D18" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E18" s="6">
+      <c r="E18" s="11">
         <v>172960</v>
       </c>
-      <c r="H18" s="3"/>
+      <c r="H18" s="13"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
+      <c r="A19" s="8">
         <v>34121</v>
       </c>
-      <c r="B19" s="4">
+      <c r="B19" s="9">
         <v>34151</v>
       </c>
       <c r="C19" s="10">
@@ -890,16 +887,16 @@
       <c r="D19" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E19" s="6">
+      <c r="E19" s="11">
         <v>173018</v>
       </c>
-      <c r="H19" s="3"/>
+      <c r="H19" s="13"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
+      <c r="A20" s="8">
         <v>34151</v>
       </c>
-      <c r="B20" s="4">
+      <c r="B20" s="9">
         <v>34182</v>
       </c>
       <c r="C20" s="10">
@@ -908,16 +905,16 @@
       <c r="D20" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E20" s="6">
+      <c r="E20" s="11">
         <v>175822</v>
       </c>
-      <c r="H20" s="3"/>
+      <c r="H20" s="13"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
+      <c r="A21" s="8">
         <v>34182</v>
       </c>
-      <c r="B21" s="4">
+      <c r="B21" s="9">
         <v>34213</v>
       </c>
       <c r="C21" s="10">
@@ -926,16 +923,16 @@
       <c r="D21" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E21" s="6">
+      <c r="E21" s="11">
         <v>175233</v>
       </c>
-      <c r="H21" s="3"/>
+      <c r="H21" s="13"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
+      <c r="A22" s="8">
         <v>34213</v>
       </c>
-      <c r="B22" s="4">
+      <c r="B22" s="9">
         <v>34243</v>
       </c>
       <c r="C22" s="10">
@@ -944,16 +941,16 @@
       <c r="D22" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E22" s="6">
+      <c r="E22" s="11">
         <v>176608</v>
       </c>
-      <c r="H22" s="3"/>
+      <c r="H22" s="13"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
+      <c r="A23" s="8">
         <v>34243</v>
       </c>
-      <c r="B23" s="4">
+      <c r="B23" s="9">
         <v>34274</v>
       </c>
       <c r="C23" s="10">
@@ -962,16 +959,16 @@
       <c r="D23" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E23" s="6">
+      <c r="E23" s="11">
         <v>177588</v>
       </c>
-      <c r="H23" s="3"/>
+      <c r="H23" s="13"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
+      <c r="A24" s="8">
         <v>34274</v>
       </c>
-      <c r="B24" s="4">
+      <c r="B24" s="9">
         <v>34304</v>
       </c>
       <c r="C24" s="10">
@@ -980,16 +977,16 @@
       <c r="D24" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E24" s="6">
+      <c r="E24" s="11">
         <v>179758</v>
       </c>
-      <c r="H24" s="3"/>
+      <c r="H24" s="13"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
+      <c r="A25" s="8">
         <v>34304</v>
       </c>
-      <c r="B25" s="4">
+      <c r="B25" s="9">
         <v>34335</v>
       </c>
       <c r="C25" s="10">
@@ -998,16 +995,16 @@
       <c r="D25" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E25" s="6">
+      <c r="E25" s="11">
         <v>181077</v>
       </c>
-      <c r="H25" s="3"/>
+      <c r="H25" s="13"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="1">
+      <c r="A26" s="8">
         <v>34335</v>
       </c>
-      <c r="B26" s="4">
+      <c r="B26" s="9">
         <v>34366</v>
       </c>
       <c r="C26" s="10">
@@ -1016,16 +1013,16 @@
       <c r="D26" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E26" s="6">
+      <c r="E26" s="11">
         <v>179615</v>
       </c>
-      <c r="H26" s="3"/>
+      <c r="H26" s="13"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="1">
+      <c r="A27" s="8">
         <v>34366</v>
       </c>
-      <c r="B27" s="4">
+      <c r="B27" s="9">
         <v>34394</v>
       </c>
       <c r="C27" s="10">
@@ -1034,16 +1031,16 @@
       <c r="D27" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E27" s="6">
+      <c r="E27" s="11">
         <v>183101</v>
       </c>
-      <c r="H27" s="3"/>
+      <c r="H27" s="13"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="1">
+      <c r="A28" s="8">
         <v>34394</v>
       </c>
-      <c r="B28" s="4">
+      <c r="B28" s="9">
         <v>34425</v>
       </c>
       <c r="C28" s="10">
@@ -1052,16 +1049,16 @@
       <c r="D28" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E28" s="6">
+      <c r="E28" s="11">
         <v>186721</v>
       </c>
-      <c r="H28" s="3"/>
+      <c r="H28" s="13"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="1">
+      <c r="A29" s="8">
         <v>34425</v>
       </c>
-      <c r="B29" s="4">
+      <c r="B29" s="9">
         <v>34455</v>
       </c>
       <c r="C29" s="10">
@@ -1070,16 +1067,16 @@
       <c r="D29" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E29" s="6">
+      <c r="E29" s="11">
         <v>186423</v>
       </c>
-      <c r="H29" s="3"/>
+      <c r="H29" s="13"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="1">
+      <c r="A30" s="8">
         <v>34455</v>
       </c>
-      <c r="B30" s="4">
+      <c r="B30" s="9">
         <v>34486</v>
       </c>
       <c r="C30" s="10">
@@ -1088,16 +1085,16 @@
       <c r="D30" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E30" s="6">
+      <c r="E30" s="11">
         <v>185616</v>
       </c>
-      <c r="H30" s="3"/>
+      <c r="H30" s="13"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="1">
+      <c r="A31" s="8">
         <v>34486</v>
       </c>
-      <c r="B31" s="4">
+      <c r="B31" s="9">
         <v>34516</v>
       </c>
       <c r="C31" s="10">
@@ -1106,16 +1103,16 @@
       <c r="D31" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E31" s="6">
+      <c r="E31" s="11">
         <v>187800</v>
       </c>
-      <c r="H31" s="3"/>
+      <c r="H31" s="13"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="1">
+      <c r="A32" s="8">
         <v>34516</v>
       </c>
-      <c r="B32" s="4">
+      <c r="B32" s="9">
         <v>34547</v>
       </c>
       <c r="C32" s="10">
@@ -1124,16 +1121,16 @@
       <c r="D32" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E32" s="6">
+      <c r="E32" s="11">
         <v>188062</v>
       </c>
-      <c r="H32" s="3"/>
+      <c r="H32" s="13"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="1">
+      <c r="A33" s="8">
         <v>34547</v>
       </c>
-      <c r="B33" s="4">
+      <c r="B33" s="9">
         <v>34578</v>
       </c>
       <c r="C33" s="10">
@@ -1142,16 +1139,16 @@
       <c r="D33" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E33" s="6">
+      <c r="E33" s="11">
         <v>190771</v>
       </c>
-      <c r="H33" s="3"/>
+      <c r="H33" s="13"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="1">
+      <c r="A34" s="8">
         <v>34578</v>
       </c>
-      <c r="B34" s="4">
+      <c r="B34" s="9">
         <v>34608</v>
       </c>
       <c r="C34" s="10">
@@ -1160,16 +1157,16 @@
       <c r="D34" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E34" s="6">
+      <c r="E34" s="11">
         <v>192585</v>
       </c>
-      <c r="H34" s="3"/>
+      <c r="H34" s="13"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="1">
+      <c r="A35" s="8">
         <v>34608</v>
       </c>
-      <c r="B35" s="4">
+      <c r="B35" s="9">
         <v>34639</v>
       </c>
       <c r="C35" s="10">
@@ -1178,16 +1175,16 @@
       <c r="D35" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E35" s="6">
+      <c r="E35" s="11">
         <v>193914</v>
       </c>
-      <c r="H35" s="3"/>
+      <c r="H35" s="13"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="1">
+      <c r="A36" s="8">
         <v>34639</v>
       </c>
-      <c r="B36" s="4">
+      <c r="B36" s="9">
         <v>34669</v>
       </c>
       <c r="C36" s="10">
@@ -1196,16 +1193,16 @@
       <c r="D36" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E36" s="6">
+      <c r="E36" s="11">
         <v>194425</v>
       </c>
-      <c r="H36" s="3"/>
+      <c r="H36" s="13"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="1">
+      <c r="A37" s="8">
         <v>34669</v>
       </c>
-      <c r="B37" s="4">
+      <c r="B37" s="9">
         <v>34700</v>
       </c>
       <c r="C37" s="10">
@@ -1214,16 +1211,16 @@
       <c r="D37" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E37" s="6">
+      <c r="E37" s="11">
         <v>194939</v>
       </c>
-      <c r="H37" s="3"/>
+      <c r="H37" s="13"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="1">
+      <c r="A38" s="8">
         <v>34700</v>
       </c>
-      <c r="B38" s="4">
+      <c r="B38" s="9">
         <v>34731</v>
       </c>
       <c r="C38" s="10">
@@ -1232,16 +1229,16 @@
       <c r="D38" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E38" s="6">
+      <c r="E38" s="11">
         <v>195908</v>
       </c>
-      <c r="H38" s="3"/>
+      <c r="H38" s="13"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="1">
+      <c r="A39" s="8">
         <v>34731</v>
       </c>
-      <c r="B39" s="4">
+      <c r="B39" s="9">
         <v>34759</v>
       </c>
       <c r="C39" s="10">
@@ -1250,16 +1247,16 @@
       <c r="D39" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E39" s="6">
+      <c r="E39" s="11">
         <v>193068</v>
       </c>
-      <c r="H39" s="3"/>
+      <c r="H39" s="13"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="1">
+      <c r="A40" s="8">
         <v>34759</v>
       </c>
-      <c r="B40" s="4">
+      <c r="B40" s="9">
         <v>34790</v>
       </c>
       <c r="C40" s="10">
@@ -1268,16 +1265,16 @@
       <c r="D40" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E40" s="6">
+      <c r="E40" s="11">
         <v>195179</v>
       </c>
-      <c r="H40" s="3"/>
+      <c r="H40" s="13"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="1">
+      <c r="A41" s="8">
         <v>34790</v>
       </c>
-      <c r="B41" s="4">
+      <c r="B41" s="9">
         <v>34820</v>
       </c>
       <c r="C41" s="10">
@@ -1286,16 +1283,16 @@
       <c r="D41" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E41" s="6">
+      <c r="E41" s="11">
         <v>195310</v>
       </c>
-      <c r="H41" s="3"/>
+      <c r="H41" s="13"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="1">
+      <c r="A42" s="8">
         <v>34820</v>
       </c>
-      <c r="B42" s="4">
+      <c r="B42" s="9">
         <v>34851</v>
       </c>
       <c r="C42" s="10">
@@ -1304,16 +1301,16 @@
       <c r="D42" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E42" s="6">
+      <c r="E42" s="11">
         <v>198060</v>
       </c>
-      <c r="H42" s="3"/>
+      <c r="H42" s="13"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="1">
+      <c r="A43" s="8">
         <v>34851</v>
       </c>
-      <c r="B43" s="4">
+      <c r="B43" s="9">
         <v>34881</v>
       </c>
       <c r="C43" s="10">
@@ -1322,16 +1319,16 @@
       <c r="D43" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E43" s="6">
+      <c r="E43" s="11">
         <v>200383</v>
       </c>
-      <c r="H43" s="3"/>
+      <c r="H43" s="13"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="1">
+      <c r="A44" s="8">
         <v>34881</v>
       </c>
-      <c r="B44" s="4">
+      <c r="B44" s="9">
         <v>34912</v>
       </c>
       <c r="C44" s="10">
@@ -1340,16 +1337,16 @@
       <c r="D44" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E44" s="6">
+      <c r="E44" s="11">
         <v>199110</v>
       </c>
-      <c r="H44" s="3"/>
+      <c r="H44" s="13"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="1">
+      <c r="A45" s="8">
         <v>34912</v>
       </c>
-      <c r="B45" s="4">
+      <c r="B45" s="9">
         <v>34943</v>
       </c>
       <c r="C45" s="10">
@@ -1358,16 +1355,16 @@
       <c r="D45" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E45" s="6">
+      <c r="E45" s="11">
         <v>201078</v>
       </c>
-      <c r="H45" s="3"/>
+      <c r="H45" s="13"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="1">
+      <c r="A46" s="8">
         <v>34943</v>
       </c>
-      <c r="B46" s="4">
+      <c r="B46" s="9">
         <v>34973</v>
       </c>
       <c r="C46" s="10">
@@ -1376,16 +1373,16 @@
       <c r="D46" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E46" s="6">
+      <c r="E46" s="11">
         <v>201337</v>
       </c>
-      <c r="H46" s="3"/>
+      <c r="H46" s="13"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="1">
+      <c r="A47" s="8">
         <v>34973</v>
       </c>
-      <c r="B47" s="4">
+      <c r="B47" s="9">
         <v>35004</v>
       </c>
       <c r="C47" s="10">
@@ -1394,16 +1391,16 @@
       <c r="D47" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E47" s="6">
+      <c r="E47" s="11">
         <v>200597</v>
       </c>
-      <c r="H47" s="3"/>
+      <c r="H47" s="13"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="1">
+      <c r="A48" s="8">
         <v>35004</v>
       </c>
-      <c r="B48" s="4">
+      <c r="B48" s="9">
         <v>35034</v>
       </c>
       <c r="C48" s="10">
@@ -1412,16 +1409,16 @@
       <c r="D48" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E48" s="6">
+      <c r="E48" s="11">
         <v>203545</v>
       </c>
-      <c r="H48" s="3"/>
+      <c r="H48" s="13"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="1">
+      <c r="A49" s="8">
         <v>35034</v>
       </c>
-      <c r="B49" s="4">
+      <c r="B49" s="9">
         <v>35065</v>
       </c>
       <c r="C49" s="10">
@@ -1430,16 +1427,16 @@
       <c r="D49" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E49" s="6">
+      <c r="E49" s="11">
         <v>204032</v>
       </c>
-      <c r="H49" s="3"/>
+      <c r="H49" s="13"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="1">
+      <c r="A50" s="8">
         <v>35065</v>
       </c>
-      <c r="B50" s="4">
+      <c r="B50" s="9">
         <v>35096</v>
       </c>
       <c r="C50" s="10">
@@ -1448,16 +1445,16 @@
       <c r="D50" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E50" s="6">
+      <c r="E50" s="11">
         <v>203793</v>
       </c>
-      <c r="H50" s="3"/>
+      <c r="H50" s="13"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="1">
+      <c r="A51" s="8">
         <v>35096</v>
       </c>
-      <c r="B51" s="4">
+      <c r="B51" s="9">
         <v>35125</v>
       </c>
       <c r="C51" s="10">
@@ -1466,16 +1463,16 @@
       <c r="D51" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E51" s="6">
+      <c r="E51" s="11">
         <v>206875</v>
       </c>
-      <c r="H51" s="3"/>
+      <c r="H51" s="13"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="1">
+      <c r="A52" s="8">
         <v>35125</v>
       </c>
-      <c r="B52" s="4">
+      <c r="B52" s="9">
         <v>35156</v>
       </c>
       <c r="C52" s="10">
@@ -1484,16 +1481,16 @@
       <c r="D52" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E52" s="6">
+      <c r="E52" s="11">
         <v>207650</v>
       </c>
-      <c r="H52" s="3"/>
+      <c r="H52" s="13"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="1">
+      <c r="A53" s="8">
         <v>35156</v>
       </c>
-      <c r="B53" s="4">
+      <c r="B53" s="9">
         <v>35186</v>
       </c>
       <c r="C53" s="10">
@@ -1502,16 +1499,16 @@
       <c r="D53" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E53" s="6">
+      <c r="E53" s="11">
         <v>209294</v>
       </c>
-      <c r="H53" s="3"/>
+      <c r="H53" s="13"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="1">
+      <c r="A54" s="8">
         <v>35186</v>
       </c>
-      <c r="B54" s="4">
+      <c r="B54" s="9">
         <v>35217</v>
       </c>
       <c r="C54" s="10">
@@ -1520,16 +1517,16 @@
       <c r="D54" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E54" s="6">
+      <c r="E54" s="11">
         <v>211157</v>
       </c>
-      <c r="H54" s="3"/>
+      <c r="H54" s="13"/>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="1">
+      <c r="A55" s="8">
         <v>35217</v>
       </c>
-      <c r="B55" s="4">
+      <c r="B55" s="9">
         <v>35247</v>
       </c>
       <c r="C55" s="10">
@@ -1538,16 +1535,16 @@
       <c r="D55" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E55" s="6">
+      <c r="E55" s="11">
         <v>209474</v>
       </c>
-      <c r="H55" s="3"/>
+      <c r="H55" s="13"/>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="1">
+      <c r="A56" s="8">
         <v>35247</v>
       </c>
-      <c r="B56" s="4">
+      <c r="B56" s="9">
         <v>35278</v>
       </c>
       <c r="C56" s="10">
@@ -1556,16 +1553,16 @@
       <c r="D56" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E56" s="6">
+      <c r="E56" s="11">
         <v>210827</v>
       </c>
-      <c r="H56" s="3"/>
+      <c r="H56" s="13"/>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="1">
+      <c r="A57" s="8">
         <v>35278</v>
       </c>
-      <c r="B57" s="4">
+      <c r="B57" s="9">
         <v>35309</v>
       </c>
       <c r="C57" s="10">
@@ -1574,16 +1571,16 @@
       <c r="D57" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E57" s="6">
+      <c r="E57" s="11">
         <v>210846</v>
       </c>
-      <c r="H57" s="3"/>
+      <c r="H57" s="13"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="1">
+      <c r="A58" s="8">
         <v>35309</v>
       </c>
-      <c r="B58" s="4">
+      <c r="B58" s="9">
         <v>35339</v>
       </c>
       <c r="C58" s="10">
@@ -1592,16 +1589,16 @@
       <c r="D58" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E58" s="6">
+      <c r="E58" s="11">
         <v>213233</v>
       </c>
-      <c r="H58" s="3"/>
+      <c r="H58" s="13"/>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="1">
+      <c r="A59" s="8">
         <v>35339</v>
       </c>
-      <c r="B59" s="4">
+      <c r="B59" s="9">
         <v>35370</v>
       </c>
       <c r="C59" s="10">
@@ -1610,16 +1607,16 @@
       <c r="D59" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E59" s="6">
+      <c r="E59" s="11">
         <v>215526</v>
       </c>
-      <c r="H59" s="3"/>
+      <c r="H59" s="13"/>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="1">
+      <c r="A60" s="8">
         <v>35370</v>
       </c>
-      <c r="B60" s="4">
+      <c r="B60" s="9">
         <v>35400</v>
       </c>
       <c r="C60" s="10">
@@ -1628,16 +1625,16 @@
       <c r="D60" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E60" s="6">
+      <c r="E60" s="11">
         <v>215167</v>
       </c>
-      <c r="H60" s="3"/>
+      <c r="H60" s="13"/>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="1">
+      <c r="A61" s="8">
         <v>35400</v>
       </c>
-      <c r="B61" s="4">
+      <c r="B61" s="9">
         <v>35431</v>
       </c>
       <c r="C61" s="10">
@@ -1646,16 +1643,16 @@
       <c r="D61" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E61" s="6">
+      <c r="E61" s="11">
         <v>215690</v>
       </c>
-      <c r="H61" s="3"/>
+      <c r="H61" s="13"/>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="1">
+      <c r="A62" s="8">
         <v>35431</v>
       </c>
-      <c r="B62" s="4">
+      <c r="B62" s="9">
         <v>35462</v>
       </c>
       <c r="C62" s="10">
@@ -1664,16 +1661,16 @@
       <c r="D62" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E62" s="6">
+      <c r="E62" s="11">
         <v>218124</v>
       </c>
-      <c r="H62" s="3"/>
+      <c r="H62" s="13"/>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="1">
+      <c r="A63" s="8">
         <v>35462</v>
       </c>
-      <c r="B63" s="4">
+      <c r="B63" s="9">
         <v>35490</v>
       </c>
       <c r="C63" s="10">
@@ -1682,16 +1679,16 @@
       <c r="D63" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E63" s="6">
+      <c r="E63" s="11">
         <v>219587</v>
       </c>
-      <c r="H63" s="3"/>
+      <c r="H63" s="13"/>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="1">
+      <c r="A64" s="8">
         <v>35490</v>
       </c>
-      <c r="B64" s="4">
+      <c r="B64" s="9">
         <v>35521</v>
       </c>
       <c r="C64" s="10">
@@ -1700,16 +1697,16 @@
       <c r="D64" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E64" s="6">
+      <c r="E64" s="11">
         <v>221189</v>
       </c>
-      <c r="H64" s="3"/>
+      <c r="H64" s="13"/>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="1">
+      <c r="A65" s="8">
         <v>35521</v>
       </c>
-      <c r="B65" s="4">
+      <c r="B65" s="9">
         <v>35551</v>
       </c>
       <c r="C65" s="10">
@@ -1718,16 +1715,16 @@
       <c r="D65" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E65" s="6">
+      <c r="E65" s="11">
         <v>217925</v>
       </c>
-      <c r="H65" s="3"/>
+      <c r="H65" s="13"/>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="1">
+      <c r="A66" s="8">
         <v>35551</v>
       </c>
-      <c r="B66" s="4">
+      <c r="B66" s="9">
         <v>35582</v>
       </c>
       <c r="C66" s="10">
@@ -1736,16 +1733,16 @@
       <c r="D66" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E66" s="6">
+      <c r="E66" s="11">
         <v>217771</v>
       </c>
-      <c r="H66" s="3"/>
+      <c r="H66" s="13"/>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="1">
+      <c r="A67" s="8">
         <v>35582</v>
       </c>
-      <c r="B67" s="4">
+      <c r="B67" s="9">
         <v>35612</v>
       </c>
       <c r="C67" s="10">
@@ -1754,16 +1751,16 @@
       <c r="D67" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E67" s="6">
+      <c r="E67" s="11">
         <v>220233</v>
       </c>
-      <c r="H67" s="3"/>
+      <c r="H67" s="13"/>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="1">
+      <c r="A68" s="8">
         <v>35612</v>
       </c>
-      <c r="B68" s="4">
+      <c r="B68" s="9">
         <v>35643</v>
       </c>
       <c r="C68" s="10">
@@ -1772,16 +1769,16 @@
       <c r="D68" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E68" s="6">
+      <c r="E68" s="11">
         <v>222985</v>
       </c>
-      <c r="H68" s="3"/>
+      <c r="H68" s="13"/>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="1">
+      <c r="A69" s="8">
         <v>35643</v>
       </c>
-      <c r="B69" s="4">
+      <c r="B69" s="9">
         <v>35674</v>
       </c>
       <c r="C69" s="10">
@@ -1790,16 +1787,16 @@
       <c r="D69" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E69" s="6">
+      <c r="E69" s="11">
         <v>223120</v>
       </c>
-      <c r="H69" s="3"/>
+      <c r="H69" s="13"/>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="1">
+      <c r="A70" s="8">
         <v>35674</v>
       </c>
-      <c r="B70" s="4">
+      <c r="B70" s="9">
         <v>35704</v>
       </c>
       <c r="C70" s="10">
@@ -1808,16 +1805,16 @@
       <c r="D70" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E70" s="6">
+      <c r="E70" s="11">
         <v>224509</v>
       </c>
-      <c r="H70" s="3"/>
+      <c r="H70" s="13"/>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="1">
+      <c r="A71" s="8">
         <v>35704</v>
       </c>
-      <c r="B71" s="4">
+      <c r="B71" s="9">
         <v>35735</v>
       </c>
       <c r="C71" s="10">
@@ -1826,16 +1823,16 @@
       <c r="D71" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E71" s="6">
+      <c r="E71" s="11">
         <v>224300</v>
       </c>
-      <c r="H71" s="3"/>
+      <c r="H71" s="13"/>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="1">
+      <c r="A72" s="8">
         <v>35735</v>
       </c>
-      <c r="B72" s="4">
+      <c r="B72" s="9">
         <v>35765</v>
       </c>
       <c r="C72" s="10">
@@ -1844,16 +1841,16 @@
       <c r="D72" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E72" s="6">
+      <c r="E72" s="11">
         <v>223718</v>
       </c>
-      <c r="H72" s="3"/>
+      <c r="H72" s="13"/>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="1">
+      <c r="A73" s="8">
         <v>35765</v>
       </c>
-      <c r="B73" s="4">
+      <c r="B73" s="9">
         <v>35796</v>
       </c>
       <c r="C73" s="10">
@@ -1862,16 +1859,16 @@
       <c r="D73" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E73" s="6">
+      <c r="E73" s="11">
         <v>225236</v>
       </c>
-      <c r="H73" s="3"/>
+      <c r="H73" s="13"/>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="1">
+      <c r="A74" s="8">
         <v>35796</v>
       </c>
-      <c r="B74" s="4">
+      <c r="B74" s="9">
         <v>35827</v>
       </c>
       <c r="C74" s="10">
@@ -1880,16 +1877,16 @@
       <c r="D74" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E74" s="6">
+      <c r="E74" s="11">
         <v>225954</v>
       </c>
-      <c r="H74" s="3"/>
+      <c r="H74" s="13"/>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="1">
+      <c r="A75" s="8">
         <v>35827</v>
       </c>
-      <c r="B75" s="4">
+      <c r="B75" s="9">
         <v>35855</v>
       </c>
       <c r="C75" s="10">
@@ -1898,16 +1895,16 @@
       <c r="D75" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E75" s="6">
+      <c r="E75" s="11">
         <v>225746</v>
       </c>
-      <c r="H75" s="3"/>
+      <c r="H75" s="13"/>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="1">
+      <c r="A76" s="8">
         <v>35855</v>
       </c>
-      <c r="B76" s="4">
+      <c r="B76" s="9">
         <v>35886</v>
       </c>
       <c r="C76" s="10">
@@ -1916,16 +1913,16 @@
       <c r="D76" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E76" s="6">
+      <c r="E76" s="11">
         <v>226889</v>
       </c>
-      <c r="H76" s="3"/>
+      <c r="H76" s="13"/>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="1">
+      <c r="A77" s="8">
         <v>35886</v>
       </c>
-      <c r="B77" s="4">
+      <c r="B77" s="9">
         <v>35916</v>
       </c>
       <c r="C77" s="10">
@@ -1934,16 +1931,16 @@
       <c r="D77" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E77" s="6">
+      <c r="E77" s="11">
         <v>230409</v>
       </c>
-      <c r="H77" s="3"/>
+      <c r="H77" s="13"/>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="1">
+      <c r="A78" s="8">
         <v>35916</v>
       </c>
-      <c r="B78" s="4">
+      <c r="B78" s="9">
         <v>35947</v>
       </c>
       <c r="C78" s="10">
@@ -1952,16 +1949,16 @@
       <c r="D78" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E78" s="6">
+      <c r="E78" s="11">
         <v>230995</v>
       </c>
-      <c r="H78" s="3"/>
+      <c r="H78" s="13"/>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="1">
+      <c r="A79" s="8">
         <v>35947</v>
       </c>
-      <c r="B79" s="4">
+      <c r="B79" s="9">
         <v>35977</v>
       </c>
       <c r="C79" s="10">
@@ -1970,16 +1967,16 @@
       <c r="D79" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E79" s="6">
+      <c r="E79" s="11">
         <v>233207</v>
       </c>
-      <c r="H79" s="3"/>
+      <c r="H79" s="13"/>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="1">
+      <c r="A80" s="8">
         <v>35977</v>
       </c>
-      <c r="B80" s="4">
+      <c r="B80" s="9">
         <v>36008</v>
       </c>
       <c r="C80" s="10">
@@ -1988,16 +1985,16 @@
       <c r="D80" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E80" s="6">
+      <c r="E80" s="11">
         <v>231551</v>
       </c>
-      <c r="H80" s="3"/>
+      <c r="H80" s="13"/>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A81" s="1">
+      <c r="A81" s="8">
         <v>36008</v>
       </c>
-      <c r="B81" s="4">
+      <c r="B81" s="9">
         <v>36039</v>
       </c>
       <c r="C81" s="10">
@@ -2006,16 +2003,16 @@
       <c r="D81" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E81" s="6">
+      <c r="E81" s="11">
         <v>229792</v>
       </c>
-      <c r="H81" s="3"/>
+      <c r="H81" s="13"/>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" s="1">
+      <c r="A82" s="8">
         <v>36039</v>
       </c>
-      <c r="B82" s="4">
+      <c r="B82" s="9">
         <v>36069</v>
       </c>
       <c r="C82" s="10">
@@ -2024,16 +2021,16 @@
       <c r="D82" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E82" s="6">
+      <c r="E82" s="11">
         <v>232308</v>
       </c>
-      <c r="H82" s="3"/>
+      <c r="H82" s="13"/>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A83" s="1">
+      <c r="A83" s="8">
         <v>36069</v>
       </c>
-      <c r="B83" s="4">
+      <c r="B83" s="9">
         <v>36100</v>
       </c>
       <c r="C83" s="10">
@@ -2042,16 +2039,16 @@
       <c r="D83" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E83" s="6">
+      <c r="E83" s="11">
         <v>236174</v>
       </c>
-      <c r="H83" s="3"/>
+      <c r="H83" s="13"/>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="1">
+      <c r="A84" s="8">
         <v>36100</v>
       </c>
-      <c r="B84" s="4">
+      <c r="B84" s="9">
         <v>36130</v>
       </c>
       <c r="C84" s="10">
@@ -2060,16 +2057,16 @@
       <c r="D84" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E84" s="6">
+      <c r="E84" s="11">
         <v>237592</v>
       </c>
-      <c r="H84" s="3"/>
+      <c r="H84" s="13"/>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A85" s="1">
+      <c r="A85" s="8">
         <v>36130</v>
       </c>
-      <c r="B85" s="4">
+      <c r="B85" s="9">
         <v>36161</v>
       </c>
       <c r="C85" s="10">
@@ -2078,16 +2075,16 @@
       <c r="D85" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E85" s="6">
+      <c r="E85" s="11">
         <v>240140</v>
       </c>
-      <c r="H85" s="3"/>
+      <c r="H85" s="13"/>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A86" s="1">
+      <c r="A86" s="8">
         <v>36161</v>
       </c>
-      <c r="B86" s="4">
+      <c r="B86" s="9">
         <v>36192</v>
       </c>
       <c r="C86" s="10">
@@ -2096,16 +2093,16 @@
       <c r="D86" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E86" s="6">
+      <c r="E86" s="11">
         <v>240269</v>
       </c>
-      <c r="H86" s="3"/>
+      <c r="H86" s="13"/>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A87" s="1">
+      <c r="A87" s="8">
         <v>36192</v>
       </c>
-      <c r="B87" s="4">
+      <c r="B87" s="9">
         <v>36220</v>
       </c>
       <c r="C87" s="10">
@@ -2114,16 +2111,16 @@
       <c r="D87" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E87" s="6">
+      <c r="E87" s="11">
         <v>243346</v>
       </c>
-      <c r="H87" s="3"/>
+      <c r="H87" s="13"/>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A88" s="1">
+      <c r="A88" s="8">
         <v>36220</v>
       </c>
-      <c r="B88" s="4">
+      <c r="B88" s="9">
         <v>36251</v>
       </c>
       <c r="C88" s="10">
@@ -2132,16 +2129,16 @@
       <c r="D88" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E88" s="6">
+      <c r="E88" s="11">
         <v>244687</v>
       </c>
-      <c r="H88" s="3"/>
+      <c r="H88" s="13"/>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A89" s="1">
+      <c r="A89" s="8">
         <v>36251</v>
       </c>
-      <c r="B89" s="4">
+      <c r="B89" s="9">
         <v>36281</v>
       </c>
       <c r="C89" s="10">
@@ -2150,16 +2147,16 @@
       <c r="D89" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E89" s="6">
+      <c r="E89" s="11">
         <v>246628</v>
       </c>
-      <c r="H89" s="3"/>
+      <c r="H89" s="13"/>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A90" s="1">
+      <c r="A90" s="8">
         <v>36281</v>
       </c>
-      <c r="B90" s="4">
+      <c r="B90" s="9">
         <v>36312</v>
       </c>
       <c r="C90" s="10">
@@ -2168,16 +2165,16 @@
       <c r="D90" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E90" s="6">
+      <c r="E90" s="11">
         <v>248367</v>
       </c>
-      <c r="H90" s="3"/>
+      <c r="H90" s="13"/>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A91" s="1">
+      <c r="A91" s="8">
         <v>36312</v>
       </c>
-      <c r="B91" s="4">
+      <c r="B91" s="9">
         <v>36342</v>
       </c>
       <c r="C91" s="10">
@@ -2186,16 +2183,16 @@
       <c r="D91" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E91" s="6">
+      <c r="E91" s="11">
         <v>249329</v>
       </c>
-      <c r="H91" s="3"/>
+      <c r="H91" s="13"/>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A92" s="1">
+      <c r="A92" s="8">
         <v>36342</v>
       </c>
-      <c r="B92" s="4">
+      <c r="B92" s="9">
         <v>36373</v>
       </c>
       <c r="C92" s="10">
@@ -2204,16 +2201,16 @@
       <c r="D92" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E92" s="6">
+      <c r="E92" s="11">
         <v>251263</v>
       </c>
-      <c r="H92" s="3"/>
+      <c r="H92" s="13"/>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A93" s="1">
+      <c r="A93" s="8">
         <v>36373</v>
       </c>
-      <c r="B93" s="4">
+      <c r="B93" s="9">
         <v>36404</v>
       </c>
       <c r="C93" s="10">
@@ -2222,16 +2219,16 @@
       <c r="D93" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E93" s="6">
+      <c r="E93" s="11">
         <v>253844</v>
       </c>
-      <c r="H93" s="3"/>
+      <c r="H93" s="13"/>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A94" s="1">
+      <c r="A94" s="8">
         <v>36404</v>
       </c>
-      <c r="B94" s="4">
+      <c r="B94" s="9">
         <v>36434</v>
       </c>
       <c r="C94" s="10">
@@ -2240,16 +2237,16 @@
       <c r="D94" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E94" s="6">
+      <c r="E94" s="11">
         <v>255029</v>
       </c>
-      <c r="H94" s="3"/>
+      <c r="H94" s="13"/>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A95" s="1">
+      <c r="A95" s="8">
         <v>36434</v>
       </c>
-      <c r="B95" s="4">
+      <c r="B95" s="9">
         <v>36465</v>
       </c>
       <c r="C95" s="10">
@@ -2258,16 +2255,16 @@
       <c r="D95" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E95" s="6">
+      <c r="E95" s="11">
         <v>254816</v>
       </c>
-      <c r="H95" s="3"/>
+      <c r="H95" s="13"/>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A96" s="1">
+      <c r="A96" s="8">
         <v>36465</v>
       </c>
-      <c r="B96" s="4">
+      <c r="B96" s="9">
         <v>36495</v>
       </c>
       <c r="C96" s="10">
@@ -2276,16 +2273,16 @@
       <c r="D96" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E96" s="6">
+      <c r="E96" s="11">
         <v>258133</v>
       </c>
-      <c r="H96" s="3"/>
+      <c r="H96" s="13"/>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A97" s="1">
+      <c r="A97" s="8">
         <v>36495</v>
       </c>
-      <c r="B97" s="4">
+      <c r="B97" s="9">
         <v>36526</v>
       </c>
       <c r="C97" s="10">
@@ -2294,16 +2291,16 @@
       <c r="D97" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E97" s="6">
+      <c r="E97" s="11">
         <v>263311</v>
       </c>
-      <c r="H97" s="3"/>
+      <c r="H97" s="13"/>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A98" s="1">
+      <c r="A98" s="8">
         <v>36526</v>
       </c>
-      <c r="B98" s="4">
+      <c r="B98" s="9">
         <v>36557</v>
       </c>
       <c r="C98" s="10">
@@ -2312,16 +2309,16 @@
       <c r="D98" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E98" s="6">
+      <c r="E98" s="11">
         <v>261545</v>
       </c>
-      <c r="H98" s="3"/>
+      <c r="H98" s="13"/>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A99" s="1">
+      <c r="A99" s="8">
         <v>36557</v>
       </c>
-      <c r="B99" s="4">
+      <c r="B99" s="9">
         <v>36586</v>
       </c>
       <c r="C99" s="10">
@@ -2330,16 +2327,16 @@
       <c r="D99" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E99" s="6">
+      <c r="E99" s="11">
         <v>265686</v>
       </c>
-      <c r="H99" s="3"/>
+      <c r="H99" s="13"/>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A100" s="1">
+      <c r="A100" s="8">
         <v>36586</v>
       </c>
-      <c r="B100" s="4">
+      <c r="B100" s="9">
         <v>36617</v>
       </c>
       <c r="C100" s="10">
@@ -2348,16 +2345,16 @@
       <c r="D100" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E100" s="6">
+      <c r="E100" s="11">
         <v>269019</v>
       </c>
-      <c r="H100" s="3"/>
+      <c r="H100" s="13"/>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A101" s="1">
+      <c r="A101" s="8">
         <v>36617</v>
       </c>
-      <c r="B101" s="4">
+      <c r="B101" s="9">
         <v>36647</v>
       </c>
       <c r="C101" s="10">
@@ -2366,16 +2363,16 @@
       <c r="D101" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E101" s="6">
+      <c r="E101" s="11">
         <v>264067</v>
       </c>
-      <c r="H101" s="3"/>
+      <c r="H101" s="13"/>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A102" s="1">
+      <c r="A102" s="8">
         <v>36647</v>
       </c>
-      <c r="B102" s="4">
+      <c r="B102" s="9">
         <v>36678</v>
       </c>
       <c r="C102" s="10">
@@ -2384,16 +2381,16 @@
       <c r="D102" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E102" s="6">
+      <c r="E102" s="11">
         <v>265992</v>
       </c>
-      <c r="H102" s="3"/>
+      <c r="H102" s="13"/>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A103" s="1">
+      <c r="A103" s="8">
         <v>36678</v>
       </c>
-      <c r="B103" s="4">
+      <c r="B103" s="9">
         <v>36708</v>
       </c>
       <c r="C103" s="10">
@@ -2402,16 +2399,16 @@
       <c r="D103" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E103" s="6">
+      <c r="E103" s="11">
         <v>267750</v>
       </c>
-      <c r="H103" s="3"/>
+      <c r="H103" s="13"/>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A104" s="1">
+      <c r="A104" s="8">
         <v>36708</v>
       </c>
-      <c r="B104" s="4">
+      <c r="B104" s="9">
         <v>36739</v>
       </c>
       <c r="C104" s="10">
@@ -2420,16 +2417,16 @@
       <c r="D104" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E104" s="6">
+      <c r="E104" s="11">
         <v>265683</v>
       </c>
-      <c r="H104" s="3"/>
+      <c r="H104" s="13"/>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A105" s="1">
+      <c r="A105" s="8">
         <v>36739</v>
       </c>
-      <c r="B105" s="4">
+      <c r="B105" s="9">
         <v>36770</v>
       </c>
       <c r="C105" s="10">
@@ -2438,16 +2435,16 @@
       <c r="D105" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E105" s="6">
+      <c r="E105" s="11">
         <v>266885</v>
       </c>
-      <c r="H105" s="3"/>
+      <c r="H105" s="13"/>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A106" s="1">
+      <c r="A106" s="8">
         <v>36770</v>
       </c>
-      <c r="B106" s="4">
+      <c r="B106" s="9">
         <v>36800</v>
       </c>
       <c r="C106" s="10">
@@ -2456,16 +2453,16 @@
       <c r="D106" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E106" s="6">
+      <c r="E106" s="11">
         <v>270523</v>
       </c>
-      <c r="H106" s="3"/>
+      <c r="H106" s="13"/>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A107" s="1">
+      <c r="A107" s="8">
         <v>36800</v>
       </c>
-      <c r="B107" s="4">
+      <c r="B107" s="9">
         <v>36831</v>
       </c>
       <c r="C107" s="10">
@@ -2474,16 +2471,16 @@
       <c r="D107" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E107" s="6">
+      <c r="E107" s="11">
         <v>270339</v>
       </c>
-      <c r="H107" s="3"/>
+      <c r="H107" s="13"/>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A108" s="1">
+      <c r="A108" s="8">
         <v>36831</v>
       </c>
-      <c r="B108" s="4">
+      <c r="B108" s="9">
         <v>36861</v>
       </c>
       <c r="C108" s="10">
@@ -2492,16 +2489,16 @@
       <c r="D108" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E108" s="6">
+      <c r="E108" s="11">
         <v>268850</v>
       </c>
-      <c r="H108" s="3"/>
+      <c r="H108" s="13"/>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A109" s="1">
+      <c r="A109" s="8">
         <v>36861</v>
       </c>
-      <c r="B109" s="4">
+      <c r="B109" s="9">
         <v>36892</v>
       </c>
       <c r="C109" s="10">
@@ -2510,16 +2507,16 @@
       <c r="D109" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E109" s="6">
+      <c r="E109" s="11">
         <v>268338</v>
       </c>
-      <c r="H109" s="3"/>
+      <c r="H109" s="13"/>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A110" s="1">
+      <c r="A110" s="8">
         <v>36892</v>
       </c>
-      <c r="B110" s="4">
+      <c r="B110" s="9">
         <v>36923</v>
       </c>
       <c r="C110" s="10">
@@ -2528,16 +2525,16 @@
       <c r="D110" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E110" s="6">
+      <c r="E110" s="11">
         <v>272881</v>
       </c>
-      <c r="H110" s="3"/>
+      <c r="H110" s="13"/>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A111" s="1">
+      <c r="A111" s="8">
         <v>36923</v>
       </c>
-      <c r="B111" s="4">
+      <c r="B111" s="9">
         <v>36951</v>
       </c>
       <c r="C111" s="10">
@@ -2546,16 +2543,16 @@
       <c r="D111" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E111" s="6">
+      <c r="E111" s="11">
         <v>272627</v>
       </c>
-      <c r="H111" s="3"/>
+      <c r="H111" s="13"/>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A112" s="1">
+      <c r="A112" s="8">
         <v>36951</v>
       </c>
-      <c r="B112" s="4">
+      <c r="B112" s="9">
         <v>36982</v>
       </c>
       <c r="C112" s="10">
@@ -2564,16 +2561,16 @@
       <c r="D112" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E112" s="6">
+      <c r="E112" s="11">
         <v>269820</v>
       </c>
-      <c r="H112" s="3"/>
+      <c r="H112" s="13"/>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A113" s="1">
+      <c r="A113" s="8">
         <v>36982</v>
       </c>
-      <c r="B113" s="4">
+      <c r="B113" s="9">
         <v>37012</v>
       </c>
       <c r="C113" s="10">
@@ -2582,16 +2579,16 @@
       <c r="D113" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E113" s="6">
+      <c r="E113" s="11">
         <v>274410</v>
       </c>
-      <c r="H113" s="3"/>
+      <c r="H113" s="13"/>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A114" s="1">
+      <c r="A114" s="8">
         <v>37012</v>
       </c>
-      <c r="B114" s="4">
+      <c r="B114" s="9">
         <v>37055</v>
       </c>
       <c r="C114" s="10">
@@ -2600,16 +2597,16 @@
       <c r="D114" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E114" s="6">
+      <c r="E114" s="11">
         <v>275769</v>
       </c>
-      <c r="H114" s="3"/>
+      <c r="H114" s="13"/>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A115" s="1">
+      <c r="A115" s="8">
         <v>37043</v>
       </c>
-      <c r="B115" s="4">
+      <c r="B115" s="9">
         <v>37085</v>
       </c>
       <c r="C115" s="10">
@@ -2618,16 +2615,16 @@
       <c r="D115" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E115" s="6">
+      <c r="E115" s="11">
         <v>274474</v>
       </c>
-      <c r="H115" s="3"/>
+      <c r="H115" s="13"/>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A116" s="1">
+      <c r="A116" s="8">
         <v>37073</v>
       </c>
-      <c r="B116" s="4">
+      <c r="B116" s="9">
         <v>37117</v>
       </c>
       <c r="C116" s="10">
@@ -2636,16 +2633,16 @@
       <c r="D116" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E116" s="6">
+      <c r="E116" s="11">
         <v>273098</v>
       </c>
-      <c r="H116" s="3"/>
+      <c r="H116" s="13"/>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A117" s="1">
+      <c r="A117" s="8">
         <v>37104</v>
       </c>
-      <c r="B117" s="4">
+      <c r="B117" s="9">
         <v>37148</v>
       </c>
       <c r="C117" s="10">
@@ -2654,16 +2651,16 @@
       <c r="D117" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E117" s="6">
+      <c r="E117" s="11">
         <v>275659</v>
       </c>
-      <c r="H117" s="3"/>
+      <c r="H117" s="13"/>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A118" s="1">
+      <c r="A118" s="8">
         <v>37135</v>
       </c>
-      <c r="B118" s="4">
+      <c r="B118" s="9">
         <v>37176</v>
       </c>
       <c r="C118" s="10">
@@ -2672,16 +2669,16 @@
       <c r="D118" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E118" s="6">
+      <c r="E118" s="11">
         <v>268652</v>
       </c>
-      <c r="H118" s="3"/>
+      <c r="H118" s="13"/>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A119" s="1">
+      <c r="A119" s="8">
         <v>37165</v>
       </c>
-      <c r="B119" s="4">
+      <c r="B119" s="9">
         <v>37209</v>
       </c>
       <c r="C119" s="10">
@@ -2690,16 +2687,16 @@
       <c r="D119" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E119" s="6">
+      <c r="E119" s="11">
         <v>288632</v>
       </c>
-      <c r="H119" s="3"/>
+      <c r="H119" s="13"/>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A120" s="1">
+      <c r="A120" s="8">
         <v>37196</v>
       </c>
-      <c r="B120" s="4">
+      <c r="B120" s="9">
         <v>37238</v>
       </c>
       <c r="C120" s="10">
@@ -2708,16 +2705,16 @@
       <c r="D120" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E120" s="6">
+      <c r="E120" s="11">
         <v>280033</v>
       </c>
-      <c r="H120" s="3"/>
+      <c r="H120" s="13"/>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A121" s="1">
+      <c r="A121" s="8">
         <v>37226</v>
       </c>
-      <c r="B121" s="4">
+      <c r="B121" s="9">
         <v>37271</v>
       </c>
       <c r="C121" s="10">
@@ -2726,16 +2723,16 @@
       <c r="D121" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E121" s="6">
+      <c r="E121" s="11">
         <v>276302</v>
       </c>
-      <c r="H121" s="3"/>
+      <c r="H121" s="13"/>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A122" s="1">
+      <c r="A122" s="8">
         <v>37257</v>
       </c>
-      <c r="B122" s="4">
+      <c r="B122" s="9">
         <v>37300</v>
       </c>
       <c r="C122" s="10">
@@ -2744,16 +2741,16 @@
       <c r="D122" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E122" s="6">
+      <c r="E122" s="11">
         <v>277135</v>
       </c>
-      <c r="H122" s="3"/>
+      <c r="H122" s="13"/>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A123" s="1">
+      <c r="A123" s="8">
         <v>37288</v>
       </c>
-      <c r="B123" s="4">
+      <c r="B123" s="9">
         <v>37328</v>
       </c>
       <c r="C123" s="10">
@@ -2762,16 +2759,16 @@
       <c r="D123" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E123" s="6">
+      <c r="E123" s="11">
         <v>278869</v>
       </c>
-      <c r="H123" s="3"/>
+      <c r="H123" s="13"/>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A124" s="1">
+      <c r="A124" s="8">
         <v>37316</v>
       </c>
-      <c r="B124" s="4">
+      <c r="B124" s="9">
         <v>37358</v>
       </c>
       <c r="C124" s="10">
@@ -2780,16 +2777,16 @@
       <c r="D124" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E124" s="6">
+      <c r="E124" s="11">
         <v>278079</v>
       </c>
-      <c r="H124" s="3"/>
+      <c r="H124" s="13"/>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A125" s="1">
+      <c r="A125" s="8">
         <v>37347</v>
       </c>
-      <c r="B125" s="4">
+      <c r="B125" s="9">
         <v>37390</v>
       </c>
       <c r="C125" s="10">
@@ -2798,16 +2795,16 @@
       <c r="D125" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E125" s="6">
+      <c r="E125" s="11">
         <v>281147</v>
       </c>
-      <c r="H125" s="3"/>
+      <c r="H125" s="13"/>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A126" s="1">
+      <c r="A126" s="8">
         <v>37377</v>
       </c>
-      <c r="B126" s="4">
+      <c r="B126" s="9">
         <v>37420</v>
       </c>
       <c r="C126" s="10">
@@ -2816,16 +2813,16 @@
       <c r="D126" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E126" s="6">
+      <c r="E126" s="11">
         <v>278966</v>
       </c>
-      <c r="H126" s="3"/>
+      <c r="H126" s="13"/>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A127" s="1">
+      <c r="A127" s="8">
         <v>37408</v>
       </c>
-      <c r="B127" s="4">
+      <c r="B127" s="9">
         <v>37449</v>
       </c>
       <c r="C127" s="10">
@@ -2834,16 +2831,16 @@
       <c r="D127" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E127" s="6">
+      <c r="E127" s="11">
         <v>280426</v>
       </c>
-      <c r="H127" s="3"/>
+      <c r="H127" s="13"/>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A128" s="1">
+      <c r="A128" s="8">
         <v>37438</v>
       </c>
-      <c r="B128" s="4">
+      <c r="B128" s="9">
         <v>37481</v>
       </c>
       <c r="C128" s="10">
@@ -2852,16 +2849,16 @@
       <c r="D128" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E128" s="6">
+      <c r="E128" s="11">
         <v>284161</v>
       </c>
-      <c r="H128" s="3"/>
+      <c r="H128" s="13"/>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A129" s="1">
+      <c r="A129" s="8">
         <v>37469</v>
       </c>
-      <c r="B129" s="4">
+      <c r="B129" s="9">
         <v>37512</v>
       </c>
       <c r="C129" s="10">
@@ -2870,16 +2867,16 @@
       <c r="D129" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E129" s="6">
+      <c r="E129" s="11">
         <v>285884</v>
       </c>
-      <c r="H129" s="3"/>
+      <c r="H129" s="13"/>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A130" s="1">
+      <c r="A130" s="8">
         <v>37500</v>
       </c>
-      <c r="B130" s="4">
+      <c r="B130" s="9">
         <v>37540</v>
       </c>
       <c r="C130" s="10">
@@ -2888,16 +2885,16 @@
       <c r="D130" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E130" s="6">
+      <c r="E130" s="11">
         <v>281064</v>
       </c>
-      <c r="H130" s="3"/>
+      <c r="H130" s="13"/>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A131" s="1">
+      <c r="A131" s="8">
         <v>37530</v>
       </c>
-      <c r="B131" s="4">
+      <c r="B131" s="9">
         <v>37574</v>
       </c>
       <c r="C131" s="10">
@@ -2906,16 +2903,16 @@
       <c r="D131" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E131" s="6">
+      <c r="E131" s="11">
         <v>282940</v>
       </c>
-      <c r="H131" s="3"/>
+      <c r="H131" s="13"/>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A132" s="1">
+      <c r="A132" s="8">
         <v>37561</v>
       </c>
-      <c r="B132" s="4">
+      <c r="B132" s="9">
         <v>37602</v>
       </c>
       <c r="C132" s="10">
@@ -2924,16 +2921,16 @@
       <c r="D132" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E132" s="6">
+      <c r="E132" s="11">
         <v>283408</v>
       </c>
-      <c r="H132" s="3"/>
+      <c r="H132" s="13"/>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A133" s="1">
+      <c r="A133" s="8">
         <v>37591</v>
       </c>
-      <c r="B133" s="4">
+      <c r="B133" s="9">
         <v>37635</v>
       </c>
       <c r="C133" s="10">
@@ -2942,16 +2939,16 @@
       <c r="D133" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E133" s="6">
+      <c r="E133" s="11">
         <v>286646</v>
       </c>
-      <c r="H133" s="3"/>
+      <c r="H133" s="13"/>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A134" s="1">
+      <c r="A134" s="8">
         <v>37622</v>
       </c>
-      <c r="B134" s="4">
+      <c r="B134" s="9">
         <v>37665</v>
       </c>
       <c r="C134" s="10">
@@ -2960,16 +2957,16 @@
       <c r="D134" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E134" s="6">
+      <c r="E134" s="11">
         <v>288657</v>
       </c>
-      <c r="H134" s="3"/>
+      <c r="H134" s="13"/>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A135" s="1">
+      <c r="A135" s="8">
         <v>37653</v>
       </c>
-      <c r="B135" s="4">
+      <c r="B135" s="9">
         <v>37693</v>
       </c>
       <c r="C135" s="10">
@@ -2978,16 +2975,16 @@
       <c r="D135" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E135" s="6">
+      <c r="E135" s="11">
         <v>284696</v>
       </c>
-      <c r="H135" s="3"/>
+      <c r="H135" s="13"/>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A136" s="1">
+      <c r="A136" s="8">
         <v>37681</v>
       </c>
-      <c r="B136" s="4">
+      <c r="B136" s="9">
         <v>37722</v>
       </c>
       <c r="C136" s="10">
@@ -2996,16 +2993,16 @@
       <c r="D136" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E136" s="6">
+      <c r="E136" s="11">
         <v>288177</v>
       </c>
-      <c r="H136" s="3"/>
+      <c r="H136" s="13"/>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A137" s="1">
+      <c r="A137" s="8">
         <v>37712</v>
       </c>
-      <c r="B137" s="4">
+      <c r="B137" s="9">
         <v>37755</v>
       </c>
       <c r="C137" s="10">
@@ -3014,16 +3011,16 @@
       <c r="D137" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E137" s="6">
+      <c r="E137" s="11">
         <v>289053</v>
       </c>
-      <c r="H137" s="3"/>
+      <c r="H137" s="13"/>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A138" s="1">
+      <c r="A138" s="8">
         <v>37742</v>
       </c>
-      <c r="B138" s="4">
+      <c r="B138" s="9">
         <v>37784</v>
       </c>
       <c r="C138" s="10">
@@ -3032,16 +3029,16 @@
       <c r="D138" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E138" s="6">
+      <c r="E138" s="11">
         <v>289619</v>
       </c>
-      <c r="H138" s="3"/>
+      <c r="H138" s="13"/>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A139" s="1">
+      <c r="A139" s="8">
         <v>37773</v>
       </c>
-      <c r="B139" s="4">
+      <c r="B139" s="9">
         <v>37817</v>
       </c>
       <c r="C139" s="10">
@@ -3050,16 +3047,16 @@
       <c r="D139" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E139" s="6">
+      <c r="E139" s="11">
         <v>293671</v>
       </c>
-      <c r="H139" s="3"/>
+      <c r="H139" s="13"/>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A140" s="1">
+      <c r="A140" s="8">
         <v>37803</v>
       </c>
-      <c r="B140" s="4">
+      <c r="B140" s="9">
         <v>37846</v>
       </c>
       <c r="C140" s="10">
@@ -3068,16 +3065,16 @@
       <c r="D140" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E140" s="6">
+      <c r="E140" s="11">
         <v>296207</v>
       </c>
-      <c r="H140" s="3"/>
+      <c r="H140" s="13"/>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A141" s="1">
+      <c r="A141" s="8">
         <v>37834</v>
       </c>
-      <c r="B141" s="4">
+      <c r="B141" s="9">
         <v>37876</v>
       </c>
       <c r="C141" s="10">
@@ -3086,16 +3083,16 @@
       <c r="D141" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E141" s="6">
+      <c r="E141" s="11">
         <v>299592</v>
       </c>
-      <c r="H141" s="3"/>
+      <c r="H141" s="13"/>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A142" s="1">
+      <c r="A142" s="8">
         <v>37865</v>
       </c>
-      <c r="B142" s="4">
+      <c r="B142" s="9">
         <v>37909</v>
       </c>
       <c r="C142" s="10">
@@ -3104,16 +3101,16 @@
       <c r="D142" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E142" s="6">
+      <c r="E142" s="11">
         <v>298921</v>
       </c>
-      <c r="H142" s="3"/>
+      <c r="H142" s="13"/>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A143" s="1">
+      <c r="A143" s="8">
         <v>37895</v>
       </c>
-      <c r="B143" s="4">
+      <c r="B143" s="9">
         <v>37939</v>
       </c>
       <c r="C143" s="10">
@@ -3122,16 +3119,16 @@
       <c r="D143" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E143" s="6">
+      <c r="E143" s="11">
         <v>298205</v>
       </c>
-      <c r="H143" s="3"/>
+      <c r="H143" s="13"/>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A144" s="1">
+      <c r="A144" s="8">
         <v>37926</v>
       </c>
-      <c r="B144" s="4">
+      <c r="B144" s="9">
         <v>37966</v>
       </c>
       <c r="C144" s="10">
@@ -3140,16 +3137,16 @@
       <c r="D144" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E144" s="6">
+      <c r="E144" s="11">
         <v>299433</v>
       </c>
-      <c r="H144" s="3"/>
+      <c r="H144" s="13"/>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A145" s="1">
+      <c r="A145" s="8">
         <v>37956</v>
       </c>
-      <c r="B145" s="4">
+      <c r="B145" s="9">
         <v>38001</v>
       </c>
       <c r="C145" s="10">
@@ -3158,16 +3155,16 @@
       <c r="D145" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E145" s="6">
+      <c r="E145" s="11">
         <v>300702</v>
       </c>
-      <c r="H145" s="3"/>
+      <c r="H145" s="13"/>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A146" s="1">
+      <c r="A146" s="8">
         <v>37987</v>
       </c>
-      <c r="B146" s="4">
+      <c r="B146" s="9">
         <v>38029</v>
       </c>
       <c r="C146" s="10">
@@ -3176,16 +3173,16 @@
       <c r="D146" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E146" s="6">
+      <c r="E146" s="11">
         <v>301993</v>
       </c>
-      <c r="H146" s="3"/>
+      <c r="H146" s="13"/>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A147" s="1">
+      <c r="A147" s="8">
         <v>38018</v>
       </c>
-      <c r="B147" s="4">
+      <c r="B147" s="9">
         <v>38057</v>
       </c>
       <c r="C147" s="10">
@@ -3194,16 +3191,16 @@
       <c r="D147" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E147" s="6">
+      <c r="E147" s="11">
         <v>303915</v>
       </c>
-      <c r="H147" s="3"/>
+      <c r="H147" s="13"/>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A148" s="1">
+      <c r="A148" s="8">
         <v>38047</v>
       </c>
-      <c r="B148" s="4">
+      <c r="B148" s="9">
         <v>38090</v>
       </c>
       <c r="C148" s="10">
@@ -3212,16 +3209,16 @@
       <c r="D148" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E148" s="6">
+      <c r="E148" s="11">
         <v>309471</v>
       </c>
-      <c r="H148" s="3"/>
+      <c r="H148" s="13"/>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A149" s="1">
+      <c r="A149" s="8">
         <v>38078</v>
       </c>
-      <c r="B149" s="4">
+      <c r="B149" s="9">
         <v>38120</v>
       </c>
       <c r="C149" s="10">
@@ -3230,16 +3227,16 @@
       <c r="D149" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E149" s="6">
+      <c r="E149" s="11">
         <v>307358</v>
       </c>
-      <c r="H149" s="3"/>
+      <c r="H149" s="13"/>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A150" s="1">
+      <c r="A150" s="8">
         <v>38108</v>
       </c>
-      <c r="B150" s="4">
+      <c r="B150" s="9">
         <v>38152</v>
       </c>
       <c r="C150" s="10">
@@ -3248,16 +3245,16 @@
       <c r="D150" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E150" s="6">
+      <c r="E150" s="11">
         <v>311088</v>
       </c>
-      <c r="H150" s="3"/>
+      <c r="H150" s="13"/>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A151" s="1">
+      <c r="A151" s="8">
         <v>38139</v>
       </c>
-      <c r="B151" s="4">
+      <c r="B151" s="9">
         <v>38182</v>
       </c>
       <c r="C151" s="10">
@@ -3266,16 +3263,16 @@
       <c r="D151" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E151" s="6">
+      <c r="E151" s="11">
         <v>309127</v>
       </c>
-      <c r="H151" s="3"/>
+      <c r="H151" s="13"/>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A152" s="1">
+      <c r="A152" s="8">
         <v>38169</v>
       </c>
-      <c r="B152" s="4">
+      <c r="B152" s="9">
         <v>38211</v>
       </c>
       <c r="C152" s="10">
@@ -3284,16 +3281,16 @@
       <c r="D152" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E152" s="6">
+      <c r="E152" s="11">
         <v>311681</v>
       </c>
-      <c r="H152" s="3"/>
+      <c r="H152" s="13"/>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A153" s="1">
+      <c r="A153" s="8">
         <v>38200</v>
       </c>
-      <c r="B153" s="4">
+      <c r="B153" s="9">
         <v>38244</v>
       </c>
       <c r="C153" s="10">
@@ -3302,16 +3299,16 @@
       <c r="D153" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E153" s="6">
+      <c r="E153" s="11">
         <v>311192</v>
       </c>
-      <c r="H153" s="3"/>
+      <c r="H153" s="13"/>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A154" s="1">
+      <c r="A154" s="8">
         <v>38231</v>
       </c>
-      <c r="B154" s="4">
+      <c r="B154" s="9">
         <v>38275</v>
       </c>
       <c r="C154" s="10">
@@ -3320,16 +3317,16 @@
       <c r="D154" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E154" s="6">
+      <c r="E154" s="11">
         <v>317446</v>
       </c>
-      <c r="H154" s="3"/>
+      <c r="H154" s="13"/>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A155" s="1">
+      <c r="A155" s="8">
         <v>38261</v>
       </c>
-      <c r="B155" s="4">
+      <c r="B155" s="9">
         <v>38303</v>
       </c>
       <c r="C155" s="10">
@@ -3338,16 +3335,16 @@
       <c r="D155" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E155" s="6">
+      <c r="E155" s="11">
         <v>318476</v>
       </c>
-      <c r="H155" s="3"/>
+      <c r="H155" s="13"/>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A156" s="1">
+      <c r="A156" s="8">
         <v>38292</v>
       </c>
-      <c r="B156" s="4">
+      <c r="B156" s="9">
         <v>38334</v>
       </c>
       <c r="C156" s="10">
@@ -3356,16 +3353,16 @@
       <c r="D156" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E156" s="6">
+      <c r="E156" s="11">
         <v>320520</v>
       </c>
-      <c r="H156" s="3"/>
+      <c r="H156" s="13"/>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A157" s="1">
+      <c r="A157" s="8">
         <v>38322</v>
       </c>
-      <c r="B157" s="4">
+      <c r="B157" s="9">
         <v>38365</v>
       </c>
       <c r="C157" s="10">
@@ -3374,16 +3371,16 @@
       <c r="D157" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E157" s="6">
+      <c r="E157" s="11">
         <v>324672</v>
       </c>
-      <c r="H157" s="3"/>
+      <c r="H157" s="13"/>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A158" s="1">
+      <c r="A158" s="8">
         <v>38353</v>
       </c>
-      <c r="B158" s="4">
+      <c r="B158" s="9">
         <v>38398</v>
       </c>
       <c r="C158" s="10">
@@ -3392,16 +3389,16 @@
       <c r="D158" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E158" s="6">
+      <c r="E158" s="11">
         <v>321272</v>
       </c>
-      <c r="H158" s="3"/>
+      <c r="H158" s="13"/>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A159" s="1">
+      <c r="A159" s="8">
         <v>38384</v>
       </c>
-      <c r="B159" s="4">
+      <c r="B159" s="9">
         <v>38426</v>
       </c>
       <c r="C159" s="10">
@@ -3410,16 +3407,16 @@
       <c r="D159" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E159" s="6">
+      <c r="E159" s="11">
         <v>325308</v>
       </c>
-      <c r="H159" s="3"/>
+      <c r="H159" s="13"/>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A160" s="1">
+      <c r="A160" s="8">
         <v>38412</v>
       </c>
-      <c r="B160" s="4">
+      <c r="B160" s="9">
         <v>38455</v>
       </c>
       <c r="C160" s="10">
@@ -3428,16 +3425,16 @@
       <c r="D160" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E160" s="6">
+      <c r="E160" s="11">
         <v>326179</v>
       </c>
-      <c r="H160" s="3"/>
+      <c r="H160" s="13"/>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A161" s="1">
+      <c r="A161" s="8">
         <v>38443</v>
       </c>
-      <c r="B161" s="4">
+      <c r="B161" s="9">
         <v>38484</v>
       </c>
       <c r="C161" s="10">
@@ -3446,16 +3443,16 @@
       <c r="D161" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E161" s="6">
+      <c r="E161" s="11">
         <v>329124</v>
       </c>
-      <c r="H161" s="3"/>
+      <c r="H161" s="13"/>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A162" s="1">
+      <c r="A162" s="8">
         <v>38473</v>
       </c>
-      <c r="B162" s="4">
+      <c r="B162" s="9">
         <v>38517</v>
       </c>
       <c r="C162" s="10">
@@ -3464,16 +3461,16 @@
       <c r="D162" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E162" s="6">
+      <c r="E162" s="11">
         <v>327233</v>
       </c>
-      <c r="H162" s="3"/>
+      <c r="H162" s="13"/>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A163" s="1">
+      <c r="A163" s="8">
         <v>38504</v>
       </c>
-      <c r="B163" s="4">
+      <c r="B163" s="9">
         <v>38547</v>
       </c>
       <c r="C163" s="10">
@@ -3482,16 +3479,16 @@
       <c r="D163" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E163" s="6">
+      <c r="E163" s="11">
         <v>337219</v>
       </c>
-      <c r="H163" s="3"/>
+      <c r="H163" s="13"/>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A164" s="1">
+      <c r="A164" s="8">
         <v>38534</v>
       </c>
-      <c r="B164" s="4">
+      <c r="B164" s="9">
         <v>38575</v>
       </c>
       <c r="C164" s="10">
@@ -3500,16 +3497,16 @@
       <c r="D164" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E164" s="6">
+      <c r="E164" s="11">
         <v>339529</v>
       </c>
-      <c r="H164" s="3"/>
+      <c r="H164" s="13"/>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A165" s="1">
+      <c r="A165" s="8">
         <v>38565</v>
       </c>
-      <c r="B165" s="4">
+      <c r="B165" s="9">
         <v>38609</v>
       </c>
       <c r="C165" s="10">
@@ -3518,16 +3515,16 @@
       <c r="D165" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E165" s="6">
+      <c r="E165" s="11">
         <v>335605</v>
       </c>
-      <c r="H165" s="3"/>
+      <c r="H165" s="13"/>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A166" s="1">
+      <c r="A166" s="8">
         <v>38596</v>
       </c>
-      <c r="B166" s="4">
+      <c r="B166" s="9">
         <v>38639</v>
       </c>
       <c r="C166" s="10">
@@ -3536,16 +3533,16 @@
       <c r="D166" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E166" s="6">
+      <c r="E166" s="11">
         <v>336600</v>
       </c>
-      <c r="H166" s="3"/>
+      <c r="H166" s="13"/>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A167" s="1">
+      <c r="A167" s="8">
         <v>38626</v>
       </c>
-      <c r="B167" s="4">
+      <c r="B167" s="9">
         <v>38671</v>
       </c>
       <c r="C167" s="10">
@@ -3554,16 +3551,16 @@
       <c r="D167" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E167" s="6">
+      <c r="E167" s="11">
         <v>336753</v>
       </c>
-      <c r="H167" s="3"/>
+      <c r="H167" s="13"/>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A168" s="1">
+      <c r="A168" s="8">
         <v>38657</v>
       </c>
-      <c r="B168" s="4">
+      <c r="B168" s="9">
         <v>38699</v>
       </c>
       <c r="C168" s="10">
@@ -3572,16 +3569,16 @@
       <c r="D168" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E168" s="6">
+      <c r="E168" s="11">
         <v>339719</v>
       </c>
-      <c r="H168" s="3"/>
+      <c r="H168" s="13"/>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A169" s="1">
+      <c r="A169" s="8">
         <v>38687</v>
       </c>
-      <c r="B169" s="4">
+      <c r="B169" s="9">
         <v>38730</v>
       </c>
       <c r="C169" s="10">
@@ -3590,16 +3587,16 @@
       <c r="D169" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E169" s="6">
+      <c r="E169" s="11">
         <v>339895</v>
       </c>
-      <c r="H169" s="3"/>
+      <c r="H169" s="13"/>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A170" s="1">
+      <c r="A170" s="8">
         <v>38718</v>
       </c>
-      <c r="B170" s="4">
+      <c r="B170" s="9">
         <v>38762</v>
       </c>
       <c r="C170" s="10">
@@ -3608,16 +3605,16 @@
       <c r="D170" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E170" s="6">
+      <c r="E170" s="11">
         <v>349664</v>
       </c>
-      <c r="H170" s="3"/>
+      <c r="H170" s="13"/>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A171" s="1">
+      <c r="A171" s="8">
         <v>38749</v>
       </c>
-      <c r="B171" s="4">
+      <c r="B171" s="9">
         <v>38790</v>
       </c>
       <c r="C171" s="10">
@@ -3626,16 +3623,16 @@
       <c r="D171" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E171" s="6">
+      <c r="E171" s="11">
         <v>347021</v>
       </c>
-      <c r="H171" s="3"/>
+      <c r="H171" s="13"/>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A172" s="1">
+      <c r="A172" s="8">
         <v>38777</v>
       </c>
-      <c r="B172" s="4">
+      <c r="B172" s="9">
         <v>38820</v>
       </c>
       <c r="C172" s="10">
@@ -3644,16 +3641,16 @@
       <c r="D172" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E172" s="6">
+      <c r="E172" s="11">
         <v>348357</v>
       </c>
-      <c r="H172" s="3"/>
+      <c r="H172" s="13"/>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A173" s="1">
+      <c r="A173" s="8">
         <v>38808</v>
       </c>
-      <c r="B173" s="4">
+      <c r="B173" s="9">
         <v>38848</v>
       </c>
       <c r="C173" s="10">
@@ -3662,16 +3659,16 @@
       <c r="D173" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E173" s="6">
+      <c r="E173" s="11">
         <v>350072</v>
       </c>
-      <c r="H173" s="3"/>
+      <c r="H173" s="13"/>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A174" s="1">
+      <c r="A174" s="8">
         <v>38838</v>
       </c>
-      <c r="B174" s="4">
+      <c r="B174" s="9">
         <v>38881</v>
       </c>
       <c r="C174" s="10">
@@ -3680,16 +3677,16 @@
       <c r="D174" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E174" s="6">
+      <c r="E174" s="11">
         <v>348889</v>
       </c>
-      <c r="H174" s="3"/>
+      <c r="H174" s="13"/>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A175" s="1">
+      <c r="A175" s="8">
         <v>38869</v>
       </c>
-      <c r="B175" s="4">
+      <c r="B175" s="9">
         <v>38912</v>
       </c>
       <c r="C175" s="10">
@@ -3698,16 +3695,16 @@
       <c r="D175" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E175" s="6">
+      <c r="E175" s="11">
         <v>350795</v>
       </c>
-      <c r="H175" s="3"/>
+      <c r="H175" s="13"/>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A176" s="1">
+      <c r="A176" s="8">
         <v>38899</v>
       </c>
-      <c r="B176" s="4">
+      <c r="B176" s="9">
         <v>38940</v>
       </c>
       <c r="C176" s="10">
@@ -3716,16 +3713,16 @@
       <c r="D176" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E176" s="6">
+      <c r="E176" s="11">
         <v>351916</v>
       </c>
-      <c r="H176" s="3"/>
+      <c r="H176" s="13"/>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A177" s="1">
+      <c r="A177" s="8">
         <v>38930</v>
       </c>
-      <c r="B177" s="4">
+      <c r="B177" s="9">
         <v>38974</v>
       </c>
       <c r="C177" s="10">
@@ -3734,16 +3731,16 @@
       <c r="D177" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E177" s="6">
+      <c r="E177" s="11">
         <v>353285</v>
       </c>
-      <c r="H177" s="3"/>
+      <c r="H177" s="13"/>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A178" s="1">
+      <c r="A178" s="8">
         <v>38961</v>
       </c>
-      <c r="B178" s="4">
+      <c r="B178" s="9">
         <v>39003</v>
       </c>
       <c r="C178" s="10">
@@ -3752,16 +3749,16 @@
       <c r="D178" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E178" s="6">
+      <c r="E178" s="11">
         <v>351240</v>
       </c>
-      <c r="H178" s="3"/>
+      <c r="H178" s="13"/>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A179" s="1">
+      <c r="A179" s="8">
         <v>38991</v>
       </c>
-      <c r="B179" s="4">
+      <c r="B179" s="9">
         <v>39035</v>
       </c>
       <c r="C179" s="10">
@@ -3770,16 +3767,16 @@
       <c r="D179" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E179" s="6">
+      <c r="E179" s="11">
         <v>351035</v>
       </c>
-      <c r="H179" s="3"/>
+      <c r="H179" s="13"/>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A180" s="1">
+      <c r="A180" s="8">
         <v>39022</v>
       </c>
-      <c r="B180" s="4">
+      <c r="B180" s="9">
         <v>39064</v>
       </c>
       <c r="C180" s="10">
@@ -3788,16 +3785,16 @@
       <c r="D180" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E180" s="6">
+      <c r="E180" s="11">
         <v>352116</v>
       </c>
-      <c r="H180" s="3"/>
+      <c r="H180" s="13"/>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A181" s="1">
+      <c r="A181" s="8">
         <v>39052</v>
       </c>
-      <c r="B181" s="4">
+      <c r="B181" s="9">
         <v>39094</v>
       </c>
       <c r="C181" s="10">
@@ -3806,16 +3803,16 @@
       <c r="D181" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E181" s="6">
+      <c r="E181" s="11">
         <v>356367</v>
       </c>
-      <c r="H181" s="3"/>
+      <c r="H181" s="13"/>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A182" s="1">
+      <c r="A182" s="8">
         <v>39083</v>
       </c>
-      <c r="B182" s="4">
+      <c r="B182" s="9">
         <v>39127</v>
       </c>
       <c r="C182" s="10">
@@ -3824,16 +3821,16 @@
       <c r="D182" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E182" s="6">
+      <c r="E182" s="11">
         <v>355792</v>
       </c>
-      <c r="H182" s="3"/>
+      <c r="H182" s="13"/>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A183" s="1">
+      <c r="A183" s="8">
         <v>39114</v>
       </c>
-      <c r="B183" s="4">
+      <c r="B183" s="9">
         <v>39154</v>
       </c>
       <c r="C183" s="10">
@@ -3842,16 +3839,16 @@
       <c r="D183" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E183" s="6">
+      <c r="E183" s="11">
         <v>356545</v>
       </c>
-      <c r="H183" s="3"/>
+      <c r="H183" s="13"/>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A184" s="1">
+      <c r="A184" s="8">
         <v>39142</v>
       </c>
-      <c r="B184" s="4">
+      <c r="B184" s="9">
         <v>39188</v>
       </c>
       <c r="C184" s="10">
@@ -3860,16 +3857,16 @@
       <c r="D184" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E184" s="6">
+      <c r="E184" s="11">
         <v>359415</v>
       </c>
-      <c r="H184" s="3"/>
+      <c r="H184" s="13"/>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A185" s="1">
+      <c r="A185" s="8">
         <v>39173</v>
       </c>
-      <c r="B185" s="4">
+      <c r="B185" s="9">
         <v>39213</v>
       </c>
       <c r="C185" s="10">
@@ -3878,16 +3875,16 @@
       <c r="D185" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E185" s="6">
+      <c r="E185" s="11">
         <v>358562</v>
       </c>
-      <c r="H185" s="3"/>
+      <c r="H185" s="13"/>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A186" s="1">
+      <c r="A186" s="8">
         <v>39203</v>
       </c>
-      <c r="B186" s="4">
+      <c r="B186" s="9">
         <v>39246</v>
       </c>
       <c r="C186" s="10">
@@ -3896,16 +3893,16 @@
       <c r="D186" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E186" s="6">
+      <c r="E186" s="11">
         <v>363085</v>
       </c>
-      <c r="H186" s="3"/>
+      <c r="H186" s="13"/>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A187" s="1">
+      <c r="A187" s="8">
         <v>39234</v>
       </c>
-      <c r="B187" s="4">
+      <c r="B187" s="9">
         <v>39276</v>
       </c>
       <c r="C187" s="10">
@@ -3914,16 +3911,16 @@
       <c r="D187" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E187" s="6">
+      <c r="E187" s="11">
         <v>360234</v>
       </c>
-      <c r="H187" s="3"/>
+      <c r="H187" s="13"/>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A188" s="1">
+      <c r="A188" s="8">
         <v>39264</v>
       </c>
-      <c r="B188" s="4">
+      <c r="B188" s="9">
         <v>39307</v>
       </c>
       <c r="C188" s="10">
@@ -3932,16 +3929,16 @@
       <c r="D188" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E188" s="6">
+      <c r="E188" s="11">
         <v>361770</v>
       </c>
-      <c r="H188" s="3"/>
+      <c r="H188" s="13"/>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A189" s="1">
+      <c r="A189" s="8">
         <v>39295</v>
       </c>
-      <c r="B189" s="4">
+      <c r="B189" s="9">
         <v>39339</v>
       </c>
       <c r="C189" s="10">
@@ -3950,16 +3947,16 @@
       <c r="D189" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E189" s="6">
+      <c r="E189" s="11">
         <v>363676</v>
       </c>
-      <c r="H189" s="3"/>
+      <c r="H189" s="13"/>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A190" s="1">
+      <c r="A190" s="8">
         <v>39326</v>
       </c>
-      <c r="B190" s="4">
+      <c r="B190" s="9">
         <v>39367</v>
       </c>
       <c r="C190" s="10">
@@ -3968,16 +3965,16 @@
       <c r="D190" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E190" s="6">
+      <c r="E190" s="11">
         <v>365178</v>
       </c>
-      <c r="H190" s="3"/>
+      <c r="H190" s="13"/>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A191" s="1">
+      <c r="A191" s="8">
         <v>39356</v>
       </c>
-      <c r="B191" s="4">
+      <c r="B191" s="9">
         <v>39400</v>
       </c>
       <c r="C191" s="10">
@@ -3986,16 +3983,16 @@
       <c r="D191" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E191" s="6">
+      <c r="E191" s="11">
         <v>367322</v>
       </c>
-      <c r="H191" s="3"/>
+      <c r="H191" s="13"/>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A192" s="1">
+      <c r="A192" s="8">
         <v>39387</v>
       </c>
-      <c r="B192" s="4">
+      <c r="B192" s="9">
         <v>39429</v>
       </c>
       <c r="C192" s="10">
@@ -4004,16 +4001,16 @@
       <c r="D192" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E192" s="6">
+      <c r="E192" s="11">
         <v>370776</v>
       </c>
-      <c r="H192" s="3"/>
+      <c r="H192" s="13"/>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A193" s="1">
+      <c r="A193" s="8">
         <v>39417</v>
       </c>
-      <c r="B193" s="4">
+      <c r="B193" s="9">
         <v>39462</v>
       </c>
       <c r="C193" s="10">
@@ -4022,16 +4019,16 @@
       <c r="D193" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E193" s="6">
+      <c r="E193" s="11">
         <v>366569</v>
       </c>
-      <c r="H193" s="3"/>
+      <c r="H193" s="13"/>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A194" s="1">
+      <c r="A194" s="8">
         <v>39448</v>
       </c>
-      <c r="B194" s="4">
+      <c r="B194" s="9">
         <v>39491</v>
       </c>
       <c r="C194" s="10">
@@ -4040,16 +4037,16 @@
       <c r="D194" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E194" s="6">
+      <c r="E194" s="11">
         <v>367368</v>
       </c>
-      <c r="H194" s="3"/>
+      <c r="H194" s="13"/>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A195" s="1">
+      <c r="A195" s="8">
         <v>39479</v>
       </c>
-      <c r="B195" s="4">
+      <c r="B195" s="9">
         <v>39520</v>
       </c>
       <c r="C195" s="10">
@@ -4058,16 +4055,16 @@
       <c r="D195" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E195" s="6">
+      <c r="E195" s="11">
         <v>364126</v>
       </c>
-      <c r="H195" s="3"/>
+      <c r="H195" s="13"/>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A196" s="1">
+      <c r="A196" s="8">
         <v>39508</v>
       </c>
-      <c r="B196" s="4">
+      <c r="B196" s="9">
         <v>39552</v>
       </c>
       <c r="C196" s="10">
@@ -4076,16 +4073,16 @@
       <c r="D196" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E196" s="6">
+      <c r="E196" s="11">
         <v>365164</v>
       </c>
-      <c r="H196" s="3"/>
+      <c r="H196" s="13"/>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A197" s="1">
+      <c r="A197" s="8">
         <v>39539</v>
       </c>
-      <c r="B197" s="4">
+      <c r="B197" s="9">
         <v>39581</v>
       </c>
       <c r="C197" s="10">
@@ -4094,16 +4091,16 @@
       <c r="D197" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E197" s="6">
+      <c r="E197" s="11">
         <v>364816</v>
       </c>
-      <c r="H197" s="3"/>
+      <c r="H197" s="13"/>
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A198" s="1">
+      <c r="A198" s="8">
         <v>39569</v>
       </c>
-      <c r="B198" s="4">
+      <c r="B198" s="9">
         <v>39611</v>
       </c>
       <c r="C198" s="10">
@@ -4112,16 +4109,16 @@
       <c r="D198" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E198" s="6">
+      <c r="E198" s="11">
         <v>368255</v>
       </c>
-      <c r="H198" s="3"/>
+      <c r="H198" s="13"/>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A199" s="1">
+      <c r="A199" s="8">
         <v>39600</v>
       </c>
-      <c r="B199" s="4">
+      <c r="B199" s="9">
         <v>39644</v>
       </c>
       <c r="C199" s="10">
@@ -4130,16 +4127,16 @@
       <c r="D199" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E199" s="6">
+      <c r="E199" s="11">
         <v>368926</v>
       </c>
-      <c r="H199" s="3"/>
+      <c r="H199" s="13"/>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A200" s="1">
+      <c r="A200" s="8">
         <v>39630</v>
       </c>
-      <c r="B200" s="4">
+      <c r="B200" s="9">
         <v>39673</v>
       </c>
       <c r="C200" s="10">
@@ -4148,16 +4145,16 @@
       <c r="D200" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E200" s="6">
+      <c r="E200" s="11">
         <v>367594</v>
       </c>
-      <c r="H200" s="3"/>
+      <c r="H200" s="13"/>
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A201" s="1">
+      <c r="A201" s="8">
         <v>39661</v>
       </c>
-      <c r="B201" s="4">
+      <c r="B201" s="9">
         <v>39703</v>
       </c>
       <c r="C201" s="10">
@@ -4166,16 +4163,16 @@
       <c r="D201" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E201" s="6">
+      <c r="E201" s="11">
         <v>364611</v>
       </c>
-      <c r="H201" s="3"/>
+      <c r="H201" s="13"/>
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A202" s="1">
+      <c r="A202" s="8">
         <v>39692</v>
       </c>
-      <c r="B202" s="4">
+      <c r="B202" s="9">
         <v>39736</v>
       </c>
       <c r="C202" s="10">
@@ -4184,16 +4181,16 @@
       <c r="D202" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E202" s="6">
+      <c r="E202" s="11">
         <v>358991</v>
       </c>
-      <c r="H202" s="3"/>
+      <c r="H202" s="13"/>
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A203" s="1">
+      <c r="A203" s="8">
         <v>39722</v>
       </c>
-      <c r="B203" s="4">
+      <c r="B203" s="9">
         <v>39766</v>
       </c>
       <c r="C203" s="10">
@@ -4202,16 +4199,16 @@
       <c r="D203" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E203" s="6">
+      <c r="E203" s="11">
         <v>346137</v>
       </c>
-      <c r="H203" s="3"/>
+      <c r="H203" s="13"/>
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A204" s="1">
+      <c r="A204" s="8">
         <v>39753</v>
       </c>
-      <c r="B204" s="4">
+      <c r="B204" s="9">
         <v>39794</v>
       </c>
       <c r="C204" s="10">
@@ -4220,16 +4217,16 @@
       <c r="D204" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E204" s="6">
+      <c r="E204" s="11">
         <v>332498</v>
       </c>
-      <c r="H204" s="3"/>
+      <c r="H204" s="13"/>
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A205" s="1">
+      <c r="A205" s="8">
         <v>39783</v>
       </c>
-      <c r="B205" s="4">
+      <c r="B205" s="9">
         <v>39827</v>
       </c>
       <c r="C205" s="10">
@@ -4238,16 +4235,16 @@
       <c r="D205" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E205" s="6">
+      <c r="E205" s="11">
         <v>324767</v>
       </c>
-      <c r="H205" s="3"/>
+      <c r="H205" s="13"/>
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A206" s="1">
+      <c r="A206" s="8">
         <v>39814</v>
       </c>
-      <c r="B206" s="4">
+      <c r="B206" s="9">
         <v>39856</v>
       </c>
       <c r="C206" s="10">
@@ -4256,16 +4253,16 @@
       <c r="D206" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E206" s="6">
+      <c r="E206" s="11">
         <v>329787</v>
       </c>
-      <c r="H206" s="3"/>
+      <c r="H206" s="13"/>
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A207" s="1">
+      <c r="A207" s="8">
         <v>39845</v>
       </c>
-      <c r="B207" s="4">
+      <c r="B207" s="9">
         <v>39884</v>
       </c>
       <c r="C207" s="10">
@@ -4274,16 +4271,16 @@
       <c r="D207" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E207" s="6">
+      <c r="E207" s="11">
         <v>328376</v>
       </c>
-      <c r="H207" s="3"/>
+      <c r="H207" s="13"/>
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A208" s="1">
+      <c r="A208" s="8">
         <v>39873</v>
       </c>
-      <c r="B208" s="4">
+      <c r="B208" s="9">
         <v>39917</v>
       </c>
       <c r="C208" s="10">
@@ -4292,16 +4289,16 @@
       <c r="D208" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E208" s="6">
+      <c r="E208" s="11">
         <v>322634</v>
       </c>
-      <c r="H208" s="3"/>
+      <c r="H208" s="13"/>
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A209" s="1">
+      <c r="A209" s="8">
         <v>39904</v>
       </c>
-      <c r="B209" s="4">
+      <c r="B209" s="9">
         <v>39946</v>
       </c>
       <c r="C209" s="10">
@@ -4310,16 +4307,16 @@
       <c r="D209" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E209" s="6">
+      <c r="E209" s="11">
         <v>324323</v>
       </c>
-      <c r="H209" s="3"/>
+      <c r="H209" s="13"/>
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A210" s="1">
+      <c r="A210" s="8">
         <v>39934</v>
       </c>
-      <c r="B210" s="4">
+      <c r="B210" s="9">
         <v>39975</v>
       </c>
       <c r="C210" s="10">
@@ -4328,16 +4325,16 @@
       <c r="D210" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E210" s="6">
+      <c r="E210" s="11">
         <v>327011</v>
       </c>
-      <c r="H210" s="3"/>
+      <c r="H210" s="13"/>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A211" s="1">
+      <c r="A211" s="8">
         <v>39965</v>
       </c>
-      <c r="B211" s="4">
+      <c r="B211" s="9">
         <v>40008</v>
       </c>
       <c r="C211" s="10">
@@ -4346,16 +4343,16 @@
       <c r="D211" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E211" s="6">
+      <c r="E211" s="11">
         <v>332227</v>
       </c>
-      <c r="H211" s="3"/>
+      <c r="H211" s="13"/>
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A212" s="1">
+      <c r="A212" s="8">
         <v>39995</v>
       </c>
-      <c r="B212" s="4">
+      <c r="B212" s="9">
         <v>40038</v>
       </c>
       <c r="C212" s="10">
@@ -4364,16 +4361,16 @@
       <c r="D212" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E212" s="6">
+      <c r="E212" s="11">
         <v>333670</v>
       </c>
-      <c r="H212" s="3"/>
+      <c r="H212" s="13"/>
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A213" s="1">
+      <c r="A213" s="8">
         <v>40026</v>
       </c>
-      <c r="B213" s="4">
+      <c r="B213" s="9">
         <v>40071</v>
       </c>
       <c r="C213" s="10">
@@ -4382,16 +4379,16 @@
       <c r="D213" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E213" s="6">
+      <c r="E213" s="11">
         <v>339586</v>
       </c>
-      <c r="H213" s="3"/>
+      <c r="H213" s="13"/>
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A214" s="1">
+      <c r="A214" s="8">
         <v>40057</v>
       </c>
-      <c r="B214" s="4">
+      <c r="B214" s="9">
         <v>40100</v>
       </c>
       <c r="C214" s="10">
@@ -4400,16 +4397,16 @@
       <c r="D214" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E214" s="6">
+      <c r="E214" s="11">
         <v>330998</v>
       </c>
-      <c r="H214" s="3"/>
+      <c r="H214" s="13"/>
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A215" s="1">
+      <c r="A215" s="8">
         <v>40087</v>
       </c>
-      <c r="B215" s="4">
+      <c r="B215" s="9">
         <v>40133</v>
       </c>
       <c r="C215" s="10">
@@ -4418,16 +4415,16 @@
       <c r="D215" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E215" s="6">
+      <c r="E215" s="11">
         <v>334595</v>
       </c>
-      <c r="H215" s="3"/>
+      <c r="H215" s="13"/>
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A216" s="1">
+      <c r="A216" s="8">
         <v>40118</v>
       </c>
-      <c r="B216" s="4">
+      <c r="B216" s="9">
         <v>40158</v>
       </c>
       <c r="C216" s="10">
@@ -4436,16 +4433,16 @@
       <c r="D216" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E216" s="6">
+      <c r="E216" s="11">
         <v>337321</v>
       </c>
-      <c r="H216" s="3"/>
+      <c r="H216" s="13"/>
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A217" s="1">
+      <c r="A217" s="8">
         <v>40148</v>
       </c>
-      <c r="B217" s="4">
+      <c r="B217" s="9">
         <v>40192</v>
       </c>
       <c r="C217" s="10">
@@ -4454,16 +4451,16 @@
       <c r="D217" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E217" s="6">
+      <c r="E217" s="11">
         <v>338736</v>
       </c>
-      <c r="H217" s="3"/>
+      <c r="H217" s="13"/>
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A218" s="1">
+      <c r="A218" s="8">
         <v>40179</v>
       </c>
-      <c r="B218" s="4">
+      <c r="B218" s="9">
         <v>40221</v>
       </c>
       <c r="C218" s="10">
@@ -4472,16 +4469,16 @@
       <c r="D218" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E218" s="6">
+      <c r="E218" s="11">
         <v>339093</v>
       </c>
-      <c r="H218" s="3"/>
+      <c r="H218" s="13"/>
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A219" s="1">
+      <c r="A219" s="8">
         <v>40210</v>
       </c>
-      <c r="B219" s="4">
+      <c r="B219" s="9">
         <v>40249</v>
       </c>
       <c r="C219" s="10">
@@ -4490,16 +4487,16 @@
       <c r="D219" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E219" s="6">
+      <c r="E219" s="11">
         <v>339580</v>
       </c>
-      <c r="H219" s="3"/>
+      <c r="H219" s="13"/>
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A220" s="1">
+      <c r="A220" s="8">
         <v>40238</v>
       </c>
-      <c r="B220" s="4">
+      <c r="B220" s="9">
         <v>40282</v>
       </c>
       <c r="C220" s="10">
@@ -4508,16 +4505,16 @@
       <c r="D220" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E220" s="6">
+      <c r="E220" s="11">
         <v>346974</v>
       </c>
-      <c r="H220" s="3"/>
+      <c r="H220" s="13"/>
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A221" s="1">
+      <c r="A221" s="8">
         <v>40269</v>
       </c>
-      <c r="B221" s="4">
+      <c r="B221" s="9">
         <v>40312</v>
       </c>
       <c r="C221" s="10">
@@ -4526,16 +4523,16 @@
       <c r="D221" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E221" s="6">
+      <c r="E221" s="11">
         <v>349869</v>
       </c>
-      <c r="H221" s="3"/>
+      <c r="H221" s="13"/>
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A222" s="1">
+      <c r="A222" s="8">
         <v>40299</v>
       </c>
-      <c r="B222" s="4">
+      <c r="B222" s="9">
         <v>40340</v>
       </c>
       <c r="C222" s="10">
@@ -4544,16 +4541,16 @@
       <c r="D222" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E222" s="6">
+      <c r="E222" s="11">
         <v>346858</v>
       </c>
-      <c r="H222" s="3"/>
+      <c r="H222" s="13"/>
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A223" s="1">
+      <c r="A223" s="8">
         <v>40330</v>
       </c>
-      <c r="B223" s="4">
+      <c r="B223" s="9">
         <v>40373</v>
       </c>
       <c r="C223" s="10">
@@ -4562,16 +4559,16 @@
       <c r="D223" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E223" s="6">
+      <c r="E223" s="11">
         <v>346516</v>
       </c>
-      <c r="H223" s="3"/>
+      <c r="H223" s="13"/>
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A224" s="1">
+      <c r="A224" s="8">
         <v>40360</v>
       </c>
-      <c r="B224" s="4">
+      <c r="B224" s="9">
         <v>40403</v>
       </c>
       <c r="C224" s="10">
@@ -4580,16 +4577,16 @@
       <c r="D224" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E224" s="6">
+      <c r="E224" s="11">
         <v>347612</v>
       </c>
-      <c r="H224" s="3"/>
+      <c r="H224" s="13"/>
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A225" s="1">
+      <c r="A225" s="8">
         <v>40391</v>
       </c>
-      <c r="B225" s="4">
+      <c r="B225" s="9">
         <v>40435</v>
       </c>
       <c r="C225" s="10">
@@ -4598,16 +4595,16 @@
       <c r="D225" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E225" s="6">
+      <c r="E225" s="11">
         <v>349188</v>
       </c>
-      <c r="H225" s="3"/>
+      <c r="H225" s="13"/>
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A226" s="1">
+      <c r="A226" s="8">
         <v>40422</v>
       </c>
-      <c r="B226" s="4">
+      <c r="B226" s="9">
         <v>40466</v>
       </c>
       <c r="C226" s="10">
@@ -4616,16 +4613,16 @@
       <c r="D226" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E226" s="6">
+      <c r="E226" s="11">
         <v>352179</v>
       </c>
-      <c r="H226" s="3"/>
+      <c r="H226" s="13"/>
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A227" s="1">
+      <c r="A227" s="8">
         <v>40452</v>
       </c>
-      <c r="B227" s="4">
+      <c r="B227" s="9">
         <v>40497</v>
       </c>
       <c r="C227" s="10">
@@ -4634,16 +4631,16 @@
       <c r="D227" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E227" s="6">
+      <c r="E227" s="11">
         <v>356215</v>
       </c>
-      <c r="H227" s="3"/>
+      <c r="H227" s="13"/>
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A228" s="1">
+      <c r="A228" s="8">
         <v>40483</v>
       </c>
-      <c r="B228" s="4">
+      <c r="B228" s="9">
         <v>40526</v>
       </c>
       <c r="C228" s="10">
@@ -4652,16 +4649,16 @@
       <c r="D228" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E228" s="6">
+      <c r="E228" s="11">
         <v>359450</v>
       </c>
-      <c r="H228" s="3"/>
+      <c r="H228" s="13"/>
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A229" s="1">
+      <c r="A229" s="8">
         <v>40513</v>
       </c>
-      <c r="B229" s="4">
+      <c r="B229" s="9">
         <v>40557</v>
       </c>
       <c r="C229" s="10">
@@ -4670,16 +4667,16 @@
       <c r="D229" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E229" s="6">
+      <c r="E229" s="11">
         <v>361979</v>
       </c>
-      <c r="H229" s="3"/>
+      <c r="H229" s="13"/>
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A230" s="1">
+      <c r="A230" s="8">
         <v>40544</v>
       </c>
-      <c r="B230" s="4">
+      <c r="B230" s="9">
         <v>40589</v>
       </c>
       <c r="C230" s="10">
@@ -4688,16 +4685,16 @@
       <c r="D230" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E230" s="6">
+      <c r="E230" s="11">
         <v>364394</v>
       </c>
-      <c r="H230" s="3"/>
+      <c r="H230" s="13"/>
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A231" s="1">
+      <c r="A231" s="8">
         <v>40575</v>
       </c>
-      <c r="B231" s="4">
+      <c r="B231" s="9">
         <v>40613</v>
       </c>
       <c r="C231" s="10">
@@ -4706,16 +4703,16 @@
       <c r="D231" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E231" s="6">
+      <c r="E231" s="11">
         <v>367475</v>
       </c>
-      <c r="H231" s="3"/>
+      <c r="H231" s="13"/>
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A232" s="1">
+      <c r="A232" s="8">
         <v>40603</v>
       </c>
-      <c r="B232" s="4">
+      <c r="B232" s="9">
         <v>40646</v>
       </c>
       <c r="C232" s="10">
@@ -4724,16 +4721,16 @@
       <c r="D232" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E232" s="6">
+      <c r="E232" s="11">
         <v>370775</v>
       </c>
-      <c r="H232" s="3"/>
+      <c r="H232" s="13"/>
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A233" s="1">
+      <c r="A233" s="8">
         <v>40634</v>
       </c>
-      <c r="B233" s="4">
+      <c r="B233" s="9">
         <v>40675</v>
       </c>
       <c r="C233" s="10">
@@ -4742,16 +4739,16 @@
       <c r="D233" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E233" s="6">
+      <c r="E233" s="11">
         <v>372820</v>
       </c>
-      <c r="H233" s="3"/>
+      <c r="H233" s="13"/>
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A234" s="1">
+      <c r="A234" s="8">
         <v>40664</v>
       </c>
-      <c r="B234" s="4">
+      <c r="B234" s="9">
         <v>40708</v>
       </c>
       <c r="C234" s="10">
@@ -4760,16 +4757,16 @@
       <c r="D234" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E234" s="6">
+      <c r="E234" s="11">
         <v>372505</v>
       </c>
-      <c r="H234" s="3"/>
+      <c r="H234" s="13"/>
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A235" s="1">
+      <c r="A235" s="8">
         <v>40695</v>
       </c>
-      <c r="B235" s="4">
+      <c r="B235" s="9">
         <v>40738</v>
       </c>
       <c r="C235" s="10">
@@ -4778,16 +4775,16 @@
       <c r="D235" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E235" s="6">
+      <c r="E235" s="11">
         <v>375587</v>
       </c>
-      <c r="H235" s="3"/>
+      <c r="H235" s="13"/>
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A236" s="1">
+      <c r="A236" s="8">
         <v>40725</v>
       </c>
-      <c r="B236" s="4">
+      <c r="B236" s="9">
         <v>40767</v>
       </c>
       <c r="C236" s="10">
@@ -4796,16 +4793,16 @@
       <c r="D236" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E236" s="6">
+      <c r="E236" s="11">
         <v>375442</v>
       </c>
-      <c r="H236" s="3"/>
+      <c r="H236" s="13"/>
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A237" s="1">
+      <c r="A237" s="8">
         <v>40756</v>
       </c>
-      <c r="B237" s="4">
+      <c r="B237" s="9">
         <v>40800</v>
       </c>
       <c r="C237" s="10">
@@ -4814,16 +4811,16 @@
       <c r="D237" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E237" s="6">
+      <c r="E237" s="11">
         <v>375860</v>
       </c>
-      <c r="H237" s="3"/>
+      <c r="H237" s="13"/>
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A238" s="1">
+      <c r="A238" s="8">
         <v>40787</v>
       </c>
-      <c r="B238" s="4">
+      <c r="B238" s="9">
         <v>40830</v>
       </c>
       <c r="C238" s="10">
@@ -4832,16 +4829,16 @@
       <c r="D238" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E238" s="6">
+      <c r="E238" s="11">
         <v>380042</v>
       </c>
-      <c r="H238" s="3"/>
+      <c r="H238" s="13"/>
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A239" s="1">
+      <c r="A239" s="8">
         <v>40817</v>
       </c>
-      <c r="B239" s="4">
+      <c r="B239" s="9">
         <v>40862</v>
       </c>
       <c r="C239" s="10">
@@ -4850,16 +4847,16 @@
       <c r="D239" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E239" s="6">
+      <c r="E239" s="11">
         <v>382207</v>
       </c>
-      <c r="H239" s="3"/>
+      <c r="H239" s="13"/>
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A240" s="1">
+      <c r="A240" s="8">
         <v>40848</v>
       </c>
-      <c r="B240" s="4">
+      <c r="B240" s="9">
         <v>40890</v>
       </c>
       <c r="C240" s="10">
@@ -4868,16 +4865,16 @@
       <c r="D240" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E240" s="6">
+      <c r="E240" s="11">
         <v>383422</v>
       </c>
-      <c r="H240" s="3"/>
+      <c r="H240" s="13"/>
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A241" s="1">
+      <c r="A241" s="8">
         <v>40878</v>
       </c>
-      <c r="B241" s="4">
+      <c r="B241" s="9">
         <v>40920</v>
       </c>
       <c r="C241" s="10">
@@ -4886,16 +4883,16 @@
       <c r="D241" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E241" s="6">
+      <c r="E241" s="11">
         <v>383985</v>
       </c>
-      <c r="H241" s="3"/>
+      <c r="H241" s="13"/>
     </row>
     <row r="242" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A242" s="1">
+      <c r="A242" s="8">
         <v>40909</v>
       </c>
-      <c r="B242" s="4">
+      <c r="B242" s="9">
         <v>40953</v>
       </c>
       <c r="C242" s="10">
@@ -4904,16 +4901,16 @@
       <c r="D242" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E242" s="6">
+      <c r="E242" s="11">
         <v>387531</v>
       </c>
-      <c r="H242" s="3"/>
+      <c r="H242" s="13"/>
     </row>
     <row r="243" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A243" s="1">
+      <c r="A243" s="8">
         <v>40940</v>
       </c>
-      <c r="B243" s="4">
+      <c r="B243" s="9">
         <v>40981</v>
       </c>
       <c r="C243" s="10">
@@ -4922,16 +4919,16 @@
       <c r="D243" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E243" s="6">
+      <c r="E243" s="11">
         <v>392310</v>
       </c>
-      <c r="H243" s="3"/>
+      <c r="H243" s="13"/>
     </row>
     <row r="244" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A244" s="1">
+      <c r="A244" s="8">
         <v>40969</v>
       </c>
-      <c r="B244" s="4">
+      <c r="B244" s="9">
         <v>41015</v>
       </c>
       <c r="C244" s="10">
@@ -4940,16 +4937,16 @@
       <c r="D244" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E244" s="6">
+      <c r="E244" s="11">
         <v>393698</v>
       </c>
-      <c r="H244" s="3"/>
+      <c r="H244" s="13"/>
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A245" s="1">
+      <c r="A245" s="8">
         <v>41000</v>
       </c>
-      <c r="B245" s="4">
+      <c r="B245" s="9">
         <v>41044</v>
       </c>
       <c r="C245" s="10">
@@ -4958,16 +4955,16 @@
       <c r="D245" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E245" s="6">
+      <c r="E245" s="11">
         <v>392073</v>
       </c>
-      <c r="H245" s="3"/>
+      <c r="H245" s="13"/>
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A246" s="1">
+      <c r="A246" s="8">
         <v>41030</v>
       </c>
-      <c r="B246" s="4">
+      <c r="B246" s="9">
         <v>41073</v>
       </c>
       <c r="C246" s="10">
@@ -4976,16 +4973,16 @@
       <c r="D246" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E246" s="6">
+      <c r="E246" s="11">
         <v>391376</v>
       </c>
-      <c r="H246" s="3"/>
+      <c r="H246" s="13"/>
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A247" s="1">
+      <c r="A247" s="8">
         <v>41061</v>
       </c>
-      <c r="B247" s="4">
+      <c r="B247" s="9">
         <v>41106</v>
       </c>
       <c r="C247" s="10">
@@ -4994,16 +4991,16 @@
       <c r="D247" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E247" s="6">
+      <c r="E247" s="11">
         <v>387901</v>
       </c>
-      <c r="H247" s="3"/>
+      <c r="H247" s="13"/>
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A248" s="1">
+      <c r="A248" s="8">
         <v>41091</v>
       </c>
-      <c r="B248" s="4">
+      <c r="B248" s="9">
         <v>41135</v>
       </c>
       <c r="C248" s="10">
@@ -5012,16 +5009,16 @@
       <c r="D248" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E248" s="6">
+      <c r="E248" s="11">
         <v>389686</v>
       </c>
-      <c r="H248" s="3"/>
+      <c r="H248" s="13"/>
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A249" s="1">
+      <c r="A249" s="8">
         <v>41122</v>
       </c>
-      <c r="B249" s="4">
+      <c r="B249" s="9">
         <v>41166</v>
       </c>
       <c r="C249" s="10">
@@ -5030,16 +5027,16 @@
       <c r="D249" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E249" s="6">
+      <c r="E249" s="11">
         <v>394524</v>
       </c>
-      <c r="H249" s="3"/>
+      <c r="H249" s="13"/>
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A250" s="1">
+      <c r="A250" s="8">
         <v>41153</v>
       </c>
-      <c r="B250" s="4">
+      <c r="B250" s="9">
         <v>41197</v>
       </c>
       <c r="C250" s="10">
@@ -5048,16 +5045,16 @@
       <c r="D250" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E250" s="6">
+      <c r="E250" s="11">
         <v>397681</v>
       </c>
-      <c r="H250" s="3"/>
+      <c r="H250" s="13"/>
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A251" s="1">
+      <c r="A251" s="8">
         <v>41183</v>
       </c>
-      <c r="B251" s="4">
+      <c r="B251" s="9">
         <v>41227</v>
       </c>
       <c r="C251" s="10">
@@ -5066,16 +5063,16 @@
       <c r="D251" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E251" s="6">
+      <c r="E251" s="11">
         <v>397494</v>
       </c>
-      <c r="H251" s="3"/>
+      <c r="H251" s="13"/>
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A252" s="1">
+      <c r="A252" s="8">
         <v>41214</v>
       </c>
-      <c r="B252" s="4">
+      <c r="B252" s="9">
         <v>41256</v>
       </c>
       <c r="C252" s="10">
@@ -5084,16 +5081,16 @@
       <c r="D252" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E252" s="6">
+      <c r="E252" s="11">
         <v>399708</v>
       </c>
-      <c r="H252" s="3"/>
+      <c r="H252" s="13"/>
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A253" s="1">
+      <c r="A253" s="8">
         <v>41244</v>
       </c>
-      <c r="B253" s="4">
+      <c r="B253" s="9">
         <v>41289</v>
       </c>
       <c r="C253" s="10">
@@ -5102,16 +5099,16 @@
       <c r="D253" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E253" s="6">
+      <c r="E253" s="11">
         <v>401093</v>
       </c>
-      <c r="H253" s="3"/>
+      <c r="H253" s="13"/>
     </row>
     <row r="254" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A254" s="1">
+      <c r="A254" s="8">
         <v>41275</v>
       </c>
-      <c r="B254" s="4">
+      <c r="B254" s="9">
         <v>41318</v>
       </c>
       <c r="C254" s="10">
@@ -5120,16 +5117,16 @@
       <c r="D254" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E254" s="6">
+      <c r="E254" s="11">
         <v>404434</v>
       </c>
-      <c r="H254" s="3"/>
+      <c r="H254" s="13"/>
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A255" s="1">
+      <c r="A255" s="8">
         <v>41306</v>
       </c>
-      <c r="B255" s="4">
+      <c r="B255" s="9">
         <v>41346</v>
       </c>
       <c r="C255" s="10">
@@ -5138,16 +5135,16 @@
       <c r="D255" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E255" s="6">
+      <c r="E255" s="11">
         <v>409118</v>
       </c>
-      <c r="H255" s="3"/>
+      <c r="H255" s="13"/>
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A256" s="1">
+      <c r="A256" s="8">
         <v>41334</v>
       </c>
-      <c r="B256" s="4">
+      <c r="B256" s="9">
         <v>41376</v>
       </c>
       <c r="C256" s="10">
@@ -5156,16 +5153,16 @@
       <c r="D256" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E256" s="6">
+      <c r="E256" s="11">
         <v>406223</v>
       </c>
-      <c r="H256" s="3"/>
+      <c r="H256" s="13"/>
     </row>
     <row r="257" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A257" s="1">
+      <c r="A257" s="8">
         <v>41365</v>
       </c>
-      <c r="B257" s="4">
+      <c r="B257" s="9">
         <v>41407</v>
       </c>
       <c r="C257" s="10">
@@ -5174,16 +5171,16 @@
       <c r="D257" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E257" s="6">
+      <c r="E257" s="11">
         <v>404231</v>
       </c>
-      <c r="H257" s="3"/>
+      <c r="H257" s="13"/>
     </row>
     <row r="258" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A258" s="1">
+      <c r="A258" s="8">
         <v>41395</v>
       </c>
-      <c r="B258" s="4">
+      <c r="B258" s="9">
         <v>41438</v>
       </c>
       <c r="C258" s="10">
@@ -5192,16 +5189,16 @@
       <c r="D258" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E258" s="6">
+      <c r="E258" s="11">
         <v>406677</v>
       </c>
-      <c r="H258" s="3"/>
+      <c r="H258" s="13"/>
     </row>
     <row r="259" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A259" s="1">
+      <c r="A259" s="8">
         <v>41426</v>
       </c>
-      <c r="B259" s="4">
+      <c r="B259" s="9">
         <v>41470</v>
       </c>
       <c r="C259" s="10">
@@ -5210,16 +5207,16 @@
       <c r="D259" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E259" s="6">
+      <c r="E259" s="11">
         <v>407921</v>
       </c>
-      <c r="H259" s="3"/>
+      <c r="H259" s="13"/>
     </row>
     <row r="260" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A260" s="1">
+      <c r="A260" s="8">
         <v>41456</v>
       </c>
-      <c r="B260" s="4">
+      <c r="B260" s="9">
         <v>41499</v>
       </c>
       <c r="C260" s="10">
@@ -5228,16 +5225,16 @@
       <c r="D260" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E260" s="6">
+      <c r="E260" s="11">
         <v>410268</v>
       </c>
-      <c r="H260" s="3"/>
+      <c r="H260" s="13"/>
     </row>
     <row r="261" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A261" s="1">
+      <c r="A261" s="8">
         <v>41487</v>
       </c>
-      <c r="B261" s="4">
+      <c r="B261" s="9">
         <v>41530</v>
       </c>
       <c r="C261" s="10">
@@ -5246,16 +5243,16 @@
       <c r="D261" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E261" s="6">
+      <c r="E261" s="11">
         <v>409691</v>
       </c>
-      <c r="H261" s="3"/>
+      <c r="H261" s="13"/>
     </row>
     <row r="262" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A262" s="1">
+      <c r="A262" s="8">
         <v>41518</v>
       </c>
-      <c r="B262" s="4">
+      <c r="B262" s="9">
         <v>41576</v>
       </c>
       <c r="C262" s="10">
@@ -5264,16 +5261,16 @@
       <c r="D262" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E262" s="6">
+      <c r="E262" s="11">
         <v>410044</v>
       </c>
-      <c r="H262" s="3"/>
+      <c r="H262" s="13"/>
     </row>
     <row r="263" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A263" s="1">
+      <c r="A263" s="8">
         <v>41548</v>
       </c>
-      <c r="B263" s="4">
+      <c r="B263" s="9">
         <v>41598</v>
       </c>
       <c r="C263" s="10">
@@ -5282,16 +5279,16 @@
       <c r="D263" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E263" s="6">
+      <c r="E263" s="11">
         <v>411399</v>
       </c>
-      <c r="H263" s="3"/>
+      <c r="H263" s="13"/>
     </row>
     <row r="264" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A264" s="1">
+      <c r="A264" s="8">
         <v>41579</v>
       </c>
-      <c r="B264" s="4">
+      <c r="B264" s="9">
         <v>41620</v>
       </c>
       <c r="C264" s="10">
@@ -5300,16 +5297,16 @@
       <c r="D264" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E264" s="6">
+      <c r="E264" s="11">
         <v>412561</v>
       </c>
-      <c r="H264" s="3"/>
+      <c r="H264" s="13"/>
     </row>
     <row r="265" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A265" s="1">
+      <c r="A265" s="8">
         <v>41609</v>
       </c>
-      <c r="B265" s="4">
+      <c r="B265" s="9">
         <v>41653</v>
       </c>
       <c r="C265" s="10">
@@ -5318,16 +5315,16 @@
       <c r="D265" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E265" s="6">
+      <c r="E265" s="11">
         <v>414812</v>
       </c>
-      <c r="H265" s="3"/>
+      <c r="H265" s="13"/>
     </row>
     <row r="266" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A266" s="1">
+      <c r="A266" s="8">
         <v>41640</v>
       </c>
-      <c r="B266" s="4">
+      <c r="B266" s="9">
         <v>41683</v>
       </c>
       <c r="C266" s="10">
@@ -5336,16 +5333,16 @@
       <c r="D266" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E266" s="6">
+      <c r="E266" s="11">
         <v>411561</v>
       </c>
-      <c r="H266" s="3"/>
+      <c r="H266" s="13"/>
     </row>
     <row r="267" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A267" s="1">
+      <c r="A267" s="8">
         <v>41671</v>
       </c>
-      <c r="B267" s="4">
+      <c r="B267" s="9">
         <v>41711</v>
       </c>
       <c r="C267" s="10">
@@ -5354,16 +5351,16 @@
       <c r="D267" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E267" s="6">
+      <c r="E267" s="11">
         <v>416736</v>
       </c>
-      <c r="H267" s="3"/>
+      <c r="H267" s="13"/>
     </row>
     <row r="268" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A268" s="1">
+      <c r="A268" s="8">
         <v>41699</v>
       </c>
-      <c r="B268" s="4">
+      <c r="B268" s="9">
         <v>41743</v>
       </c>
       <c r="C268" s="10">
@@ -5372,16 +5369,16 @@
       <c r="D268" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E268" s="6">
+      <c r="E268" s="11">
         <v>421230</v>
       </c>
-      <c r="H268" s="3"/>
+      <c r="H268" s="13"/>
     </row>
     <row r="269" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A269" s="1">
+      <c r="A269" s="8">
         <v>41730</v>
       </c>
-      <c r="B269" s="4">
+      <c r="B269" s="9">
         <v>41772</v>
       </c>
       <c r="C269" s="10">
@@ -5390,16 +5387,16 @@
       <c r="D269" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E269" s="6">
+      <c r="E269" s="11">
         <v>425546</v>
       </c>
-      <c r="H269" s="3"/>
+      <c r="H269" s="13"/>
     </row>
     <row r="270" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A270" s="1">
+      <c r="A270" s="8">
         <v>41760</v>
       </c>
-      <c r="B270" s="4">
+      <c r="B270" s="9">
         <v>41802</v>
       </c>
       <c r="C270" s="10">
@@ -5408,16 +5405,16 @@
       <c r="D270" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E270" s="6">
+      <c r="E270" s="11">
         <v>426253</v>
       </c>
-      <c r="H270" s="3"/>
+      <c r="H270" s="13"/>
     </row>
     <row r="271" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A271" s="1">
+      <c r="A271" s="8">
         <v>41791</v>
       </c>
-      <c r="B271" s="4">
+      <c r="B271" s="9">
         <v>41835</v>
       </c>
       <c r="C271" s="10">
@@ -5426,16 +5423,16 @@
       <c r="D271" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E271" s="6">
+      <c r="E271" s="11">
         <v>427305</v>
       </c>
-      <c r="H271" s="3"/>
+      <c r="H271" s="13"/>
     </row>
     <row r="272" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A272" s="1">
+      <c r="A272" s="8">
         <v>41821</v>
       </c>
-      <c r="B272" s="4">
+      <c r="B272" s="9">
         <v>41864</v>
       </c>
       <c r="C272" s="10">
@@ -5444,16 +5441,16 @@
       <c r="D272" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E272" s="6">
+      <c r="E272" s="11">
         <v>428079</v>
       </c>
-      <c r="H272" s="3"/>
+      <c r="H272" s="13"/>
     </row>
     <row r="273" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A273" s="1">
+      <c r="A273" s="8">
         <v>41852</v>
       </c>
-      <c r="B273" s="4">
+      <c r="B273" s="9">
         <v>41894</v>
       </c>
       <c r="C273" s="10">
@@ -5462,16 +5459,16 @@
       <c r="D273" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E273" s="6">
+      <c r="E273" s="11">
         <v>431379</v>
       </c>
-      <c r="H273" s="3"/>
+      <c r="H273" s="13"/>
     </row>
     <row r="274" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A274" s="1">
+      <c r="A274" s="8">
         <v>41883</v>
       </c>
-      <c r="B274" s="4">
+      <c r="B274" s="9">
         <v>41927</v>
       </c>
       <c r="C274" s="10">
@@ -5480,16 +5477,16 @@
       <c r="D274" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E274" s="6">
+      <c r="E274" s="11">
         <v>430189</v>
       </c>
-      <c r="H274" s="3"/>
+      <c r="H274" s="13"/>
     </row>
     <row r="275" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A275" s="1">
+      <c r="A275" s="8">
         <v>41913</v>
       </c>
-      <c r="B275" s="4">
+      <c r="B275" s="9">
         <v>41957</v>
       </c>
       <c r="C275" s="10">
@@ -5498,16 +5495,16 @@
       <c r="D275" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E275" s="6">
+      <c r="E275" s="11">
         <v>431903</v>
       </c>
-      <c r="H275" s="3"/>
+      <c r="H275" s="13"/>
     </row>
     <row r="276" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A276" s="1">
+      <c r="A276" s="8">
         <v>41944</v>
       </c>
-      <c r="B276" s="4">
+      <c r="B276" s="9">
         <v>41984</v>
       </c>
       <c r="C276" s="10">
@@ -5516,16 +5513,16 @@
       <c r="D276" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E276" s="6">
+      <c r="E276" s="11">
         <v>433113</v>
       </c>
-      <c r="H276" s="3"/>
+      <c r="H276" s="13"/>
     </row>
     <row r="277" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A277" s="1">
+      <c r="A277" s="8">
         <v>41974</v>
       </c>
-      <c r="B277" s="4">
+      <c r="B277" s="9">
         <v>42018</v>
       </c>
       <c r="C277" s="10">
@@ -5534,16 +5531,16 @@
       <c r="D277" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E277" s="6">
+      <c r="E277" s="11">
         <v>430110</v>
       </c>
-      <c r="H277" s="3"/>
+      <c r="H277" s="13"/>
     </row>
     <row r="278" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A278" s="1">
+      <c r="A278" s="8">
         <v>42005</v>
       </c>
-      <c r="B278" s="4">
+      <c r="B278" s="9">
         <v>42047</v>
       </c>
       <c r="C278" s="10">
@@ -5552,16 +5549,16 @@
       <c r="D278" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E278" s="6">
+      <c r="E278" s="11">
         <v>428208</v>
       </c>
-      <c r="H278" s="3"/>
+      <c r="H278" s="13"/>
     </row>
     <row r="279" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A279" s="1">
+      <c r="A279" s="8">
         <v>42036</v>
       </c>
-      <c r="B279" s="4">
+      <c r="B279" s="9">
         <v>42075</v>
       </c>
       <c r="C279" s="10">
@@ -5570,16 +5567,16 @@
       <c r="D279" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E279" s="6">
+      <c r="E279" s="11">
         <v>427119</v>
       </c>
-      <c r="H279" s="3"/>
+      <c r="H279" s="13"/>
     </row>
     <row r="280" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A280" s="1">
+      <c r="A280" s="8">
         <v>42064</v>
       </c>
-      <c r="B280" s="4">
+      <c r="B280" s="9">
         <v>42108</v>
       </c>
       <c r="C280" s="10">
@@ -5588,16 +5585,16 @@
       <c r="D280" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E280" s="6">
+      <c r="E280" s="11">
         <v>433647</v>
       </c>
-      <c r="H280" s="3"/>
+      <c r="H280" s="13"/>
     </row>
     <row r="281" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A281" s="1">
+      <c r="A281" s="8">
         <v>42095</v>
       </c>
-      <c r="B281" s="4">
+      <c r="B281" s="9">
         <v>42137</v>
       </c>
       <c r="C281" s="10">
@@ -5606,16 +5603,16 @@
       <c r="D281" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E281" s="6">
+      <c r="E281" s="11">
         <v>434470</v>
       </c>
-      <c r="H281" s="3"/>
+      <c r="H281" s="13"/>
     </row>
     <row r="282" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A282" s="1">
+      <c r="A282" s="8">
         <v>42125</v>
       </c>
-      <c r="B282" s="4">
+      <c r="B282" s="9">
         <v>42166</v>
       </c>
       <c r="C282" s="10">
@@ -5624,16 +5621,16 @@
       <c r="D282" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E282" s="6">
+      <c r="E282" s="11">
         <v>437865</v>
       </c>
-      <c r="H282" s="3"/>
+      <c r="H282" s="13"/>
     </row>
     <row r="283" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A283" s="1">
+      <c r="A283" s="8">
         <v>42156</v>
       </c>
-      <c r="B283" s="4">
+      <c r="B283" s="9">
         <v>42199</v>
       </c>
       <c r="C283" s="10">
@@ -5642,16 +5639,16 @@
       <c r="D283" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E283" s="6">
+      <c r="E283" s="11">
         <v>437951</v>
       </c>
-      <c r="H283" s="3"/>
+      <c r="H283" s="13"/>
     </row>
     <row r="284" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A284" s="1">
+      <c r="A284" s="8">
         <v>42186</v>
       </c>
-      <c r="B284" s="4">
+      <c r="B284" s="9">
         <v>42229</v>
       </c>
       <c r="C284" s="10">
@@ -5660,16 +5657,16 @@
       <c r="D284" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E284" s="6">
+      <c r="E284" s="11">
         <v>441942</v>
       </c>
-      <c r="H284" s="3"/>
+      <c r="H284" s="13"/>
     </row>
     <row r="285" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A285" s="1">
+      <c r="A285" s="8">
         <v>42217</v>
       </c>
-      <c r="B285" s="4">
+      <c r="B285" s="9">
         <v>42262</v>
       </c>
       <c r="C285" s="10">
@@ -5678,16 +5675,16 @@
       <c r="D285" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E285" s="6">
+      <c r="E285" s="11">
         <v>441849</v>
       </c>
-      <c r="H285" s="3"/>
+      <c r="H285" s="13"/>
     </row>
     <row r="286" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A286" s="1">
+      <c r="A286" s="8">
         <v>42248</v>
       </c>
-      <c r="B286" s="4">
+      <c r="B286" s="9">
         <v>42291</v>
       </c>
       <c r="C286" s="10">
@@ -5696,16 +5693,16 @@
       <c r="D286" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E286" s="6">
+      <c r="E286" s="11">
         <v>439867</v>
       </c>
-      <c r="H286" s="3"/>
+      <c r="H286" s="13"/>
     </row>
     <row r="287" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A287" s="1">
+      <c r="A287" s="8">
         <v>42278</v>
       </c>
-      <c r="B287" s="4">
+      <c r="B287" s="9">
         <v>42321</v>
       </c>
       <c r="C287" s="10">
@@ -5714,16 +5711,16 @@
       <c r="D287" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E287" s="6">
+      <c r="E287" s="11">
         <v>438693</v>
       </c>
-      <c r="H287" s="3"/>
+      <c r="H287" s="13"/>
     </row>
     <row r="288" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A288" s="1">
+      <c r="A288" s="8">
         <v>42309</v>
       </c>
-      <c r="B288" s="4">
+      <c r="B288" s="9">
         <v>42349</v>
       </c>
       <c r="C288" s="10">
@@ -5732,16 +5729,16 @@
       <c r="D288" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E288" s="6">
+      <c r="E288" s="11">
         <v>440303</v>
       </c>
-      <c r="H288" s="3"/>
+      <c r="H288" s="13"/>
     </row>
     <row r="289" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A289" s="1">
+      <c r="A289" s="8">
         <v>42339</v>
       </c>
-      <c r="B289" s="4">
+      <c r="B289" s="9">
         <v>42384</v>
       </c>
       <c r="C289" s="10">
@@ -5750,16 +5747,16 @@
       <c r="D289" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E289" s="6">
+      <c r="E289" s="11">
         <v>442149</v>
       </c>
-      <c r="H289" s="3"/>
+      <c r="H289" s="13"/>
     </row>
     <row r="290" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A290" s="1">
+      <c r="A290" s="8">
         <v>42370</v>
       </c>
-      <c r="B290" s="4">
+      <c r="B290" s="9">
         <v>42412</v>
       </c>
       <c r="C290" s="10">
@@ -5768,16 +5765,16 @@
       <c r="D290" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E290" s="6">
+      <c r="E290" s="11">
         <v>439466</v>
       </c>
-      <c r="H290" s="3"/>
+      <c r="H290" s="13"/>
     </row>
     <row r="291" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A291" s="1">
+      <c r="A291" s="8">
         <v>42401</v>
       </c>
-      <c r="B291" s="4">
+      <c r="B291" s="9">
         <v>42444</v>
       </c>
       <c r="C291" s="10">
@@ -5786,16 +5783,16 @@
       <c r="D291" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E291" s="6">
+      <c r="E291" s="11">
         <v>443117</v>
       </c>
-      <c r="H291" s="3"/>
+      <c r="H291" s="13"/>
     </row>
     <row r="292" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A292" s="1">
+      <c r="A292" s="8">
         <v>42430</v>
       </c>
-      <c r="B292" s="4">
+      <c r="B292" s="9">
         <v>42473</v>
       </c>
       <c r="C292" s="10">
@@ -5804,16 +5801,16 @@
       <c r="D292" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E292" s="6">
+      <c r="E292" s="11">
         <v>441856</v>
       </c>
-      <c r="H292" s="3"/>
+      <c r="H292" s="13"/>
     </row>
     <row r="293" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A293" s="1">
+      <c r="A293" s="8">
         <v>42461</v>
       </c>
-      <c r="B293" s="4">
+      <c r="B293" s="9">
         <v>42503</v>
       </c>
       <c r="C293" s="10">
@@ -5822,16 +5819,16 @@
       <c r="D293" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E293" s="6">
+      <c r="E293" s="11">
         <v>444254</v>
       </c>
-      <c r="H293" s="3"/>
+      <c r="H293" s="13"/>
     </row>
     <row r="294" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A294" s="1">
+      <c r="A294" s="8">
         <v>42491</v>
       </c>
-      <c r="B294" s="4">
+      <c r="B294" s="9">
         <v>42535</v>
       </c>
       <c r="C294" s="10">
@@ -5840,16 +5837,16 @@
       <c r="D294" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E294" s="6">
+      <c r="E294" s="11">
         <v>445490</v>
       </c>
-      <c r="H294" s="3"/>
+      <c r="H294" s="13"/>
     </row>
     <row r="295" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A295" s="1">
+      <c r="A295" s="8">
         <v>42522</v>
       </c>
-      <c r="B295" s="4">
+      <c r="B295" s="9">
         <v>42566</v>
       </c>
       <c r="C295" s="10">
@@ -5858,16 +5855,16 @@
       <c r="D295" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E295" s="6">
+      <c r="E295" s="11">
         <v>450237</v>
       </c>
-      <c r="H295" s="3"/>
+      <c r="H295" s="13"/>
     </row>
     <row r="296" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A296" s="1">
+      <c r="A296" s="8">
         <v>42552</v>
       </c>
-      <c r="B296" s="4">
+      <c r="B296" s="9">
         <v>42594</v>
       </c>
       <c r="C296" s="10">
@@ -5876,16 +5873,16 @@
       <c r="D296" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E296" s="6">
+      <c r="E296" s="11">
         <v>449789</v>
       </c>
-      <c r="H296" s="3"/>
+      <c r="H296" s="13"/>
     </row>
     <row r="297" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A297" s="1">
+      <c r="A297" s="8">
         <v>42583</v>
       </c>
-      <c r="B297" s="4">
+      <c r="B297" s="9">
         <v>42628</v>
       </c>
       <c r="C297" s="10">
@@ -5894,16 +5891,16 @@
       <c r="D297" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E297" s="6">
+      <c r="E297" s="11">
         <v>449946</v>
       </c>
-      <c r="H297" s="3"/>
+      <c r="H297" s="13"/>
     </row>
     <row r="298" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A298" s="1">
+      <c r="A298" s="8">
         <v>42614</v>
       </c>
-      <c r="B298" s="4">
+      <c r="B298" s="9">
         <v>42657</v>
       </c>
       <c r="C298" s="10">
@@ -5912,16 +5909,16 @@
       <c r="D298" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E298" s="6">
+      <c r="E298" s="11">
         <v>453056</v>
       </c>
-      <c r="H298" s="3"/>
+      <c r="H298" s="13"/>
     </row>
     <row r="299" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A299" s="1">
+      <c r="A299" s="8">
         <v>42644</v>
       </c>
-      <c r="B299" s="4">
+      <c r="B299" s="9">
         <v>42689</v>
       </c>
       <c r="C299" s="10">
@@ -5930,16 +5927,16 @@
       <c r="D299" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E299" s="6">
+      <c r="E299" s="11">
         <v>453847</v>
       </c>
-      <c r="H299" s="3"/>
+      <c r="H299" s="13"/>
     </row>
     <row r="300" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A300" s="1">
+      <c r="A300" s="8">
         <v>42675</v>
       </c>
-      <c r="B300" s="4">
+      <c r="B300" s="9">
         <v>42718</v>
       </c>
       <c r="C300" s="10">
@@ -5948,16 +5945,16 @@
       <c r="D300" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E300" s="6">
+      <c r="E300" s="11">
         <v>453892</v>
       </c>
-      <c r="H300" s="3"/>
+      <c r="H300" s="13"/>
     </row>
     <row r="301" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A301" s="1">
+      <c r="A301" s="8">
         <v>42705</v>
       </c>
-      <c r="B301" s="4">
+      <c r="B301" s="9">
         <v>42748</v>
       </c>
       <c r="C301" s="10">
@@ -5966,16 +5963,16 @@
       <c r="D301" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E301" s="6">
+      <c r="E301" s="11">
         <v>459305</v>
       </c>
-      <c r="H301" s="3"/>
+      <c r="H301" s="13"/>
     </row>
     <row r="302" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A302" s="1">
+      <c r="A302" s="8">
         <v>42736</v>
       </c>
-      <c r="B302" s="4">
+      <c r="B302" s="9">
         <v>42781</v>
       </c>
       <c r="C302" s="10">
@@ -5984,16 +5981,16 @@
       <c r="D302" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E302" s="6">
+      <c r="E302" s="11">
         <v>464412</v>
       </c>
-      <c r="H302" s="3"/>
+      <c r="H302" s="13"/>
     </row>
     <row r="303" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A303" s="1">
+      <c r="A303" s="8">
         <v>42767</v>
       </c>
-      <c r="B303" s="4">
+      <c r="B303" s="9">
         <v>42809</v>
       </c>
       <c r="C303" s="10">
@@ -6002,16 +5999,16 @@
       <c r="D303" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E303" s="6">
+      <c r="E303" s="11">
         <v>464284</v>
       </c>
-      <c r="H303" s="3"/>
+      <c r="H303" s="13"/>
     </row>
     <row r="304" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A304" s="1">
+      <c r="A304" s="8">
         <v>42795</v>
       </c>
-      <c r="B304" s="4">
+      <c r="B304" s="9">
         <v>42839</v>
       </c>
       <c r="C304" s="10">
@@ -6020,16 +6017,16 @@
       <c r="D304" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E304" s="6">
+      <c r="E304" s="11">
         <v>463674</v>
       </c>
-      <c r="H304" s="3"/>
+      <c r="H304" s="13"/>
     </row>
     <row r="305" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A305" s="1">
+      <c r="A305" s="8">
         <v>42826</v>
       </c>
-      <c r="B305" s="4">
+      <c r="B305" s="9">
         <v>42867</v>
       </c>
       <c r="C305" s="10">
@@ -6038,16 +6035,16 @@
       <c r="D305" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E305" s="6">
+      <c r="E305" s="11">
         <v>465276</v>
       </c>
-      <c r="H305" s="3"/>
+      <c r="H305" s="13"/>
     </row>
     <row r="306" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A306" s="1">
+      <c r="A306" s="8">
         <v>42856</v>
       </c>
-      <c r="B306" s="4">
+      <c r="B306" s="9">
         <v>42900</v>
       </c>
       <c r="C306" s="10">
@@ -6056,16 +6053,16 @@
       <c r="D306" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E306" s="6">
+      <c r="E306" s="11">
         <v>462754</v>
       </c>
-      <c r="H306" s="3"/>
+      <c r="H306" s="13"/>
     </row>
     <row r="307" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A307" s="1">
+      <c r="A307" s="8">
         <v>42887</v>
       </c>
-      <c r="B307" s="4">
+      <c r="B307" s="9">
         <v>42930</v>
       </c>
       <c r="C307" s="10">
@@ -6074,16 +6071,16 @@
       <c r="D307" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E307" s="6">
+      <c r="E307" s="11">
         <v>465130</v>
       </c>
-      <c r="H307" s="3"/>
+      <c r="H307" s="13"/>
     </row>
     <row r="308" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A308" s="1">
+      <c r="A308" s="8">
         <v>42917</v>
       </c>
-      <c r="B308" s="4">
+      <c r="B308" s="9">
         <v>42962</v>
       </c>
       <c r="C308" s="10">
@@ -6092,16 +6089,16 @@
       <c r="D308" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E308" s="6">
+      <c r="E308" s="11">
         <v>465089</v>
       </c>
-      <c r="H308" s="3"/>
+      <c r="H308" s="13"/>
     </row>
     <row r="309" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A309" s="1">
+      <c r="A309" s="8">
         <v>42948</v>
       </c>
-      <c r="B309" s="4">
+      <c r="B309" s="9">
         <v>42993</v>
       </c>
       <c r="C309" s="10">
@@ -6110,16 +6107,16 @@
       <c r="D309" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E309" s="6">
+      <c r="E309" s="11">
         <v>466020</v>
       </c>
-      <c r="H309" s="3"/>
+      <c r="H309" s="13"/>
     </row>
     <row r="310" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A310" s="1">
+      <c r="A310" s="8">
         <v>42979</v>
       </c>
-      <c r="B310" s="4">
+      <c r="B310" s="9">
         <v>43021</v>
       </c>
       <c r="C310" s="10">
@@ -6128,16 +6125,16 @@
       <c r="D310" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E310" s="6">
+      <c r="E310" s="11">
         <v>475724</v>
       </c>
-      <c r="H310" s="3"/>
+      <c r="H310" s="13"/>
     </row>
     <row r="311" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A311" s="1">
+      <c r="A311" s="8">
         <v>43009</v>
       </c>
-      <c r="B311" s="4">
+      <c r="B311" s="9">
         <v>43054</v>
       </c>
       <c r="C311" s="10">
@@ -6146,16 +6143,16 @@
       <c r="D311" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E311" s="6">
+      <c r="E311" s="11">
         <v>476107</v>
       </c>
-      <c r="H311" s="3"/>
+      <c r="H311" s="13"/>
     </row>
     <row r="312" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A312" s="1">
+      <c r="A312" s="8">
         <v>43040</v>
       </c>
-      <c r="B312" s="4">
+      <c r="B312" s="9">
         <v>43083</v>
       </c>
       <c r="C312" s="10">
@@ -6164,16 +6161,16 @@
       <c r="D312" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E312" s="6">
+      <c r="E312" s="11">
         <v>480949</v>
       </c>
-      <c r="H312" s="3"/>
+      <c r="H312" s="13"/>
     </row>
     <row r="313" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A313" s="1">
+      <c r="A313" s="8">
         <v>43070</v>
       </c>
-      <c r="B313" s="4">
+      <c r="B313" s="9">
         <v>43112</v>
       </c>
       <c r="C313" s="10">
@@ -6182,16 +6179,16 @@
       <c r="D313" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E313" s="6">
+      <c r="E313" s="11">
         <v>483586</v>
       </c>
-      <c r="H313" s="3"/>
+      <c r="H313" s="13"/>
     </row>
     <row r="314" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A314" s="1">
+      <c r="A314" s="8">
         <v>43101</v>
       </c>
-      <c r="B314" s="4">
+      <c r="B314" s="9">
         <v>43145</v>
       </c>
       <c r="C314" s="10">
@@ -6200,16 +6197,16 @@
       <c r="D314" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E314" s="6">
+      <c r="E314" s="11">
         <v>481414</v>
       </c>
-      <c r="H314" s="3"/>
+      <c r="H314" s="13"/>
     </row>
     <row r="315" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A315" s="1">
+      <c r="A315" s="8">
         <v>43132</v>
       </c>
-      <c r="B315" s="4">
+      <c r="B315" s="9">
         <v>43173</v>
       </c>
       <c r="C315" s="10">
@@ -6218,15 +6215,15 @@
       <c r="D315" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E315" s="6">
+      <c r="E315" s="11">
         <v>484031</v>
       </c>
     </row>
     <row r="316" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A316" s="1">
+      <c r="A316" s="8">
         <v>43160</v>
       </c>
-      <c r="B316" s="4">
+      <c r="B316" s="9">
         <v>43206</v>
       </c>
       <c r="C316" s="10">
@@ -6235,15 +6232,15 @@
       <c r="D316" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E316" s="6">
+      <c r="E316" s="11">
         <v>484110</v>
       </c>
     </row>
     <row r="317" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A317" s="1">
+      <c r="A317" s="8">
         <v>43191</v>
       </c>
-      <c r="B317" s="4">
+      <c r="B317" s="9">
         <v>43235</v>
       </c>
       <c r="C317" s="10">
@@ -6252,15 +6249,15 @@
       <c r="D317" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E317" s="6">
+      <c r="E317" s="11">
         <v>484154</v>
       </c>
     </row>
     <row r="318" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A318" s="1">
+      <c r="A318" s="8">
         <v>43221</v>
       </c>
-      <c r="B318" s="4">
+      <c r="B318" s="9">
         <v>43265</v>
       </c>
       <c r="C318" s="10">
@@ -6269,15 +6266,15 @@
       <c r="D318" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E318" s="6">
+      <c r="E318" s="11">
         <v>491960</v>
       </c>
     </row>
     <row r="319" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A319" s="1">
+      <c r="A319" s="8">
         <v>43252</v>
       </c>
-      <c r="B319" s="4">
+      <c r="B319" s="9">
         <v>43297</v>
       </c>
       <c r="C319" s="10">
@@ -6286,15 +6283,15 @@
       <c r="D319" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E319" s="6">
+      <c r="E319" s="11">
         <v>490228</v>
       </c>
     </row>
     <row r="320" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A320" s="1">
+      <c r="A320" s="8">
         <v>43282</v>
       </c>
-      <c r="B320" s="4">
+      <c r="B320" s="9">
         <v>43327</v>
       </c>
       <c r="C320" s="10">
@@ -6303,15 +6300,15 @@
       <c r="D320" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E320" s="6">
+      <c r="E320" s="11">
         <v>493142</v>
       </c>
     </row>
     <row r="321" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A321" s="1">
+      <c r="A321" s="8">
         <v>43313</v>
       </c>
-      <c r="B321" s="4">
+      <c r="B321" s="9">
         <v>43357</v>
       </c>
       <c r="C321" s="10">
@@ -6320,15 +6317,15 @@
       <c r="D321" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E321" s="6">
+      <c r="E321" s="11">
         <v>493445</v>
       </c>
     </row>
     <row r="322" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A322" s="1">
+      <c r="A322" s="8">
         <v>43344</v>
       </c>
-      <c r="B322" s="4">
+      <c r="B322" s="9">
         <v>43388</v>
       </c>
       <c r="C322" s="10">
@@ -6337,15 +6334,15 @@
       <c r="D322" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E322" s="6">
+      <c r="E322" s="11">
         <v>491507</v>
       </c>
     </row>
     <row r="323" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A323" s="1">
+      <c r="A323" s="8">
         <v>43374</v>
       </c>
-      <c r="B323" s="4">
+      <c r="B323" s="9">
         <v>43419</v>
       </c>
       <c r="C323" s="10">
@@ -6354,15 +6351,15 @@
       <c r="D323" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E323" s="6">
+      <c r="E323" s="11">
         <v>496416</v>
       </c>
     </row>
     <row r="324" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A324" s="1">
+      <c r="A324" s="8">
         <v>43405</v>
       </c>
-      <c r="B324" s="4">
+      <c r="B324" s="9">
         <v>43448</v>
       </c>
       <c r="C324" s="10">
@@ -6371,15 +6368,15 @@
       <c r="D324" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E324" s="6">
+      <c r="E324" s="11">
         <v>498854</v>
       </c>
     </row>
     <row r="325" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A325" s="1">
+      <c r="A325" s="8">
         <v>43435</v>
       </c>
-      <c r="B325" s="4">
+      <c r="B325" s="9">
         <v>43510</v>
       </c>
       <c r="C325" s="10">
@@ -6388,15 +6385,15 @@
       <c r="D325" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E325" s="6">
+      <c r="E325" s="11">
         <v>489113</v>
       </c>
     </row>
     <row r="326" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A326" s="1">
+      <c r="A326" s="8">
         <v>43466</v>
       </c>
-      <c r="B326" s="4">
+      <c r="B326" s="9">
         <v>43535</v>
       </c>
       <c r="C326" s="10">
@@ -6405,15 +6402,15 @@
       <c r="D326" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E326" s="6">
+      <c r="E326" s="11">
         <v>490440</v>
       </c>
     </row>
     <row r="327" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A327" s="1">
+      <c r="A327" s="8">
         <v>43497</v>
       </c>
-      <c r="B327" s="4">
+      <c r="B327" s="9">
         <v>43556</v>
       </c>
       <c r="C327" s="10">
@@ -6422,15 +6419,15 @@
       <c r="D327" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E327" s="6">
+      <c r="E327" s="11">
         <v>491751</v>
       </c>
     </row>
     <row r="328" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A328" s="1">
+      <c r="A328" s="8">
         <v>43525</v>
       </c>
-      <c r="B328" s="4">
+      <c r="B328" s="9">
         <v>43573</v>
       </c>
       <c r="C328" s="10">
@@ -6439,15 +6436,15 @@
       <c r="D328" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E328" s="6">
+      <c r="E328" s="11">
         <v>499292</v>
       </c>
     </row>
     <row r="329" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A329" s="1">
+      <c r="A329" s="8">
         <v>43556</v>
       </c>
-      <c r="B329" s="4">
+      <c r="B329" s="9">
         <v>43600</v>
       </c>
       <c r="C329" s="10">
@@ -6456,15 +6453,15 @@
       <c r="D329" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E329" s="6">
+      <c r="E329" s="11">
         <v>499343</v>
       </c>
     </row>
     <row r="330" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A330" s="1">
+      <c r="A330" s="8">
         <v>43586</v>
       </c>
-      <c r="B330" s="4">
+      <c r="B330" s="9">
         <v>43630</v>
       </c>
       <c r="C330" s="10">
@@ -6473,15 +6470,15 @@
       <c r="D330" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E330" s="6">
+      <c r="E330" s="11">
         <v>504741</v>
       </c>
     </row>
     <row r="331" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A331" s="1">
+      <c r="A331" s="8">
         <v>43617</v>
       </c>
-      <c r="B331" s="4">
+      <c r="B331" s="9">
         <v>43662</v>
       </c>
       <c r="C331" s="10">
@@ -6490,15 +6487,15 @@
       <c r="D331" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E331" s="6">
+      <c r="E331" s="11">
         <v>505251</v>
       </c>
     </row>
     <row r="332" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A332" s="1">
+      <c r="A332" s="8">
         <v>43647</v>
       </c>
-      <c r="B332" s="4">
+      <c r="B332" s="9">
         <v>43692</v>
       </c>
       <c r="C332" s="10">
@@ -6507,15 +6504,15 @@
       <c r="D332" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E332" s="6">
+      <c r="E332" s="11">
         <v>509091</v>
       </c>
     </row>
     <row r="333" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A333" s="1">
+      <c r="A333" s="8">
         <v>43678</v>
       </c>
-      <c r="B333" s="4">
+      <c r="B333" s="9">
         <v>43721</v>
       </c>
       <c r="C333" s="10">
@@ -6524,15 +6521,15 @@
       <c r="D333" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E333" s="6">
+      <c r="E333" s="11">
         <v>512561</v>
       </c>
     </row>
     <row r="334" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A334" s="1">
+      <c r="A334" s="8">
         <v>43709</v>
       </c>
-      <c r="B334" s="4">
+      <c r="B334" s="9">
         <v>43754</v>
       </c>
       <c r="C334" s="10">
@@ -6541,15 +6538,15 @@
       <c r="D334" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E334" s="6">
+      <c r="E334" s="11">
         <v>509282</v>
       </c>
     </row>
     <row r="335" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A335" s="1">
+      <c r="A335" s="8">
         <v>43739</v>
       </c>
-      <c r="B335" s="4">
+      <c r="B335" s="9">
         <v>43784</v>
       </c>
       <c r="C335" s="10">
@@ -6558,15 +6555,15 @@
       <c r="D335" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E335" s="6">
+      <c r="E335" s="11">
         <v>510648</v>
       </c>
     </row>
     <row r="336" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A336" s="1">
+      <c r="A336" s="8">
         <v>43770</v>
       </c>
-      <c r="B336" s="4">
+      <c r="B336" s="9">
         <v>43812</v>
       </c>
       <c r="C336" s="10">
@@ -6575,15 +6572,15 @@
       <c r="D336" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E336" s="6">
+      <c r="E336" s="11">
         <v>514215</v>
       </c>
     </row>
     <row r="337" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A337" s="1">
+      <c r="A337" s="8">
         <v>43800</v>
       </c>
-      <c r="B337" s="4">
+      <c r="B337" s="9">
         <v>43846</v>
       </c>
       <c r="C337" s="10">
@@ -6592,15 +6589,15 @@
       <c r="D337" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E337" s="6">
+      <c r="E337" s="11">
         <v>515866</v>
       </c>
     </row>
     <row r="338" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A338" s="1">
+      <c r="A338" s="8">
         <v>43831</v>
       </c>
-      <c r="B338" s="4">
+      <c r="B338" s="9">
         <v>43875</v>
       </c>
       <c r="C338" s="10">
@@ -6609,15 +6606,15 @@
       <c r="D338" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E338" s="6">
+      <c r="E338" s="11">
         <v>515119</v>
       </c>
     </row>
     <row r="339" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A339" s="1">
+      <c r="A339" s="8">
         <v>43862</v>
       </c>
-      <c r="B339" s="4">
+      <c r="B339" s="9">
         <v>43907</v>
       </c>
       <c r="C339" s="10">
@@ -6626,15 +6623,15 @@
       <c r="D339" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E339" s="6">
+      <c r="E339" s="11">
         <v>515330</v>
       </c>
     </row>
     <row r="340" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A340" s="1">
+      <c r="A340" s="8">
         <v>43891</v>
       </c>
-      <c r="B340" s="4">
+      <c r="B340" s="9">
         <v>43936</v>
       </c>
       <c r="C340" s="10">
@@ -6643,15 +6640,15 @@
       <c r="D340" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E340" s="6">
+      <c r="E340" s="11">
         <v>468324</v>
       </c>
     </row>
     <row r="341" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A341" s="1">
+      <c r="A341" s="8">
         <v>43922</v>
       </c>
-      <c r="B341" s="4">
+      <c r="B341" s="9">
         <v>43966</v>
       </c>
       <c r="C341" s="10">
@@ -6660,15 +6657,15 @@
       <c r="D341" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E341" s="6">
+      <c r="E341" s="11">
         <v>401028</v>
       </c>
     </row>
     <row r="342" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A342" s="1">
+      <c r="A342" s="8">
         <v>43952</v>
       </c>
-      <c r="B342" s="4">
+      <c r="B342" s="9">
         <v>43998</v>
       </c>
       <c r="C342" s="10">
@@ -6677,15 +6674,15 @@
       <c r="D342" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E342" s="6">
+      <c r="E342" s="11">
         <v>478449</v>
       </c>
     </row>
     <row r="343" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A343" s="1">
+      <c r="A343" s="8">
         <v>43983</v>
       </c>
-      <c r="B343" s="4">
+      <c r="B343" s="9">
         <v>44028</v>
       </c>
       <c r="C343" s="10">
@@ -6694,15 +6691,15 @@
       <c r="D343" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E343" s="6">
+      <c r="E343" s="11">
         <v>518038</v>
       </c>
     </row>
     <row r="344" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A344" s="1">
+      <c r="A344" s="8">
         <v>44013</v>
       </c>
-      <c r="B344" s="4">
+      <c r="B344" s="9">
         <v>44057</v>
       </c>
       <c r="C344" s="10">
@@ -6711,15 +6708,15 @@
       <c r="D344" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E344" s="6">
+      <c r="E344" s="11">
         <v>526304</v>
       </c>
     </row>
     <row r="345" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A345" s="1">
+      <c r="A345" s="8">
         <v>44044</v>
       </c>
-      <c r="B345" s="4">
+      <c r="B345" s="9">
         <v>44090</v>
       </c>
       <c r="C345" s="10">
@@ -6728,15 +6725,15 @@
       <c r="D345" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E345" s="6">
+      <c r="E345" s="11">
         <v>530735</v>
       </c>
     </row>
     <row r="346" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A346" s="1">
+      <c r="A346" s="8">
         <v>44075</v>
       </c>
-      <c r="B346" s="4">
+      <c r="B346" s="9">
         <v>44120</v>
       </c>
       <c r="C346" s="10">
@@ -6745,15 +6742,15 @@
       <c r="D346" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E346" s="6">
+      <c r="E346" s="11">
         <v>541302</v>
       </c>
     </row>
     <row r="347" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A347" s="1">
+      <c r="A347" s="8">
         <v>44105</v>
       </c>
-      <c r="B347" s="4">
+      <c r="B347" s="9">
         <v>44152</v>
       </c>
       <c r="C347" s="10">
@@ -6762,15 +6759,15 @@
       <c r="D347" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E347" s="6">
+      <c r="E347" s="11">
         <v>539114</v>
       </c>
     </row>
     <row r="348" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A348" s="1">
+      <c r="A348" s="8">
         <v>44136</v>
       </c>
-      <c r="B348" s="4">
+      <c r="B348" s="9">
         <v>44181</v>
       </c>
       <c r="C348" s="10">
@@ -6779,21 +6776,21 @@
       <c r="D348" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E348" s="6">
+      <c r="E348" s="11">
         <v>533941</v>
       </c>
-      <c r="F348" s="5">
+      <c r="F348" s="12">
         <v>4.1000000000000002E-2</v>
       </c>
-      <c r="G348" s="5">
+      <c r="G348" s="12">
         <v>5.4899999999999997E-2</v>
       </c>
     </row>
     <row r="349" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A349" s="1">
+      <c r="A349" s="8">
         <v>44166</v>
       </c>
-      <c r="B349" s="4">
+      <c r="B349" s="9">
         <v>44211</v>
       </c>
       <c r="C349" s="10">
@@ -6802,21 +6799,21 @@
       <c r="D349" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E349" s="6">
+      <c r="E349" s="11">
         <v>538548</v>
       </c>
-      <c r="F349" s="5">
+      <c r="F349" s="12">
         <v>2.9000000000000001E-2</v>
       </c>
-      <c r="G349" s="5">
+      <c r="G349" s="12">
         <v>3.6799999999999999E-2</v>
       </c>
     </row>
     <row r="350" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A350" s="1">
+      <c r="A350" s="8">
         <v>44197</v>
       </c>
-      <c r="B350" s="4">
+      <c r="B350" s="9">
         <v>44244</v>
       </c>
       <c r="C350" s="10">
@@ -6825,21 +6822,21 @@
       <c r="D350" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E350" s="6">
+      <c r="E350" s="11">
         <v>559230</v>
       </c>
-      <c r="F350" s="5">
+      <c r="F350" s="12">
         <v>7.4300000000000005E-2</v>
       </c>
-      <c r="G350" s="5">
+      <c r="G350" s="12">
         <v>2.53E-2</v>
       </c>
     </row>
     <row r="351" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A351" s="1">
+      <c r="A351" s="8">
         <v>44228</v>
       </c>
-      <c r="B351" s="4">
+      <c r="B351" s="9">
         <v>44271</v>
       </c>
       <c r="C351" s="10">
@@ -6848,21 +6845,21 @@
       <c r="D351" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E351" s="6">
+      <c r="E351" s="11">
         <v>544891</v>
       </c>
-      <c r="F351" s="5">
+      <c r="F351" s="12">
         <v>6.2700000000000006E-2</v>
       </c>
-      <c r="G351" s="5">
+      <c r="G351" s="12">
         <v>9.5100000000000004E-2</v>
       </c>
     </row>
     <row r="352" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A352" s="1">
+      <c r="A352" s="8">
         <v>44256</v>
       </c>
-      <c r="B352" s="4">
+      <c r="B352" s="9">
         <v>44301</v>
       </c>
       <c r="C352" s="10">
@@ -6871,21 +6868,21 @@
       <c r="D352" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E352" s="6">
+      <c r="E352" s="11">
         <v>603581</v>
       </c>
-      <c r="F352" s="5">
+      <c r="F352" s="12">
         <v>0.28160000000000002</v>
       </c>
-      <c r="G352" s="5">
+      <c r="G352" s="12">
         <v>6.6600000000000006E-2</v>
       </c>
     </row>
     <row r="353" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A353" s="1">
+      <c r="A353" s="8">
         <v>44287</v>
       </c>
-      <c r="B353" s="4">
+      <c r="B353" s="9">
         <v>44330</v>
       </c>
       <c r="C353" s="10">
@@ -6894,21 +6891,21 @@
       <c r="D353" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E353" s="6">
+      <c r="E353" s="11">
         <v>608961</v>
       </c>
-      <c r="F353" s="5">
+      <c r="F353" s="12">
         <v>0.51219999999999999</v>
       </c>
-      <c r="G353" s="5">
+      <c r="G353" s="12">
         <v>0.29010000000000002</v>
       </c>
     </row>
     <row r="354" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A354" s="1">
+      <c r="A354" s="8">
         <v>44317</v>
       </c>
-      <c r="B354" s="4">
+      <c r="B354" s="9">
         <v>44362</v>
       </c>
       <c r="C354" s="10">
@@ -6917,21 +6914,21 @@
       <c r="D354" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E354" s="6">
+      <c r="E354" s="11">
         <v>605282</v>
       </c>
-      <c r="F354" s="5">
+      <c r="F354" s="12">
         <v>0.28149999999999997</v>
       </c>
-      <c r="G354" s="5">
+      <c r="G354" s="12">
         <v>0.53400000000000003</v>
       </c>
     </row>
     <row r="355" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A355" s="1">
+      <c r="A355" s="8">
         <v>44348</v>
       </c>
-      <c r="B355" s="4">
+      <c r="B355" s="9">
         <v>44393</v>
       </c>
       <c r="C355" s="10">
@@ -6940,21 +6937,21 @@
       <c r="D355" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E355" s="6">
+      <c r="E355" s="11">
         <v>611950</v>
       </c>
-      <c r="F355" s="5">
+      <c r="F355" s="12">
         <v>0.17979999999999999</v>
       </c>
-      <c r="G355" s="5">
+      <c r="G355" s="12">
         <v>0.27600000000000002</v>
       </c>
     </row>
     <row r="356" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A356" s="1">
+      <c r="A356" s="8">
         <v>44378</v>
       </c>
-      <c r="B356" s="4">
+      <c r="B356" s="9">
         <v>44425</v>
       </c>
       <c r="C356" s="10">
@@ -6963,21 +6960,21 @@
       <c r="D356" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E356" s="6">
+      <c r="E356" s="11">
         <v>601817</v>
       </c>
-      <c r="F356" s="5">
+      <c r="F356" s="12">
         <v>0.1578</v>
       </c>
-      <c r="G356" s="5">
+      <c r="G356" s="12">
         <v>0.18729999999999999</v>
       </c>
     </row>
     <row r="357" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A357" s="1">
+      <c r="A357" s="8">
         <v>44409</v>
       </c>
-      <c r="B357" s="4">
+      <c r="B357" s="9">
         <v>44455</v>
       </c>
       <c r="C357" s="10">
@@ -6986,21 +6983,21 @@
       <c r="D357" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E357" s="6">
+      <c r="E357" s="11">
         <v>605533</v>
       </c>
-      <c r="F357" s="5">
+      <c r="F357" s="12">
         <v>0.13450000000000001</v>
       </c>
-      <c r="G357" s="5">
+      <c r="G357" s="12">
         <v>0.15140000000000001</v>
       </c>
     </row>
     <row r="358" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A358" s="1">
+      <c r="A358" s="8">
         <v>44440</v>
       </c>
-      <c r="B358" s="4">
+      <c r="B358" s="9">
         <v>44484</v>
       </c>
       <c r="C358" s="10">
@@ -7009,21 +7006,21 @@
       <c r="D358" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E358" s="6">
+      <c r="E358" s="11">
         <v>609671</v>
       </c>
-      <c r="F358" s="5">
+      <c r="F358" s="12">
         <v>0.13950000000000001</v>
       </c>
-      <c r="G358" s="5">
+      <c r="G358" s="12">
         <v>0.154</v>
       </c>
     </row>
     <row r="359" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A359" s="1">
+      <c r="A359" s="8">
         <v>44470</v>
       </c>
-      <c r="B359" s="4">
+      <c r="B359" s="9">
         <v>44516</v>
       </c>
       <c r="C359" s="10">
@@ -7032,21 +7029,21 @@
       <c r="D359" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E359" s="6">
+      <c r="E359" s="11">
         <v>618573</v>
       </c>
-      <c r="F359" s="5">
+      <c r="F359" s="12">
         <v>0.16309999999999999</v>
       </c>
-      <c r="G359" s="5">
+      <c r="G359" s="12">
         <v>0.1426</v>
       </c>
     </row>
     <row r="360" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A360" s="1">
+      <c r="A360" s="8">
         <v>44501</v>
       </c>
-      <c r="B360" s="4">
+      <c r="B360" s="9">
         <v>44545</v>
       </c>
       <c r="C360" s="10">
@@ -7055,21 +7052,21 @@
       <c r="D360" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E360" s="6">
+      <c r="E360" s="11">
         <v>624874</v>
       </c>
-      <c r="F360" s="5">
+      <c r="F360" s="12">
         <v>0.18210000000000001</v>
       </c>
-      <c r="G360" s="5">
+      <c r="G360" s="12">
         <v>0.16259999999999999</v>
       </c>
     </row>
     <row r="361" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A361" s="1">
+      <c r="A361" s="8">
         <v>44531</v>
       </c>
-      <c r="B361" s="4">
+      <c r="B361" s="9">
         <v>44575</v>
       </c>
       <c r="C361" s="10">
@@ -7078,21 +7075,21 @@
       <c r="D361" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E361" s="6">
+      <c r="E361" s="11">
         <v>619938</v>
       </c>
-      <c r="F361" s="5">
+      <c r="F361" s="12">
         <v>0.16950000000000001</v>
       </c>
-      <c r="G361" s="5">
+      <c r="G361" s="12">
         <v>0.18240000000000001</v>
       </c>
     </row>
     <row r="362" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A362" s="1">
+      <c r="A362" s="8">
         <v>44562</v>
       </c>
-      <c r="B362" s="4">
+      <c r="B362" s="9">
         <v>44608</v>
       </c>
       <c r="C362" s="10">
@@ -7101,21 +7098,21 @@
       <c r="D362" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E362" s="6">
+      <c r="E362" s="11">
         <v>631509</v>
       </c>
-      <c r="F362" s="5">
+      <c r="F362" s="12">
         <v>0.12959999999999999</v>
       </c>
-      <c r="G362" s="5">
+      <c r="G362" s="12">
         <v>0.1671</v>
       </c>
     </row>
     <row r="363" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A363" s="1">
+      <c r="A363" s="8">
         <v>44593</v>
       </c>
-      <c r="B363" s="4">
+      <c r="B363" s="9">
         <v>44636</v>
       </c>
       <c r="C363" s="10">
@@ -7124,21 +7121,21 @@
       <c r="D363" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E363" s="6">
+      <c r="E363" s="11">
         <v>638101</v>
       </c>
-      <c r="F363" s="5">
+      <c r="F363" s="12">
         <v>0.1762</v>
       </c>
-      <c r="G363" s="5">
+      <c r="G363" s="12">
         <v>0.14000000000000001</v>
       </c>
     </row>
     <row r="364" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A364" s="1">
+      <c r="A364" s="8">
         <v>44621</v>
       </c>
-      <c r="B364" s="4">
+      <c r="B364" s="9">
         <v>44665</v>
       </c>
       <c r="C364" s="10">
@@ -7147,21 +7144,21 @@
       <c r="D364" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E364" s="6">
+      <c r="E364" s="11">
         <v>651027</v>
       </c>
-      <c r="F364" s="5">
+      <c r="F364" s="12">
         <v>6.88E-2</v>
       </c>
-      <c r="G364" s="5">
+      <c r="G364" s="12">
         <v>0.18179999999999999</v>
       </c>
     </row>
     <row r="365" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A365" s="1">
+      <c r="A365" s="8">
         <v>44652</v>
       </c>
-      <c r="B365" s="4">
+      <c r="B365" s="9">
         <v>44698</v>
       </c>
       <c r="C365" s="10">
@@ -7170,21 +7167,21 @@
       <c r="D365" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E365" s="6">
+      <c r="E365" s="11">
         <v>660194</v>
       </c>
-      <c r="F365" s="5">
+      <c r="F365" s="12">
         <v>8.1900000000000001E-2</v>
       </c>
-      <c r="G365" s="5">
+      <c r="G365" s="12">
         <v>7.3400000000000007E-2</v>
       </c>
     </row>
     <row r="366" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A366" s="1">
+      <c r="A366" s="8">
         <v>44682</v>
       </c>
-      <c r="B366" s="4">
+      <c r="B366" s="9">
         <v>44727</v>
       </c>
       <c r="C366" s="10">
@@ -7193,21 +7190,21 @@
       <c r="D366" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E366" s="6">
+      <c r="E366" s="11">
         <v>659847</v>
       </c>
-      <c r="F366" s="5">
+      <c r="F366" s="12">
         <v>8.09E-2</v>
       </c>
-      <c r="G366" s="5">
+      <c r="G366" s="12">
         <v>7.8200000000000006E-2</v>
       </c>
     </row>
     <row r="367" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A367" s="1">
+      <c r="A367" s="8">
         <v>44713</v>
       </c>
-      <c r="B367" s="4">
+      <c r="B367" s="9">
         <v>44757</v>
       </c>
       <c r="C367" s="10">
@@ -7216,21 +7213,21 @@
       <c r="D367" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E367" s="6">
+      <c r="E367" s="11">
         <v>666113</v>
       </c>
-      <c r="F367" s="5">
+      <c r="F367" s="12">
         <v>8.4199999999999997E-2</v>
       </c>
-      <c r="G367" s="5">
+      <c r="G367" s="12">
         <v>8.1799999999999998E-2</v>
       </c>
     </row>
     <row r="368" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A368" s="1">
+      <c r="A368" s="8">
         <v>44743</v>
       </c>
-      <c r="B368" s="4">
+      <c r="B368" s="9">
         <v>44790</v>
       </c>
       <c r="C368" s="10">
@@ -7239,21 +7236,21 @@
       <c r="D368" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E368" s="6">
+      <c r="E368" s="11">
         <v>659550</v>
       </c>
-      <c r="F368" s="5">
+      <c r="F368" s="12">
         <v>0.1002</v>
       </c>
-      <c r="G368" s="5">
+      <c r="G368" s="12">
         <v>8.5400000000000004E-2</v>
       </c>
     </row>
     <row r="369" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A369" s="1">
+      <c r="A369" s="8">
         <v>44774</v>
       </c>
-      <c r="B369" s="4">
+      <c r="B369" s="9">
         <v>44819</v>
       </c>
       <c r="C369" s="10">
@@ -7262,21 +7259,21 @@
       <c r="D369" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E369" s="6">
+      <c r="E369" s="11">
         <v>663566</v>
       </c>
-      <c r="F369" s="5">
+      <c r="F369" s="12">
         <v>9.0999999999999998E-2</v>
       </c>
-      <c r="G369" s="5">
+      <c r="G369" s="12">
         <v>0.10059999999999999</v>
       </c>
     </row>
     <row r="370" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A370" s="1">
+      <c r="A370" s="8">
         <v>44805</v>
       </c>
-      <c r="B370" s="4">
+      <c r="B370" s="9">
         <v>44848</v>
       </c>
       <c r="C370" s="10">
@@ -7285,21 +7282,21 @@
       <c r="D370" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E370" s="6">
+      <c r="E370" s="11">
         <v>661854</v>
       </c>
-      <c r="F370" s="5">
+      <c r="F370" s="12">
         <v>8.4099999999999994E-2</v>
       </c>
-      <c r="G370" s="5">
+      <c r="G370" s="12">
         <v>9.4399999999999998E-2</v>
       </c>
     </row>
     <row r="371" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A371" s="1">
+      <c r="A371" s="8">
         <v>44835</v>
       </c>
-      <c r="B371" s="4">
+      <c r="B371" s="9">
         <v>44881</v>
       </c>
       <c r="C371" s="10">
@@ -7308,21 +7305,21 @@
       <c r="D371" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E371" s="6">
+      <c r="E371" s="11">
         <v>668671</v>
       </c>
-      <c r="F371" s="5">
+      <c r="F371" s="12">
         <v>8.3699999999999997E-2</v>
       </c>
-      <c r="G371" s="5">
+      <c r="G371" s="12">
         <v>8.5900000000000004E-2</v>
       </c>
     </row>
     <row r="372" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A372" s="1">
+      <c r="A372" s="8">
         <v>44866</v>
       </c>
-      <c r="B372" s="4">
+      <c r="B372" s="9">
         <v>44910</v>
       </c>
       <c r="C372" s="10">
@@ -7331,21 +7328,21 @@
       <c r="D372" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E372" s="6">
+      <c r="E372" s="11">
         <v>659458</v>
       </c>
-      <c r="F372" s="5">
+      <c r="F372" s="12">
         <v>7.5999999999999998E-2</v>
       </c>
-      <c r="G372" s="5">
+      <c r="G372" s="12">
         <v>7.51E-2</v>
       </c>
     </row>
     <row r="373" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A373" s="1">
+      <c r="A373" s="8">
         <v>44896</v>
       </c>
-      <c r="B373" s="4">
+      <c r="B373" s="9">
         <v>44944</v>
       </c>
       <c r="C373" s="10">
@@ -7354,21 +7351,21 @@
       <c r="D373" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E373" s="6">
+      <c r="E373" s="11">
         <v>651763</v>
       </c>
-      <c r="F373" s="5">
+      <c r="F373" s="12">
         <v>6.0199999999999997E-2</v>
       </c>
-      <c r="G373" s="5">
+      <c r="G373" s="12">
         <v>6.0100000000000001E-2</v>
       </c>
     </row>
     <row r="374" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A374" s="1">
+      <c r="A374" s="8">
         <v>44927</v>
       </c>
-      <c r="B374" s="4">
+      <c r="B374" s="9">
         <v>44972</v>
       </c>
       <c r="C374" s="10">
@@ -7377,21 +7374,21 @@
       <c r="D374" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E374" s="6">
+      <c r="E374" s="11">
         <v>680253</v>
       </c>
-      <c r="F374" s="5">
+      <c r="F374" s="12">
         <v>6.3799999999999996E-2</v>
       </c>
-      <c r="G374" s="5">
+      <c r="G374" s="12">
         <v>5.8900000000000001E-2</v>
       </c>
     </row>
     <row r="375" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A375" s="1">
+      <c r="A375" s="8">
         <v>44958</v>
       </c>
-      <c r="B375" s="4">
+      <c r="B375" s="9">
         <v>45000</v>
       </c>
       <c r="C375" s="10">
@@ -7400,21 +7397,21 @@
       <c r="D375" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E375" s="6">
+      <c r="E375" s="11">
         <v>672152</v>
       </c>
-      <c r="F375" s="5">
+      <c r="F375" s="12">
         <v>5.3900000000000003E-2</v>
       </c>
-      <c r="G375" s="5">
+      <c r="G375" s="12">
         <v>7.6799999999999993E-2</v>
       </c>
     </row>
     <row r="376" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A376" s="1">
+      <c r="A376" s="8">
         <v>44986</v>
       </c>
-      <c r="B376" s="4">
+      <c r="B376" s="9">
         <v>45030</v>
       </c>
       <c r="C376" s="10">
@@ -7423,21 +7420,21 @@
       <c r="D376" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E376" s="6">
+      <c r="E376" s="11">
         <v>665071</v>
       </c>
-      <c r="F376" s="5">
+      <c r="F376" s="12">
         <v>2.9399999999999999E-2</v>
       </c>
-      <c r="G376" s="5">
+      <c r="G376" s="12">
         <v>5.8799999999999998E-2</v>
       </c>
     </row>
     <row r="377" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A377" s="1">
+      <c r="A377" s="8">
         <v>45017</v>
       </c>
-      <c r="B377" s="4">
+      <c r="B377" s="9">
         <v>45062</v>
       </c>
       <c r="C377" s="10">
@@ -7446,21 +7443,21 @@
       <c r="D377" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E377" s="6">
+      <c r="E377" s="11">
         <v>670494</v>
       </c>
-      <c r="F377" s="5">
+      <c r="F377" s="12">
         <v>1.6E-2</v>
       </c>
-      <c r="G377" s="5">
+      <c r="G377" s="12">
         <v>2.4199999999999999E-2</v>
       </c>
     </row>
     <row r="378" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A378" s="1">
+      <c r="A378" s="8">
         <v>45047</v>
       </c>
-      <c r="B378" s="4">
+      <c r="B378" s="9">
         <v>45092</v>
       </c>
       <c r="C378" s="10">
@@ -7469,21 +7466,21 @@
       <c r="D378" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E378" s="6">
+      <c r="E378" s="11">
         <v>673902</v>
       </c>
-      <c r="F378" s="5">
+      <c r="F378" s="12">
         <v>1.61E-2</v>
       </c>
-      <c r="G378" s="5">
+      <c r="G378" s="12">
         <v>1.23E-2</v>
       </c>
     </row>
     <row r="379" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A379" s="1">
+      <c r="A379" s="8">
         <v>45078</v>
       </c>
-      <c r="B379" s="4">
+      <c r="B379" s="9">
         <v>45125</v>
       </c>
       <c r="C379" s="10">
@@ -7492,21 +7489,21 @@
       <c r="D379" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E379" s="6">
+      <c r="E379" s="11">
         <v>677117</v>
       </c>
-      <c r="F379" s="5">
+      <c r="F379" s="12">
         <v>1.49E-2</v>
       </c>
-      <c r="G379" s="5">
+      <c r="G379" s="12">
         <v>1.9599999999999999E-2</v>
       </c>
     </row>
     <row r="380" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A380" s="1">
+      <c r="A380" s="8">
         <v>45108</v>
       </c>
-      <c r="B380" s="4">
+      <c r="B380" s="9">
         <v>45153</v>
       </c>
       <c r="C380" s="10">
@@ -7515,21 +7512,21 @@
       <c r="D380" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E380" s="6">
+      <c r="E380" s="11">
         <v>678424</v>
       </c>
-      <c r="F380" s="5">
+      <c r="F380" s="12">
         <v>3.1699999999999999E-2</v>
       </c>
-      <c r="G380" s="5">
+      <c r="G380" s="12">
         <v>1.5900000000000001E-2</v>
       </c>
     </row>
     <row r="381" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A381" s="1">
+      <c r="A381" s="8">
         <v>45139</v>
       </c>
-      <c r="B381" s="4">
+      <c r="B381" s="9">
         <v>45183</v>
       </c>
       <c r="C381" s="10">
@@ -7538,21 +7535,21 @@
       <c r="D381" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E381" s="6">
+      <c r="E381" s="11">
         <v>684755</v>
       </c>
-      <c r="F381" s="5">
+      <c r="F381" s="12">
         <v>2.4899999999999999E-2</v>
       </c>
-      <c r="G381" s="5">
+      <c r="G381" s="12">
         <v>2.64E-2</v>
       </c>
     </row>
     <row r="382" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A382" s="1">
+      <c r="A382" s="8">
         <v>45170</v>
       </c>
-      <c r="B382" s="4">
+      <c r="B382" s="9">
         <v>45216</v>
       </c>
       <c r="C382" s="10">
@@ -7561,21 +7558,21 @@
       <c r="D382" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E382" s="6">
+      <c r="E382" s="11">
         <v>689403</v>
       </c>
-      <c r="F382" s="5">
+      <c r="F382" s="12">
         <v>3.7499999999999999E-2</v>
       </c>
-      <c r="G382" s="5">
+      <c r="G382" s="12">
         <v>2.8899999999999999E-2</v>
       </c>
     </row>
     <row r="383" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A383" s="1">
+      <c r="A383" s="8">
         <v>45200</v>
       </c>
-      <c r="B383" s="4">
+      <c r="B383" s="9">
         <v>45245</v>
       </c>
       <c r="C383" s="10">
@@ -7584,21 +7581,21 @@
       <c r="D383" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E383" s="6">
+      <c r="E383" s="11">
         <v>686148</v>
       </c>
-      <c r="F383" s="5">
+      <c r="F383" s="12">
         <v>2.4799999999999999E-2</v>
       </c>
-      <c r="G383" s="5">
+      <c r="G383" s="12">
         <v>4.0500000000000001E-2</v>
       </c>
     </row>
     <row r="384" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A384" s="1">
+      <c r="A384" s="8">
         <v>45231</v>
       </c>
-      <c r="B384" s="4">
+      <c r="B384" s="9">
         <v>45274</v>
       </c>
       <c r="C384" s="10">
@@ -7607,21 +7604,21 @@
       <c r="D384" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E384" s="6">
+      <c r="E384" s="11">
         <v>685328</v>
       </c>
-      <c r="F384" s="5">
+      <c r="F384" s="12">
         <v>4.0899999999999999E-2</v>
       </c>
-      <c r="G384" s="5">
+      <c r="G384" s="12">
         <v>2.24E-2</v>
       </c>
     </row>
     <row r="385" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A385" s="1">
+      <c r="A385" s="8">
         <v>45261</v>
       </c>
-      <c r="B385" s="4">
+      <c r="B385" s="9">
         <v>45308</v>
       </c>
       <c r="C385" s="10">
@@ -7630,21 +7627,21 @@
       <c r="D385" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E385" s="6">
+      <c r="E385" s="11">
         <v>686277</v>
       </c>
-      <c r="F385" s="5">
+      <c r="F385" s="12">
         <v>5.5899999999999998E-2</v>
       </c>
-      <c r="G385" s="5">
+      <c r="G385" s="12">
         <v>3.9699999999999999E-2</v>
       </c>
     </row>
     <row r="386" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A386" s="1">
+      <c r="A386" s="8">
         <v>45292</v>
       </c>
-      <c r="B386" s="4">
+      <c r="B386" s="9">
         <v>45337</v>
       </c>
       <c r="C386" s="10">
@@ -7653,21 +7650,21 @@
       <c r="D386" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E386" s="6">
+      <c r="E386" s="11">
         <v>680456</v>
       </c>
-      <c r="F386" s="5">
+      <c r="F386" s="12">
         <v>6.4999999999999997E-3</v>
       </c>
-      <c r="G386" s="5">
+      <c r="G386" s="12">
         <v>5.3100000000000001E-2</v>
       </c>
     </row>
     <row r="387" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A387" s="1">
+      <c r="A387" s="8">
         <v>45323</v>
       </c>
-      <c r="B387" s="4">
+      <c r="B387" s="9">
         <v>45365</v>
       </c>
       <c r="C387" s="10">
@@ -7676,21 +7673,21 @@
       <c r="D387" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E387" s="6">
+      <c r="E387" s="11">
         <v>685280</v>
       </c>
-      <c r="F387" s="5">
+      <c r="F387" s="12">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="G387" s="5">
+      <c r="G387" s="12">
         <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="388" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A388" s="1">
+      <c r="A388" s="8">
         <v>45352</v>
       </c>
-      <c r="B388" s="4">
+      <c r="B388" s="9">
         <v>45397</v>
       </c>
       <c r="C388" s="10">
@@ -7699,21 +7696,21 @@
       <c r="D388" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E388" s="6">
+      <c r="E388" s="11">
         <v>687641</v>
       </c>
-      <c r="F388" s="5">
+      <c r="F388" s="12">
         <v>4.02E-2</v>
       </c>
-      <c r="G388" s="5">
+      <c r="G388" s="12">
         <v>2.1100000000000001E-2</v>
       </c>
     </row>
     <row r="389" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A389" s="1">
+      <c r="A389" s="8">
         <v>45383</v>
       </c>
-      <c r="B389" s="4">
+      <c r="B389" s="9">
         <v>45427</v>
       </c>
       <c r="C389" s="10">
@@ -7722,21 +7719,21 @@
       <c r="D389" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E389" s="6">
+      <c r="E389" s="11">
         <v>687602</v>
       </c>
-      <c r="F389" s="5">
+      <c r="F389" s="12">
         <v>3.04E-2</v>
       </c>
-      <c r="G389" s="5">
+      <c r="G389" s="12">
         <v>3.8300000000000001E-2</v>
       </c>
     </row>
     <row r="390" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A390" s="1">
+      <c r="A390" s="8">
         <v>45413</v>
       </c>
-      <c r="B390" s="4">
+      <c r="B390" s="9">
         <v>45461</v>
       </c>
       <c r="C390" s="10">
@@ -7745,21 +7742,21 @@
       <c r="D390" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E390" s="6">
+      <c r="E390" s="11">
         <v>692774</v>
       </c>
-      <c r="F390" s="5">
+      <c r="F390" s="12">
         <v>2.2700000000000001E-2</v>
       </c>
-      <c r="G390" s="5">
+      <c r="G390" s="12">
         <v>2.7400000000000001E-2</v>
       </c>
     </row>
     <row r="391" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A391" s="1">
+      <c r="A391" s="8">
         <v>45444</v>
       </c>
-      <c r="B391" s="4">
+      <c r="B391" s="9">
         <v>45489</v>
       </c>
       <c r="C391" s="10">
@@ -7768,21 +7765,21 @@
       <c r="D391" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E391" s="6">
+      <c r="E391" s="11">
         <v>692449</v>
       </c>
-      <c r="F391" s="5">
+      <c r="F391" s="12">
         <v>2.2800000000000001E-2</v>
       </c>
-      <c r="G391" s="5">
+      <c r="G391" s="12">
         <v>2.5899999999999999E-2</v>
       </c>
     </row>
     <row r="392" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A392" s="1">
+      <c r="A392" s="8">
         <v>45474</v>
       </c>
-      <c r="B392" s="4">
+      <c r="B392" s="9">
         <v>45519</v>
       </c>
       <c r="C392" s="10">
@@ -7791,21 +7788,21 @@
       <c r="D392" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E392" s="6">
+      <c r="E392" s="11">
         <v>698835</v>
       </c>
-      <c r="F392" s="5">
+      <c r="F392" s="12">
         <v>2.6599999999999999E-2</v>
       </c>
-      <c r="G392" s="5">
+      <c r="G392" s="12">
         <v>2.0400000000000001E-2</v>
       </c>
     </row>
     <row r="393" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A393" s="1">
+      <c r="A393" s="8">
         <v>45505</v>
       </c>
-      <c r="B393" s="4">
+      <c r="B393" s="9">
         <v>45552</v>
       </c>
       <c r="C393" s="10">
@@ -7814,21 +7811,21 @@
       <c r="D393" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E393" s="6">
+      <c r="E393" s="11">
         <v>697039</v>
       </c>
-      <c r="F393" s="5">
+      <c r="F393" s="12">
         <v>2.1299999999999999E-2</v>
       </c>
-      <c r="G393" s="5">
+      <c r="G393" s="12">
         <v>2.86E-2</v>
       </c>
     </row>
     <row r="394" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A394" s="1">
+      <c r="A394" s="8">
         <v>45536</v>
       </c>
-      <c r="B394" s="4">
+      <c r="B394" s="9">
         <v>45582</v>
       </c>
       <c r="C394" s="10">
@@ -7837,21 +7834,21 @@
       <c r="D394" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E394" s="6">
+      <c r="E394" s="11">
         <v>703285</v>
       </c>
-      <c r="F394" s="5">
+      <c r="F394" s="12">
         <v>1.7399999999999999E-2</v>
       </c>
-      <c r="G394" s="5">
+      <c r="G394" s="12">
         <v>2.1600000000000001E-2</v>
       </c>
     </row>
     <row r="395" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A395" s="1">
+      <c r="A395" s="8">
         <v>45566</v>
       </c>
-      <c r="B395" s="4">
+      <c r="B395" s="9">
         <v>45611</v>
       </c>
       <c r="C395" s="10">
@@ -7860,21 +7857,21 @@
       <c r="D395" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E395" s="6">
+      <c r="E395" s="11">
         <v>707613</v>
       </c>
-      <c r="F395" s="5">
+      <c r="F395" s="12">
         <v>2.8500000000000001E-2</v>
       </c>
-      <c r="G395" s="5">
+      <c r="G395" s="12">
         <v>1.9800000000000002E-2</v>
       </c>
     </row>
     <row r="396" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A396" s="1">
+      <c r="A396" s="8">
         <v>45597</v>
       </c>
-      <c r="B396" s="4">
+      <c r="B396" s="9">
         <v>45643</v>
       </c>
       <c r="C396" s="10">
@@ -7883,21 +7880,21 @@
       <c r="D396" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E396" s="6">
+      <c r="E396" s="11">
         <v>712145</v>
       </c>
-      <c r="F396" s="5">
+      <c r="F396" s="12">
         <v>3.7999999999999999E-2</v>
       </c>
-      <c r="G396" s="5">
+      <c r="G396" s="12">
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
     <row r="397" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A397" s="1">
+      <c r="A397" s="8">
         <v>45627</v>
       </c>
-      <c r="B397" s="4">
+      <c r="B397" s="9">
         <v>45673</v>
       </c>
       <c r="C397" s="10">
@@ -7906,21 +7903,21 @@
       <c r="D397" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E397" s="6">
+      <c r="E397" s="11">
         <v>717662</v>
       </c>
-      <c r="F397" s="5">
+      <c r="F397" s="12">
         <v>3.9199999999999999E-2</v>
       </c>
-      <c r="G397" s="5">
+      <c r="G397" s="12">
         <v>4.1200000000000001E-2</v>
       </c>
     </row>
     <row r="398" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A398" s="1">
+      <c r="A398" s="8">
         <v>45658</v>
       </c>
-      <c r="B398" s="4">
+      <c r="B398" s="9">
         <v>45702</v>
       </c>
       <c r="C398" s="10">
@@ -7929,21 +7926,21 @@
       <c r="D398" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E398" s="6">
+      <c r="E398" s="11">
         <v>711461</v>
       </c>
-      <c r="F398" s="5">
+      <c r="F398" s="12">
         <v>4.2000000000000003E-2</v>
       </c>
-      <c r="G398" s="5">
+      <c r="G398" s="12">
         <v>4.36E-2</v>
       </c>
     </row>
     <row r="399" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A399" s="1">
+      <c r="A399" s="8">
         <v>45689</v>
       </c>
-      <c r="B399" s="4">
+      <c r="B399" s="9">
         <v>45733</v>
       </c>
       <c r="C399" s="10">
@@ -7952,21 +7949,21 @@
       <c r="D399" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E399" s="6">
+      <c r="E399" s="11">
         <v>711757</v>
       </c>
-      <c r="F399" s="5">
+      <c r="F399" s="12">
         <v>3.1E-2</v>
       </c>
-      <c r="G399" s="5">
+      <c r="G399" s="12">
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
     <row r="400" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A400" s="1">
+      <c r="A400" s="8">
         <v>45717</v>
       </c>
-      <c r="B400" s="4">
+      <c r="B400" s="9">
         <v>45763</v>
       </c>
       <c r="C400" s="10">
@@ -7975,21 +7972,21 @@
       <c r="D400" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E400" s="6">
+      <c r="E400" s="11">
         <v>722572</v>
       </c>
-      <c r="F400" s="5">
+      <c r="F400" s="12">
         <v>4.5999999999999999E-2</v>
       </c>
-      <c r="G400" s="5">
+      <c r="G400" s="12">
         <v>3.5400000000000001E-2</v>
       </c>
     </row>
     <row r="401" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A401" s="1">
+      <c r="A401" s="8">
         <v>45748</v>
       </c>
-      <c r="B401" s="4">
+      <c r="B401" s="9">
         <v>45792</v>
       </c>
       <c r="C401" s="10">
@@ -7998,21 +7995,21 @@
       <c r="D401" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E401" s="6">
+      <c r="E401" s="11">
         <v>721789</v>
       </c>
-      <c r="F401" s="5">
+      <c r="F401" s="12">
         <v>5.16E-2</v>
       </c>
-      <c r="G401" s="5">
+      <c r="G401" s="12">
         <v>5.2499999999999998E-2</v>
       </c>
     </row>
     <row r="402" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A402" s="1">
+      <c r="A402" s="8">
         <v>45778</v>
       </c>
-      <c r="B402" s="4">
+      <c r="B402" s="9">
         <v>45825</v>
       </c>
       <c r="C402" s="10">
@@ -8021,21 +8018,21 @@
       <c r="D402" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E402" s="6">
+      <c r="E402" s="11">
         <v>716101</v>
       </c>
-      <c r="F402" s="5">
+      <c r="F402" s="12">
         <v>3.2899999999999999E-2</v>
       </c>
-      <c r="G402" s="5">
+      <c r="G402" s="12">
         <v>0.05</v>
       </c>
     </row>
     <row r="403" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A403" s="1">
+      <c r="A403" s="8">
         <v>45809</v>
       </c>
-      <c r="B403" s="4">
+      <c r="B403" s="9">
         <v>45855</v>
       </c>
       <c r="C403" s="10">
@@ -8044,21 +8041,21 @@
       <c r="D403" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E403" s="6">
+      <c r="E403" s="11">
         <v>723033</v>
       </c>
-      <c r="F403" s="5">
+      <c r="F403" s="12">
         <v>3.9199999999999999E-2</v>
       </c>
-      <c r="G403" s="5">
+      <c r="G403" s="12">
         <v>3.2899999999999999E-2</v>
       </c>
     </row>
     <row r="404" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A404" s="1">
+      <c r="A404" s="8">
         <v>45839</v>
       </c>
-      <c r="B404" s="4">
+      <c r="B404" s="9">
         <v>45884</v>
       </c>
       <c r="C404" s="10">
@@ -8067,21 +8064,21 @@
       <c r="D404" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E404" s="6">
+      <c r="E404" s="11">
         <v>727727</v>
       </c>
-      <c r="F404" s="5">
+      <c r="F404" s="12">
         <v>3.9199999999999999E-2</v>
       </c>
-      <c r="G404" s="5">
+      <c r="G404" s="12">
         <v>4.3499999999999997E-2</v>
       </c>
     </row>
     <row r="405" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A405" s="1">
+      <c r="A405" s="8">
         <v>45870</v>
       </c>
-      <c r="B405" s="4">
+      <c r="B405" s="9">
         <v>45916</v>
       </c>
       <c r="C405" s="10">
@@ -8090,21 +8087,21 @@
       <c r="D405" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E405" s="6">
+      <c r="E405" s="11">
         <v>732059</v>
       </c>
-      <c r="F405" s="5">
+      <c r="F405" s="12">
         <v>0.05</v>
       </c>
-      <c r="G405" s="5">
+      <c r="G405" s="12">
         <v>4.0899999999999999E-2</v>
       </c>
     </row>
     <row r="406" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A406" s="1">
+      <c r="A406" s="8">
         <v>45901</v>
       </c>
-      <c r="B406" s="4">
+      <c r="B406" s="9">
         <v>45986</v>
       </c>
       <c r="C406" s="10">
@@ -8113,21 +8110,21 @@
       <c r="D406" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E406" s="6">
+      <c r="E406" s="11">
         <v>733258</v>
       </c>
-      <c r="F406" s="5">
+      <c r="F406" s="12">
         <v>4.2599999999999999E-2</v>
       </c>
-      <c r="G406" s="5">
+      <c r="G406" s="12">
         <v>5.0200000000000002E-2</v>
       </c>
     </row>
     <row r="407" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A407" s="1">
+      <c r="A407" s="8">
         <v>45931</v>
       </c>
-      <c r="B407" s="4">
+      <c r="B407" s="9">
         <v>46007</v>
       </c>
       <c r="C407" s="10">
@@ -8136,21 +8133,21 @@
       <c r="D407" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E407" s="6">
+      <c r="E407" s="11">
         <v>732633</v>
       </c>
-      <c r="F407" s="5">
+      <c r="F407" s="12">
         <v>3.4700000000000002E-2</v>
       </c>
-      <c r="G407" s="5">
+      <c r="G407" s="12">
         <v>4.1799999999999997E-2</v>
       </c>
     </row>
     <row r="408" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A408" s="1">
+      <c r="A408" s="8">
         <v>45962</v>
       </c>
-      <c r="B408" s="4">
+      <c r="B408" s="9">
         <v>46036</v>
       </c>
       <c r="C408" s="10">
@@ -8159,14 +8156,14 @@
       <c r="D408" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G408" s="5">
+      <c r="G408" s="12">
         <v>3.4700000000000002E-2</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -8176,15 +8173,15 @@
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="1" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/macro/USA/Retail Sales.xlsx
+++ b/data/macro/USA/Retail Sales.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\macro\USA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64EFA29B-39C0-4CA2-9518-78792984D266}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96184B16-38E6-4EF9-BBA0-978A34CF2F9D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11475" yWindow="780" windowWidth="18000" windowHeight="20685" xr2:uid="{30656A32-0D37-469D-885D-F50C8A2BA9DC}"/>
   </bookViews>
   <sheets>
     <sheet name="Retail Sales" sheetId="1" r:id="rId1"/>
-    <sheet name="info" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
+    <sheet name="info" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -233,6 +234,3339 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ko-KR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ko-KR"/>
+              <a:t>US Retail Sales</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Retail Sales'!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v> RSAFS </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Retail Sales'!$B$2:$B$408</c:f>
+              <c:numCache>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="407"/>
+                <c:pt idx="0">
+                  <c:v>33635</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>33664</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>33695</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>33725</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>33756</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>33786</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>33817</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>33848</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>33878</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>33909</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>33939</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>33970</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>34001</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>34029</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>34060</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>34090</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>34121</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>34151</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>34182</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>34213</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>34243</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>34274</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>34304</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>34335</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>34366</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>34394</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>34425</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>34455</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>34486</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>34516</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>34547</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>34578</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>34608</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>34639</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>34669</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>34700</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>34731</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>34759</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>34790</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>34820</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>34851</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>34881</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>34912</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>34943</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>34973</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>35004</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>35034</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>35065</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>35096</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>35125</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>35156</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>35186</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>35217</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>35247</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>35278</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>35309</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>35339</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>35370</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>35400</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>35431</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>35462</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>35490</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>35521</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>35551</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>35582</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>35612</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>35643</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>35674</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>35704</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>35735</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>35765</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>35796</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>35827</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>35855</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>35886</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>35916</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>35947</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>35977</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>36008</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>36039</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>36069</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>36100</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>36130</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>36161</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>36192</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>36220</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>36251</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>36281</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>36312</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>36342</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>36373</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>36404</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>36434</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>36465</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>36495</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>36526</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>36557</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>36586</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>36617</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>36647</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>36678</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>36708</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>36739</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>36770</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>36800</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>36831</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>36861</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>36892</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>36923</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>36951</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>36982</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>37012</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>37055</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>37085</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>37117</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>37148</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>37176</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>37209</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>37238</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>37271</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>37300</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>37328</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>37358</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>37390</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>37420</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>37449</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>37481</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>37512</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>37540</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>37574</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>37602</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>37635</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>37665</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>37693</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>37722</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>37755</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>37784</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>37817</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>37846</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>37876</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>37909</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>37939</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>37966</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>38001</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>38029</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>38057</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>38090</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>38120</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>38152</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>38182</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>38211</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>38244</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>38275</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>38303</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>38334</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>38365</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>38398</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>38426</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>38455</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>38484</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>38517</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>38547</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>38575</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>38609</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>38639</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>38671</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>38699</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>38730</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>38762</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>38790</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>38820</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>38848</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>38881</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>38912</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>38940</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>38974</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>39003</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>39035</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>39064</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>39094</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>39127</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>39154</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>39188</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>39213</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>39246</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>39276</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>39307</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>39339</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>39367</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>39400</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>39429</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>39462</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>39491</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>39520</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>39552</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>39581</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>39611</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>39644</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>39673</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>39703</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>39736</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>39766</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>39794</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>39827</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>39856</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>39884</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>39917</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>39946</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>39975</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>40008</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>40038</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>40071</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>40100</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>40133</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>40158</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>40192</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>40221</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>40249</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>40282</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>40312</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>40340</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>40373</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>40403</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>40435</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>40466</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>40497</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>40526</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>40557</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>40589</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>40613</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>40646</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>40675</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>40708</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>40738</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>40767</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>40800</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>40830</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>40862</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>40890</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>40920</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>40953</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>40981</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>41015</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>41044</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>41073</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>41106</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>41135</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>41166</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>41197</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>41227</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>41256</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>41289</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>41318</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>41346</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>41376</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>41407</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>41438</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>41470</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>41499</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>41530</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>41576</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>41598</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>41620</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>41653</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>41683</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>41711</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>41743</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>41772</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>41802</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>41835</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>41864</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>41894</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>41927</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>41957</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>41984</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>42018</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>42047</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>42075</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>42108</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>42137</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>42166</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>42199</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>42229</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>42262</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>42291</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>42321</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>42349</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>42384</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>42412</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>42444</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>42473</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>42503</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>42535</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>42566</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>42594</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>42628</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>42657</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>42689</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>42718</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>42748</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>42781</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>42809</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>42839</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>42867</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>42900</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>42930</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>42962</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>42993</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>43021</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>43054</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>43083</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>43112</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>43145</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>43173</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>43206</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>43235</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>43265</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>43297</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>43327</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>43357</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>43388</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>43419</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>43448</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>43510</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>43535</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>43556</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>43573</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>43600</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>43630</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>43662</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>43692</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>43721</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>43754</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>43784</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>43812</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>43846</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>43875</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>43907</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>43936</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>43966</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>43998</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>44028</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>44057</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>44090</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>44120</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>44152</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>44181</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>44211</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>44244</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>44271</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>44301</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>44330</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>44362</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>44393</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>44425</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>44455</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>44484</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>44516</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>44545</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>44575</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>44608</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>44636</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>44665</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>44698</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>44727</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>44757</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>44790</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>44819</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>44848</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>44881</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>44910</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>44944</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>44972</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>45000</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>45030</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>45062</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>45092</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>45125</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>45153</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>45183</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>45216</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>45245</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>45274</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>45308</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>45337</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>45365</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>45397</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>45427</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>45461</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>45489</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>45519</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>45552</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>45582</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>45611</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>45643</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>45673</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>45702</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>45733</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>45763</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>45792</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>45825</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>45855</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>45884</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>45916</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>45986</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>46007</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>46036</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Retail Sales'!$E$2:$E$408</c:f>
+              <c:numCache>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
+                <c:ptCount val="407"/>
+                <c:pt idx="0">
+                  <c:v>159177</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>159189</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>158647</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>159921</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>160471</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>161205</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>162855</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>162412</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>164361</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>166063</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>166124</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>167691</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>169500</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>168840</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>167682</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>172102</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>172960</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>173018</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>175822</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>175233</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>176608</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>177588</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>179758</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>181077</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>179615</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>183101</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>186721</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>186423</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>185616</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>187800</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>188062</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>190771</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>192585</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>193914</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>194425</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>194939</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>195908</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>193068</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>195179</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>195310</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>198060</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>200383</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>199110</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>201078</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>201337</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>200597</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>203545</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>204032</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>203793</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>206875</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>207650</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>209294</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>211157</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>209474</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>210827</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>210846</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>213233</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>215526</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>215167</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>215690</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>218124</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>219587</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>221189</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>217925</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>217771</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>220233</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>222985</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>223120</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>224509</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>224300</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>223718</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>225236</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>225954</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>225746</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>226889</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>230409</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>230995</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>233207</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>231551</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>229792</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>232308</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>236174</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>237592</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>240140</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>240269</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>243346</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>244687</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>246628</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>248367</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>249329</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>251263</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>253844</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>255029</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>254816</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>258133</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>263311</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>261545</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>265686</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>269019</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>264067</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>265992</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>267750</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>265683</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>266885</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>270523</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>270339</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>268850</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>268338</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>272881</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>272627</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>269820</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>274410</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>275769</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>274474</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>273098</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>275659</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>268652</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>288632</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>280033</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>276302</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>277135</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>278869</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>278079</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>281147</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>278966</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>280426</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>284161</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>285884</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>281064</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>282940</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>283408</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>286646</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>288657</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>284696</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>288177</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>289053</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>289619</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>293671</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>296207</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>299592</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>298921</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>298205</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>299433</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>300702</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>301993</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>303915</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>309471</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>307358</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>311088</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>309127</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>311681</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>311192</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>317446</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>318476</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>320520</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>324672</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>321272</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>325308</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>326179</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>329124</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>327233</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>337219</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>339529</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>335605</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>336600</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>336753</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>339719</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>339895</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>349664</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>347021</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>348357</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>350072</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>348889</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>350795</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>351916</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>353285</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>351240</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>351035</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>352116</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>356367</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>355792</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>356545</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>359415</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>358562</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>363085</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>360234</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>361770</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>363676</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>365178</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>367322</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>370776</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>366569</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>367368</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>364126</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>365164</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>364816</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>368255</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>368926</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>367594</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>364611</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>358991</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>346137</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>332498</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>324767</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>329787</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>328376</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>322634</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>324323</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>327011</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>332227</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>333670</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>339586</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>330998</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>334595</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>337321</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>338736</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>339093</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>339580</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>346974</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>349869</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>346858</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>346516</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>347612</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>349188</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>352179</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>356215</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>359450</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>361979</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>364394</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>367475</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>370775</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>372820</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>372505</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>375587</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>375442</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>375860</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>380042</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>382207</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>383422</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>383985</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>387531</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>392310</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>393698</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>392073</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>391376</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>387901</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>389686</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>394524</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>397681</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>397494</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>399708</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>401093</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>404434</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>409118</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>406223</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>404231</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>406677</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>407921</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>410268</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>409691</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>410044</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>411399</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>412561</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>414812</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>411561</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>416736</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>421230</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>425546</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>426253</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>427305</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>428079</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>431379</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>430189</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>431903</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>433113</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>430110</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>428208</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>427119</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>433647</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>434470</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>437865</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>437951</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>441942</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>441849</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>439867</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>438693</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>440303</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>442149</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>439466</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>443117</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>441856</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>444254</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>445490</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>450237</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>449789</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>449946</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>453056</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>453847</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>453892</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>459305</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>464412</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>464284</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>463674</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>465276</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>462754</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>465130</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>465089</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>466020</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>475724</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>476107</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>480949</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>483586</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>481414</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>484031</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>484110</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>484154</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>491960</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>490228</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>493142</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>493445</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>491507</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>496416</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>498854</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>489113</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>490440</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>491751</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>499292</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>499343</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>504741</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>505251</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>509091</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>512561</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>509282</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>510648</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>514215</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>515866</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>515119</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>515330</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>468324</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>401028</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>478449</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>518038</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>526304</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>530735</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>541302</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>539114</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>533941</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>538548</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>559230</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>544891</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>603581</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>608961</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>605282</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>611950</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>601817</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>605533</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>609671</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>618573</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>624874</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>619938</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>631509</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>638101</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>651027</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>660194</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>659847</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>666113</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>659550</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>663566</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>661854</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>668671</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>659458</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>651763</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>680253</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>672152</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>665071</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>670494</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>673902</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>677117</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>678424</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>684755</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>689403</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>686148</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>685328</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>686277</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>680456</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>685280</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>687641</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>687602</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>692774</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>692449</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>698835</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>697039</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>703285</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>707613</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>712145</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>717662</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>711461</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>711757</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>722572</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>721789</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>716101</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>723033</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>727727</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>732059</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>733258</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>732633</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4F45-476A-A2CC-B716E595B015}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1853672975"/>
+        <c:axId val="1753566319"/>
+      </c:lineChart>
+      <c:dateAx>
+        <c:axId val="1853672975"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="46387"/>
+          <c:min val="42005"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="yyyy;@" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1753566319"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblOffset val="100"/>
+        <c:baseTimeUnit val="days"/>
+      </c:dateAx>
+      <c:valAx>
+        <c:axId val="1753566319"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="300000"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1853672975"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="100000"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ko-KR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>609599</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>171449</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>600074</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>161924</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="차트 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{49E53EE4-8613-47B4-A2B0-6AF933D63C13}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8168,6 +11502,17 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EED7C336-5A38-44EE-8A4B-F68941BA5B49}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D57F73F-5FFC-47C2-9B16-318BC0BDC7A6}">
   <dimension ref="B2:C3"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
